--- a/templates/Templates_REG.xlsx
+++ b/templates/Templates_REG.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aletheia/Desktop/Paediatrics/Admin/RosterApp/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aletheia/Desktop/Paediatrics/Admin/RosterApp/roster/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE4487B-7786-1F47-967E-FA6C1E301CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4452EEC1-D930-5449-AA27-6DB883F22508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="840" yWindow="1280" windowWidth="28560" windowHeight="16600" activeTab="2" xr2:uid="{B6EBF472-D0B5-0C4E-A945-41133059122F}"/>
   </bookViews>
@@ -19477,42 +19477,42 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6259ADDC-6A2D-4608-B8DB-929D80D80DDB}">
-  <dimension ref="C1:BP75"/>
+  <dimension ref="B1:BO75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="1"/>
-    <col min="2" max="2" width="1.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5" style="3" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" style="3" customWidth="1"/>
-    <col min="7" max="8" width="9.5" style="3" customWidth="1"/>
-    <col min="9" max="48" width="9" style="1" customWidth="1"/>
-    <col min="49" max="49" width="3.1640625" style="1" customWidth="1"/>
-    <col min="50" max="56" width="8.5" style="1" customWidth="1"/>
-    <col min="57" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="1" width="6.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" style="3" customWidth="1"/>
+    <col min="6" max="7" width="9.5" style="3" customWidth="1"/>
+    <col min="8" max="47" width="9" style="1" customWidth="1"/>
+    <col min="48" max="48" width="3.1640625" style="1" customWidth="1"/>
+    <col min="49" max="55" width="8.5" style="1" customWidth="1"/>
+    <col min="56" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:68" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C1" s="332" t="s">
+    <row r="1" spans="2:67" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="332" t="s">
         <v>261</v>
       </c>
-      <c r="E1" s="353" t="s">
+      <c r="D1" s="353" t="s">
         <v>159</v>
       </c>
+      <c r="E1" s="353"/>
       <c r="F1" s="353"/>
       <c r="G1" s="353"/>
-      <c r="H1" s="353"/>
+      <c r="H1" s="354"/>
       <c r="I1" s="354"/>
       <c r="J1" s="354"/>
       <c r="K1" s="354"/>
-      <c r="L1" s="354"/>
+      <c r="L1" s="354" t="s">
+        <v>193</v>
+      </c>
       <c r="M1" s="354" t="s">
         <v>193</v>
       </c>
-      <c r="N1" s="354" t="s">
-        <v>193</v>
-      </c>
+      <c r="N1" s="354"/>
       <c r="O1" s="354"/>
       <c r="P1" s="354"/>
       <c r="Q1" s="354"/>
@@ -19546,185 +19546,185 @@
       <c r="AS1" s="354"/>
       <c r="AT1" s="354"/>
       <c r="AU1" s="354"/>
-      <c r="AV1" s="354"/>
     </row>
-    <row r="2" spans="3:68" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="332"/>
-      <c r="E2" s="353" t="s">
+    <row r="2" spans="2:67" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="332"/>
+      <c r="D2" s="353" t="s">
         <v>263</v>
       </c>
+      <c r="E2" s="353"/>
       <c r="F2" s="353"/>
       <c r="G2" s="353"/>
-      <c r="H2" s="353"/>
+      <c r="H2" s="354">
+        <f t="shared" ref="H2:AM2" si="0">WEEKDAY(H5,2)</f>
+        <v>2</v>
+      </c>
       <c r="I2" s="354">
-        <f t="shared" ref="I2:AN2" si="0">WEEKDAY(I5,2)</f>
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="J2" s="354">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" s="354">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2" s="354">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M2" s="354">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N2" s="354">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O2" s="354">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P2" s="354">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q2" s="354">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R2" s="354">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S2" s="354">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T2" s="354">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U2" s="354">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="V2" s="354">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W2" s="354">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X2" s="354">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y2" s="354">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z2" s="354">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA2" s="354">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB2" s="354">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AC2" s="354">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD2" s="354">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE2" s="354">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF2" s="354">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG2" s="354">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH2" s="354">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI2" s="354">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AJ2" s="354">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK2" s="354">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL2" s="354">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM2" s="354">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN2" s="354">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" ref="AN2:AU2" si="1">WEEKDAY(AN5,2)</f>
+        <v>6</v>
       </c>
       <c r="AO2" s="354">
-        <f t="shared" ref="AO2:AV2" si="1">WEEKDAY(AO5,2)</f>
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="AP2" s="354">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AQ2" s="354">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR2" s="354">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS2" s="354">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT2" s="354">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU2" s="354">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="AV2" s="354">
-        <f t="shared" si="1"/>
         <v>6</v>
       </c>
+      <c r="BD2" s="355"/>
       <c r="BE2" s="355"/>
-      <c r="BF2" s="355"/>
     </row>
-    <row r="3" spans="3:68" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="332"/>
+    <row r="3" spans="2:67" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="332"/>
+      <c r="D3" s="353"/>
       <c r="E3" s="353"/>
       <c r="F3" s="353"/>
       <c r="G3" s="353"/>
-      <c r="H3" s="353"/>
+      <c r="H3" s="354"/>
       <c r="I3" s="354"/>
       <c r="J3" s="354"/>
       <c r="K3" s="354"/>
@@ -19764,270 +19764,270 @@
       <c r="AS3" s="354"/>
       <c r="AT3" s="354"/>
       <c r="AU3" s="354"/>
-      <c r="AV3" s="354"/>
-      <c r="AX3" s="390" t="s">
+      <c r="AW3" s="390" t="s">
         <v>176</v>
       </c>
+      <c r="AX3" s="396"/>
       <c r="AY3" s="396"/>
       <c r="AZ3" s="396"/>
       <c r="BA3" s="396"/>
       <c r="BB3" s="396"/>
-      <c r="BC3" s="396"/>
-      <c r="BD3" s="391"/>
-      <c r="BE3" s="390" t="s">
+      <c r="BC3" s="391"/>
+      <c r="BD3" s="390" t="s">
         <v>188</v>
       </c>
-      <c r="BF3" s="391"/>
-      <c r="BG3" s="390" t="s">
+      <c r="BE3" s="391"/>
+      <c r="BF3" s="390" t="s">
         <v>273</v>
       </c>
-      <c r="BH3" s="391"/>
+      <c r="BG3" s="391"/>
     </row>
-    <row r="4" spans="3:68" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G4" s="394" t="s">
+    <row r="4" spans="2:67" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F4" s="394" t="s">
         <v>133</v>
       </c>
-      <c r="H4" s="395"/>
-      <c r="AX4" s="375" t="s">
+      <c r="G4" s="395"/>
+      <c r="AW4" s="375" t="s">
         <v>288</v>
       </c>
+      <c r="AX4" s="363" t="s">
+        <v>18</v>
+      </c>
       <c r="AY4" s="363" t="s">
-        <v>18</v>
+        <v>283</v>
       </c>
       <c r="AZ4" s="363" t="s">
-        <v>283</v>
+        <v>10</v>
       </c>
       <c r="BA4" s="363" t="s">
-        <v>10</v>
-      </c>
-      <c r="BB4" s="363" t="s">
         <v>5</v>
       </c>
-      <c r="BC4" s="18" t="s">
+      <c r="BB4" s="18" t="s">
         <v>282</v>
       </c>
-      <c r="BD4" s="26" t="s">
+      <c r="BC4" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="BE4" s="392"/>
-      <c r="BF4" s="393"/>
-      <c r="BG4" s="392"/>
-      <c r="BH4" s="393"/>
+      <c r="BD4" s="392"/>
+      <c r="BE4" s="393"/>
+      <c r="BF4" s="392"/>
+      <c r="BG4" s="393"/>
     </row>
-    <row r="5" spans="3:68" x14ac:dyDescent="0.2">
-      <c r="C5" s="357" t="s">
+    <row r="5" spans="2:67" x14ac:dyDescent="0.2">
+      <c r="B5" s="357" t="s">
         <v>250</v>
       </c>
+      <c r="C5" s="66" t="s">
+        <v>276</v>
+      </c>
       <c r="D5" s="66" t="s">
-        <v>276</v>
-      </c>
-      <c r="E5" s="66" t="s">
         <v>265</v>
       </c>
-      <c r="F5" s="277" t="s">
+      <c r="E5" s="277" t="s">
         <v>277</v>
       </c>
-      <c r="G5" s="387">
-        <f>I5-2</f>
+      <c r="F5" s="387">
+        <f>H5-2</f>
         <v>46117</v>
       </c>
-      <c r="H5" s="362">
-        <f>I5-1</f>
+      <c r="G5" s="362">
+        <f>H5-1</f>
         <v>46118</v>
       </c>
-      <c r="I5" s="364">
+      <c r="H5" s="364">
         <v>46119</v>
+      </c>
+      <c r="I5" s="361">
+        <f>H5+1</f>
+        <v>46120</v>
       </c>
       <c r="J5" s="361">
         <f>I5+1</f>
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="K5" s="361">
         <f>J5+1</f>
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="L5" s="361">
-        <f>K5+1</f>
-        <v>46122</v>
+        <f t="shared" ref="L5:AG5" si="2">K5+1</f>
+        <v>46123</v>
       </c>
       <c r="M5" s="361">
-        <f t="shared" ref="M5:AH5" si="2">L5+1</f>
-        <v>46123</v>
+        <f t="shared" si="2"/>
+        <v>46124</v>
       </c>
       <c r="N5" s="361">
         <f t="shared" si="2"/>
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="O5" s="361">
         <f t="shared" si="2"/>
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="P5" s="361">
         <f t="shared" si="2"/>
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="Q5" s="361">
         <f t="shared" si="2"/>
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="R5" s="361">
         <f t="shared" si="2"/>
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="S5" s="361">
         <f t="shared" si="2"/>
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="T5" s="361">
         <f t="shared" si="2"/>
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="U5" s="361">
         <f t="shared" si="2"/>
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="V5" s="361">
         <f t="shared" si="2"/>
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="W5" s="361">
         <f t="shared" si="2"/>
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="X5" s="361">
         <f t="shared" si="2"/>
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="Y5" s="361">
         <f t="shared" si="2"/>
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="Z5" s="361">
         <f t="shared" si="2"/>
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AA5" s="361">
         <f t="shared" si="2"/>
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="AB5" s="361">
         <f t="shared" si="2"/>
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="AC5" s="361">
         <f t="shared" si="2"/>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="AD5" s="361">
         <f t="shared" si="2"/>
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="AE5" s="361">
         <f t="shared" si="2"/>
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="AF5" s="361">
         <f t="shared" si="2"/>
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="AG5" s="361">
         <f t="shared" si="2"/>
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="AH5" s="361">
-        <f t="shared" si="2"/>
-        <v>46144</v>
+        <f>AG5+1</f>
+        <v>46145</v>
       </c>
       <c r="AI5" s="361">
-        <f>AH5+1</f>
-        <v>46145</v>
+        <f t="shared" ref="AI5:AM5" si="3">AH5+1</f>
+        <v>46146</v>
       </c>
       <c r="AJ5" s="361">
-        <f t="shared" ref="AJ5:AN5" si="3">AI5+1</f>
-        <v>46146</v>
+        <f t="shared" si="3"/>
+        <v>46147</v>
       </c>
       <c r="AK5" s="361">
         <f t="shared" si="3"/>
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="AL5" s="361">
         <f t="shared" si="3"/>
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="AM5" s="361">
         <f t="shared" si="3"/>
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="AN5" s="361">
-        <f t="shared" si="3"/>
-        <v>46150</v>
+        <f t="shared" ref="AN5" si="4">AM5+1</f>
+        <v>46151</v>
       </c>
       <c r="AO5" s="361">
-        <f t="shared" ref="AO5" si="4">AN5+1</f>
-        <v>46151</v>
+        <f t="shared" ref="AO5" si="5">AN5+1</f>
+        <v>46152</v>
       </c>
       <c r="AP5" s="361">
-        <f t="shared" ref="AP5" si="5">AO5+1</f>
-        <v>46152</v>
+        <f t="shared" ref="AP5" si="6">AO5+1</f>
+        <v>46153</v>
       </c>
       <c r="AQ5" s="361">
-        <f t="shared" ref="AQ5" si="6">AP5+1</f>
-        <v>46153</v>
+        <f t="shared" ref="AQ5" si="7">AP5+1</f>
+        <v>46154</v>
       </c>
       <c r="AR5" s="361">
-        <f t="shared" ref="AR5" si="7">AQ5+1</f>
-        <v>46154</v>
+        <f t="shared" ref="AR5" si="8">AQ5+1</f>
+        <v>46155</v>
       </c>
       <c r="AS5" s="361">
-        <f t="shared" ref="AS5" si="8">AR5+1</f>
-        <v>46155</v>
+        <f t="shared" ref="AS5" si="9">AR5+1</f>
+        <v>46156</v>
       </c>
       <c r="AT5" s="361">
-        <f t="shared" ref="AT5" si="9">AS5+1</f>
-        <v>46156</v>
-      </c>
-      <c r="AU5" s="361">
-        <f t="shared" ref="AU5" si="10">AT5+1</f>
+        <f t="shared" ref="AT5" si="10">AS5+1</f>
         <v>46157</v>
       </c>
-      <c r="AV5" s="362">
-        <f t="shared" ref="AV5" si="11">AU5+1</f>
+      <c r="AU5" s="362">
+        <f t="shared" ref="AU5" si="11">AT5+1</f>
         <v>46158</v>
       </c>
-      <c r="AW5" s="5"/>
-      <c r="AX5" s="383" t="s">
+      <c r="AV5" s="5"/>
+      <c r="AW5" s="383" t="s">
         <v>289</v>
+      </c>
+      <c r="AX5" s="384" t="s">
+        <v>284</v>
       </c>
       <c r="AY5" s="384" t="s">
         <v>284</v>
       </c>
       <c r="AZ5" s="384" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="BA5" s="384" t="s">
-        <v>285</v>
-      </c>
-      <c r="BB5" s="384" t="s">
         <v>286</v>
       </c>
-      <c r="BC5" s="385" t="s">
+      <c r="BB5" s="385" t="s">
         <v>287</v>
       </c>
-      <c r="BD5" s="386" t="s">
+      <c r="BC5" s="386" t="s">
         <v>290</v>
       </c>
-      <c r="BE5" s="234" t="s">
+      <c r="BD5" s="234" t="s">
         <v>171</v>
       </c>
-      <c r="BF5" s="236" t="s">
+      <c r="BE5" s="236" t="s">
         <v>172</v>
       </c>
-      <c r="BG5" s="234" t="s">
+      <c r="BF5" s="234" t="s">
         <v>274</v>
       </c>
-      <c r="BH5" s="236" t="s">
+      <c r="BG5" s="236" t="s">
         <v>275</v>
       </c>
+      <c r="BH5" s="5"/>
       <c r="BI5" s="5"/>
       <c r="BJ5" s="5"/>
       <c r="BK5" s="5"/>
@@ -20035,26 +20035,26 @@
       <c r="BM5" s="5"/>
       <c r="BN5" s="5"/>
       <c r="BO5" s="5"/>
-      <c r="BP5" s="5"/>
     </row>
-    <row r="6" spans="3:68" x14ac:dyDescent="0.2">
-      <c r="C6" s="71" t="s">
+    <row r="6" spans="2:67" x14ac:dyDescent="0.2">
+      <c r="B6" s="71" t="s">
         <v>281</v>
       </c>
+      <c r="C6" s="18"/>
       <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="307"/>
-      <c r="G6" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C6,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C6,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H6" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C6,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C7,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I6" s="24"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="356"/>
+      <c r="E6" s="307"/>
+      <c r="F6" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B6,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B6,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B6,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B7,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="24"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="356"/>
+      <c r="K6" s="18"/>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
       <c r="N6" s="18"/>
@@ -20062,10 +20062,10 @@
       <c r="P6" s="18"/>
       <c r="Q6" s="18"/>
       <c r="R6" s="18"/>
-      <c r="S6" s="18"/>
+      <c r="S6" s="356"/>
       <c r="T6" s="356"/>
-      <c r="U6" s="356"/>
-      <c r="V6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="356"/>
       <c r="W6" s="356"/>
       <c r="X6" s="356"/>
       <c r="Y6" s="356"/>
@@ -20080,9 +20080,9 @@
       <c r="AH6" s="356"/>
       <c r="AI6" s="356"/>
       <c r="AJ6" s="356"/>
-      <c r="AK6" s="356"/>
+      <c r="AK6" s="18"/>
       <c r="AL6" s="18"/>
-      <c r="AM6" s="18"/>
+      <c r="AM6" s="356"/>
       <c r="AN6" s="356"/>
       <c r="AO6" s="356"/>
       <c r="AP6" s="356"/>
@@ -20090,69 +20090,69 @@
       <c r="AR6" s="356"/>
       <c r="AS6" s="356"/>
       <c r="AT6" s="356"/>
-      <c r="AU6" s="356"/>
-      <c r="AV6" s="358"/>
-      <c r="AX6" s="42">
-        <f>COUNTIFS(I6:AV6,"R3",$I$2:$AV$2,"&lt;5", $I$1:$AV$1,"&lt;&gt;Y")</f>
-        <v>0</v>
-      </c>
-      <c r="AY6" s="23" cm="1">
-        <f t="array" ref="AY6">SUM(COUNTIFS(I6:AV6,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ6" s="23">
-        <f>COUNTIFS(I6:AV6,"R3",$I$2:$AV$2,"5", $I$1:$AV$1,"&lt;&gt;Y")</f>
-        <v>0</v>
-      </c>
-      <c r="BA6" s="23" cm="1">
-        <f t="array" ref="BA6">SUM(COUNTIFS(I6:AV6,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB6" s="23">
-        <f>COUNTIFS(I6:AV6,"R3",$I$2:$AV$2,"6", $I$1:$AV$1,"&lt;&gt;Y")</f>
-        <v>0</v>
-      </c>
-      <c r="BC6" s="278">
-        <f>COUNTIFS(I6:AV6,"R*",$I$2:$AV$2,"7", $I$1:$AV$1,"&lt;&gt;Y") + COUNTIFS(I6:AV6, "R*", $I$1:$AV$1,"Y")</f>
-        <v>0</v>
-      </c>
-      <c r="BD6" s="39">
-        <f>COUNTIF(I6:AV6,"WR")</f>
-        <v>0</v>
-      </c>
-      <c r="BE6" s="25">
-        <f>SUM(AX6:BC6)</f>
-        <v>0</v>
-      </c>
-      <c r="BF6" s="26">
-        <f>AX6*0.5+AY6*1+AZ6*1+BA6*2+BB6*4+BC6*3</f>
-        <v>0</v>
-      </c>
-      <c r="BG6" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C6,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH6" s="26">
-        <f>BF6+BG6</f>
+      <c r="AU6" s="358"/>
+      <c r="AW6" s="42">
+        <f>COUNTIFS(H6:AU6,"R3",$H$2:$AU$2,"&lt;5", $H$1:$AU$1,"&lt;&gt;Y")</f>
+        <v>0</v>
+      </c>
+      <c r="AX6" s="23" cm="1">
+        <f t="array" ref="AX6">SUM(COUNTIFS(H6:AU6,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY6" s="23">
+        <f>COUNTIFS(H6:AU6,"R3",$H$2:$AU$2,"5", $H$1:$AU$1,"&lt;&gt;Y")</f>
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="23" cm="1">
+        <f t="array" ref="AZ6">SUM(COUNTIFS(H6:AU6,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA6" s="23">
+        <f>COUNTIFS(H6:AU6,"R3",$H$2:$AU$2,"6", $H$1:$AU$1,"&lt;&gt;Y")</f>
+        <v>0</v>
+      </c>
+      <c r="BB6" s="278">
+        <f>COUNTIFS(H6:AU6,"R*",$H$2:$AU$2,"7", $H$1:$AU$1,"&lt;&gt;Y") + COUNTIFS(H6:AU6, "R*", $H$1:$AU$1,"Y")</f>
+        <v>0</v>
+      </c>
+      <c r="BC6" s="39">
+        <f>COUNTIF(H6:AU6,"WR")</f>
+        <v>0</v>
+      </c>
+      <c r="BD6" s="25">
+        <f>SUM(AW6:BB6)</f>
+        <v>0</v>
+      </c>
+      <c r="BE6" s="26">
+        <f>AW6*0.5+AX6*1+AY6*1+AZ6*2+BA6*4+BB6*3</f>
+        <v>0</v>
+      </c>
+      <c r="BF6" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B6,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG6" s="26">
+        <f>BE6+BF6</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="3:68" x14ac:dyDescent="0.2">
-      <c r="C7" s="71"/>
+    <row r="7" spans="2:67" x14ac:dyDescent="0.2">
+      <c r="B7" s="71"/>
+      <c r="C7" s="18"/>
       <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="307"/>
-      <c r="G7" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C7,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C7,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H7" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C7,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C8,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I7" s="24"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="356"/>
+      <c r="E7" s="307"/>
+      <c r="F7" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B7,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B7,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B7,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B8,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="24"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="356"/>
+      <c r="K7" s="18"/>
       <c r="L7" s="18"/>
       <c r="M7" s="18"/>
       <c r="N7" s="18"/>
@@ -20160,10 +20160,10 @@
       <c r="P7" s="18"/>
       <c r="Q7" s="18"/>
       <c r="R7" s="18"/>
-      <c r="S7" s="18"/>
+      <c r="S7" s="356"/>
       <c r="T7" s="356"/>
-      <c r="U7" s="356"/>
-      <c r="V7" s="18"/>
+      <c r="U7" s="18"/>
+      <c r="V7" s="356"/>
       <c r="W7" s="356"/>
       <c r="X7" s="356"/>
       <c r="Y7" s="356"/>
@@ -20178,9 +20178,9 @@
       <c r="AH7" s="356"/>
       <c r="AI7" s="356"/>
       <c r="AJ7" s="356"/>
-      <c r="AK7" s="356"/>
+      <c r="AK7" s="18"/>
       <c r="AL7" s="18"/>
-      <c r="AM7" s="18"/>
+      <c r="AM7" s="356"/>
       <c r="AN7" s="356"/>
       <c r="AO7" s="356"/>
       <c r="AP7" s="356"/>
@@ -20188,67 +20188,67 @@
       <c r="AR7" s="356"/>
       <c r="AS7" s="356"/>
       <c r="AT7" s="356"/>
-      <c r="AU7" s="356"/>
-      <c r="AV7" s="358"/>
-      <c r="AX7" s="42">
-        <f t="shared" ref="AX7:AX55" si="12">COUNTIFS(I7:AV7,"R3",$I$2:$AV$2,"&lt;5", $I$1:$AV$1,"&lt;&gt;Y")</f>
-        <v>0</v>
-      </c>
-      <c r="AY7" s="23" cm="1">
-        <f t="array" ref="AY7">SUM(COUNTIFS(I7:AV7,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ7" s="23">
-        <f t="shared" ref="AZ7:AZ55" si="13">COUNTIFS(I7:AV7,"R3",$I$2:$AV$2,"5", $I$1:$AV$1,"&lt;&gt;Y")</f>
-        <v>0</v>
-      </c>
-      <c r="BA7" s="23" cm="1">
-        <f t="array" ref="BA7">SUM(COUNTIFS(I7:AV7,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB7" s="23">
-        <f t="shared" ref="BB7:BB55" si="14">COUNTIFS(I7:AV7,"R3",$I$2:$AV$2,"6", $I$1:$AV$1,"&lt;&gt;Y")</f>
-        <v>0</v>
-      </c>
-      <c r="BC7" s="278">
-        <f t="shared" ref="BC7:BC55" si="15">COUNTIFS(I7:AV7,"R*",$I$2:$AV$2,"7", $I$1:$AV$1,"&lt;&gt;Y") + COUNTIFS(I7:AV7, "R*", $I$1:$AV$1,"Y")</f>
-        <v>0</v>
-      </c>
-      <c r="BD7" s="39">
-        <f t="shared" ref="BD7:BD55" si="16">COUNTIF(I7:AV7,"WR")</f>
-        <v>0</v>
-      </c>
-      <c r="BE7" s="25">
-        <f t="shared" ref="BE7:BE55" si="17">SUM(AX7:BC7)</f>
-        <v>0</v>
-      </c>
-      <c r="BF7" s="26">
-        <f t="shared" ref="BF7:BF55" si="18">AX7*0.5+AY7*1+AZ7*1+BA7*2+BB7*4+BC7*3</f>
-        <v>0</v>
-      </c>
-      <c r="BG7" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C7,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH7" s="26">
-        <f t="shared" ref="BH7:BH55" si="19">BF7+BG7</f>
+      <c r="AU7" s="358"/>
+      <c r="AW7" s="42">
+        <f t="shared" ref="AW7:AW55" si="12">COUNTIFS(H7:AU7,"R3",$H$2:$AU$2,"&lt;5", $H$1:$AU$1,"&lt;&gt;Y")</f>
+        <v>0</v>
+      </c>
+      <c r="AX7" s="23" cm="1">
+        <f t="array" ref="AX7">SUM(COUNTIFS(H7:AU7,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY7" s="23">
+        <f t="shared" ref="AY7:AY55" si="13">COUNTIFS(H7:AU7,"R3",$H$2:$AU$2,"5", $H$1:$AU$1,"&lt;&gt;Y")</f>
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="23" cm="1">
+        <f t="array" ref="AZ7">SUM(COUNTIFS(H7:AU7,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA7" s="23">
+        <f t="shared" ref="BA7:BA55" si="14">COUNTIFS(H7:AU7,"R3",$H$2:$AU$2,"6", $H$1:$AU$1,"&lt;&gt;Y")</f>
+        <v>0</v>
+      </c>
+      <c r="BB7" s="278">
+        <f t="shared" ref="BB7:BB55" si="15">COUNTIFS(H7:AU7,"R*",$H$2:$AU$2,"7", $H$1:$AU$1,"&lt;&gt;Y") + COUNTIFS(H7:AU7, "R*", $H$1:$AU$1,"Y")</f>
+        <v>0</v>
+      </c>
+      <c r="BC7" s="39">
+        <f t="shared" ref="BC7:BC55" si="16">COUNTIF(H7:AU7,"WR")</f>
+        <v>0</v>
+      </c>
+      <c r="BD7" s="25">
+        <f t="shared" ref="BD7:BD55" si="17">SUM(AW7:BB7)</f>
+        <v>0</v>
+      </c>
+      <c r="BE7" s="26">
+        <f t="shared" ref="BE7:BE55" si="18">AW7*0.5+AX7*1+AY7*1+AZ7*2+BA7*4+BB7*3</f>
+        <v>0</v>
+      </c>
+      <c r="BF7" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B7,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG7" s="26">
+        <f t="shared" ref="BG7:BG55" si="19">BE7+BF7</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="3:68" x14ac:dyDescent="0.2">
-      <c r="C8" s="71"/>
+    <row r="8" spans="2:67" x14ac:dyDescent="0.2">
+      <c r="B8" s="71"/>
+      <c r="C8" s="18"/>
       <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="307"/>
-      <c r="G8" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C8,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C8,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H8" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C8,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C9,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I8" s="24"/>
+      <c r="E8" s="307"/>
+      <c r="F8" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B8,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B8,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B8,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B9,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="24"/>
+      <c r="I8" s="18"/>
       <c r="J8" s="18"/>
       <c r="K8" s="18"/>
       <c r="L8" s="18"/>
@@ -20264,7 +20264,7 @@
       <c r="V8" s="18"/>
       <c r="W8" s="18"/>
       <c r="X8" s="18"/>
-      <c r="Y8" s="18"/>
+      <c r="Y8" s="356"/>
       <c r="Z8" s="356"/>
       <c r="AA8" s="356"/>
       <c r="AB8" s="356"/>
@@ -20272,7 +20272,7 @@
       <c r="AD8" s="356"/>
       <c r="AE8" s="356"/>
       <c r="AF8" s="356"/>
-      <c r="AG8" s="356"/>
+      <c r="AG8" s="18"/>
       <c r="AH8" s="18"/>
       <c r="AI8" s="18"/>
       <c r="AJ8" s="18"/>
@@ -20286,95 +20286,95 @@
       <c r="AR8" s="18"/>
       <c r="AS8" s="18"/>
       <c r="AT8" s="18"/>
-      <c r="AU8" s="18"/>
-      <c r="AV8" s="26"/>
-      <c r="AX8" s="42">
+      <c r="AU8" s="26"/>
+      <c r="AW8" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY8" s="23" cm="1">
-        <f t="array" ref="AY8">SUM(COUNTIFS(I8:AV8,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ8" s="23">
+      <c r="AX8" s="23" cm="1">
+        <f t="array" ref="AX8">SUM(COUNTIFS(H8:AU8,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY8" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA8" s="23" cm="1">
-        <f t="array" ref="BA8">SUM(COUNTIFS(I8:AV8,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB8" s="23">
+      <c r="AZ8" s="23" cm="1">
+        <f t="array" ref="AZ8">SUM(COUNTIFS(H8:AU8,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA8" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC8" s="278">
+      <c r="BB8" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD8" s="39">
+      <c r="BC8" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE8" s="25">
+      <c r="BD8" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF8" s="26">
+      <c r="BE8" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG8" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C8,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH8" s="26">
+      <c r="BF8" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B8,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG8" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="3:68" x14ac:dyDescent="0.2">
-      <c r="C9" s="71"/>
+    <row r="9" spans="2:67" x14ac:dyDescent="0.2">
+      <c r="B9" s="71"/>
+      <c r="C9" s="18"/>
       <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="307"/>
-      <c r="G9" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C9,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C9,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H9" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C9,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C10,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I9" s="24"/>
+      <c r="E9" s="307"/>
+      <c r="F9" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B9,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B9,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B9,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B10,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="24"/>
+      <c r="I9" s="356"/>
       <c r="J9" s="356"/>
-      <c r="K9" s="356"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="356"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="356"/>
+      <c r="M9" s="18"/>
       <c r="N9" s="18"/>
       <c r="O9" s="18"/>
       <c r="P9" s="18"/>
       <c r="Q9" s="18"/>
-      <c r="R9" s="18"/>
-      <c r="S9" s="356"/>
+      <c r="R9" s="356"/>
+      <c r="S9" s="18"/>
       <c r="T9" s="18"/>
       <c r="U9" s="18"/>
       <c r="V9" s="18"/>
       <c r="W9" s="18"/>
       <c r="X9" s="18"/>
       <c r="Y9" s="18"/>
-      <c r="Z9" s="18"/>
+      <c r="Z9" s="356"/>
       <c r="AA9" s="356"/>
-      <c r="AB9" s="356"/>
+      <c r="AB9" s="18"/>
       <c r="AC9" s="18"/>
       <c r="AD9" s="18"/>
       <c r="AE9" s="18"/>
       <c r="AF9" s="18"/>
       <c r="AG9" s="18"/>
-      <c r="AH9" s="18"/>
+      <c r="AH9" s="356"/>
       <c r="AI9" s="356"/>
       <c r="AJ9" s="356"/>
-      <c r="AK9" s="356"/>
+      <c r="AK9" s="18"/>
       <c r="AL9" s="18"/>
       <c r="AM9" s="18"/>
       <c r="AN9" s="18"/>
@@ -20384,95 +20384,95 @@
       <c r="AR9" s="18"/>
       <c r="AS9" s="18"/>
       <c r="AT9" s="18"/>
-      <c r="AU9" s="18"/>
-      <c r="AV9" s="26"/>
-      <c r="AX9" s="42">
+      <c r="AU9" s="26"/>
+      <c r="AW9" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY9" s="23" cm="1">
-        <f t="array" ref="AY9">SUM(COUNTIFS(I9:AV9,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ9" s="23">
+      <c r="AX9" s="23" cm="1">
+        <f t="array" ref="AX9">SUM(COUNTIFS(H9:AU9,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY9" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA9" s="23" cm="1">
-        <f t="array" ref="BA9">SUM(COUNTIFS(I9:AV9,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB9" s="23">
+      <c r="AZ9" s="23" cm="1">
+        <f t="array" ref="AZ9">SUM(COUNTIFS(H9:AU9,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA9" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC9" s="278">
+      <c r="BB9" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD9" s="39">
+      <c r="BC9" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE9" s="25">
+      <c r="BD9" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF9" s="26">
+      <c r="BE9" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG9" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C9,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH9" s="26">
+      <c r="BF9" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B9,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG9" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="3:68" x14ac:dyDescent="0.2">
-      <c r="C10" s="71"/>
+    <row r="10" spans="2:67" x14ac:dyDescent="0.2">
+      <c r="B10" s="71"/>
+      <c r="C10" s="18"/>
       <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="307"/>
-      <c r="G10" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C10,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C10,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H10" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C10,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C11,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I10" s="24"/>
+      <c r="E10" s="307"/>
+      <c r="F10" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B10,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B10,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B10,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B11,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="24"/>
+      <c r="I10" s="356"/>
       <c r="J10" s="356"/>
-      <c r="K10" s="356"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="356"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="356"/>
+      <c r="M10" s="18"/>
       <c r="N10" s="18"/>
       <c r="O10" s="18"/>
       <c r="P10" s="18"/>
       <c r="Q10" s="18"/>
-      <c r="R10" s="18"/>
-      <c r="S10" s="356"/>
+      <c r="R10" s="356"/>
+      <c r="S10" s="18"/>
       <c r="T10" s="18"/>
       <c r="U10" s="18"/>
       <c r="V10" s="18"/>
       <c r="W10" s="18"/>
       <c r="X10" s="18"/>
       <c r="Y10" s="18"/>
-      <c r="Z10" s="18"/>
+      <c r="Z10" s="356"/>
       <c r="AA10" s="356"/>
-      <c r="AB10" s="356"/>
+      <c r="AB10" s="18"/>
       <c r="AC10" s="18"/>
       <c r="AD10" s="18"/>
       <c r="AE10" s="18"/>
       <c r="AF10" s="18"/>
       <c r="AG10" s="18"/>
-      <c r="AH10" s="18"/>
+      <c r="AH10" s="356"/>
       <c r="AI10" s="356"/>
       <c r="AJ10" s="356"/>
-      <c r="AK10" s="356"/>
+      <c r="AK10" s="18"/>
       <c r="AL10" s="18"/>
       <c r="AM10" s="18"/>
       <c r="AN10" s="18"/>
@@ -20482,95 +20482,95 @@
       <c r="AR10" s="18"/>
       <c r="AS10" s="18"/>
       <c r="AT10" s="18"/>
-      <c r="AU10" s="18"/>
-      <c r="AV10" s="26"/>
-      <c r="AX10" s="42">
+      <c r="AU10" s="26"/>
+      <c r="AW10" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY10" s="23" cm="1">
-        <f t="array" ref="AY10">SUM(COUNTIFS(I10:AV10,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ10" s="23">
+      <c r="AX10" s="23" cm="1">
+        <f t="array" ref="AX10">SUM(COUNTIFS(H10:AU10,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY10" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA10" s="23" cm="1">
-        <f t="array" ref="BA10">SUM(COUNTIFS(I10:AV10,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB10" s="23">
+      <c r="AZ10" s="23" cm="1">
+        <f t="array" ref="AZ10">SUM(COUNTIFS(H10:AU10,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA10" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC10" s="278">
+      <c r="BB10" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD10" s="39">
+      <c r="BC10" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE10" s="25">
+      <c r="BD10" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF10" s="26">
+      <c r="BE10" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG10" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C10,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH10" s="26">
+      <c r="BF10" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B10,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG10" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="3:68" x14ac:dyDescent="0.2">
-      <c r="C11" s="71"/>
+    <row r="11" spans="2:67" x14ac:dyDescent="0.2">
+      <c r="B11" s="71"/>
+      <c r="C11" s="18"/>
       <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="307"/>
-      <c r="G11" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C11,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C11,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C11,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C12,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I11" s="24"/>
+      <c r="E11" s="307"/>
+      <c r="F11" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B11,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B11,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B11,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B12,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="24"/>
+      <c r="I11" s="356"/>
       <c r="J11" s="356"/>
-      <c r="K11" s="356"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="356"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="356"/>
+      <c r="M11" s="18"/>
       <c r="N11" s="18"/>
       <c r="O11" s="18"/>
       <c r="P11" s="18"/>
       <c r="Q11" s="18"/>
-      <c r="R11" s="18"/>
-      <c r="S11" s="356"/>
+      <c r="R11" s="356"/>
+      <c r="S11" s="18"/>
       <c r="T11" s="18"/>
       <c r="U11" s="18"/>
       <c r="V11" s="18"/>
       <c r="W11" s="18"/>
       <c r="X11" s="18"/>
       <c r="Y11" s="18"/>
-      <c r="Z11" s="18"/>
+      <c r="Z11" s="356"/>
       <c r="AA11" s="356"/>
-      <c r="AB11" s="356"/>
+      <c r="AB11" s="18"/>
       <c r="AC11" s="18"/>
       <c r="AD11" s="18"/>
       <c r="AE11" s="18"/>
       <c r="AF11" s="18"/>
       <c r="AG11" s="18"/>
-      <c r="AH11" s="18"/>
+      <c r="AH11" s="356"/>
       <c r="AI11" s="356"/>
       <c r="AJ11" s="356"/>
-      <c r="AK11" s="356"/>
+      <c r="AK11" s="18"/>
       <c r="AL11" s="18"/>
       <c r="AM11" s="18"/>
       <c r="AN11" s="18"/>
@@ -20580,69 +20580,69 @@
       <c r="AR11" s="18"/>
       <c r="AS11" s="18"/>
       <c r="AT11" s="18"/>
-      <c r="AU11" s="18"/>
-      <c r="AV11" s="26"/>
-      <c r="AX11" s="42">
+      <c r="AU11" s="26"/>
+      <c r="AW11" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY11" s="23" cm="1">
-        <f t="array" ref="AY11">SUM(COUNTIFS(I11:AV11,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ11" s="23">
+      <c r="AX11" s="23" cm="1">
+        <f t="array" ref="AX11">SUM(COUNTIFS(H11:AU11,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY11" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA11" s="23" cm="1">
-        <f t="array" ref="BA11">SUM(COUNTIFS(I11:AV11,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB11" s="23">
+      <c r="AZ11" s="23" cm="1">
+        <f t="array" ref="AZ11">SUM(COUNTIFS(H11:AU11,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA11" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC11" s="278">
+      <c r="BB11" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD11" s="39">
+      <c r="BC11" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE11" s="25">
+      <c r="BD11" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF11" s="26">
+      <c r="BE11" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG11" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C11,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH11" s="26">
+      <c r="BF11" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B11,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG11" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="3:68" x14ac:dyDescent="0.2">
-      <c r="C12" s="71"/>
+    <row r="12" spans="2:67" x14ac:dyDescent="0.2">
+      <c r="B12" s="71"/>
+      <c r="C12" s="18"/>
       <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="307"/>
-      <c r="G12" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C12,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C12,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C12,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C13,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I12" s="365"/>
+      <c r="E12" s="307"/>
+      <c r="F12" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B12,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B12,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B12,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B13,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="365"/>
+      <c r="I12" s="356"/>
       <c r="J12" s="356"/>
-      <c r="K12" s="356"/>
+      <c r="K12" s="18"/>
       <c r="L12" s="18"/>
       <c r="M12" s="18"/>
       <c r="N12" s="18"/>
@@ -20653,24 +20653,24 @@
       <c r="S12" s="18"/>
       <c r="T12" s="18"/>
       <c r="U12" s="18"/>
-      <c r="V12" s="18"/>
+      <c r="V12" s="356"/>
       <c r="W12" s="356"/>
       <c r="X12" s="356"/>
       <c r="Y12" s="356"/>
       <c r="Z12" s="356"/>
-      <c r="AA12" s="356"/>
-      <c r="AB12" s="18"/>
-      <c r="AC12" s="356"/>
+      <c r="AA12" s="18"/>
+      <c r="AB12" s="356"/>
+      <c r="AC12" s="18"/>
       <c r="AD12" s="18"/>
       <c r="AE12" s="18"/>
-      <c r="AF12" s="18"/>
+      <c r="AF12" s="356"/>
       <c r="AG12" s="356"/>
       <c r="AH12" s="356"/>
-      <c r="AI12" s="356"/>
+      <c r="AI12" s="18"/>
       <c r="AJ12" s="18"/>
       <c r="AK12" s="18"/>
       <c r="AL12" s="18"/>
-      <c r="AM12" s="18"/>
+      <c r="AM12" s="356"/>
       <c r="AN12" s="356"/>
       <c r="AO12" s="356"/>
       <c r="AP12" s="356"/>
@@ -20678,86 +20678,86 @@
       <c r="AR12" s="356"/>
       <c r="AS12" s="356"/>
       <c r="AT12" s="356"/>
-      <c r="AU12" s="356"/>
-      <c r="AV12" s="358"/>
-      <c r="AX12" s="42">
+      <c r="AU12" s="358"/>
+      <c r="AW12" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY12" s="23" cm="1">
-        <f t="array" ref="AY12">SUM(COUNTIFS(I12:AV12,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ12" s="23">
+      <c r="AX12" s="23" cm="1">
+        <f t="array" ref="AX12">SUM(COUNTIFS(H12:AU12,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY12" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA12" s="23" cm="1">
-        <f t="array" ref="BA12">SUM(COUNTIFS(I12:AV12,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB12" s="23">
+      <c r="AZ12" s="23" cm="1">
+        <f t="array" ref="AZ12">SUM(COUNTIFS(H12:AU12,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA12" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC12" s="278">
+      <c r="BB12" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD12" s="39">
+      <c r="BC12" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE12" s="25">
+      <c r="BD12" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF12" s="26">
+      <c r="BE12" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG12" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C12,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH12" s="26">
+      <c r="BF12" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B12,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG12" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="3:68" x14ac:dyDescent="0.2">
-      <c r="C13" s="71"/>
+    <row r="13" spans="2:67" x14ac:dyDescent="0.2">
+      <c r="B13" s="71"/>
+      <c r="C13" s="18"/>
       <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="307"/>
-      <c r="G13" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C13,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C13,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C13,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C14,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I13" s="24"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="356"/>
-      <c r="L13" s="18"/>
-      <c r="M13" s="356"/>
-      <c r="N13" s="18"/>
+      <c r="E13" s="307"/>
+      <c r="F13" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B13,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B13,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B13,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B14,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="24"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="356"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="356"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="356"/>
       <c r="O13" s="356"/>
       <c r="P13" s="356"/>
       <c r="Q13" s="356"/>
       <c r="R13" s="356"/>
       <c r="S13" s="356"/>
-      <c r="T13" s="356"/>
+      <c r="T13" s="18"/>
       <c r="U13" s="18"/>
       <c r="V13" s="18"/>
       <c r="W13" s="18"/>
-      <c r="X13" s="18"/>
+      <c r="X13" s="356"/>
       <c r="Y13" s="356"/>
       <c r="Z13" s="356"/>
       <c r="AA13" s="356"/>
-      <c r="AB13" s="356"/>
+      <c r="AB13" s="18"/>
       <c r="AC13" s="18"/>
       <c r="AD13" s="18"/>
       <c r="AE13" s="18"/>
@@ -20776,86 +20776,86 @@
       <c r="AR13" s="18"/>
       <c r="AS13" s="18"/>
       <c r="AT13" s="18"/>
-      <c r="AU13" s="18"/>
-      <c r="AV13" s="26"/>
-      <c r="AX13" s="42">
+      <c r="AU13" s="26"/>
+      <c r="AW13" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY13" s="23" cm="1">
-        <f t="array" ref="AY13">SUM(COUNTIFS(I13:AV13,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ13" s="23">
+      <c r="AX13" s="23" cm="1">
+        <f t="array" ref="AX13">SUM(COUNTIFS(H13:AU13,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY13" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA13" s="23" cm="1">
-        <f t="array" ref="BA13">SUM(COUNTIFS(I13:AV13,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB13" s="23">
+      <c r="AZ13" s="23" cm="1">
+        <f t="array" ref="AZ13">SUM(COUNTIFS(H13:AU13,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA13" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC13" s="278">
+      <c r="BB13" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD13" s="39">
+      <c r="BC13" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE13" s="25">
+      <c r="BD13" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF13" s="26">
+      <c r="BE13" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG13" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C13,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH13" s="26">
+      <c r="BF13" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B13,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG13" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="3:68" x14ac:dyDescent="0.2">
-      <c r="C14" s="71"/>
+    <row r="14" spans="2:67" x14ac:dyDescent="0.2">
+      <c r="B14" s="71"/>
+      <c r="C14" s="18"/>
       <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="307"/>
-      <c r="G14" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C14,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C14,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C14,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C15,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I14" s="24"/>
+      <c r="E14" s="307"/>
+      <c r="F14" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B14,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B14,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B14,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B15,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="24"/>
+      <c r="I14" s="18"/>
       <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="356"/>
+      <c r="K14" s="356"/>
+      <c r="L14" s="18"/>
       <c r="M14" s="18"/>
       <c r="N14" s="18"/>
       <c r="O14" s="18"/>
       <c r="P14" s="18"/>
-      <c r="Q14" s="18"/>
-      <c r="R14" s="356"/>
+      <c r="Q14" s="356"/>
+      <c r="R14" s="18"/>
       <c r="S14" s="18"/>
       <c r="T14" s="18"/>
-      <c r="U14" s="18"/>
+      <c r="U14" s="356"/>
       <c r="V14" s="356"/>
       <c r="W14" s="356"/>
-      <c r="X14" s="356"/>
+      <c r="X14" s="18"/>
       <c r="Y14" s="18"/>
-      <c r="Z14" s="18"/>
+      <c r="Z14" s="356"/>
       <c r="AA14" s="356"/>
-      <c r="AB14" s="356"/>
+      <c r="AB14" s="18"/>
       <c r="AC14" s="18"/>
       <c r="AD14" s="18"/>
       <c r="AE14" s="18"/>
@@ -20874,93 +20874,93 @@
       <c r="AR14" s="18"/>
       <c r="AS14" s="18"/>
       <c r="AT14" s="18"/>
-      <c r="AU14" s="18"/>
-      <c r="AV14" s="26"/>
-      <c r="AX14" s="42">
+      <c r="AU14" s="26"/>
+      <c r="AW14" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY14" s="23" cm="1">
-        <f t="array" ref="AY14">SUM(COUNTIFS(I14:AV14,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ14" s="23">
+      <c r="AX14" s="23" cm="1">
+        <f t="array" ref="AX14">SUM(COUNTIFS(H14:AU14,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY14" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA14" s="23" cm="1">
-        <f t="array" ref="BA14">SUM(COUNTIFS(I14:AV14,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB14" s="23">
+      <c r="AZ14" s="23" cm="1">
+        <f t="array" ref="AZ14">SUM(COUNTIFS(H14:AU14,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA14" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC14" s="278">
+      <c r="BB14" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD14" s="39">
+      <c r="BC14" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE14" s="25">
+      <c r="BD14" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF14" s="26">
+      <c r="BE14" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG14" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C14,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH14" s="26">
+      <c r="BF14" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B14,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG14" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="3:68" x14ac:dyDescent="0.2">
-      <c r="C15" s="71"/>
+    <row r="15" spans="2:67" x14ac:dyDescent="0.2">
+      <c r="B15" s="71"/>
+      <c r="C15" s="18"/>
       <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="307"/>
-      <c r="G15" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C15,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C15,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C15,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C16,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I15" s="24"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="356"/>
-      <c r="L15" s="18"/>
+      <c r="E15" s="307"/>
+      <c r="F15" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B15,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B15,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B15,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B16,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="24"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="356"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="356"/>
       <c r="M15" s="356"/>
       <c r="N15" s="356"/>
       <c r="O15" s="356"/>
       <c r="P15" s="356"/>
       <c r="Q15" s="356"/>
       <c r="R15" s="356"/>
-      <c r="S15" s="356"/>
-      <c r="T15" s="18"/>
+      <c r="S15" s="18"/>
+      <c r="T15" s="356"/>
       <c r="U15" s="356"/>
       <c r="V15" s="356"/>
       <c r="W15" s="356"/>
-      <c r="X15" s="356"/>
+      <c r="X15" s="18"/>
       <c r="Y15" s="18"/>
-      <c r="Z15" s="18"/>
+      <c r="Z15" s="356"/>
       <c r="AA15" s="356"/>
-      <c r="AB15" s="356"/>
+      <c r="AB15" s="18"/>
       <c r="AC15" s="18"/>
       <c r="AD15" s="18"/>
       <c r="AE15" s="18"/>
-      <c r="AF15" s="18"/>
+      <c r="AF15" s="356"/>
       <c r="AG15" s="356"/>
       <c r="AH15" s="356"/>
-      <c r="AI15" s="356"/>
+      <c r="AI15" s="18"/>
       <c r="AJ15" s="18"/>
       <c r="AK15" s="18"/>
       <c r="AL15" s="18"/>
@@ -20972,97 +20972,97 @@
       <c r="AR15" s="18"/>
       <c r="AS15" s="18"/>
       <c r="AT15" s="18"/>
-      <c r="AU15" s="18"/>
-      <c r="AV15" s="26"/>
-      <c r="AX15" s="42">
+      <c r="AU15" s="26"/>
+      <c r="AW15" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY15" s="23" cm="1">
-        <f t="array" ref="AY15">SUM(COUNTIFS(I15:AV15,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ15" s="23">
+      <c r="AX15" s="23" cm="1">
+        <f t="array" ref="AX15">SUM(COUNTIFS(H15:AU15,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY15" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA15" s="23" cm="1">
-        <f t="array" ref="BA15">SUM(COUNTIFS(I15:AV15,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB15" s="23">
+      <c r="AZ15" s="23" cm="1">
+        <f t="array" ref="AZ15">SUM(COUNTIFS(H15:AU15,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA15" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC15" s="278">
+      <c r="BB15" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD15" s="39">
+      <c r="BC15" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE15" s="25">
+      <c r="BD15" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF15" s="26">
+      <c r="BE15" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG15" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C15,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH15" s="26">
+      <c r="BF15" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B15,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG15" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="3:68" x14ac:dyDescent="0.2">
-      <c r="C16" s="71"/>
+    <row r="16" spans="2:67" x14ac:dyDescent="0.2">
+      <c r="B16" s="71"/>
+      <c r="C16" s="18"/>
       <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="307"/>
-      <c r="G16" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C16,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C16,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C16,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C17,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I16" s="24"/>
+      <c r="E16" s="307"/>
+      <c r="F16" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B16,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B16,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B16,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B17,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="24"/>
+      <c r="I16" s="18"/>
       <c r="J16" s="18"/>
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
       <c r="M16" s="18"/>
       <c r="N16" s="18"/>
       <c r="O16" s="18"/>
-      <c r="P16" s="18"/>
+      <c r="P16" s="356"/>
       <c r="Q16" s="356"/>
       <c r="R16" s="356"/>
       <c r="S16" s="356"/>
-      <c r="T16" s="356"/>
+      <c r="T16" s="18"/>
       <c r="U16" s="18"/>
       <c r="V16" s="18"/>
       <c r="W16" s="18"/>
       <c r="X16" s="18"/>
       <c r="Y16" s="18"/>
-      <c r="Z16" s="18"/>
+      <c r="Z16" s="356"/>
       <c r="AA16" s="356"/>
-      <c r="AB16" s="356"/>
+      <c r="AB16" s="18"/>
       <c r="AC16" s="18"/>
       <c r="AD16" s="18"/>
       <c r="AE16" s="18"/>
       <c r="AF16" s="18"/>
-      <c r="AG16" s="18"/>
-      <c r="AH16" s="356"/>
+      <c r="AG16" s="356"/>
+      <c r="AH16" s="18"/>
       <c r="AI16" s="18"/>
       <c r="AJ16" s="18"/>
-      <c r="AK16" s="18"/>
-      <c r="AL16" s="356"/>
-      <c r="AM16" s="18"/>
+      <c r="AK16" s="356"/>
+      <c r="AL16" s="18"/>
+      <c r="AM16" s="356"/>
       <c r="AN16" s="356"/>
       <c r="AO16" s="356"/>
       <c r="AP16" s="356"/>
@@ -21070,68 +21070,68 @@
       <c r="AR16" s="356"/>
       <c r="AS16" s="356"/>
       <c r="AT16" s="356"/>
-      <c r="AU16" s="356"/>
-      <c r="AV16" s="358"/>
-      <c r="AX16" s="42">
+      <c r="AU16" s="358"/>
+      <c r="AW16" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY16" s="23" cm="1">
-        <f t="array" ref="AY16">SUM(COUNTIFS(I16:AV16,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ16" s="23">
+      <c r="AX16" s="23" cm="1">
+        <f t="array" ref="AX16">SUM(COUNTIFS(H16:AU16,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY16" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA16" s="23" cm="1">
-        <f t="array" ref="BA16">SUM(COUNTIFS(I16:AV16,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB16" s="23">
+      <c r="AZ16" s="23" cm="1">
+        <f t="array" ref="AZ16">SUM(COUNTIFS(H16:AU16,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA16" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC16" s="278">
+      <c r="BB16" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD16" s="39">
+      <c r="BC16" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE16" s="25">
+      <c r="BD16" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF16" s="26">
+      <c r="BE16" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG16" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C16,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH16" s="26">
+      <c r="BF16" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B16,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG16" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C17" s="71"/>
+    <row r="17" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B17" s="71"/>
+      <c r="C17" s="18"/>
       <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="307"/>
-      <c r="G17" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C17,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C17,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C17,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C18,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I17" s="24"/>
-      <c r="J17" s="18"/>
+      <c r="E17" s="307"/>
+      <c r="F17" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B17,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B17,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B17,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B18,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="24"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="356"/>
       <c r="K17" s="356"/>
       <c r="L17" s="356"/>
       <c r="M17" s="356"/>
@@ -21142,25 +21142,25 @@
       <c r="R17" s="356"/>
       <c r="S17" s="356"/>
       <c r="T17" s="356"/>
-      <c r="U17" s="356"/>
+      <c r="U17" s="18"/>
       <c r="V17" s="18"/>
       <c r="W17" s="18"/>
-      <c r="X17" s="18"/>
-      <c r="Y17" s="356"/>
-      <c r="Z17" s="18"/>
-      <c r="AA17" s="356"/>
+      <c r="X17" s="356"/>
+      <c r="Y17" s="18"/>
+      <c r="Z17" s="356"/>
+      <c r="AA17" s="18"/>
       <c r="AB17" s="18"/>
       <c r="AC17" s="18"/>
       <c r="AD17" s="18"/>
       <c r="AE17" s="18"/>
       <c r="AF17" s="18"/>
-      <c r="AG17" s="18"/>
+      <c r="AG17" s="356"/>
       <c r="AH17" s="356"/>
-      <c r="AI17" s="356"/>
+      <c r="AI17" s="18"/>
       <c r="AJ17" s="18"/>
       <c r="AK17" s="18"/>
       <c r="AL17" s="18"/>
-      <c r="AM17" s="18"/>
+      <c r="AM17" s="356"/>
       <c r="AN17" s="356"/>
       <c r="AO17" s="356"/>
       <c r="AP17" s="356"/>
@@ -21168,78 +21168,78 @@
       <c r="AR17" s="356"/>
       <c r="AS17" s="356"/>
       <c r="AT17" s="356"/>
-      <c r="AU17" s="356"/>
-      <c r="AV17" s="358"/>
-      <c r="AX17" s="42">
+      <c r="AU17" s="358"/>
+      <c r="AW17" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY17" s="23" cm="1">
-        <f t="array" ref="AY17">SUM(COUNTIFS(I17:AV17,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ17" s="23">
+      <c r="AX17" s="23" cm="1">
+        <f t="array" ref="AX17">SUM(COUNTIFS(H17:AU17,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY17" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA17" s="23" cm="1">
-        <f t="array" ref="BA17">SUM(COUNTIFS(I17:AV17,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB17" s="23">
+      <c r="AZ17" s="23" cm="1">
+        <f t="array" ref="AZ17">SUM(COUNTIFS(H17:AU17,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA17" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC17" s="278">
+      <c r="BB17" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD17" s="39">
+      <c r="BC17" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE17" s="25">
+      <c r="BD17" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF17" s="26">
+      <c r="BE17" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG17" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C17,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH17" s="26">
+      <c r="BF17" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B17,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG17" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C18" s="71"/>
+    <row r="18" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B18" s="71"/>
+      <c r="C18" s="18"/>
       <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="307"/>
-      <c r="G18" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C18,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C18,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C18,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C19,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I18" s="24"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="356"/>
+      <c r="E18" s="307"/>
+      <c r="F18" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B18,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B18,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B18,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B19,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="24"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="356"/>
+      <c r="K18" s="18"/>
       <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="356"/>
+      <c r="M18" s="356"/>
+      <c r="N18" s="18"/>
       <c r="O18" s="18"/>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="356"/>
+      <c r="P18" s="356"/>
+      <c r="Q18" s="18"/>
       <c r="R18" s="18"/>
-      <c r="S18" s="18"/>
-      <c r="T18" s="356"/>
+      <c r="S18" s="356"/>
+      <c r="T18" s="18"/>
       <c r="U18" s="18"/>
       <c r="V18" s="18"/>
       <c r="W18" s="18"/>
@@ -21249,15 +21249,15 @@
       <c r="AA18" s="18"/>
       <c r="AB18" s="18"/>
       <c r="AC18" s="18"/>
-      <c r="AD18" s="18"/>
-      <c r="AE18" s="356"/>
+      <c r="AD18" s="356"/>
+      <c r="AE18" s="18"/>
       <c r="AF18" s="18"/>
-      <c r="AG18" s="18"/>
-      <c r="AH18" s="356"/>
+      <c r="AG18" s="356"/>
+      <c r="AH18" s="18"/>
       <c r="AI18" s="18"/>
       <c r="AJ18" s="18"/>
       <c r="AK18" s="18"/>
-      <c r="AL18" s="18"/>
+      <c r="AL18" s="356"/>
       <c r="AM18" s="356"/>
       <c r="AN18" s="356"/>
       <c r="AO18" s="356"/>
@@ -21266,97 +21266,97 @@
       <c r="AR18" s="356"/>
       <c r="AS18" s="356"/>
       <c r="AT18" s="356"/>
-      <c r="AU18" s="356"/>
-      <c r="AV18" s="358"/>
-      <c r="AX18" s="42">
+      <c r="AU18" s="358"/>
+      <c r="AW18" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY18" s="23" cm="1">
-        <f t="array" ref="AY18">SUM(COUNTIFS(I18:AV18,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ18" s="23">
+      <c r="AX18" s="23" cm="1">
+        <f t="array" ref="AX18">SUM(COUNTIFS(H18:AU18,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY18" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA18" s="23" cm="1">
-        <f t="array" ref="BA18">SUM(COUNTIFS(I18:AV18,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB18" s="23">
+      <c r="AZ18" s="23" cm="1">
+        <f t="array" ref="AZ18">SUM(COUNTIFS(H18:AU18,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA18" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC18" s="278">
+      <c r="BB18" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD18" s="39">
+      <c r="BC18" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE18" s="25">
+      <c r="BD18" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF18" s="26">
+      <c r="BE18" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG18" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C18,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH18" s="26">
+      <c r="BF18" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B18,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG18" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C19" s="71"/>
+    <row r="19" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B19" s="71"/>
+      <c r="C19" s="18"/>
       <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="307"/>
-      <c r="G19" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C19,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C19,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C19,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C20,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I19" s="24"/>
+      <c r="E19" s="307"/>
+      <c r="F19" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B19,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B19,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B19,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B20,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="24"/>
+      <c r="I19" s="18"/>
       <c r="J19" s="18"/>
       <c r="K19" s="18"/>
       <c r="L19" s="18"/>
       <c r="M19" s="18"/>
       <c r="N19" s="18"/>
       <c r="O19" s="18"/>
-      <c r="P19" s="18"/>
+      <c r="P19" s="356"/>
       <c r="Q19" s="356"/>
       <c r="R19" s="356"/>
-      <c r="S19" s="356"/>
+      <c r="S19" s="18"/>
       <c r="T19" s="18"/>
       <c r="U19" s="18"/>
-      <c r="V19" s="18"/>
-      <c r="W19" s="356"/>
+      <c r="V19" s="356"/>
+      <c r="W19" s="18"/>
       <c r="X19" s="18"/>
       <c r="Y19" s="18"/>
-      <c r="Z19" s="18"/>
-      <c r="AA19" s="356"/>
+      <c r="Z19" s="356"/>
+      <c r="AA19" s="18"/>
       <c r="AB19" s="18"/>
-      <c r="AC19" s="18"/>
-      <c r="AD19" s="356"/>
+      <c r="AC19" s="356"/>
+      <c r="AD19" s="18"/>
       <c r="AE19" s="18"/>
-      <c r="AF19" s="18"/>
+      <c r="AF19" s="356"/>
       <c r="AG19" s="356"/>
-      <c r="AH19" s="356"/>
+      <c r="AH19" s="18"/>
       <c r="AI19" s="18"/>
       <c r="AJ19" s="18"/>
       <c r="AK19" s="18"/>
       <c r="AL19" s="18"/>
-      <c r="AM19" s="18"/>
+      <c r="AM19" s="356"/>
       <c r="AN19" s="356"/>
       <c r="AO19" s="356"/>
       <c r="AP19" s="356"/>
@@ -21364,69 +21364,69 @@
       <c r="AR19" s="356"/>
       <c r="AS19" s="356"/>
       <c r="AT19" s="356"/>
-      <c r="AU19" s="356"/>
-      <c r="AV19" s="358"/>
-      <c r="AX19" s="42">
+      <c r="AU19" s="358"/>
+      <c r="AW19" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY19" s="23" cm="1">
-        <f t="array" ref="AY19">SUM(COUNTIFS(I19:AV19,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ19" s="23">
+      <c r="AX19" s="23" cm="1">
+        <f t="array" ref="AX19">SUM(COUNTIFS(H19:AU19,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY19" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA19" s="23" cm="1">
-        <f t="array" ref="BA19">SUM(COUNTIFS(I19:AV19,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB19" s="23">
+      <c r="AZ19" s="23" cm="1">
+        <f t="array" ref="AZ19">SUM(COUNTIFS(H19:AU19,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA19" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC19" s="278">
+      <c r="BB19" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD19" s="39">
+      <c r="BC19" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE19" s="25">
+      <c r="BD19" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF19" s="26">
+      <c r="BE19" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG19" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C19,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH19" s="26">
+      <c r="BF19" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B19,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG19" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C20" s="71"/>
+    <row r="20" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B20" s="71"/>
+      <c r="C20" s="18"/>
       <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="307"/>
-      <c r="G20" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C20,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C20,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C20,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C21,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I20" s="24"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="356"/>
+      <c r="E20" s="307"/>
+      <c r="F20" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B20,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B20,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B20,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B21,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="24"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="356"/>
+      <c r="K20" s="18"/>
       <c r="L20" s="18"/>
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
@@ -21434,12 +21434,12 @@
       <c r="P20" s="18"/>
       <c r="Q20" s="18"/>
       <c r="R20" s="18"/>
-      <c r="S20" s="18"/>
-      <c r="T20" s="356"/>
+      <c r="S20" s="356"/>
+      <c r="T20" s="18"/>
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
       <c r="W20" s="18"/>
-      <c r="X20" s="18"/>
+      <c r="X20" s="356"/>
       <c r="Y20" s="356"/>
       <c r="Z20" s="356"/>
       <c r="AA20" s="356"/>
@@ -21453,7 +21453,7 @@
       <c r="AI20" s="356"/>
       <c r="AJ20" s="356"/>
       <c r="AK20" s="356"/>
-      <c r="AL20" s="356"/>
+      <c r="AL20" s="18"/>
       <c r="AM20" s="18"/>
       <c r="AN20" s="18"/>
       <c r="AO20" s="18"/>
@@ -21462,67 +21462,67 @@
       <c r="AR20" s="18"/>
       <c r="AS20" s="18"/>
       <c r="AT20" s="18"/>
-      <c r="AU20" s="18"/>
-      <c r="AV20" s="26"/>
-      <c r="AX20" s="42">
+      <c r="AU20" s="26"/>
+      <c r="AW20" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY20" s="23" cm="1">
-        <f t="array" ref="AY20">SUM(COUNTIFS(I20:AV20,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ20" s="23">
+      <c r="AX20" s="23" cm="1">
+        <f t="array" ref="AX20">SUM(COUNTIFS(H20:AU20,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY20" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA20" s="23" cm="1">
-        <f t="array" ref="BA20">SUM(COUNTIFS(I20:AV20,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB20" s="23">
+      <c r="AZ20" s="23" cm="1">
+        <f t="array" ref="AZ20">SUM(COUNTIFS(H20:AU20,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA20" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC20" s="278">
+      <c r="BB20" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD20" s="39">
+      <c r="BC20" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE20" s="25">
+      <c r="BD20" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF20" s="26">
+      <c r="BE20" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG20" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C20,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH20" s="26">
+      <c r="BF20" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B20,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG20" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C21" s="71"/>
+    <row r="21" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B21" s="71"/>
+      <c r="C21" s="18"/>
       <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="307"/>
-      <c r="G21" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C21,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C21,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C21,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C22,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I21" s="24"/>
+      <c r="E21" s="307"/>
+      <c r="F21" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B21,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B21,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B21,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B22,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="24"/>
+      <c r="I21" s="18"/>
       <c r="J21" s="18"/>
       <c r="K21" s="18"/>
       <c r="L21" s="18"/>
@@ -21530,16 +21530,16 @@
       <c r="N21" s="18"/>
       <c r="O21" s="18"/>
       <c r="P21" s="18"/>
-      <c r="Q21" s="18"/>
-      <c r="R21" s="356"/>
+      <c r="Q21" s="356"/>
+      <c r="R21" s="18"/>
       <c r="S21" s="18"/>
       <c r="T21" s="18"/>
       <c r="U21" s="18"/>
-      <c r="V21" s="18"/>
-      <c r="W21" s="356"/>
-      <c r="X21" s="18"/>
-      <c r="Y21" s="356"/>
-      <c r="Z21" s="18"/>
+      <c r="V21" s="356"/>
+      <c r="W21" s="18"/>
+      <c r="X21" s="356"/>
+      <c r="Y21" s="18"/>
+      <c r="Z21" s="356"/>
       <c r="AA21" s="356"/>
       <c r="AB21" s="356"/>
       <c r="AC21" s="356"/>
@@ -21551,8 +21551,8 @@
       <c r="AI21" s="356"/>
       <c r="AJ21" s="356"/>
       <c r="AK21" s="356"/>
-      <c r="AL21" s="356"/>
-      <c r="AM21" s="18"/>
+      <c r="AL21" s="18"/>
+      <c r="AM21" s="356"/>
       <c r="AN21" s="356"/>
       <c r="AO21" s="356"/>
       <c r="AP21" s="356"/>
@@ -21560,76 +21560,76 @@
       <c r="AR21" s="356"/>
       <c r="AS21" s="356"/>
       <c r="AT21" s="356"/>
-      <c r="AU21" s="356"/>
-      <c r="AV21" s="358"/>
-      <c r="AX21" s="42">
+      <c r="AU21" s="358"/>
+      <c r="AW21" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY21" s="23" cm="1">
-        <f t="array" ref="AY21">SUM(COUNTIFS(I21:AV21,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ21" s="23">
+      <c r="AX21" s="23" cm="1">
+        <f t="array" ref="AX21">SUM(COUNTIFS(H21:AU21,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY21" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA21" s="23" cm="1">
-        <f t="array" ref="BA21">SUM(COUNTIFS(I21:AV21,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB21" s="23">
+      <c r="AZ21" s="23" cm="1">
+        <f t="array" ref="AZ21">SUM(COUNTIFS(H21:AU21,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA21" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC21" s="278">
+      <c r="BB21" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD21" s="39">
+      <c r="BC21" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE21" s="25">
+      <c r="BD21" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF21" s="26">
+      <c r="BE21" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG21" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C21,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH21" s="26">
+      <c r="BF21" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B21,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG21" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C22" s="71"/>
+    <row r="22" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B22" s="71"/>
+      <c r="C22" s="18"/>
       <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="307"/>
-      <c r="G22" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C22,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C22,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C22,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C23,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I22" s="24"/>
+      <c r="E22" s="307"/>
+      <c r="F22" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B22,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B22,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B22,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B23,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="24"/>
+      <c r="I22" s="18"/>
       <c r="J22" s="18"/>
       <c r="K22" s="18"/>
       <c r="L22" s="18"/>
       <c r="M22" s="18"/>
-      <c r="N22" s="18"/>
+      <c r="N22" s="356"/>
       <c r="O22" s="356"/>
-      <c r="P22" s="356"/>
+      <c r="P22" s="18"/>
       <c r="Q22" s="18"/>
-      <c r="R22" s="18"/>
+      <c r="R22" s="356"/>
       <c r="S22" s="356"/>
       <c r="T22" s="356"/>
       <c r="U22" s="356"/>
@@ -21641,12 +21641,12 @@
       <c r="AA22" s="356"/>
       <c r="AB22" s="356"/>
       <c r="AC22" s="356"/>
-      <c r="AD22" s="356"/>
+      <c r="AD22" s="18"/>
       <c r="AE22" s="18"/>
       <c r="AF22" s="18"/>
-      <c r="AG22" s="18"/>
+      <c r="AG22" s="356"/>
       <c r="AH22" s="356"/>
-      <c r="AI22" s="356"/>
+      <c r="AI22" s="18"/>
       <c r="AJ22" s="18"/>
       <c r="AK22" s="18"/>
       <c r="AL22" s="18"/>
@@ -21658,70 +21658,70 @@
       <c r="AR22" s="18"/>
       <c r="AS22" s="18"/>
       <c r="AT22" s="18"/>
-      <c r="AU22" s="18"/>
-      <c r="AV22" s="26"/>
-      <c r="AX22" s="42">
+      <c r="AU22" s="26"/>
+      <c r="AW22" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY22" s="23" cm="1">
-        <f t="array" ref="AY22">SUM(COUNTIFS(I22:AV22,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ22" s="23">
+      <c r="AX22" s="23" cm="1">
+        <f t="array" ref="AX22">SUM(COUNTIFS(H22:AU22,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY22" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA22" s="23" cm="1">
-        <f t="array" ref="BA22">SUM(COUNTIFS(I22:AV22,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB22" s="23">
+      <c r="AZ22" s="23" cm="1">
+        <f t="array" ref="AZ22">SUM(COUNTIFS(H22:AU22,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA22" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC22" s="278">
+      <c r="BB22" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD22" s="39">
+      <c r="BC22" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE22" s="25">
+      <c r="BD22" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF22" s="26">
+      <c r="BE22" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG22" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C22,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH22" s="26">
+      <c r="BF22" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B22,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG22" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C23" s="71"/>
+    <row r="23" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B23" s="71"/>
+      <c r="C23" s="18"/>
       <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="307"/>
-      <c r="G23" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C23,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C23,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C23,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C24,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I23" s="24"/>
-      <c r="J23" s="18"/>
+      <c r="E23" s="307"/>
+      <c r="F23" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B23,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B23,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B23,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B24,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="24"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="356"/>
       <c r="K23" s="356"/>
-      <c r="L23" s="356"/>
+      <c r="L23" s="18"/>
       <c r="M23" s="18"/>
       <c r="N23" s="18"/>
       <c r="O23" s="18"/>
@@ -21729,12 +21729,12 @@
       <c r="Q23" s="18"/>
       <c r="R23" s="18"/>
       <c r="S23" s="18"/>
-      <c r="T23" s="18"/>
+      <c r="T23" s="356"/>
       <c r="U23" s="356"/>
       <c r="V23" s="356"/>
       <c r="W23" s="356"/>
       <c r="X23" s="356"/>
-      <c r="Y23" s="356"/>
+      <c r="Y23" s="18"/>
       <c r="Z23" s="18"/>
       <c r="AA23" s="18"/>
       <c r="AB23" s="18"/>
@@ -21743,12 +21743,12 @@
       <c r="AE23" s="18"/>
       <c r="AF23" s="18"/>
       <c r="AG23" s="18"/>
-      <c r="AH23" s="18"/>
-      <c r="AI23" s="356"/>
+      <c r="AH23" s="356"/>
+      <c r="AI23" s="18"/>
       <c r="AJ23" s="18"/>
       <c r="AK23" s="18"/>
       <c r="AL23" s="18"/>
-      <c r="AM23" s="18"/>
+      <c r="AM23" s="356"/>
       <c r="AN23" s="356"/>
       <c r="AO23" s="356"/>
       <c r="AP23" s="356"/>
@@ -21756,68 +21756,68 @@
       <c r="AR23" s="356"/>
       <c r="AS23" s="356"/>
       <c r="AT23" s="356"/>
-      <c r="AU23" s="356"/>
-      <c r="AV23" s="358"/>
-      <c r="AX23" s="42">
+      <c r="AU23" s="358"/>
+      <c r="AW23" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY23" s="23" cm="1">
-        <f t="array" ref="AY23">SUM(COUNTIFS(I23:AV23,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ23" s="23">
+      <c r="AX23" s="23" cm="1">
+        <f t="array" ref="AX23">SUM(COUNTIFS(H23:AU23,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY23" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA23" s="23" cm="1">
-        <f t="array" ref="BA23">SUM(COUNTIFS(I23:AV23,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB23" s="23">
+      <c r="AZ23" s="23" cm="1">
+        <f t="array" ref="AZ23">SUM(COUNTIFS(H23:AU23,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA23" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC23" s="278">
+      <c r="BB23" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD23" s="39">
+      <c r="BC23" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE23" s="25">
+      <c r="BD23" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF23" s="26">
+      <c r="BE23" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG23" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C23,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH23" s="26">
+      <c r="BF23" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B23,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG23" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C24" s="71"/>
+    <row r="24" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B24" s="71"/>
+      <c r="C24" s="18"/>
       <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="307"/>
-      <c r="G24" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C24,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C24,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C24,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C25,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I24" s="24"/>
-      <c r="J24" s="356"/>
+      <c r="E24" s="307"/>
+      <c r="F24" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B24,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B24,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B24,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B25,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="24"/>
+      <c r="I24" s="356"/>
+      <c r="J24" s="18"/>
       <c r="K24" s="18"/>
       <c r="L24" s="18"/>
       <c r="M24" s="18"/>
@@ -21826,11 +21826,11 @@
       <c r="P24" s="18"/>
       <c r="Q24" s="18"/>
       <c r="R24" s="18"/>
-      <c r="S24" s="18"/>
+      <c r="S24" s="356"/>
       <c r="T24" s="356"/>
-      <c r="U24" s="356"/>
+      <c r="U24" s="18"/>
       <c r="V24" s="18"/>
-      <c r="W24" s="18"/>
+      <c r="W24" s="356"/>
       <c r="X24" s="356"/>
       <c r="Y24" s="356"/>
       <c r="Z24" s="356"/>
@@ -21839,14 +21839,14 @@
       <c r="AC24" s="356"/>
       <c r="AD24" s="356"/>
       <c r="AE24" s="356"/>
-      <c r="AF24" s="356"/>
-      <c r="AG24" s="18"/>
+      <c r="AF24" s="18"/>
+      <c r="AG24" s="356"/>
       <c r="AH24" s="356"/>
       <c r="AI24" s="356"/>
       <c r="AJ24" s="356"/>
-      <c r="AK24" s="356"/>
+      <c r="AK24" s="18"/>
       <c r="AL24" s="18"/>
-      <c r="AM24" s="18"/>
+      <c r="AM24" s="356"/>
       <c r="AN24" s="356"/>
       <c r="AO24" s="356"/>
       <c r="AP24" s="356"/>
@@ -21854,84 +21854,84 @@
       <c r="AR24" s="356"/>
       <c r="AS24" s="356"/>
       <c r="AT24" s="356"/>
-      <c r="AU24" s="356"/>
-      <c r="AV24" s="358"/>
-      <c r="AX24" s="42">
+      <c r="AU24" s="358"/>
+      <c r="AW24" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY24" s="23" cm="1">
-        <f t="array" ref="AY24">SUM(COUNTIFS(I24:AV24,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ24" s="23">
+      <c r="AX24" s="23" cm="1">
+        <f t="array" ref="AX24">SUM(COUNTIFS(H24:AU24,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY24" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA24" s="23" cm="1">
-        <f t="array" ref="BA24">SUM(COUNTIFS(I24:AV24,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB24" s="23">
+      <c r="AZ24" s="23" cm="1">
+        <f t="array" ref="AZ24">SUM(COUNTIFS(H24:AU24,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA24" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC24" s="278">
+      <c r="BB24" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD24" s="39">
+      <c r="BC24" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE24" s="25">
+      <c r="BD24" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF24" s="26">
+      <c r="BE24" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG24" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C24,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH24" s="26">
+      <c r="BF24" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B24,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG24" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C25" s="71"/>
+    <row r="25" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B25" s="71"/>
+      <c r="C25" s="18"/>
       <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="307"/>
-      <c r="G25" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C25,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C25,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C25,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C26,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I25" s="24"/>
+      <c r="E25" s="307"/>
+      <c r="F25" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B25,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B25,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B25,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B26,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="24"/>
+      <c r="I25" s="18"/>
       <c r="J25" s="18"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="356"/>
-      <c r="M25" s="18"/>
-      <c r="N25" s="356"/>
+      <c r="K25" s="356"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="356"/>
+      <c r="N25" s="18"/>
       <c r="O25" s="18"/>
       <c r="P25" s="18"/>
       <c r="Q25" s="18"/>
       <c r="R25" s="18"/>
       <c r="S25" s="18"/>
-      <c r="T25" s="18"/>
-      <c r="U25" s="356"/>
+      <c r="T25" s="356"/>
+      <c r="U25" s="18"/>
       <c r="V25" s="18"/>
       <c r="W25" s="18"/>
-      <c r="X25" s="18"/>
+      <c r="X25" s="356"/>
       <c r="Y25" s="356"/>
-      <c r="Z25" s="356"/>
+      <c r="Z25" s="18"/>
       <c r="AA25" s="18"/>
       <c r="AB25" s="18"/>
       <c r="AC25" s="18"/>
@@ -21944,7 +21944,7 @@
       <c r="AJ25" s="18"/>
       <c r="AK25" s="18"/>
       <c r="AL25" s="18"/>
-      <c r="AM25" s="18"/>
+      <c r="AM25" s="356"/>
       <c r="AN25" s="356"/>
       <c r="AO25" s="356"/>
       <c r="AP25" s="356"/>
@@ -21952,70 +21952,70 @@
       <c r="AR25" s="356"/>
       <c r="AS25" s="356"/>
       <c r="AT25" s="356"/>
-      <c r="AU25" s="356"/>
-      <c r="AV25" s="358"/>
-      <c r="AX25" s="42">
+      <c r="AU25" s="358"/>
+      <c r="AW25" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY25" s="23" cm="1">
-        <f t="array" ref="AY25">SUM(COUNTIFS(I25:AV25,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ25" s="23">
+      <c r="AX25" s="23" cm="1">
+        <f t="array" ref="AX25">SUM(COUNTIFS(H25:AU25,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA25" s="23" cm="1">
-        <f t="array" ref="BA25">SUM(COUNTIFS(I25:AV25,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB25" s="23">
+      <c r="AZ25" s="23" cm="1">
+        <f t="array" ref="AZ25">SUM(COUNTIFS(H25:AU25,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA25" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC25" s="278">
+      <c r="BB25" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD25" s="39">
+      <c r="BC25" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE25" s="25">
+      <c r="BD25" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF25" s="26">
+      <c r="BE25" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG25" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C25,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH25" s="26">
+      <c r="BF25" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B25,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG25" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C26" s="71"/>
+    <row r="26" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B26" s="71"/>
+      <c r="C26" s="18"/>
       <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="307"/>
-      <c r="G26" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C26,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C26,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C26,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C27,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I26" s="24"/>
+      <c r="E26" s="307"/>
+      <c r="F26" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B26,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B26,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B26,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B27,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="24"/>
+      <c r="I26" s="18"/>
       <c r="J26" s="18"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="356"/>
+      <c r="K26" s="356"/>
+      <c r="L26" s="18"/>
       <c r="M26" s="18"/>
       <c r="N26" s="18"/>
       <c r="O26" s="18"/>
@@ -22028,21 +22028,21 @@
       <c r="V26" s="18"/>
       <c r="W26" s="18"/>
       <c r="X26" s="18"/>
-      <c r="Y26" s="18"/>
+      <c r="Y26" s="356"/>
       <c r="Z26" s="356"/>
       <c r="AA26" s="356"/>
-      <c r="AB26" s="356"/>
+      <c r="AB26" s="18"/>
       <c r="AC26" s="18"/>
       <c r="AD26" s="18"/>
       <c r="AE26" s="18"/>
-      <c r="AF26" s="18"/>
+      <c r="AF26" s="356"/>
       <c r="AG26" s="356"/>
-      <c r="AH26" s="356"/>
+      <c r="AH26" s="18"/>
       <c r="AI26" s="18"/>
       <c r="AJ26" s="18"/>
-      <c r="AK26" s="18"/>
+      <c r="AK26" s="356"/>
       <c r="AL26" s="356"/>
-      <c r="AM26" s="356"/>
+      <c r="AM26" s="18"/>
       <c r="AN26" s="18"/>
       <c r="AO26" s="18"/>
       <c r="AP26" s="18"/>
@@ -22050,70 +22050,70 @@
       <c r="AR26" s="18"/>
       <c r="AS26" s="18"/>
       <c r="AT26" s="18"/>
-      <c r="AU26" s="18"/>
-      <c r="AV26" s="26"/>
-      <c r="AX26" s="42">
+      <c r="AU26" s="26"/>
+      <c r="AW26" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY26" s="23" cm="1">
-        <f t="array" ref="AY26">SUM(COUNTIFS(I26:AV26,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ26" s="23">
+      <c r="AX26" s="23" cm="1">
+        <f t="array" ref="AX26">SUM(COUNTIFS(H26:AU26,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY26" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA26" s="23" cm="1">
-        <f t="array" ref="BA26">SUM(COUNTIFS(I26:AV26,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB26" s="23">
+      <c r="AZ26" s="23" cm="1">
+        <f t="array" ref="AZ26">SUM(COUNTIFS(H26:AU26,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA26" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC26" s="278">
+      <c r="BB26" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD26" s="39">
+      <c r="BC26" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE26" s="25">
+      <c r="BD26" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF26" s="26">
+      <c r="BE26" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG26" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C26,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH26" s="26">
+      <c r="BF26" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B26,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG26" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C27" s="71"/>
+    <row r="27" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B27" s="71"/>
+      <c r="C27" s="18"/>
       <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="307"/>
-      <c r="G27" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C27,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C27,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C27,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C28,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I27" s="24"/>
+      <c r="E27" s="307"/>
+      <c r="F27" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B27,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B27,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B27,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B28,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="24"/>
+      <c r="I27" s="18"/>
       <c r="J27" s="18"/>
-      <c r="K27" s="18"/>
-      <c r="L27" s="356"/>
+      <c r="K27" s="356"/>
+      <c r="L27" s="18"/>
       <c r="M27" s="18"/>
       <c r="N27" s="18"/>
       <c r="O27" s="18"/>
@@ -22126,21 +22126,21 @@
       <c r="V27" s="18"/>
       <c r="W27" s="18"/>
       <c r="X27" s="18"/>
-      <c r="Y27" s="18"/>
+      <c r="Y27" s="356"/>
       <c r="Z27" s="356"/>
       <c r="AA27" s="356"/>
-      <c r="AB27" s="356"/>
+      <c r="AB27" s="18"/>
       <c r="AC27" s="18"/>
       <c r="AD27" s="18"/>
       <c r="AE27" s="18"/>
-      <c r="AF27" s="18"/>
+      <c r="AF27" s="356"/>
       <c r="AG27" s="356"/>
-      <c r="AH27" s="356"/>
+      <c r="AH27" s="18"/>
       <c r="AI27" s="18"/>
       <c r="AJ27" s="18"/>
-      <c r="AK27" s="18"/>
+      <c r="AK27" s="356"/>
       <c r="AL27" s="356"/>
-      <c r="AM27" s="356"/>
+      <c r="AM27" s="18"/>
       <c r="AN27" s="18"/>
       <c r="AO27" s="18"/>
       <c r="AP27" s="18"/>
@@ -22148,70 +22148,70 @@
       <c r="AR27" s="18"/>
       <c r="AS27" s="18"/>
       <c r="AT27" s="18"/>
-      <c r="AU27" s="18"/>
-      <c r="AV27" s="26"/>
-      <c r="AX27" s="42">
+      <c r="AU27" s="26"/>
+      <c r="AW27" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY27" s="23" cm="1">
-        <f t="array" ref="AY27">SUM(COUNTIFS(I27:AV27,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ27" s="23">
+      <c r="AX27" s="23" cm="1">
+        <f t="array" ref="AX27">SUM(COUNTIFS(H27:AU27,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY27" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA27" s="23" cm="1">
-        <f t="array" ref="BA27">SUM(COUNTIFS(I27:AV27,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB27" s="23">
+      <c r="AZ27" s="23" cm="1">
+        <f t="array" ref="AZ27">SUM(COUNTIFS(H27:AU27,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA27" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC27" s="278">
+      <c r="BB27" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD27" s="39">
+      <c r="BC27" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE27" s="25">
+      <c r="BD27" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF27" s="26">
+      <c r="BE27" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG27" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C27,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH27" s="26">
+      <c r="BF27" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B27,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG27" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C28" s="71"/>
+    <row r="28" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B28" s="71"/>
+      <c r="C28" s="18"/>
       <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="307"/>
-      <c r="G28" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C28,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C28,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C28,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C29,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I28" s="24"/>
+      <c r="E28" s="307"/>
+      <c r="F28" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B28,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B28,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B28,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B29,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="24"/>
+      <c r="I28" s="18"/>
       <c r="J28" s="18"/>
-      <c r="K28" s="18"/>
-      <c r="L28" s="356"/>
+      <c r="K28" s="356"/>
+      <c r="L28" s="18"/>
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
       <c r="O28" s="18"/>
@@ -22224,21 +22224,21 @@
       <c r="V28" s="18"/>
       <c r="W28" s="18"/>
       <c r="X28" s="18"/>
-      <c r="Y28" s="18"/>
+      <c r="Y28" s="356"/>
       <c r="Z28" s="356"/>
       <c r="AA28" s="356"/>
-      <c r="AB28" s="356"/>
+      <c r="AB28" s="18"/>
       <c r="AC28" s="18"/>
       <c r="AD28" s="18"/>
       <c r="AE28" s="18"/>
-      <c r="AF28" s="18"/>
+      <c r="AF28" s="356"/>
       <c r="AG28" s="356"/>
-      <c r="AH28" s="356"/>
+      <c r="AH28" s="18"/>
       <c r="AI28" s="18"/>
       <c r="AJ28" s="18"/>
-      <c r="AK28" s="18"/>
+      <c r="AK28" s="356"/>
       <c r="AL28" s="356"/>
-      <c r="AM28" s="356"/>
+      <c r="AM28" s="18"/>
       <c r="AN28" s="18"/>
       <c r="AO28" s="18"/>
       <c r="AP28" s="18"/>
@@ -22246,70 +22246,70 @@
       <c r="AR28" s="18"/>
       <c r="AS28" s="18"/>
       <c r="AT28" s="18"/>
-      <c r="AU28" s="18"/>
-      <c r="AV28" s="26"/>
-      <c r="AX28" s="42">
+      <c r="AU28" s="26"/>
+      <c r="AW28" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY28" s="23" cm="1">
-        <f t="array" ref="AY28">SUM(COUNTIFS(I28:AV28,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ28" s="23">
+      <c r="AX28" s="23" cm="1">
+        <f t="array" ref="AX28">SUM(COUNTIFS(H28:AU28,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY28" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA28" s="23" cm="1">
-        <f t="array" ref="BA28">SUM(COUNTIFS(I28:AV28,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB28" s="23">
+      <c r="AZ28" s="23" cm="1">
+        <f t="array" ref="AZ28">SUM(COUNTIFS(H28:AU28,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA28" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC28" s="278">
+      <c r="BB28" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD28" s="39">
+      <c r="BC28" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE28" s="25">
+      <c r="BD28" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF28" s="26">
+      <c r="BE28" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG28" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C28,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH28" s="26">
+      <c r="BF28" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B28,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG28" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C29" s="71"/>
+    <row r="29" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B29" s="71"/>
+      <c r="C29" s="18"/>
       <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="307"/>
-      <c r="G29" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C29,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C29,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C29,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C30,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I29" s="24"/>
+      <c r="E29" s="307"/>
+      <c r="F29" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B29,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B29,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B29,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B30,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="24"/>
+      <c r="I29" s="18"/>
       <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="356"/>
+      <c r="K29" s="356"/>
+      <c r="L29" s="18"/>
       <c r="M29" s="18"/>
       <c r="N29" s="18"/>
       <c r="O29" s="18"/>
@@ -22322,21 +22322,21 @@
       <c r="V29" s="18"/>
       <c r="W29" s="18"/>
       <c r="X29" s="18"/>
-      <c r="Y29" s="18"/>
+      <c r="Y29" s="356"/>
       <c r="Z29" s="356"/>
       <c r="AA29" s="356"/>
-      <c r="AB29" s="356"/>
+      <c r="AB29" s="18"/>
       <c r="AC29" s="18"/>
       <c r="AD29" s="18"/>
       <c r="AE29" s="18"/>
-      <c r="AF29" s="18"/>
+      <c r="AF29" s="356"/>
       <c r="AG29" s="356"/>
-      <c r="AH29" s="356"/>
+      <c r="AH29" s="18"/>
       <c r="AI29" s="18"/>
       <c r="AJ29" s="18"/>
-      <c r="AK29" s="18"/>
+      <c r="AK29" s="356"/>
       <c r="AL29" s="356"/>
-      <c r="AM29" s="356"/>
+      <c r="AM29" s="18"/>
       <c r="AN29" s="18"/>
       <c r="AO29" s="18"/>
       <c r="AP29" s="18"/>
@@ -22344,70 +22344,70 @@
       <c r="AR29" s="18"/>
       <c r="AS29" s="18"/>
       <c r="AT29" s="18"/>
-      <c r="AU29" s="18"/>
-      <c r="AV29" s="26"/>
-      <c r="AX29" s="42">
+      <c r="AU29" s="26"/>
+      <c r="AW29" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY29" s="23" cm="1">
-        <f t="array" ref="AY29">SUM(COUNTIFS(I29:AV29,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ29" s="23">
+      <c r="AX29" s="23" cm="1">
+        <f t="array" ref="AX29">SUM(COUNTIFS(H29:AU29,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY29" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA29" s="23" cm="1">
-        <f t="array" ref="BA29">SUM(COUNTIFS(I29:AV29,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB29" s="23">
+      <c r="AZ29" s="23" cm="1">
+        <f t="array" ref="AZ29">SUM(COUNTIFS(H29:AU29,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA29" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC29" s="278">
+      <c r="BB29" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD29" s="39">
+      <c r="BC29" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE29" s="25">
+      <c r="BD29" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF29" s="26">
+      <c r="BE29" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG29" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C29,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH29" s="26">
+      <c r="BF29" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B29,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG29" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C30" s="71"/>
+    <row r="30" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B30" s="71"/>
+      <c r="C30" s="18"/>
       <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="307"/>
-      <c r="G30" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C30,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C30,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C30,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C31,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I30" s="24"/>
+      <c r="E30" s="307"/>
+      <c r="F30" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B30,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B30,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B30,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B31,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="24"/>
+      <c r="I30" s="18"/>
       <c r="J30" s="18"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="356"/>
+      <c r="K30" s="356"/>
+      <c r="L30" s="18"/>
       <c r="M30" s="18"/>
       <c r="N30" s="18"/>
       <c r="O30" s="18"/>
@@ -22420,21 +22420,21 @@
       <c r="V30" s="18"/>
       <c r="W30" s="18"/>
       <c r="X30" s="18"/>
-      <c r="Y30" s="18"/>
+      <c r="Y30" s="356"/>
       <c r="Z30" s="356"/>
       <c r="AA30" s="356"/>
-      <c r="AB30" s="356"/>
+      <c r="AB30" s="18"/>
       <c r="AC30" s="18"/>
       <c r="AD30" s="18"/>
       <c r="AE30" s="18"/>
-      <c r="AF30" s="18"/>
+      <c r="AF30" s="356"/>
       <c r="AG30" s="356"/>
-      <c r="AH30" s="356"/>
+      <c r="AH30" s="18"/>
       <c r="AI30" s="18"/>
       <c r="AJ30" s="18"/>
-      <c r="AK30" s="18"/>
+      <c r="AK30" s="356"/>
       <c r="AL30" s="356"/>
-      <c r="AM30" s="356"/>
+      <c r="AM30" s="18"/>
       <c r="AN30" s="18"/>
       <c r="AO30" s="18"/>
       <c r="AP30" s="18"/>
@@ -22442,70 +22442,70 @@
       <c r="AR30" s="18"/>
       <c r="AS30" s="18"/>
       <c r="AT30" s="18"/>
-      <c r="AU30" s="18"/>
-      <c r="AV30" s="26"/>
-      <c r="AX30" s="42">
+      <c r="AU30" s="26"/>
+      <c r="AW30" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY30" s="23" cm="1">
-        <f t="array" ref="AY30">SUM(COUNTIFS(I30:AV30,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ30" s="23">
+      <c r="AX30" s="23" cm="1">
+        <f t="array" ref="AX30">SUM(COUNTIFS(H30:AU30,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY30" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA30" s="23" cm="1">
-        <f t="array" ref="BA30">SUM(COUNTIFS(I30:AV30,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB30" s="23">
+      <c r="AZ30" s="23" cm="1">
+        <f t="array" ref="AZ30">SUM(COUNTIFS(H30:AU30,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA30" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC30" s="278">
+      <c r="BB30" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD30" s="39">
+      <c r="BC30" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE30" s="25">
+      <c r="BD30" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF30" s="26">
+      <c r="BE30" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG30" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C30,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH30" s="26">
+      <c r="BF30" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B30,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG30" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C31" s="71"/>
+    <row r="31" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B31" s="71"/>
+      <c r="C31" s="18"/>
       <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="307"/>
-      <c r="G31" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C31,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C31,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C31,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C32,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I31" s="24"/>
+      <c r="E31" s="307"/>
+      <c r="F31" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B31,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B31,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B31,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B32,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="24"/>
+      <c r="I31" s="18"/>
       <c r="J31" s="18"/>
-      <c r="K31" s="18"/>
-      <c r="L31" s="356"/>
+      <c r="K31" s="356"/>
+      <c r="L31" s="18"/>
       <c r="M31" s="18"/>
       <c r="N31" s="18"/>
       <c r="O31" s="18"/>
@@ -22518,21 +22518,21 @@
       <c r="V31" s="18"/>
       <c r="W31" s="18"/>
       <c r="X31" s="18"/>
-      <c r="Y31" s="18"/>
+      <c r="Y31" s="356"/>
       <c r="Z31" s="356"/>
       <c r="AA31" s="356"/>
-      <c r="AB31" s="356"/>
+      <c r="AB31" s="18"/>
       <c r="AC31" s="18"/>
       <c r="AD31" s="18"/>
       <c r="AE31" s="18"/>
-      <c r="AF31" s="18"/>
+      <c r="AF31" s="356"/>
       <c r="AG31" s="356"/>
-      <c r="AH31" s="356"/>
+      <c r="AH31" s="18"/>
       <c r="AI31" s="18"/>
       <c r="AJ31" s="18"/>
-      <c r="AK31" s="18"/>
+      <c r="AK31" s="356"/>
       <c r="AL31" s="356"/>
-      <c r="AM31" s="356"/>
+      <c r="AM31" s="18"/>
       <c r="AN31" s="18"/>
       <c r="AO31" s="18"/>
       <c r="AP31" s="18"/>
@@ -22540,70 +22540,70 @@
       <c r="AR31" s="18"/>
       <c r="AS31" s="18"/>
       <c r="AT31" s="18"/>
-      <c r="AU31" s="18"/>
-      <c r="AV31" s="26"/>
-      <c r="AX31" s="42">
+      <c r="AU31" s="26"/>
+      <c r="AW31" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY31" s="23" cm="1">
-        <f t="array" ref="AY31">SUM(COUNTIFS(I31:AV31,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ31" s="23">
+      <c r="AX31" s="23" cm="1">
+        <f t="array" ref="AX31">SUM(COUNTIFS(H31:AU31,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY31" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA31" s="23" cm="1">
-        <f t="array" ref="BA31">SUM(COUNTIFS(I31:AV31,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB31" s="23">
+      <c r="AZ31" s="23" cm="1">
+        <f t="array" ref="AZ31">SUM(COUNTIFS(H31:AU31,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA31" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC31" s="278">
+      <c r="BB31" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD31" s="39">
+      <c r="BC31" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE31" s="25">
+      <c r="BD31" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF31" s="26">
+      <c r="BE31" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG31" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C31,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH31" s="26">
+      <c r="BF31" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B31,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG31" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C32" s="71"/>
+    <row r="32" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B32" s="71"/>
+      <c r="C32" s="18"/>
       <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="307"/>
-      <c r="G32" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C32,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C32,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C32,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C33,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="24"/>
+      <c r="E32" s="307"/>
+      <c r="F32" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B32,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B32,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B32,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B33,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="24"/>
+      <c r="I32" s="18"/>
       <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="356"/>
+      <c r="K32" s="356"/>
+      <c r="L32" s="18"/>
       <c r="M32" s="18"/>
       <c r="N32" s="18"/>
       <c r="O32" s="18"/>
@@ -22616,21 +22616,21 @@
       <c r="V32" s="18"/>
       <c r="W32" s="18"/>
       <c r="X32" s="18"/>
-      <c r="Y32" s="18"/>
+      <c r="Y32" s="356"/>
       <c r="Z32" s="356"/>
       <c r="AA32" s="356"/>
-      <c r="AB32" s="356"/>
+      <c r="AB32" s="18"/>
       <c r="AC32" s="18"/>
       <c r="AD32" s="18"/>
       <c r="AE32" s="18"/>
-      <c r="AF32" s="18"/>
+      <c r="AF32" s="356"/>
       <c r="AG32" s="356"/>
-      <c r="AH32" s="356"/>
+      <c r="AH32" s="18"/>
       <c r="AI32" s="18"/>
       <c r="AJ32" s="18"/>
-      <c r="AK32" s="18"/>
+      <c r="AK32" s="356"/>
       <c r="AL32" s="356"/>
-      <c r="AM32" s="356"/>
+      <c r="AM32" s="18"/>
       <c r="AN32" s="18"/>
       <c r="AO32" s="18"/>
       <c r="AP32" s="18"/>
@@ -22638,70 +22638,70 @@
       <c r="AR32" s="18"/>
       <c r="AS32" s="18"/>
       <c r="AT32" s="18"/>
-      <c r="AU32" s="18"/>
-      <c r="AV32" s="26"/>
-      <c r="AX32" s="42">
+      <c r="AU32" s="26"/>
+      <c r="AW32" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY32" s="23" cm="1">
-        <f t="array" ref="AY32">SUM(COUNTIFS(I32:AV32,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ32" s="23">
+      <c r="AX32" s="23" cm="1">
+        <f t="array" ref="AX32">SUM(COUNTIFS(H32:AU32,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY32" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA32" s="23" cm="1">
-        <f t="array" ref="BA32">SUM(COUNTIFS(I32:AV32,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB32" s="23">
+      <c r="AZ32" s="23" cm="1">
+        <f t="array" ref="AZ32">SUM(COUNTIFS(H32:AU32,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA32" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC32" s="278">
+      <c r="BB32" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD32" s="39">
+      <c r="BC32" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE32" s="25">
+      <c r="BD32" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF32" s="26">
+      <c r="BE32" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG32" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C32,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH32" s="26">
+      <c r="BF32" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B32,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG32" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C33" s="71"/>
+    <row r="33" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B33" s="71"/>
+      <c r="C33" s="18"/>
       <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="307"/>
-      <c r="G33" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C33,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C33,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C33,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C34,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I33" s="24"/>
+      <c r="E33" s="307"/>
+      <c r="F33" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B33,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B33,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B33,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B34,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="24"/>
+      <c r="I33" s="18"/>
       <c r="J33" s="18"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="356"/>
+      <c r="K33" s="356"/>
+      <c r="L33" s="18"/>
       <c r="M33" s="18"/>
       <c r="N33" s="18"/>
       <c r="O33" s="18"/>
@@ -22714,21 +22714,21 @@
       <c r="V33" s="18"/>
       <c r="W33" s="18"/>
       <c r="X33" s="18"/>
-      <c r="Y33" s="18"/>
+      <c r="Y33" s="356"/>
       <c r="Z33" s="356"/>
       <c r="AA33" s="356"/>
-      <c r="AB33" s="356"/>
+      <c r="AB33" s="18"/>
       <c r="AC33" s="18"/>
       <c r="AD33" s="18"/>
       <c r="AE33" s="18"/>
-      <c r="AF33" s="18"/>
+      <c r="AF33" s="356"/>
       <c r="AG33" s="356"/>
-      <c r="AH33" s="356"/>
+      <c r="AH33" s="18"/>
       <c r="AI33" s="18"/>
       <c r="AJ33" s="18"/>
-      <c r="AK33" s="18"/>
+      <c r="AK33" s="356"/>
       <c r="AL33" s="356"/>
-      <c r="AM33" s="356"/>
+      <c r="AM33" s="18"/>
       <c r="AN33" s="18"/>
       <c r="AO33" s="18"/>
       <c r="AP33" s="18"/>
@@ -22736,70 +22736,70 @@
       <c r="AR33" s="18"/>
       <c r="AS33" s="18"/>
       <c r="AT33" s="18"/>
-      <c r="AU33" s="18"/>
-      <c r="AV33" s="26"/>
-      <c r="AX33" s="42">
+      <c r="AU33" s="26"/>
+      <c r="AW33" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY33" s="23" cm="1">
-        <f t="array" ref="AY33">SUM(COUNTIFS(I33:AV33,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ33" s="23">
+      <c r="AX33" s="23" cm="1">
+        <f t="array" ref="AX33">SUM(COUNTIFS(H33:AU33,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY33" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA33" s="23" cm="1">
-        <f t="array" ref="BA33">SUM(COUNTIFS(I33:AV33,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB33" s="23">
+      <c r="AZ33" s="23" cm="1">
+        <f t="array" ref="AZ33">SUM(COUNTIFS(H33:AU33,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA33" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC33" s="278">
+      <c r="BB33" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD33" s="39">
+      <c r="BC33" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE33" s="25">
+      <c r="BD33" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF33" s="26">
+      <c r="BE33" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG33" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C33,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH33" s="26">
+      <c r="BF33" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B33,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG33" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C34" s="71"/>
+    <row r="34" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B34" s="71"/>
+      <c r="C34" s="18"/>
       <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="307"/>
-      <c r="G34" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C34,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C34,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C34,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C35,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I34" s="24"/>
+      <c r="E34" s="307"/>
+      <c r="F34" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B34,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B34,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B34,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B35,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="24"/>
+      <c r="I34" s="18"/>
       <c r="J34" s="18"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="356"/>
+      <c r="K34" s="356"/>
+      <c r="L34" s="18"/>
       <c r="M34" s="18"/>
       <c r="N34" s="18"/>
       <c r="O34" s="18"/>
@@ -22812,21 +22812,21 @@
       <c r="V34" s="18"/>
       <c r="W34" s="18"/>
       <c r="X34" s="18"/>
-      <c r="Y34" s="18"/>
+      <c r="Y34" s="356"/>
       <c r="Z34" s="356"/>
       <c r="AA34" s="356"/>
-      <c r="AB34" s="356"/>
+      <c r="AB34" s="18"/>
       <c r="AC34" s="18"/>
       <c r="AD34" s="18"/>
       <c r="AE34" s="18"/>
-      <c r="AF34" s="18"/>
+      <c r="AF34" s="356"/>
       <c r="AG34" s="356"/>
-      <c r="AH34" s="356"/>
+      <c r="AH34" s="18"/>
       <c r="AI34" s="18"/>
       <c r="AJ34" s="18"/>
-      <c r="AK34" s="18"/>
+      <c r="AK34" s="356"/>
       <c r="AL34" s="356"/>
-      <c r="AM34" s="356"/>
+      <c r="AM34" s="18"/>
       <c r="AN34" s="18"/>
       <c r="AO34" s="18"/>
       <c r="AP34" s="18"/>
@@ -22834,92 +22834,92 @@
       <c r="AR34" s="18"/>
       <c r="AS34" s="18"/>
       <c r="AT34" s="18"/>
-      <c r="AU34" s="18"/>
-      <c r="AV34" s="26"/>
-      <c r="AX34" s="42">
+      <c r="AU34" s="26"/>
+      <c r="AW34" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY34" s="23" cm="1">
-        <f t="array" ref="AY34">SUM(COUNTIFS(I34:AV34,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ34" s="23">
+      <c r="AX34" s="23" cm="1">
+        <f t="array" ref="AX34">SUM(COUNTIFS(H34:AU34,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY34" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA34" s="23" cm="1">
-        <f t="array" ref="BA34">SUM(COUNTIFS(I34:AV34,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB34" s="23">
+      <c r="AZ34" s="23" cm="1">
+        <f t="array" ref="AZ34">SUM(COUNTIFS(H34:AU34,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA34" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC34" s="278">
+      <c r="BB34" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD34" s="39">
+      <c r="BC34" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE34" s="25">
+      <c r="BD34" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF34" s="26">
+      <c r="BE34" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG34" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C34,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH34" s="26">
+      <c r="BF34" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B34,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG34" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C35" s="71"/>
+    <row r="35" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B35" s="71"/>
+      <c r="C35" s="18"/>
       <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="307"/>
-      <c r="G35" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C35,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C35,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C35,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C36,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="24"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="356"/>
+      <c r="E35" s="307"/>
+      <c r="F35" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B35,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B35,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B35,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B36,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="24"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="356"/>
+      <c r="K35" s="18"/>
       <c r="L35" s="18"/>
       <c r="M35" s="18"/>
-      <c r="N35" s="18"/>
-      <c r="O35" s="356"/>
+      <c r="N35" s="356"/>
+      <c r="O35" s="18"/>
       <c r="P35" s="18"/>
       <c r="Q35" s="18"/>
       <c r="R35" s="18"/>
       <c r="S35" s="18"/>
       <c r="T35" s="18"/>
       <c r="U35" s="18"/>
-      <c r="V35" s="18"/>
+      <c r="V35" s="356"/>
       <c r="W35" s="356"/>
-      <c r="X35" s="356"/>
+      <c r="X35" s="18"/>
       <c r="Y35" s="18"/>
-      <c r="Z35" s="18"/>
-      <c r="AA35" s="356"/>
+      <c r="Z35" s="356"/>
+      <c r="AA35" s="18"/>
       <c r="AB35" s="18"/>
-      <c r="AC35" s="18"/>
-      <c r="AD35" s="356"/>
+      <c r="AC35" s="356"/>
+      <c r="AD35" s="18"/>
       <c r="AE35" s="18"/>
       <c r="AF35" s="18"/>
-      <c r="AG35" s="18"/>
-      <c r="AH35" s="356"/>
+      <c r="AG35" s="356"/>
+      <c r="AH35" s="18"/>
       <c r="AI35" s="18"/>
       <c r="AJ35" s="18"/>
       <c r="AK35" s="18"/>
@@ -22932,83 +22932,83 @@
       <c r="AR35" s="18"/>
       <c r="AS35" s="18"/>
       <c r="AT35" s="18"/>
-      <c r="AU35" s="18"/>
-      <c r="AV35" s="26"/>
-      <c r="AX35" s="42">
+      <c r="AU35" s="26"/>
+      <c r="AW35" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY35" s="23" cm="1">
-        <f t="array" ref="AY35">SUM(COUNTIFS(I35:AV35,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ35" s="23">
+      <c r="AX35" s="23" cm="1">
+        <f t="array" ref="AX35">SUM(COUNTIFS(H35:AU35,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY35" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA35" s="23" cm="1">
-        <f t="array" ref="BA35">SUM(COUNTIFS(I35:AV35,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB35" s="23">
+      <c r="AZ35" s="23" cm="1">
+        <f t="array" ref="AZ35">SUM(COUNTIFS(H35:AU35,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA35" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC35" s="278">
+      <c r="BB35" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD35" s="39">
+      <c r="BC35" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE35" s="25">
+      <c r="BD35" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF35" s="26">
+      <c r="BE35" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG35" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C35,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH35" s="26">
+      <c r="BF35" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B35,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG35" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C36" s="71"/>
+    <row r="36" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B36" s="71"/>
+      <c r="C36" s="18"/>
       <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="307"/>
-      <c r="G36" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C36,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C36,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C36,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C37,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="24"/>
-      <c r="J36" s="18"/>
-      <c r="K36" s="356"/>
+      <c r="E36" s="307"/>
+      <c r="F36" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B36,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B36,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B36,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B37,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="24"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="356"/>
+      <c r="K36" s="18"/>
       <c r="L36" s="18"/>
-      <c r="M36" s="18"/>
+      <c r="M36" s="356"/>
       <c r="N36" s="356"/>
       <c r="O36" s="356"/>
       <c r="P36" s="356"/>
       <c r="Q36" s="356"/>
       <c r="R36" s="356"/>
-      <c r="S36" s="356"/>
+      <c r="S36" s="18"/>
       <c r="T36" s="18"/>
       <c r="U36" s="18"/>
-      <c r="V36" s="18"/>
-      <c r="W36" s="356"/>
-      <c r="X36" s="18"/>
-      <c r="Y36" s="356"/>
+      <c r="V36" s="356"/>
+      <c r="W36" s="18"/>
+      <c r="X36" s="356"/>
+      <c r="Y36" s="18"/>
       <c r="Z36" s="18"/>
       <c r="AA36" s="18"/>
       <c r="AB36" s="18"/>
@@ -23017,12 +23017,12 @@
       <c r="AE36" s="18"/>
       <c r="AF36" s="18"/>
       <c r="AG36" s="18"/>
-      <c r="AH36" s="18"/>
+      <c r="AH36" s="356"/>
       <c r="AI36" s="356"/>
       <c r="AJ36" s="356"/>
       <c r="AK36" s="356"/>
       <c r="AL36" s="356"/>
-      <c r="AM36" s="356"/>
+      <c r="AM36" s="18"/>
       <c r="AN36" s="18"/>
       <c r="AO36" s="18"/>
       <c r="AP36" s="18"/>
@@ -23030,79 +23030,79 @@
       <c r="AR36" s="18"/>
       <c r="AS36" s="18"/>
       <c r="AT36" s="18"/>
-      <c r="AU36" s="18"/>
-      <c r="AV36" s="26"/>
-      <c r="AX36" s="42">
+      <c r="AU36" s="26"/>
+      <c r="AW36" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY36" s="23" cm="1">
-        <f t="array" ref="AY36">SUM(COUNTIFS(I36:AV36,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ36" s="23">
+      <c r="AX36" s="23" cm="1">
+        <f t="array" ref="AX36">SUM(COUNTIFS(H36:AU36,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY36" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA36" s="23" cm="1">
-        <f t="array" ref="BA36">SUM(COUNTIFS(I36:AV36,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB36" s="23">
+      <c r="AZ36" s="23" cm="1">
+        <f t="array" ref="AZ36">SUM(COUNTIFS(H36:AU36,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA36" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC36" s="278">
+      <c r="BB36" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD36" s="39">
+      <c r="BC36" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE36" s="25">
+      <c r="BD36" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF36" s="26">
+      <c r="BE36" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG36" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C36,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH36" s="26">
+      <c r="BF36" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B36,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG36" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C37" s="71"/>
+    <row r="37" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B37" s="71"/>
+      <c r="C37" s="18"/>
       <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="307"/>
-      <c r="G37" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C37,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C37,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C37,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C38,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I37" s="24"/>
+      <c r="E37" s="307"/>
+      <c r="F37" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B37,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B37,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B37,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B38,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="24"/>
+      <c r="I37" s="18"/>
       <c r="J37" s="18"/>
       <c r="K37" s="18"/>
       <c r="L37" s="18"/>
       <c r="M37" s="18"/>
       <c r="N37" s="18"/>
-      <c r="O37" s="18"/>
+      <c r="O37" s="356"/>
       <c r="P37" s="356"/>
-      <c r="Q37" s="356"/>
+      <c r="Q37" s="18"/>
       <c r="R37" s="18"/>
-      <c r="S37" s="18"/>
+      <c r="S37" s="356"/>
       <c r="T37" s="356"/>
-      <c r="U37" s="356"/>
+      <c r="U37" s="18"/>
       <c r="V37" s="18"/>
       <c r="W37" s="18"/>
       <c r="X37" s="18"/>
@@ -23112,8 +23112,8 @@
       <c r="AB37" s="18"/>
       <c r="AC37" s="18"/>
       <c r="AD37" s="18"/>
-      <c r="AE37" s="18"/>
-      <c r="AF37" s="356"/>
+      <c r="AE37" s="356"/>
+      <c r="AF37" s="18"/>
       <c r="AG37" s="18"/>
       <c r="AH37" s="18"/>
       <c r="AI37" s="18"/>
@@ -23128,79 +23128,79 @@
       <c r="AR37" s="18"/>
       <c r="AS37" s="18"/>
       <c r="AT37" s="18"/>
-      <c r="AU37" s="18"/>
-      <c r="AV37" s="26"/>
-      <c r="AX37" s="42">
+      <c r="AU37" s="26"/>
+      <c r="AW37" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY37" s="23" cm="1">
-        <f t="array" ref="AY37">SUM(COUNTIFS(I37:AV37,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ37" s="23">
+      <c r="AX37" s="23" cm="1">
+        <f t="array" ref="AX37">SUM(COUNTIFS(H37:AU37,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY37" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA37" s="23" cm="1">
-        <f t="array" ref="BA37">SUM(COUNTIFS(I37:AV37,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB37" s="23">
+      <c r="AZ37" s="23" cm="1">
+        <f t="array" ref="AZ37">SUM(COUNTIFS(H37:AU37,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA37" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC37" s="278">
+      <c r="BB37" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD37" s="39">
+      <c r="BC37" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE37" s="25">
+      <c r="BD37" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF37" s="26">
+      <c r="BE37" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG37" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C37,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH37" s="26">
+      <c r="BF37" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B37,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG37" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C38" s="71"/>
+    <row r="38" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B38" s="71"/>
+      <c r="C38" s="18"/>
       <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="307"/>
-      <c r="G38" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C38,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C38,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C38,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C39,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I38" s="24"/>
+      <c r="E38" s="307"/>
+      <c r="F38" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B38,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B38,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B38,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B39,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="24"/>
+      <c r="I38" s="18"/>
       <c r="J38" s="18"/>
       <c r="K38" s="18"/>
       <c r="L38" s="18"/>
       <c r="M38" s="18"/>
       <c r="N38" s="18"/>
-      <c r="O38" s="18"/>
+      <c r="O38" s="356"/>
       <c r="P38" s="356"/>
       <c r="Q38" s="356"/>
       <c r="R38" s="356"/>
       <c r="S38" s="356"/>
       <c r="T38" s="356"/>
-      <c r="U38" s="356"/>
+      <c r="U38" s="18"/>
       <c r="V38" s="18"/>
       <c r="W38" s="18"/>
       <c r="X38" s="18"/>
@@ -23212,13 +23212,13 @@
       <c r="AD38" s="18"/>
       <c r="AE38" s="18"/>
       <c r="AF38" s="18"/>
-      <c r="AG38" s="18"/>
-      <c r="AH38" s="356"/>
+      <c r="AG38" s="356"/>
+      <c r="AH38" s="18"/>
       <c r="AI38" s="18"/>
       <c r="AJ38" s="18"/>
       <c r="AK38" s="18"/>
       <c r="AL38" s="18"/>
-      <c r="AM38" s="18"/>
+      <c r="AM38" s="356"/>
       <c r="AN38" s="356"/>
       <c r="AO38" s="356"/>
       <c r="AP38" s="356"/>
@@ -23226,97 +23226,97 @@
       <c r="AR38" s="356"/>
       <c r="AS38" s="356"/>
       <c r="AT38" s="356"/>
-      <c r="AU38" s="356"/>
-      <c r="AV38" s="358"/>
-      <c r="AX38" s="42">
+      <c r="AU38" s="358"/>
+      <c r="AW38" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY38" s="23" cm="1">
-        <f t="array" ref="AY38">SUM(COUNTIFS(I38:AV38,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ38" s="23">
+      <c r="AX38" s="23" cm="1">
+        <f t="array" ref="AX38">SUM(COUNTIFS(H38:AU38,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY38" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA38" s="23" cm="1">
-        <f t="array" ref="BA38">SUM(COUNTIFS(I38:AV38,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB38" s="23">
+      <c r="AZ38" s="23" cm="1">
+        <f t="array" ref="AZ38">SUM(COUNTIFS(H38:AU38,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA38" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC38" s="278">
+      <c r="BB38" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD38" s="39">
+      <c r="BC38" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE38" s="25">
+      <c r="BD38" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF38" s="26">
+      <c r="BE38" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG38" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C38,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH38" s="26">
+      <c r="BF38" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B38,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG38" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C39" s="71"/>
+    <row r="39" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B39" s="71"/>
+      <c r="C39" s="18"/>
       <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="307"/>
-      <c r="G39" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C39,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C39,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C39,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C40,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I39" s="24"/>
+      <c r="E39" s="307"/>
+      <c r="F39" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B39,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B39,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B39,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B40,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="24"/>
+      <c r="I39" s="18"/>
       <c r="J39" s="18"/>
       <c r="K39" s="18"/>
-      <c r="L39" s="18"/>
-      <c r="M39" s="356"/>
-      <c r="N39" s="18"/>
+      <c r="L39" s="356"/>
+      <c r="M39" s="18"/>
+      <c r="N39" s="356"/>
       <c r="O39" s="356"/>
       <c r="P39" s="356"/>
       <c r="Q39" s="356"/>
       <c r="R39" s="356"/>
-      <c r="S39" s="356"/>
+      <c r="S39" s="18"/>
       <c r="T39" s="18"/>
       <c r="U39" s="18"/>
       <c r="V39" s="18"/>
       <c r="W39" s="18"/>
-      <c r="X39" s="18"/>
+      <c r="X39" s="356"/>
       <c r="Y39" s="356"/>
       <c r="Z39" s="356"/>
       <c r="AA39" s="356"/>
-      <c r="AB39" s="356"/>
-      <c r="AC39" s="18"/>
-      <c r="AD39" s="356"/>
+      <c r="AB39" s="18"/>
+      <c r="AC39" s="356"/>
+      <c r="AD39" s="18"/>
       <c r="AE39" s="18"/>
-      <c r="AF39" s="18"/>
+      <c r="AF39" s="356"/>
       <c r="AG39" s="356"/>
-      <c r="AH39" s="356"/>
+      <c r="AH39" s="18"/>
       <c r="AI39" s="18"/>
-      <c r="AJ39" s="18"/>
+      <c r="AJ39" s="356"/>
       <c r="AK39" s="356"/>
       <c r="AL39" s="356"/>
-      <c r="AM39" s="356"/>
+      <c r="AM39" s="18"/>
       <c r="AN39" s="18"/>
       <c r="AO39" s="18"/>
       <c r="AP39" s="18"/>
@@ -23324,92 +23324,92 @@
       <c r="AR39" s="18"/>
       <c r="AS39" s="18"/>
       <c r="AT39" s="18"/>
-      <c r="AU39" s="18"/>
-      <c r="AV39" s="26"/>
-      <c r="AX39" s="42">
+      <c r="AU39" s="26"/>
+      <c r="AW39" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY39" s="23" cm="1">
-        <f t="array" ref="AY39">SUM(COUNTIFS(I39:AV39,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ39" s="23">
+      <c r="AX39" s="23" cm="1">
+        <f t="array" ref="AX39">SUM(COUNTIFS(H39:AU39,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY39" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA39" s="23" cm="1">
-        <f t="array" ref="BA39">SUM(COUNTIFS(I39:AV39,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB39" s="23">
+      <c r="AZ39" s="23" cm="1">
+        <f t="array" ref="AZ39">SUM(COUNTIFS(H39:AU39,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA39" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC39" s="278">
+      <c r="BB39" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD39" s="39">
+      <c r="BC39" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE39" s="25">
+      <c r="BD39" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF39" s="26">
+      <c r="BE39" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG39" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C39,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH39" s="26">
+      <c r="BF39" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B39,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG39" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C40" s="71"/>
+    <row r="40" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B40" s="71"/>
+      <c r="C40" s="18"/>
       <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="307"/>
-      <c r="G40" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C40,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C40,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C40,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C41,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I40" s="24"/>
-      <c r="J40" s="18"/>
+      <c r="E40" s="307"/>
+      <c r="F40" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B40,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B40,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B40,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B41,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="24"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="356"/>
       <c r="K40" s="356"/>
       <c r="L40" s="356"/>
-      <c r="M40" s="356"/>
+      <c r="M40" s="18"/>
       <c r="N40" s="18"/>
-      <c r="O40" s="18"/>
-      <c r="P40" s="356"/>
+      <c r="O40" s="356"/>
+      <c r="P40" s="18"/>
       <c r="Q40" s="18"/>
-      <c r="R40" s="18"/>
-      <c r="S40" s="356"/>
+      <c r="R40" s="356"/>
+      <c r="S40" s="18"/>
       <c r="T40" s="18"/>
       <c r="U40" s="18"/>
       <c r="V40" s="18"/>
       <c r="W40" s="18"/>
       <c r="X40" s="18"/>
       <c r="Y40" s="18"/>
-      <c r="Z40" s="18"/>
+      <c r="Z40" s="356"/>
       <c r="AA40" s="356"/>
       <c r="AB40" s="356"/>
       <c r="AC40" s="356"/>
-      <c r="AD40" s="356"/>
+      <c r="AD40" s="18"/>
       <c r="AE40" s="18"/>
-      <c r="AF40" s="18"/>
+      <c r="AF40" s="356"/>
       <c r="AG40" s="356"/>
-      <c r="AH40" s="356"/>
+      <c r="AH40" s="18"/>
       <c r="AI40" s="18"/>
       <c r="AJ40" s="18"/>
       <c r="AK40" s="18"/>
@@ -23422,93 +23422,93 @@
       <c r="AR40" s="18"/>
       <c r="AS40" s="18"/>
       <c r="AT40" s="18"/>
-      <c r="AU40" s="18"/>
-      <c r="AV40" s="26"/>
-      <c r="AX40" s="42">
+      <c r="AU40" s="26"/>
+      <c r="AW40" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY40" s="23" cm="1">
-        <f t="array" ref="AY40">SUM(COUNTIFS(I40:AV40,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ40" s="23">
+      <c r="AX40" s="23" cm="1">
+        <f t="array" ref="AX40">SUM(COUNTIFS(H40:AU40,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY40" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA40" s="23" cm="1">
-        <f t="array" ref="BA40">SUM(COUNTIFS(I40:AV40,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB40" s="23">
+      <c r="AZ40" s="23" cm="1">
+        <f t="array" ref="AZ40">SUM(COUNTIFS(H40:AU40,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA40" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC40" s="278">
+      <c r="BB40" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD40" s="39">
+      <c r="BC40" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE40" s="25">
+      <c r="BD40" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF40" s="26">
+      <c r="BE40" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG40" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C40,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH40" s="26">
+      <c r="BF40" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B40,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG40" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C41" s="71"/>
+    <row r="41" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B41" s="71"/>
+      <c r="C41" s="18"/>
       <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="307"/>
-      <c r="G41" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C41,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C41,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C41,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C42,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="24"/>
-      <c r="J41" s="18"/>
+      <c r="E41" s="307"/>
+      <c r="F41" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B41,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B41,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B41,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B42,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="24"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="356"/>
       <c r="K41" s="356"/>
-      <c r="L41" s="356"/>
+      <c r="L41" s="18"/>
       <c r="M41" s="18"/>
       <c r="N41" s="18"/>
       <c r="O41" s="18"/>
       <c r="P41" s="18"/>
-      <c r="Q41" s="18"/>
-      <c r="R41" s="356"/>
+      <c r="Q41" s="356"/>
+      <c r="R41" s="18"/>
       <c r="S41" s="18"/>
-      <c r="T41" s="18"/>
+      <c r="T41" s="356"/>
       <c r="U41" s="356"/>
-      <c r="V41" s="356"/>
+      <c r="V41" s="18"/>
       <c r="W41" s="18"/>
-      <c r="X41" s="18"/>
-      <c r="Y41" s="356"/>
-      <c r="Z41" s="18"/>
+      <c r="X41" s="356"/>
+      <c r="Y41" s="18"/>
+      <c r="Z41" s="356"/>
       <c r="AA41" s="356"/>
-      <c r="AB41" s="356"/>
+      <c r="AB41" s="18"/>
       <c r="AC41" s="18"/>
       <c r="AD41" s="18"/>
       <c r="AE41" s="18"/>
       <c r="AF41" s="18"/>
       <c r="AG41" s="18"/>
-      <c r="AH41" s="18"/>
-      <c r="AI41" s="356"/>
+      <c r="AH41" s="356"/>
+      <c r="AI41" s="18"/>
       <c r="AJ41" s="18"/>
       <c r="AK41" s="18"/>
       <c r="AL41" s="18"/>
@@ -23520,71 +23520,71 @@
       <c r="AR41" s="18"/>
       <c r="AS41" s="18"/>
       <c r="AT41" s="18"/>
-      <c r="AU41" s="18"/>
-      <c r="AV41" s="26"/>
-      <c r="AX41" s="42">
+      <c r="AU41" s="26"/>
+      <c r="AW41" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY41" s="23" cm="1">
-        <f t="array" ref="AY41">SUM(COUNTIFS(I41:AV41,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ41" s="23">
+      <c r="AX41" s="23" cm="1">
+        <f t="array" ref="AX41">SUM(COUNTIFS(H41:AU41,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY41" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA41" s="23" cm="1">
-        <f t="array" ref="BA41">SUM(COUNTIFS(I41:AV41,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB41" s="23">
+      <c r="AZ41" s="23" cm="1">
+        <f t="array" ref="AZ41">SUM(COUNTIFS(H41:AU41,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA41" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC41" s="278">
+      <c r="BB41" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD41" s="39">
+      <c r="BC41" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE41" s="25">
+      <c r="BD41" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF41" s="26">
+      <c r="BE41" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG41" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C41,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH41" s="26">
+      <c r="BF41" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B41,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG41" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C42" s="71"/>
+    <row r="42" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B42" s="71"/>
+      <c r="C42" s="18"/>
       <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="307"/>
-      <c r="G42" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C42,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C42,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C42,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C43,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="365"/>
-      <c r="J42" s="356"/>
+      <c r="E42" s="307"/>
+      <c r="F42" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B42,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B42,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B42,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B43,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="365"/>
+      <c r="I42" s="356"/>
+      <c r="J42" s="18"/>
       <c r="K42" s="18"/>
-      <c r="L42" s="18"/>
-      <c r="M42" s="356"/>
+      <c r="L42" s="356"/>
+      <c r="M42" s="18"/>
       <c r="N42" s="18"/>
       <c r="O42" s="18"/>
       <c r="P42" s="18"/>
@@ -23595,18 +23595,18 @@
       <c r="U42" s="18"/>
       <c r="V42" s="18"/>
       <c r="W42" s="18"/>
-      <c r="X42" s="18"/>
-      <c r="Y42" s="356"/>
+      <c r="X42" s="356"/>
+      <c r="Y42" s="18"/>
       <c r="Z42" s="18"/>
-      <c r="AA42" s="18"/>
+      <c r="AA42" s="356"/>
       <c r="AB42" s="356"/>
       <c r="AC42" s="356"/>
       <c r="AD42" s="356"/>
       <c r="AE42" s="356"/>
-      <c r="AF42" s="356"/>
-      <c r="AG42" s="18"/>
+      <c r="AF42" s="18"/>
+      <c r="AG42" s="356"/>
       <c r="AH42" s="356"/>
-      <c r="AI42" s="356"/>
+      <c r="AI42" s="18"/>
       <c r="AJ42" s="18"/>
       <c r="AK42" s="18"/>
       <c r="AL42" s="18"/>
@@ -23618,97 +23618,97 @@
       <c r="AR42" s="18"/>
       <c r="AS42" s="18"/>
       <c r="AT42" s="18"/>
-      <c r="AU42" s="18"/>
-      <c r="AV42" s="26"/>
-      <c r="AX42" s="42">
+      <c r="AU42" s="26"/>
+      <c r="AW42" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY42" s="23" cm="1">
-        <f t="array" ref="AY42">SUM(COUNTIFS(I42:AV42,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ42" s="23">
+      <c r="AX42" s="23" cm="1">
+        <f t="array" ref="AX42">SUM(COUNTIFS(H42:AU42,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY42" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA42" s="23" cm="1">
-        <f t="array" ref="BA42">SUM(COUNTIFS(I42:AV42,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB42" s="23">
+      <c r="AZ42" s="23" cm="1">
+        <f t="array" ref="AZ42">SUM(COUNTIFS(H42:AU42,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA42" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC42" s="278">
+      <c r="BB42" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD42" s="39">
+      <c r="BC42" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE42" s="25">
+      <c r="BD42" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF42" s="26">
+      <c r="BE42" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG42" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C42,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH42" s="26">
+      <c r="BF42" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B42,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG42" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C43" s="71"/>
+    <row r="43" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B43" s="71"/>
+      <c r="C43" s="18"/>
       <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="307"/>
-      <c r="G43" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C43,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C43,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C43,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C44,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I43" s="365"/>
+      <c r="E43" s="307"/>
+      <c r="F43" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B43,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B43,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B43,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B44,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="365"/>
+      <c r="I43" s="356"/>
       <c r="J43" s="356"/>
       <c r="K43" s="356"/>
       <c r="L43" s="356"/>
       <c r="M43" s="356"/>
       <c r="N43" s="356"/>
       <c r="O43" s="356"/>
-      <c r="P43" s="356"/>
+      <c r="P43" s="18"/>
       <c r="Q43" s="18"/>
       <c r="R43" s="18"/>
-      <c r="S43" s="18"/>
+      <c r="S43" s="356"/>
       <c r="T43" s="356"/>
       <c r="U43" s="356"/>
-      <c r="V43" s="356"/>
+      <c r="V43" s="18"/>
       <c r="W43" s="18"/>
-      <c r="X43" s="18"/>
-      <c r="Y43" s="356"/>
-      <c r="Z43" s="18"/>
-      <c r="AA43" s="356"/>
+      <c r="X43" s="356"/>
+      <c r="Y43" s="18"/>
+      <c r="Z43" s="356"/>
+      <c r="AA43" s="18"/>
       <c r="AB43" s="18"/>
       <c r="AC43" s="18"/>
       <c r="AD43" s="18"/>
       <c r="AE43" s="18"/>
       <c r="AF43" s="18"/>
-      <c r="AG43" s="18"/>
-      <c r="AH43" s="356"/>
+      <c r="AG43" s="356"/>
+      <c r="AH43" s="18"/>
       <c r="AI43" s="18"/>
       <c r="AJ43" s="18"/>
-      <c r="AK43" s="18"/>
+      <c r="AK43" s="356"/>
       <c r="AL43" s="356"/>
-      <c r="AM43" s="356"/>
+      <c r="AM43" s="18"/>
       <c r="AN43" s="18"/>
       <c r="AO43" s="18"/>
       <c r="AP43" s="18"/>
@@ -23716,96 +23716,96 @@
       <c r="AR43" s="18"/>
       <c r="AS43" s="18"/>
       <c r="AT43" s="18"/>
-      <c r="AU43" s="18"/>
-      <c r="AV43" s="26"/>
-      <c r="AX43" s="42">
+      <c r="AU43" s="26"/>
+      <c r="AW43" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY43" s="23" cm="1">
-        <f t="array" ref="AY43">SUM(COUNTIFS(I43:AV43,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ43" s="23">
+      <c r="AX43" s="23" cm="1">
+        <f t="array" ref="AX43">SUM(COUNTIFS(H43:AU43,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY43" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA43" s="23" cm="1">
-        <f t="array" ref="BA43">SUM(COUNTIFS(I43:AV43,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB43" s="23">
+      <c r="AZ43" s="23" cm="1">
+        <f t="array" ref="AZ43">SUM(COUNTIFS(H43:AU43,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA43" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC43" s="278">
+      <c r="BB43" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD43" s="39">
+      <c r="BC43" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE43" s="25">
+      <c r="BD43" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF43" s="26">
+      <c r="BE43" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG43" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C43,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH43" s="26">
+      <c r="BF43" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B43,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG43" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C44" s="71"/>
+    <row r="44" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B44" s="71"/>
+      <c r="C44" s="18"/>
       <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="307"/>
-      <c r="G44" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C44,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C44,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C44,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C45,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I44" s="365"/>
+      <c r="E44" s="307"/>
+      <c r="F44" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B44,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B44,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B44,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B45,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="365"/>
+      <c r="I44" s="18"/>
       <c r="J44" s="18"/>
       <c r="K44" s="18"/>
       <c r="L44" s="18"/>
       <c r="M44" s="18"/>
-      <c r="N44" s="18"/>
+      <c r="N44" s="356"/>
       <c r="O44" s="356"/>
       <c r="P44" s="356"/>
       <c r="Q44" s="356"/>
       <c r="R44" s="356"/>
       <c r="S44" s="356"/>
       <c r="T44" s="356"/>
-      <c r="U44" s="356"/>
+      <c r="U44" s="18"/>
       <c r="V44" s="18"/>
       <c r="W44" s="18"/>
       <c r="X44" s="18"/>
-      <c r="Y44" s="18"/>
+      <c r="Y44" s="356"/>
       <c r="Z44" s="356"/>
       <c r="AA44" s="356"/>
-      <c r="AB44" s="356"/>
+      <c r="AB44" s="18"/>
       <c r="AC44" s="18"/>
       <c r="AD44" s="18"/>
       <c r="AE44" s="18"/>
-      <c r="AF44" s="18"/>
+      <c r="AF44" s="356"/>
       <c r="AG44" s="356"/>
       <c r="AH44" s="356"/>
       <c r="AI44" s="356"/>
-      <c r="AJ44" s="356"/>
+      <c r="AJ44" s="18"/>
       <c r="AK44" s="18"/>
-      <c r="AL44" s="18"/>
+      <c r="AL44" s="356"/>
       <c r="AM44" s="356"/>
       <c r="AN44" s="356"/>
       <c r="AO44" s="356"/>
@@ -23814,67 +23814,67 @@
       <c r="AR44" s="356"/>
       <c r="AS44" s="356"/>
       <c r="AT44" s="356"/>
-      <c r="AU44" s="356"/>
-      <c r="AV44" s="358"/>
-      <c r="AX44" s="42">
+      <c r="AU44" s="358"/>
+      <c r="AW44" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY44" s="23" cm="1">
-        <f t="array" ref="AY44">SUM(COUNTIFS(I44:AV44,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ44" s="23">
+      <c r="AX44" s="23" cm="1">
+        <f t="array" ref="AX44">SUM(COUNTIFS(H44:AU44,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY44" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA44" s="23" cm="1">
-        <f t="array" ref="BA44">SUM(COUNTIFS(I44:AV44,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB44" s="23">
+      <c r="AZ44" s="23" cm="1">
+        <f t="array" ref="AZ44">SUM(COUNTIFS(H44:AU44,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA44" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC44" s="278">
+      <c r="BB44" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD44" s="39">
+      <c r="BC44" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE44" s="25">
+      <c r="BD44" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF44" s="26">
+      <c r="BE44" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG44" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C44,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH44" s="26">
+      <c r="BF44" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B44,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG44" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C45" s="71"/>
+    <row r="45" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B45" s="71"/>
+      <c r="C45" s="18"/>
       <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="307"/>
-      <c r="G45" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C45,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C45,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C45,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C46,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I45" s="365"/>
+      <c r="E45" s="307"/>
+      <c r="F45" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B45,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B45,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B45,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B46,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="365"/>
+      <c r="I45" s="18"/>
       <c r="J45" s="18"/>
       <c r="K45" s="18"/>
       <c r="L45" s="18"/>
@@ -23885,16 +23885,16 @@
       <c r="Q45" s="18"/>
       <c r="R45" s="18"/>
       <c r="S45" s="18"/>
-      <c r="T45" s="18"/>
-      <c r="U45" s="356"/>
-      <c r="V45" s="18"/>
-      <c r="W45" s="356"/>
+      <c r="T45" s="356"/>
+      <c r="U45" s="18"/>
+      <c r="V45" s="356"/>
+      <c r="W45" s="18"/>
       <c r="X45" s="18"/>
-      <c r="Y45" s="18"/>
-      <c r="Z45" s="352"/>
-      <c r="AA45" s="18"/>
-      <c r="AB45" s="356"/>
-      <c r="AC45" s="18"/>
+      <c r="Y45" s="352"/>
+      <c r="Z45" s="18"/>
+      <c r="AA45" s="356"/>
+      <c r="AB45" s="18"/>
+      <c r="AC45" s="356"/>
       <c r="AD45" s="356"/>
       <c r="AE45" s="356"/>
       <c r="AF45" s="356"/>
@@ -23903,7 +23903,7 @@
       <c r="AI45" s="356"/>
       <c r="AJ45" s="356"/>
       <c r="AK45" s="356"/>
-      <c r="AL45" s="356"/>
+      <c r="AL45" s="18"/>
       <c r="AM45" s="18"/>
       <c r="AN45" s="18"/>
       <c r="AO45" s="18"/>
@@ -23912,92 +23912,92 @@
       <c r="AR45" s="18"/>
       <c r="AS45" s="18"/>
       <c r="AT45" s="18"/>
-      <c r="AU45" s="18"/>
-      <c r="AV45" s="26"/>
-      <c r="AX45" s="42">
+      <c r="AU45" s="26"/>
+      <c r="AW45" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY45" s="23" cm="1">
-        <f t="array" ref="AY45">SUM(COUNTIFS(I45:AV45,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ45" s="23">
+      <c r="AX45" s="23" cm="1">
+        <f t="array" ref="AX45">SUM(COUNTIFS(H45:AU45,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY45" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA45" s="23" cm="1">
-        <f t="array" ref="BA45">SUM(COUNTIFS(I45:AV45,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB45" s="23">
+      <c r="AZ45" s="23" cm="1">
+        <f t="array" ref="AZ45">SUM(COUNTIFS(H45:AU45,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA45" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC45" s="278">
+      <c r="BB45" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD45" s="39">
+      <c r="BC45" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE45" s="25">
+      <c r="BD45" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF45" s="26">
+      <c r="BE45" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG45" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C45,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH45" s="26">
+      <c r="BF45" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B45,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG45" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C46" s="71"/>
+    <row r="46" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B46" s="71"/>
+      <c r="C46" s="18"/>
       <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="307"/>
-      <c r="G46" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C46,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C46,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C46,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C47,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I46" s="24"/>
+      <c r="E46" s="307"/>
+      <c r="F46" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B46,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B46,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B46,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B47,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="24"/>
+      <c r="I46" s="18"/>
       <c r="J46" s="18"/>
       <c r="K46" s="18"/>
       <c r="L46" s="18"/>
       <c r="M46" s="18"/>
       <c r="N46" s="18"/>
-      <c r="O46" s="18"/>
-      <c r="P46" s="356"/>
-      <c r="Q46" s="18"/>
-      <c r="R46" s="356"/>
+      <c r="O46" s="356"/>
+      <c r="P46" s="18"/>
+      <c r="Q46" s="356"/>
+      <c r="R46" s="18"/>
       <c r="S46" s="18"/>
       <c r="T46" s="18"/>
-      <c r="U46" s="18"/>
+      <c r="U46" s="356"/>
       <c r="V46" s="356"/>
-      <c r="W46" s="356"/>
+      <c r="W46" s="18"/>
       <c r="X46" s="18"/>
       <c r="Y46" s="18"/>
-      <c r="Z46" s="18"/>
+      <c r="Z46" s="356"/>
       <c r="AA46" s="356"/>
-      <c r="AB46" s="356"/>
+      <c r="AB46" s="18"/>
       <c r="AC46" s="18"/>
       <c r="AD46" s="18"/>
       <c r="AE46" s="18"/>
-      <c r="AF46" s="18"/>
+      <c r="AF46" s="356"/>
       <c r="AG46" s="356"/>
-      <c r="AH46" s="356"/>
+      <c r="AH46" s="18"/>
       <c r="AI46" s="18"/>
       <c r="AJ46" s="18"/>
       <c r="AK46" s="18"/>
@@ -24010,91 +24010,91 @@
       <c r="AR46" s="18"/>
       <c r="AS46" s="18"/>
       <c r="AT46" s="18"/>
-      <c r="AU46" s="18"/>
-      <c r="AV46" s="26"/>
-      <c r="AX46" s="42">
+      <c r="AU46" s="26"/>
+      <c r="AW46" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY46" s="23" cm="1">
-        <f t="array" ref="AY46">SUM(COUNTIFS(I46:AV46,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ46" s="23">
+      <c r="AX46" s="23" cm="1">
+        <f t="array" ref="AX46">SUM(COUNTIFS(H46:AU46,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY46" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA46" s="23" cm="1">
-        <f t="array" ref="BA46">SUM(COUNTIFS(I46:AV46,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB46" s="23">
+      <c r="AZ46" s="23" cm="1">
+        <f t="array" ref="AZ46">SUM(COUNTIFS(H46:AU46,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA46" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC46" s="278">
+      <c r="BB46" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD46" s="39">
+      <c r="BC46" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE46" s="25">
+      <c r="BD46" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF46" s="26">
+      <c r="BE46" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG46" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C46,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH46" s="26">
+      <c r="BF46" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B46,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG46" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C47" s="71"/>
+    <row r="47" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B47" s="71"/>
+      <c r="C47" s="18"/>
       <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="307"/>
-      <c r="G47" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C47,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C47,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C47,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C48,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I47" s="365"/>
+      <c r="E47" s="307"/>
+      <c r="F47" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B47,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B47,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B47,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B48,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="365"/>
+      <c r="I47" s="18"/>
       <c r="J47" s="18"/>
       <c r="K47" s="18"/>
       <c r="L47" s="18"/>
-      <c r="M47" s="18"/>
+      <c r="M47" s="356"/>
       <c r="N47" s="356"/>
       <c r="O47" s="356"/>
-      <c r="P47" s="356"/>
-      <c r="Q47" s="18"/>
-      <c r="R47" s="356"/>
-      <c r="S47" s="18"/>
+      <c r="P47" s="18"/>
+      <c r="Q47" s="356"/>
+      <c r="R47" s="18"/>
+      <c r="S47" s="356"/>
       <c r="T47" s="356"/>
-      <c r="U47" s="356"/>
+      <c r="U47" s="18"/>
       <c r="V47" s="18"/>
       <c r="W47" s="18"/>
       <c r="X47" s="18"/>
-      <c r="Y47" s="18"/>
+      <c r="Y47" s="356"/>
       <c r="Z47" s="356"/>
       <c r="AA47" s="356"/>
-      <c r="AB47" s="356"/>
-      <c r="AC47" s="18"/>
+      <c r="AB47" s="18"/>
+      <c r="AC47" s="356"/>
       <c r="AD47" s="356"/>
       <c r="AE47" s="356"/>
       <c r="AF47" s="356"/>
-      <c r="AG47" s="356"/>
+      <c r="AG47" s="18"/>
       <c r="AH47" s="18"/>
       <c r="AI47" s="18"/>
       <c r="AJ47" s="18"/>
@@ -24108,84 +24108,84 @@
       <c r="AR47" s="18"/>
       <c r="AS47" s="18"/>
       <c r="AT47" s="18"/>
-      <c r="AU47" s="18"/>
-      <c r="AV47" s="26"/>
-      <c r="AX47" s="42">
+      <c r="AU47" s="26"/>
+      <c r="AW47" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY47" s="23" cm="1">
-        <f t="array" ref="AY47">SUM(COUNTIFS(I47:AV47,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ47" s="23">
+      <c r="AX47" s="23" cm="1">
+        <f t="array" ref="AX47">SUM(COUNTIFS(H47:AU47,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY47" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA47" s="23" cm="1">
-        <f t="array" ref="BA47">SUM(COUNTIFS(I47:AV47,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB47" s="23">
+      <c r="AZ47" s="23" cm="1">
+        <f t="array" ref="AZ47">SUM(COUNTIFS(H47:AU47,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA47" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC47" s="278">
+      <c r="BB47" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD47" s="39">
+      <c r="BC47" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE47" s="25">
+      <c r="BD47" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF47" s="26">
+      <c r="BE47" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG47" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C47,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH47" s="26">
+      <c r="BF47" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B47,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG47" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C48" s="71"/>
+    <row r="48" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B48" s="71"/>
+      <c r="C48" s="18"/>
       <c r="D48" s="18"/>
-      <c r="E48" s="18"/>
-      <c r="F48" s="307"/>
-      <c r="G48" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C48,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C48,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H48" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C48,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C49,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I48" s="365"/>
-      <c r="J48" s="18"/>
-      <c r="K48" s="356"/>
+      <c r="E48" s="307"/>
+      <c r="F48" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B48,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B48,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B48,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B49,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="365"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="356"/>
+      <c r="K48" s="18"/>
       <c r="L48" s="18"/>
-      <c r="M48" s="18"/>
+      <c r="M48" s="356"/>
       <c r="N48" s="356"/>
-      <c r="O48" s="356"/>
+      <c r="O48" s="18"/>
       <c r="P48" s="18"/>
-      <c r="Q48" s="18"/>
-      <c r="R48" s="356"/>
-      <c r="S48" s="18"/>
+      <c r="Q48" s="356"/>
+      <c r="R48" s="18"/>
+      <c r="S48" s="356"/>
       <c r="T48" s="356"/>
-      <c r="U48" s="356"/>
+      <c r="U48" s="18"/>
       <c r="V48" s="18"/>
       <c r="W48" s="18"/>
-      <c r="X48" s="18"/>
-      <c r="Y48" s="356"/>
-      <c r="Z48" s="18"/>
+      <c r="X48" s="356"/>
+      <c r="Y48" s="18"/>
+      <c r="Z48" s="356"/>
       <c r="AA48" s="356"/>
       <c r="AB48" s="356"/>
       <c r="AC48" s="356"/>
@@ -24194,7 +24194,7 @@
       <c r="AF48" s="356"/>
       <c r="AG48" s="356"/>
       <c r="AH48" s="356"/>
-      <c r="AI48" s="356"/>
+      <c r="AI48" s="18"/>
       <c r="AJ48" s="18"/>
       <c r="AK48" s="18"/>
       <c r="AL48" s="18"/>
@@ -24206,67 +24206,67 @@
       <c r="AR48" s="18"/>
       <c r="AS48" s="18"/>
       <c r="AT48" s="18"/>
-      <c r="AU48" s="18"/>
-      <c r="AV48" s="26"/>
-      <c r="AX48" s="42">
+      <c r="AU48" s="26"/>
+      <c r="AW48" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY48" s="23" cm="1">
-        <f t="array" ref="AY48">SUM(COUNTIFS(I48:AV48,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ48" s="23">
+      <c r="AX48" s="23" cm="1">
+        <f t="array" ref="AX48">SUM(COUNTIFS(H48:AU48,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY48" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA48" s="23" cm="1">
-        <f t="array" ref="BA48">SUM(COUNTIFS(I48:AV48,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB48" s="23">
+      <c r="AZ48" s="23" cm="1">
+        <f t="array" ref="AZ48">SUM(COUNTIFS(H48:AU48,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA48" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC48" s="278">
+      <c r="BB48" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD48" s="39">
+      <c r="BC48" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE48" s="25">
+      <c r="BD48" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF48" s="26">
+      <c r="BE48" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG48" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C48,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH48" s="26">
+      <c r="BF48" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B48,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG48" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C49" s="71"/>
+    <row r="49" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B49" s="71"/>
+      <c r="C49" s="18"/>
       <c r="D49" s="18"/>
-      <c r="E49" s="18"/>
-      <c r="F49" s="307"/>
-      <c r="G49" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C49,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C49,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C49,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C50,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I49" s="24"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B49,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B49,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B49,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B50,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="24"/>
+      <c r="I49" s="356"/>
       <c r="J49" s="356"/>
       <c r="K49" s="356"/>
       <c r="L49" s="356"/>
@@ -24275,24 +24275,24 @@
       <c r="O49" s="356"/>
       <c r="P49" s="356"/>
       <c r="Q49" s="356"/>
-      <c r="R49" s="356"/>
-      <c r="S49" s="18"/>
-      <c r="T49" s="356"/>
+      <c r="R49" s="18"/>
+      <c r="S49" s="356"/>
+      <c r="T49" s="18"/>
       <c r="U49" s="18"/>
       <c r="V49" s="18"/>
-      <c r="W49" s="18"/>
+      <c r="W49" s="356"/>
       <c r="X49" s="356"/>
       <c r="Y49" s="356"/>
       <c r="Z49" s="356"/>
-      <c r="AA49" s="356"/>
+      <c r="AA49" s="18"/>
       <c r="AB49" s="18"/>
       <c r="AC49" s="18"/>
-      <c r="AD49" s="18"/>
-      <c r="AE49" s="356"/>
-      <c r="AF49" s="18"/>
-      <c r="AG49" s="356"/>
-      <c r="AH49" s="18"/>
-      <c r="AI49" s="356"/>
+      <c r="AD49" s="356"/>
+      <c r="AE49" s="18"/>
+      <c r="AF49" s="356"/>
+      <c r="AG49" s="18"/>
+      <c r="AH49" s="356"/>
+      <c r="AI49" s="18"/>
       <c r="AJ49" s="18"/>
       <c r="AK49" s="18"/>
       <c r="AL49" s="18"/>
@@ -24304,97 +24304,97 @@
       <c r="AR49" s="18"/>
       <c r="AS49" s="18"/>
       <c r="AT49" s="18"/>
-      <c r="AU49" s="18"/>
-      <c r="AV49" s="26"/>
-      <c r="AX49" s="42">
+      <c r="AU49" s="26"/>
+      <c r="AW49" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY49" s="23" cm="1">
-        <f t="array" ref="AY49">SUM(COUNTIFS(I49:AV49,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ49" s="23">
+      <c r="AX49" s="23" cm="1">
+        <f t="array" ref="AX49">SUM(COUNTIFS(H49:AU49,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY49" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA49" s="23" cm="1">
-        <f t="array" ref="BA49">SUM(COUNTIFS(I49:AV49,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB49" s="23">
+      <c r="AZ49" s="23" cm="1">
+        <f t="array" ref="AZ49">SUM(COUNTIFS(H49:AU49,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA49" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC49" s="278">
+      <c r="BB49" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD49" s="39">
+      <c r="BC49" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE49" s="25">
+      <c r="BD49" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF49" s="26">
+      <c r="BE49" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG49" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C49,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH49" s="26">
+      <c r="BF49" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B49,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG49" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C50" s="71"/>
+    <row r="50" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B50" s="71"/>
+      <c r="C50" s="18"/>
       <c r="D50" s="18"/>
-      <c r="E50" s="18"/>
-      <c r="F50" s="307"/>
-      <c r="G50" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C50,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C50,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H50" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C50,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C51,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I50" s="24"/>
+      <c r="E50" s="307"/>
+      <c r="F50" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B50,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B50,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B50,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B51,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="24"/>
+      <c r="I50" s="18"/>
       <c r="J50" s="18"/>
-      <c r="K50" s="18"/>
-      <c r="L50" s="356"/>
+      <c r="K50" s="356"/>
+      <c r="L50" s="18"/>
       <c r="M50" s="18"/>
       <c r="N50" s="18"/>
       <c r="O50" s="18"/>
       <c r="P50" s="18"/>
-      <c r="Q50" s="18"/>
-      <c r="R50" s="356"/>
+      <c r="Q50" s="356"/>
+      <c r="R50" s="18"/>
       <c r="S50" s="18"/>
-      <c r="T50" s="18"/>
+      <c r="T50" s="356"/>
       <c r="U50" s="356"/>
-      <c r="V50" s="356"/>
+      <c r="V50" s="18"/>
       <c r="W50" s="18"/>
       <c r="X50" s="18"/>
-      <c r="Y50" s="18"/>
+      <c r="Y50" s="356"/>
       <c r="Z50" s="356"/>
       <c r="AA50" s="356"/>
-      <c r="AB50" s="356"/>
-      <c r="AC50" s="18"/>
+      <c r="AB50" s="18"/>
+      <c r="AC50" s="356"/>
       <c r="AD50" s="356"/>
       <c r="AE50" s="356"/>
       <c r="AF50" s="356"/>
-      <c r="AG50" s="356"/>
+      <c r="AG50" s="18"/>
       <c r="AH50" s="18"/>
       <c r="AI50" s="18"/>
       <c r="AJ50" s="18"/>
       <c r="AK50" s="18"/>
       <c r="AL50" s="18"/>
-      <c r="AM50" s="18"/>
+      <c r="AM50" s="356"/>
       <c r="AN50" s="356"/>
       <c r="AO50" s="356"/>
       <c r="AP50" s="356"/>
@@ -24402,82 +24402,82 @@
       <c r="AR50" s="356"/>
       <c r="AS50" s="356"/>
       <c r="AT50" s="356"/>
-      <c r="AU50" s="356"/>
-      <c r="AV50" s="358"/>
-      <c r="AX50" s="42">
+      <c r="AU50" s="358"/>
+      <c r="AW50" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY50" s="23" cm="1">
-        <f t="array" ref="AY50">SUM(COUNTIFS(I50:AV50,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ50" s="23">
+      <c r="AX50" s="23" cm="1">
+        <f t="array" ref="AX50">SUM(COUNTIFS(H50:AU50,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY50" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA50" s="23" cm="1">
-        <f t="array" ref="BA50">SUM(COUNTIFS(I50:AV50,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB50" s="23">
+      <c r="AZ50" s="23" cm="1">
+        <f t="array" ref="AZ50">SUM(COUNTIFS(H50:AU50,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA50" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC50" s="278">
+      <c r="BB50" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD50" s="39">
+      <c r="BC50" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE50" s="25">
+      <c r="BD50" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF50" s="26">
+      <c r="BE50" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG50" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C50,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH50" s="26">
+      <c r="BF50" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B50,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG50" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C51" s="71"/>
+    <row r="51" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B51" s="71"/>
+      <c r="C51" s="18"/>
       <c r="D51" s="18"/>
-      <c r="E51" s="18"/>
-      <c r="F51" s="307"/>
-      <c r="G51" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C51,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C51,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C51,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C52,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I51" s="24"/>
-      <c r="J51" s="18"/>
+      <c r="E51" s="307"/>
+      <c r="F51" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B51,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B51,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B51,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B52,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="24"/>
+      <c r="I51" s="18"/>
+      <c r="J51" s="356"/>
       <c r="K51" s="356"/>
       <c r="L51" s="356"/>
       <c r="M51" s="356"/>
       <c r="N51" s="356"/>
-      <c r="O51" s="356"/>
+      <c r="O51" s="18"/>
       <c r="P51" s="18"/>
       <c r="Q51" s="18"/>
       <c r="R51" s="18"/>
       <c r="S51" s="18"/>
-      <c r="T51" s="18"/>
+      <c r="T51" s="356"/>
       <c r="U51" s="356"/>
-      <c r="V51" s="356"/>
-      <c r="W51" s="18"/>
-      <c r="X51" s="356"/>
+      <c r="V51" s="18"/>
+      <c r="W51" s="356"/>
+      <c r="X51" s="18"/>
       <c r="Y51" s="18"/>
       <c r="Z51" s="18"/>
       <c r="AA51" s="18"/>
@@ -24485,14 +24485,14 @@
       <c r="AC51" s="18"/>
       <c r="AD51" s="18"/>
       <c r="AE51" s="18"/>
-      <c r="AF51" s="18"/>
-      <c r="AG51" s="356"/>
-      <c r="AH51" s="18"/>
-      <c r="AI51" s="356"/>
+      <c r="AF51" s="356"/>
+      <c r="AG51" s="18"/>
+      <c r="AH51" s="356"/>
+      <c r="AI51" s="18"/>
       <c r="AJ51" s="18"/>
       <c r="AK51" s="18"/>
       <c r="AL51" s="18"/>
-      <c r="AM51" s="18"/>
+      <c r="AM51" s="356"/>
       <c r="AN51" s="356"/>
       <c r="AO51" s="356"/>
       <c r="AP51" s="356"/>
@@ -24500,82 +24500,82 @@
       <c r="AR51" s="356"/>
       <c r="AS51" s="356"/>
       <c r="AT51" s="356"/>
-      <c r="AU51" s="356"/>
-      <c r="AV51" s="358"/>
-      <c r="AX51" s="42">
+      <c r="AU51" s="358"/>
+      <c r="AW51" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY51" s="23" cm="1">
-        <f t="array" ref="AY51">SUM(COUNTIFS(I51:AV51,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ51" s="23">
+      <c r="AX51" s="23" cm="1">
+        <f t="array" ref="AX51">SUM(COUNTIFS(H51:AU51,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY51" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA51" s="23" cm="1">
-        <f t="array" ref="BA51">SUM(COUNTIFS(I51:AV51,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB51" s="23">
+      <c r="AZ51" s="23" cm="1">
+        <f t="array" ref="AZ51">SUM(COUNTIFS(H51:AU51,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA51" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC51" s="278">
+      <c r="BB51" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD51" s="39">
+      <c r="BC51" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE51" s="25">
+      <c r="BD51" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF51" s="26">
+      <c r="BE51" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG51" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C51,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH51" s="26">
+      <c r="BF51" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B51,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG51" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C52" s="71"/>
+    <row r="52" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B52" s="71"/>
+      <c r="C52" s="18"/>
       <c r="D52" s="18"/>
-      <c r="E52" s="18"/>
-      <c r="F52" s="307"/>
-      <c r="G52" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C52,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C52,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H52" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C52,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C53,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I52" s="24"/>
-      <c r="J52" s="18"/>
+      <c r="E52" s="307"/>
+      <c r="F52" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B52,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B52,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G52" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B52,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B53,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H52" s="24"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="356"/>
       <c r="K52" s="356"/>
       <c r="L52" s="356"/>
       <c r="M52" s="356"/>
       <c r="N52" s="356"/>
-      <c r="O52" s="356"/>
+      <c r="O52" s="18"/>
       <c r="P52" s="18"/>
       <c r="Q52" s="18"/>
       <c r="R52" s="18"/>
       <c r="S52" s="18"/>
-      <c r="T52" s="18"/>
+      <c r="T52" s="356"/>
       <c r="U52" s="356"/>
-      <c r="V52" s="356"/>
-      <c r="W52" s="18"/>
-      <c r="X52" s="356"/>
+      <c r="V52" s="18"/>
+      <c r="W52" s="356"/>
+      <c r="X52" s="18"/>
       <c r="Y52" s="18"/>
       <c r="Z52" s="18"/>
       <c r="AA52" s="18"/>
@@ -24583,14 +24583,14 @@
       <c r="AC52" s="18"/>
       <c r="AD52" s="18"/>
       <c r="AE52" s="18"/>
-      <c r="AF52" s="18"/>
-      <c r="AG52" s="356"/>
-      <c r="AH52" s="18"/>
-      <c r="AI52" s="356"/>
+      <c r="AF52" s="356"/>
+      <c r="AG52" s="18"/>
+      <c r="AH52" s="356"/>
+      <c r="AI52" s="18"/>
       <c r="AJ52" s="18"/>
       <c r="AK52" s="18"/>
       <c r="AL52" s="18"/>
-      <c r="AM52" s="18"/>
+      <c r="AM52" s="356"/>
       <c r="AN52" s="356"/>
       <c r="AO52" s="356"/>
       <c r="AP52" s="356"/>
@@ -24598,82 +24598,82 @@
       <c r="AR52" s="356"/>
       <c r="AS52" s="356"/>
       <c r="AT52" s="356"/>
-      <c r="AU52" s="356"/>
-      <c r="AV52" s="358"/>
-      <c r="AX52" s="42">
+      <c r="AU52" s="358"/>
+      <c r="AW52" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY52" s="23" cm="1">
-        <f t="array" ref="AY52">SUM(COUNTIFS(I52:AV52,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ52" s="23">
+      <c r="AX52" s="23" cm="1">
+        <f t="array" ref="AX52">SUM(COUNTIFS(H52:AU52,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY52" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA52" s="23" cm="1">
-        <f t="array" ref="BA52">SUM(COUNTIFS(I52:AV52,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB52" s="23">
+      <c r="AZ52" s="23" cm="1">
+        <f t="array" ref="AZ52">SUM(COUNTIFS(H52:AU52,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA52" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC52" s="278">
+      <c r="BB52" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD52" s="39">
+      <c r="BC52" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE52" s="25">
+      <c r="BD52" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF52" s="26">
+      <c r="BE52" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG52" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C52,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH52" s="26">
+      <c r="BF52" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B52,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG52" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C53" s="71"/>
+    <row r="53" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B53" s="71"/>
+      <c r="C53" s="18"/>
       <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
-      <c r="F53" s="307"/>
-      <c r="G53" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C53,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C53,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H53" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C53,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C54,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I53" s="24"/>
-      <c r="J53" s="18"/>
+      <c r="E53" s="307"/>
+      <c r="F53" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B53,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B53,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G53" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B53,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B54,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H53" s="24"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="356"/>
       <c r="K53" s="356"/>
       <c r="L53" s="356"/>
       <c r="M53" s="356"/>
       <c r="N53" s="356"/>
-      <c r="O53" s="356"/>
+      <c r="O53" s="18"/>
       <c r="P53" s="18"/>
       <c r="Q53" s="18"/>
       <c r="R53" s="18"/>
       <c r="S53" s="18"/>
-      <c r="T53" s="18"/>
+      <c r="T53" s="356"/>
       <c r="U53" s="356"/>
-      <c r="V53" s="356"/>
-      <c r="W53" s="18"/>
-      <c r="X53" s="356"/>
+      <c r="V53" s="18"/>
+      <c r="W53" s="356"/>
+      <c r="X53" s="18"/>
       <c r="Y53" s="18"/>
       <c r="Z53" s="18"/>
       <c r="AA53" s="18"/>
@@ -24681,14 +24681,14 @@
       <c r="AC53" s="18"/>
       <c r="AD53" s="18"/>
       <c r="AE53" s="18"/>
-      <c r="AF53" s="18"/>
-      <c r="AG53" s="356"/>
-      <c r="AH53" s="18"/>
-      <c r="AI53" s="356"/>
+      <c r="AF53" s="356"/>
+      <c r="AG53" s="18"/>
+      <c r="AH53" s="356"/>
+      <c r="AI53" s="18"/>
       <c r="AJ53" s="18"/>
       <c r="AK53" s="18"/>
       <c r="AL53" s="18"/>
-      <c r="AM53" s="18"/>
+      <c r="AM53" s="356"/>
       <c r="AN53" s="356"/>
       <c r="AO53" s="356"/>
       <c r="AP53" s="356"/>
@@ -24696,82 +24696,82 @@
       <c r="AR53" s="356"/>
       <c r="AS53" s="356"/>
       <c r="AT53" s="356"/>
-      <c r="AU53" s="356"/>
-      <c r="AV53" s="358"/>
-      <c r="AX53" s="42">
+      <c r="AU53" s="358"/>
+      <c r="AW53" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY53" s="23" cm="1">
-        <f t="array" ref="AY53">SUM(COUNTIFS(I53:AV53,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ53" s="23">
+      <c r="AX53" s="23" cm="1">
+        <f t="array" ref="AX53">SUM(COUNTIFS(H53:AU53,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY53" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA53" s="23" cm="1">
-        <f t="array" ref="BA53">SUM(COUNTIFS(I53:AV53,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB53" s="23">
+      <c r="AZ53" s="23" cm="1">
+        <f t="array" ref="AZ53">SUM(COUNTIFS(H53:AU53,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA53" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC53" s="278">
+      <c r="BB53" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD53" s="39">
+      <c r="BC53" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE53" s="25">
+      <c r="BD53" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF53" s="26">
+      <c r="BE53" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG53" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C53,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH53" s="26">
+      <c r="BF53" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B53,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG53" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C54" s="71"/>
+    <row r="54" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B54" s="71"/>
+      <c r="C54" s="18"/>
       <c r="D54" s="18"/>
-      <c r="E54" s="18"/>
-      <c r="F54" s="307"/>
-      <c r="G54" s="25" t="str">
-        <f>IFERROR(IF(VLOOKUP($C54,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C54,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H54" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($C54,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C55,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I54" s="24"/>
-      <c r="J54" s="18"/>
+      <c r="E54" s="307"/>
+      <c r="F54" s="25" t="str">
+        <f>IFERROR(IF(VLOOKUP($B54,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B54,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G54" s="26" t="str">
+        <f>IFERROR(IF(VLOOKUP($B54,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B55,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H54" s="24"/>
+      <c r="I54" s="18"/>
+      <c r="J54" s="356"/>
       <c r="K54" s="356"/>
       <c r="L54" s="356"/>
       <c r="M54" s="356"/>
       <c r="N54" s="356"/>
-      <c r="O54" s="356"/>
+      <c r="O54" s="18"/>
       <c r="P54" s="18"/>
       <c r="Q54" s="18"/>
       <c r="R54" s="18"/>
       <c r="S54" s="18"/>
-      <c r="T54" s="18"/>
+      <c r="T54" s="356"/>
       <c r="U54" s="356"/>
-      <c r="V54" s="356"/>
-      <c r="W54" s="18"/>
-      <c r="X54" s="356"/>
+      <c r="V54" s="18"/>
+      <c r="W54" s="356"/>
+      <c r="X54" s="18"/>
       <c r="Y54" s="18"/>
       <c r="Z54" s="18"/>
       <c r="AA54" s="18"/>
@@ -24779,14 +24779,14 @@
       <c r="AC54" s="18"/>
       <c r="AD54" s="18"/>
       <c r="AE54" s="18"/>
-      <c r="AF54" s="18"/>
-      <c r="AG54" s="356"/>
-      <c r="AH54" s="18"/>
-      <c r="AI54" s="356"/>
+      <c r="AF54" s="356"/>
+      <c r="AG54" s="18"/>
+      <c r="AH54" s="356"/>
+      <c r="AI54" s="18"/>
       <c r="AJ54" s="18"/>
       <c r="AK54" s="18"/>
       <c r="AL54" s="18"/>
-      <c r="AM54" s="18"/>
+      <c r="AM54" s="356"/>
       <c r="AN54" s="356"/>
       <c r="AO54" s="356"/>
       <c r="AP54" s="356"/>
@@ -24794,97 +24794,97 @@
       <c r="AR54" s="356"/>
       <c r="AS54" s="356"/>
       <c r="AT54" s="356"/>
-      <c r="AU54" s="356"/>
-      <c r="AV54" s="358"/>
-      <c r="AX54" s="42">
+      <c r="AU54" s="358"/>
+      <c r="AW54" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY54" s="23" cm="1">
-        <f t="array" ref="AY54">SUM(COUNTIFS(I54:AV54,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ54" s="23">
+      <c r="AX54" s="23" cm="1">
+        <f t="array" ref="AX54">SUM(COUNTIFS(H54:AU54,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY54" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA54" s="23" cm="1">
-        <f t="array" ref="BA54">SUM(COUNTIFS(I54:AV54,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB54" s="23">
+      <c r="AZ54" s="23" cm="1">
+        <f t="array" ref="AZ54">SUM(COUNTIFS(H54:AU54,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA54" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC54" s="278">
+      <c r="BB54" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD54" s="39">
+      <c r="BC54" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE54" s="25">
+      <c r="BD54" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF54" s="26">
+      <c r="BE54" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG54" s="25">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C54,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH54" s="26">
+      <c r="BF54" s="25">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B54,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG54" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="3:60" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="75"/>
+    <row r="55" spans="2:59" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="75"/>
+      <c r="C55" s="34"/>
       <c r="D55" s="34"/>
-      <c r="E55" s="34"/>
-      <c r="F55" s="308"/>
-      <c r="G55" s="33" t="str">
-        <f>IFERROR(IF(VLOOKUP($C55,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($C55,'Month-1'!$B$3:$D$53,2,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H55" s="41" t="str">
-        <f>IFERROR(IF(VLOOKUP($C55,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($C56,'Month-1'!$B$3:$D$53,3,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I55" s="38"/>
-      <c r="J55" s="34"/>
-      <c r="K55" s="359"/>
-      <c r="L55" s="34"/>
-      <c r="M55" s="359"/>
+      <c r="E55" s="308"/>
+      <c r="F55" s="33" t="str">
+        <f>IFERROR(IF(VLOOKUP($B55,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B55,'Month-1'!$B$3:$D$53,2,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G55" s="41" t="str">
+        <f>IFERROR(IF(VLOOKUP($B55,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B56,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H55" s="38"/>
+      <c r="I55" s="34"/>
+      <c r="J55" s="359"/>
+      <c r="K55" s="34"/>
+      <c r="L55" s="359"/>
+      <c r="M55" s="34"/>
       <c r="N55" s="34"/>
       <c r="O55" s="34"/>
       <c r="P55" s="34"/>
-      <c r="Q55" s="34"/>
-      <c r="R55" s="359"/>
+      <c r="Q55" s="359"/>
+      <c r="R55" s="34"/>
       <c r="S55" s="34"/>
       <c r="T55" s="34"/>
       <c r="U55" s="34"/>
-      <c r="V55" s="34"/>
+      <c r="V55" s="359"/>
       <c r="W55" s="359"/>
       <c r="X55" s="359"/>
-      <c r="Y55" s="359"/>
+      <c r="Y55" s="34"/>
       <c r="Z55" s="34"/>
-      <c r="AA55" s="34"/>
-      <c r="AB55" s="359"/>
+      <c r="AA55" s="359"/>
+      <c r="AB55" s="34"/>
       <c r="AC55" s="34"/>
-      <c r="AD55" s="34"/>
+      <c r="AD55" s="359"/>
       <c r="AE55" s="359"/>
       <c r="AF55" s="359"/>
-      <c r="AG55" s="359"/>
+      <c r="AG55" s="34"/>
       <c r="AH55" s="34"/>
       <c r="AI55" s="34"/>
       <c r="AJ55" s="34"/>
-      <c r="AK55" s="34"/>
-      <c r="AL55" s="359"/>
-      <c r="AM55" s="34"/>
+      <c r="AK55" s="359"/>
+      <c r="AL55" s="34"/>
+      <c r="AM55" s="359"/>
       <c r="AN55" s="359"/>
       <c r="AO55" s="359"/>
       <c r="AP55" s="359"/>
@@ -24892,71 +24892,74 @@
       <c r="AR55" s="359"/>
       <c r="AS55" s="359"/>
       <c r="AT55" s="359"/>
-      <c r="AU55" s="359"/>
-      <c r="AV55" s="360"/>
-      <c r="AX55" s="49">
+      <c r="AU55" s="360"/>
+      <c r="AW55" s="49">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY55" s="48" cm="1">
-        <f t="array" ref="AY55">SUM(COUNTIFS(I55:AV55,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AZ55" s="48">
+      <c r="AX55" s="48" cm="1">
+        <f t="array" ref="AX55">SUM(COUNTIFS(H55:AU55,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AY55" s="48">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA55" s="48" cm="1">
-        <f t="array" ref="BA55">SUM(COUNTIFS(I55:AV55,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BB55" s="48">
+      <c r="AZ55" s="48" cm="1">
+        <f t="array" ref="AZ55">SUM(COUNTIFS(H55:AU55,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BA55" s="48">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC55" s="279">
+      <c r="BB55" s="279">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BD55" s="50">
+      <c r="BC55" s="50">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BE55" s="33">
+      <c r="BD55" s="33">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BF55" s="41">
+      <c r="BE55" s="41">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BG55" s="33">
-        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($C55,'Month-1'!$B$3:$B$53,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH55" s="41">
+      <c r="BF55" s="33">
+        <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B55,'Month-1'!$B$3:$B$53,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG55" s="41">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="3:60" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E57" s="3" t="s">
+    <row r="57" spans="2:59" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D57" s="3" t="s">
         <v>278</v>
       </c>
+      <c r="H57" s="389" t="str">
+        <f>IFERROR(INDEX($B$6:$B$55,MATCH($D57,H$6:H$55,0)), "")</f>
+        <v/>
+      </c>
       <c r="I57" s="389" t="str">
-        <f>IFERROR(INDEX($C$6:$C$55,MATCH($E57,I$6:I$55,0)), "")</f>
+        <f>IFERROR(INDEX($B$6:$B$55,MATCH($D57,I$6:I$55,0)), "")</f>
         <v/>
       </c>
       <c r="J57" s="389" t="str">
-        <f>IFERROR(INDEX($C$6:$C$55,MATCH($E57,J$6:J$55,0)), "")</f>
+        <f>IFERROR(INDEX($B$6:$B$55,MATCH($D57,J$6:J$55,0)), "")</f>
         <v/>
       </c>
       <c r="K57" s="389" t="str">
-        <f>IFERROR(INDEX($C$6:$C$55,MATCH($E57,K$6:K$55,0)), "")</f>
+        <f t="shared" ref="K57:AU62" si="20">IFERROR(INDEX($B$6:$B$55,MATCH($D57,K$6:K$55,0)), "")</f>
         <v/>
       </c>
       <c r="L57" s="389" t="str">
-        <f t="shared" ref="L57:AV62" si="20">IFERROR(INDEX($C$6:$C$55,MATCH($E57,L$6:L$55,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="M57" s="389" t="str">
@@ -25067,14 +25070,14 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN57" s="389" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
+      <c r="AN57" s="389"/>
       <c r="AO57" s="389"/>
       <c r="AP57" s="389"/>
       <c r="AQ57" s="389"/>
-      <c r="AR57" s="389"/>
+      <c r="AR57" s="389" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
       <c r="AS57" s="389" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -25087,17 +25090,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AV57" s="389" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
     </row>
-    <row r="58" spans="3:60" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E58" s="3" t="s">
+    <row r="58" spans="2:59" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D58" s="3" t="s">
         <v>279</v>
       </c>
+      <c r="H58" s="389" t="str">
+        <f t="shared" ref="H58:W62" si="21">IFERROR(INDEX($B$6:$B$55,MATCH($D58,H$6:H$55,0)), "")</f>
+        <v/>
+      </c>
       <c r="I58" s="389" t="str">
-        <f t="shared" ref="I58:X62" si="21">IFERROR(INDEX($C$6:$C$55,MATCH($E58,I$6:I$55,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="J58" s="389" t="str">
@@ -25157,7 +25160,7 @@
         <v/>
       </c>
       <c r="X58" s="389" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="Y58" s="389" t="str">
@@ -25220,14 +25223,14 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN58" s="389" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
+      <c r="AN58" s="389"/>
       <c r="AO58" s="389"/>
       <c r="AP58" s="389"/>
       <c r="AQ58" s="389"/>
-      <c r="AR58" s="389"/>
+      <c r="AR58" s="389" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
       <c r="AS58" s="389" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -25240,14 +25243,14 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AV58" s="389" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
     </row>
-    <row r="59" spans="3:60" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E59" s="3" t="s">
+    <row r="59" spans="2:59" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D59" s="3" t="s">
         <v>280</v>
+      </c>
+      <c r="H59" s="389" t="str">
+        <f t="shared" si="21"/>
+        <v/>
       </c>
       <c r="I59" s="389" t="str">
         <f t="shared" si="21"/>
@@ -25258,7 +25261,7 @@
         <v/>
       </c>
       <c r="K59" s="389" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="L59" s="389" t="str">
@@ -25373,14 +25376,14 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN59" s="389" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
+      <c r="AN59" s="389"/>
       <c r="AO59" s="389"/>
       <c r="AP59" s="389"/>
       <c r="AQ59" s="389"/>
-      <c r="AR59" s="389"/>
+      <c r="AR59" s="389" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
       <c r="AS59" s="389" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -25393,14 +25396,14 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AV59" s="389" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
     </row>
-    <row r="60" spans="3:60" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E60" s="3" t="s">
+    <row r="60" spans="2:59" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D60" s="3" t="s">
         <v>266</v>
+      </c>
+      <c r="H60" s="389" t="str">
+        <f t="shared" si="21"/>
+        <v/>
       </c>
       <c r="I60" s="389" t="str">
         <f t="shared" si="21"/>
@@ -25411,7 +25414,7 @@
         <v/>
       </c>
       <c r="K60" s="389" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="L60" s="389" t="str">
@@ -25526,14 +25529,14 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN60" s="389" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
+      <c r="AN60" s="389"/>
       <c r="AO60" s="389"/>
       <c r="AP60" s="389"/>
       <c r="AQ60" s="389"/>
-      <c r="AR60" s="389"/>
+      <c r="AR60" s="389" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
       <c r="AS60" s="389" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -25546,14 +25549,14 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AV60" s="389" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
     </row>
-    <row r="61" spans="3:60" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E61" s="3" t="s">
+    <row r="61" spans="2:59" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D61" s="3" t="s">
         <v>20</v>
+      </c>
+      <c r="H61" s="389" t="str">
+        <f t="shared" si="21"/>
+        <v/>
       </c>
       <c r="I61" s="389" t="str">
         <f t="shared" si="21"/>
@@ -25564,7 +25567,7 @@
         <v/>
       </c>
       <c r="K61" s="389" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="L61" s="389" t="str">
@@ -25679,14 +25682,14 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN61" s="389" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
+      <c r="AN61" s="389"/>
       <c r="AO61" s="389"/>
       <c r="AP61" s="389"/>
       <c r="AQ61" s="389"/>
-      <c r="AR61" s="389"/>
+      <c r="AR61" s="389" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
       <c r="AS61" s="389" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -25699,14 +25702,14 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AV61" s="389" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
     </row>
-    <row r="62" spans="3:60" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E62" s="3" t="s">
+    <row r="62" spans="2:59" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D62" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="H62" s="389" t="str">
+        <f t="shared" si="21"/>
+        <v/>
       </c>
       <c r="I62" s="389" t="str">
         <f t="shared" si="21"/>
@@ -25717,7 +25720,7 @@
         <v/>
       </c>
       <c r="K62" s="389" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="L62" s="389" t="str">
@@ -25832,14 +25835,14 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN62" s="389" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
+      <c r="AN62" s="389"/>
       <c r="AO62" s="389"/>
       <c r="AP62" s="389"/>
       <c r="AQ62" s="389"/>
-      <c r="AR62" s="389"/>
+      <c r="AR62" s="389" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
       <c r="AS62" s="389" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -25852,119 +25855,115 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AV62" s="389" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
     </row>
-    <row r="64" spans="3:60" x14ac:dyDescent="0.2">
-      <c r="C64" s="3" t="s">
+    <row r="64" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B64" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="65" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C65" s="333" t="s">
+    <row r="65" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B65" s="333" t="s">
         <v>244</v>
       </c>
-      <c r="E65" s="327" t="s">
+      <c r="D65" s="327" t="s">
         <v>213</v>
       </c>
+      <c r="E65" s="327"/>
       <c r="F65" s="327"/>
       <c r="G65" s="327"/>
-      <c r="H65" s="327"/>
     </row>
-    <row r="66" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C66" s="334" t="s">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B66" s="334" t="s">
         <v>291</v>
       </c>
-      <c r="E66" s="327" t="s">
+      <c r="D66" s="327" t="s">
         <v>292</v>
       </c>
+      <c r="E66" s="327"/>
       <c r="F66" s="327"/>
       <c r="G66" s="327"/>
-      <c r="H66" s="327"/>
     </row>
-    <row r="67" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C67" s="335" t="s">
+    <row r="67" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B67" s="335" t="s">
         <v>243</v>
       </c>
-      <c r="E67" s="327" t="s">
+      <c r="D67" s="327" t="s">
         <v>269</v>
       </c>
+      <c r="E67" s="327"/>
       <c r="F67" s="327"/>
       <c r="G67" s="327"/>
-      <c r="H67" s="327"/>
     </row>
-    <row r="68" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C68" s="376" t="s">
+    <row r="68" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B68" s="376" t="s">
         <v>267</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="D68" s="3" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="69" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C69" s="377" t="s">
+    <row r="69" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B69" s="377" t="s">
         <v>268</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="D69" s="3" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="70" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C70" s="17" t="s">
+    <row r="70" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B70" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="D70" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="71" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C71" s="336" t="s">
+    <row r="71" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B71" s="336" t="s">
         <v>212</v>
       </c>
-      <c r="E71" s="327" t="s">
+      <c r="D71" s="327" t="s">
         <v>215</v>
       </c>
+      <c r="E71" s="327"/>
       <c r="F71" s="327"/>
       <c r="G71" s="327"/>
-      <c r="H71" s="327"/>
     </row>
-    <row r="72" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="D72" s="3"/>
+    <row r="72" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C72" s="3"/>
     </row>
-    <row r="74" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C74" s="3" t="s">
+    <row r="74" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B74" s="3" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="75" spans="3:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="C75" s="388" t="s">
+    <row r="75" spans="2:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="B75" s="388" t="s">
         <v>296</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="BE3:BF4"/>
-    <mergeCell ref="BG3:BH4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="AX3:BD3"/>
+    <mergeCell ref="BD3:BE4"/>
+    <mergeCell ref="BF3:BG4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="AW3:BC3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D1:D4 D6:D1048576">
+  <conditionalFormatting sqref="C1:C4 C6:C1048576">
     <cfRule type="beginsWith" dxfId="4" priority="1" operator="beginsWith" text="HA">
-      <formula>LEFT(D1,LEN("HA"))="HA"</formula>
+      <formula>LEFT(C1,LEN("HA"))="HA"</formula>
     </cfRule>
     <cfRule type="beginsWith" dxfId="3" priority="2" operator="beginsWith" text="D">
-      <formula>LEFT(D1,LEN("D"))="D"</formula>
+      <formula>LEFT(C1,LEN("D"))="D"</formula>
     </cfRule>
     <cfRule type="beginsWith" dxfId="2" priority="3" operator="beginsWith" text="C">
-      <formula>LEFT(D1,LEN("C"))="C"</formula>
+      <formula>LEFT(C1,LEN("C"))="C"</formula>
     </cfRule>
     <cfRule type="beginsWith" dxfId="1" priority="4" operator="beginsWith" text="B">
-      <formula>LEFT(D1,LEN("B"))="B"</formula>
+      <formula>LEFT(C1,LEN("B"))="B"</formula>
     </cfRule>
     <cfRule type="beginsWith" dxfId="0" priority="5" stopIfTrue="1" operator="beginsWith" text="A">
-      <formula>LEFT(D1,LEN("A"))="A"</formula>
+      <formula>LEFT(C1,LEN("A"))="A"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25995,11 +25994,11 @@
         <v>250</v>
       </c>
       <c r="C2" s="58">
-        <f>Month!I5-2</f>
+        <f>Month!H5-2</f>
         <v>46117</v>
       </c>
       <c r="D2" s="290">
-        <f>Month!I5-1</f>
+        <f>Month!H5-1</f>
         <v>46118</v>
       </c>
       <c r="E2" s="66" t="s">
@@ -26450,7 +26449,7 @@
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="371">
-        <f>Month!I5</f>
+        <f>Month!H5</f>
         <v>46119</v>
       </c>
       <c r="B4" s="372" t="str">
@@ -26458,27 +26457,27 @@
         <v>Tuesday</v>
       </c>
       <c r="C4" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A4,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A4,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D4" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A4,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A4,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E4" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A4,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A4,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F4" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A4,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A4,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G4" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A4,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A4,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H4" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A4,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A4,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26492,27 +26491,27 @@
         <v>Wednesday</v>
       </c>
       <c r="C5" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A5,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A5,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D5" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A5,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A5,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E5" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A5,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A5,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F5" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A5,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A5,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G5" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A5,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A5,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H5" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A5,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A5,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26526,27 +26525,27 @@
         <v>Thursday</v>
       </c>
       <c r="C6" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A6,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A6,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D6" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A6,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A6,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E6" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A6,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A6,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F6" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A6,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A6,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G6" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A6,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A6,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H6" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A6,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A6,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26560,27 +26559,27 @@
         <v>Friday</v>
       </c>
       <c r="C7" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A7,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A7,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D7" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A7,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A7,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E7" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A7,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A7,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F7" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A7,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A7,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G7" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A7,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A7,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H7" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A7,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A7,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26594,27 +26593,27 @@
         <v>Saturday</v>
       </c>
       <c r="C8" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A8,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A8,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A8,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A8,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E8" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A8,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A8,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F8" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A8,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A8,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G8" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A8,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A8,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H8" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A8,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A8,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26628,27 +26627,27 @@
         <v>Sunday</v>
       </c>
       <c r="C9" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A9,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A9,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A9,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A9,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E9" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A9,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A9,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F9" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A9,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A9,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G9" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A9,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A9,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H9" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A9,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A9,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26662,27 +26661,27 @@
         <v>Monday</v>
       </c>
       <c r="C10" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A10,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A10,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A10,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A10,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E10" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A10,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A10,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F10" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A10,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A10,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G10" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A10,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A10,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H10" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A10,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A10,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26696,27 +26695,27 @@
         <v>Tuesday</v>
       </c>
       <c r="C11" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A11,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A11,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A11,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A11,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E11" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A11,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A11,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F11" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A11,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A11,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G11" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A11,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A11,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H11" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A11,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A11,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26730,27 +26729,27 @@
         <v>Wednesday</v>
       </c>
       <c r="C12" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A12,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A12,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A12,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A12,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E12" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A12,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A12,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F12" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A12,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A12,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G12" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A12,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A12,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H12" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A12,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A12,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26764,27 +26763,27 @@
         <v>Thursday</v>
       </c>
       <c r="C13" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A13,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A13,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A13,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A13,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E13" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A13,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A13,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F13" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A13,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A13,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G13" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A13,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A13,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H13" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A13,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A13,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26798,27 +26797,27 @@
         <v>Friday</v>
       </c>
       <c r="C14" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A14,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A14,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A14,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A14,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E14" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A14,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A14,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F14" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A14,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A14,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G14" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A14,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A14,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H14" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A14,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A14,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26832,27 +26831,27 @@
         <v>Saturday</v>
       </c>
       <c r="C15" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A15,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A15,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A15,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A15,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E15" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A15,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A15,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F15" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A15,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A15,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G15" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A15,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A15,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H15" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A15,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A15,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26866,27 +26865,27 @@
         <v>Sunday</v>
       </c>
       <c r="C16" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A16,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A16,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A16,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A16,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E16" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A16,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A16,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F16" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A16,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A16,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G16" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A16,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A16,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H16" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A16,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A16,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26900,27 +26899,27 @@
         <v>Monday</v>
       </c>
       <c r="C17" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A17,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A17,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A17,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A17,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E17" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A17,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A17,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F17" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A17,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A17,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G17" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A17,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A17,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H17" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A17,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A17,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26934,27 +26933,27 @@
         <v>Tuesday</v>
       </c>
       <c r="C18" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A18,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A18,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A18,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A18,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E18" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A18,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A18,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F18" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A18,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A18,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G18" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A18,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A18,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H18" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A18,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A18,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26968,27 +26967,27 @@
         <v>Wednesday</v>
       </c>
       <c r="C19" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A19,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A19,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A19,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A19,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E19" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A19,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A19,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F19" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A19,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A19,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G19" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A19,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A19,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H19" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A19,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A19,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27002,27 +27001,27 @@
         <v>Thursday</v>
       </c>
       <c r="C20" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A20,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A20,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D20" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A20,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A20,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E20" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A20,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A20,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F20" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A20,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A20,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G20" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A20,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A20,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H20" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A20,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A20,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27036,27 +27035,27 @@
         <v>Friday</v>
       </c>
       <c r="C21" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A21,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A21,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A21,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A21,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E21" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A21,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A21,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F21" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A21,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A21,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G21" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A21,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A21,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H21" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A21,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A21,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27070,27 +27069,27 @@
         <v>Saturday</v>
       </c>
       <c r="C22" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A22,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A22,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A22,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A22,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E22" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A22,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A22,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F22" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A22,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A22,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G22" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A22,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A22,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H22" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A22,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A22,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27104,27 +27103,27 @@
         <v>Sunday</v>
       </c>
       <c r="C23" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A23,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A23,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A23,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A23,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E23" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A23,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A23,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F23" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A23,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A23,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G23" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A23,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A23,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H23" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A23,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A23,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27138,27 +27137,27 @@
         <v>Monday</v>
       </c>
       <c r="C24" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A24,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A24,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A24,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A24,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E24" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A24,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A24,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F24" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A24,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A24,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G24" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A24,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A24,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H24" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A24,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A24,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27172,27 +27171,27 @@
         <v>Tuesday</v>
       </c>
       <c r="C25" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A25,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A25,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A25,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A25,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A25,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A25,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F25" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A25,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A25,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G25" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A25,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A25,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H25" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A25,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A25,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27206,27 +27205,27 @@
         <v>Wednesday</v>
       </c>
       <c r="C26" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A26,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A26,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A26,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A26,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E26" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A26,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A26,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F26" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A26,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A26,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G26" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A26,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A26,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H26" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A26,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A26,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27240,27 +27239,27 @@
         <v>Thursday</v>
       </c>
       <c r="C27" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A27,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A27,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A27,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A27,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E27" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A27,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A27,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F27" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A27,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A27,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G27" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A27,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A27,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H27" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A27,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A27,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27274,27 +27273,27 @@
         <v>Friday</v>
       </c>
       <c r="C28" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A28,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A28,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A28,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A28,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E28" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A28,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A28,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F28" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A28,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A28,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G28" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A28,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A28,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H28" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A28,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A28,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27308,27 +27307,27 @@
         <v>Saturday</v>
       </c>
       <c r="C29" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A29,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A29,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A29,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A29,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E29" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A29,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A29,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F29" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A29,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A29,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G29" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A29,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A29,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H29" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A29,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A29,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27342,27 +27341,27 @@
         <v>Sunday</v>
       </c>
       <c r="C30" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A30,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A30,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A30,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A30,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E30" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A30,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A30,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F30" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A30,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A30,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G30" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A30,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A30,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H30" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A30,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A30,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27376,27 +27375,27 @@
         <v>Monday</v>
       </c>
       <c r="C31" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A31,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A31,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A31,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A31,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E31" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A31,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A31,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F31" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A31,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A31,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G31" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A31,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A31,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H31" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A31,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A31,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27410,27 +27409,27 @@
         <v>Tuesday</v>
       </c>
       <c r="C32" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A32,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A32,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A32,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A32,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E32" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A32,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A32,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F32" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A32,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A32,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G32" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A32,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A32,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H32" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A32,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A32,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27444,27 +27443,27 @@
         <v>Wednesday</v>
       </c>
       <c r="C33" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A33,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A33,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A33,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A33,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E33" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A33,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A33,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F33" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A33,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A33,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G33" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A33,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A33,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H33" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A33,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A33,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27478,27 +27477,27 @@
         <v>Thursday</v>
       </c>
       <c r="C34" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A34,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A34,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A34,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A34,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A34,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A34,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F34" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A34,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A34,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G34" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A34,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A34,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H34" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A34,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A34,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27512,27 +27511,27 @@
         <v>Friday</v>
       </c>
       <c r="C35" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A35,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A35,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D35" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A35,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A35,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E35" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A35,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A35,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F35" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A35,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A35,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G35" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A35,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A35,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H35" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A35,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A35,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27546,27 +27545,27 @@
         <v>Saturday</v>
       </c>
       <c r="C36" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A36,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A36,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D36" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A36,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A36,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E36" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A36,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A36,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F36" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A36,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A36,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G36" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A36,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A36,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H36" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A36,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A36,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27580,27 +27579,27 @@
         <v>Sunday</v>
       </c>
       <c r="C37" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A37,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A37,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D37" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A37,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A37,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E37" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A37,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A37,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F37" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A37,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A37,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G37" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A37,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A37,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H37" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A37,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A37,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27614,27 +27613,27 @@
         <v>Monday</v>
       </c>
       <c r="C38" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A38,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A38,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D38" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A38,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A38,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E38" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A38,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A38,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F38" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A38,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A38,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G38" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A38,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A38,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H38" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A38,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A38,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27648,27 +27647,27 @@
         <v>Tuesday</v>
       </c>
       <c r="C39" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A39,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A39,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D39" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A39,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A39,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E39" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A39,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A39,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F39" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A39,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A39,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G39" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A39,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A39,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H39" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A39,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A39,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27682,27 +27681,27 @@
         <v>Wednesday</v>
       </c>
       <c r="C40" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A40,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A40,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D40" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A40,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A40,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E40" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A40,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A40,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F40" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A40,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A40,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G40" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A40,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A40,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H40" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A40,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A40,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27716,27 +27715,27 @@
         <v>Thursday</v>
       </c>
       <c r="C41" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A41,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A41,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D41" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A41,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A41,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E41" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A41,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A41,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F41" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A41,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A41,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G41" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A41,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A41,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H41" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A41,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A41,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27750,27 +27749,27 @@
         <v>Friday</v>
       </c>
       <c r="C42" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A42,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A42,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D42" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A42,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A42,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E42" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A42,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A42,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F42" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A42,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A42,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G42" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A42,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A42,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H42" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A42,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A42,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27784,27 +27783,27 @@
         <v>Saturday</v>
       </c>
       <c r="C43" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A43,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A43,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D43" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A43,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A43,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E43" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A43,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A43,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F43" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A43,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A43,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G43" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A43,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A43,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H43" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$C$6:$C$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A43,Month!$I$5:$AV$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A43,Month!$H$5:$AU$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>

--- a/templates/Templates_REG.xlsx
+++ b/templates/Templates_REG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aletheia/Desktop/Paediatrics/Admin/RosterApp/roster/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4452EEC1-D930-5449-AA27-6DB883F22508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB5A403-9353-C140-97E2-1970FA2E5835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="840" yWindow="1280" windowWidth="28560" windowHeight="16600" activeTab="2" xr2:uid="{B6EBF472-D0B5-0C4E-A945-41133059122F}"/>
   </bookViews>
@@ -19477,22 +19477,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6259ADDC-6A2D-4608-B8DB-929D80D80DDB}">
-  <dimension ref="B1:BO75"/>
+  <dimension ref="B1:BP75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="23.83203125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5" style="3" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" style="3" customWidth="1"/>
-    <col min="6" max="7" width="9.5" style="3" customWidth="1"/>
-    <col min="8" max="47" width="9" style="1" customWidth="1"/>
-    <col min="48" max="48" width="3.1640625" style="1" customWidth="1"/>
-    <col min="49" max="55" width="8.5" style="1" customWidth="1"/>
-    <col min="56" max="16384" width="10.83203125" style="1"/>
+    <col min="4" max="5" width="13.5" style="3" customWidth="1"/>
+    <col min="6" max="6" width="0.33203125" style="3" customWidth="1"/>
+    <col min="7" max="8" width="9.5" style="3" customWidth="1"/>
+    <col min="9" max="48" width="9" style="1" customWidth="1"/>
+    <col min="49" max="49" width="3.1640625" style="1" customWidth="1"/>
+    <col min="50" max="56" width="8.5" style="1" customWidth="1"/>
+    <col min="57" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:67" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:68" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="332" t="s">
         <v>261</v>
       </c>
@@ -19502,17 +19502,17 @@
       <c r="E1" s="353"/>
       <c r="F1" s="353"/>
       <c r="G1" s="353"/>
-      <c r="H1" s="354"/>
+      <c r="H1" s="353"/>
       <c r="I1" s="354"/>
       <c r="J1" s="354"/>
       <c r="K1" s="354"/>
-      <c r="L1" s="354" t="s">
-        <v>193</v>
-      </c>
+      <c r="L1" s="354"/>
       <c r="M1" s="354" t="s">
         <v>193</v>
       </c>
-      <c r="N1" s="354"/>
+      <c r="N1" s="354" t="s">
+        <v>193</v>
+      </c>
       <c r="O1" s="354"/>
       <c r="P1" s="354"/>
       <c r="Q1" s="354"/>
@@ -19546,8 +19546,9 @@
       <c r="AS1" s="354"/>
       <c r="AT1" s="354"/>
       <c r="AU1" s="354"/>
+      <c r="AV1" s="354"/>
     </row>
-    <row r="2" spans="2:67" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:68" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="332"/>
       <c r="D2" s="353" t="s">
         <v>263</v>
@@ -19555,176 +19556,177 @@
       <c r="E2" s="353"/>
       <c r="F2" s="353"/>
       <c r="G2" s="353"/>
-      <c r="H2" s="354">
-        <f t="shared" ref="H2:AM2" si="0">WEEKDAY(H5,2)</f>
+      <c r="H2" s="353"/>
+      <c r="I2" s="354">
+        <f t="shared" ref="I2:AN2" si="0">WEEKDAY(I5,2)</f>
         <v>2</v>
       </c>
-      <c r="I2" s="354">
+      <c r="J2" s="354">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="J2" s="354">
+      <c r="K2" s="354">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K2" s="354">
+      <c r="L2" s="354">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L2" s="354">
+      <c r="M2" s="354">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="M2" s="354">
+      <c r="N2" s="354">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="N2" s="354">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="O2" s="354">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P2" s="354">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q2" s="354">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R2" s="354">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S2" s="354">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T2" s="354">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U2" s="354">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V2" s="354">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W2" s="354">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X2" s="354">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y2" s="354">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z2" s="354">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA2" s="354">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB2" s="354">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC2" s="354">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD2" s="354">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE2" s="354">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF2" s="354">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG2" s="354">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH2" s="354">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI2" s="354">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AJ2" s="354">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK2" s="354">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL2" s="354">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM2" s="354">
         <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AN2" s="354">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="AN2" s="354">
-        <f t="shared" ref="AN2:AU2" si="1">WEEKDAY(AN5,2)</f>
+      <c r="AO2" s="354">
+        <f t="shared" ref="AO2:AV2" si="1">WEEKDAY(AO5,2)</f>
         <v>6</v>
       </c>
-      <c r="AO2" s="354">
+      <c r="AP2" s="354">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="AP2" s="354">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="AQ2" s="354">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR2" s="354">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS2" s="354">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT2" s="354">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU2" s="354">
         <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="AV2" s="354">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="BD2" s="355"/>
       <c r="BE2" s="355"/>
+      <c r="BF2" s="355"/>
     </row>
-    <row r="3" spans="2:67" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:68" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="332"/>
       <c r="D3" s="353"/>
       <c r="E3" s="353"/>
       <c r="F3" s="353"/>
       <c r="G3" s="353"/>
-      <c r="H3" s="354"/>
+      <c r="H3" s="353"/>
       <c r="I3" s="354"/>
       <c r="J3" s="354"/>
       <c r="K3" s="354"/>
@@ -19764,56 +19766,57 @@
       <c r="AS3" s="354"/>
       <c r="AT3" s="354"/>
       <c r="AU3" s="354"/>
-      <c r="AW3" s="390" t="s">
+      <c r="AV3" s="354"/>
+      <c r="AX3" s="390" t="s">
         <v>176</v>
       </c>
-      <c r="AX3" s="396"/>
       <c r="AY3" s="396"/>
       <c r="AZ3" s="396"/>
       <c r="BA3" s="396"/>
       <c r="BB3" s="396"/>
-      <c r="BC3" s="391"/>
-      <c r="BD3" s="390" t="s">
+      <c r="BC3" s="396"/>
+      <c r="BD3" s="391"/>
+      <c r="BE3" s="390" t="s">
         <v>188</v>
       </c>
-      <c r="BE3" s="391"/>
-      <c r="BF3" s="390" t="s">
+      <c r="BF3" s="391"/>
+      <c r="BG3" s="390" t="s">
         <v>273</v>
       </c>
-      <c r="BG3" s="391"/>
+      <c r="BH3" s="391"/>
     </row>
-    <row r="4" spans="2:67" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="F4" s="394" t="s">
+    <row r="4" spans="2:68" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G4" s="394" t="s">
         <v>133</v>
       </c>
-      <c r="G4" s="395"/>
-      <c r="AW4" s="375" t="s">
+      <c r="H4" s="395"/>
+      <c r="AX4" s="375" t="s">
         <v>288</v>
       </c>
-      <c r="AX4" s="363" t="s">
+      <c r="AY4" s="363" t="s">
         <v>18</v>
       </c>
-      <c r="AY4" s="363" t="s">
+      <c r="AZ4" s="363" t="s">
         <v>283</v>
       </c>
-      <c r="AZ4" s="363" t="s">
+      <c r="BA4" s="363" t="s">
         <v>10</v>
       </c>
-      <c r="BA4" s="363" t="s">
+      <c r="BB4" s="363" t="s">
         <v>5</v>
       </c>
-      <c r="BB4" s="18" t="s">
+      <c r="BC4" s="18" t="s">
         <v>282</v>
       </c>
-      <c r="BC4" s="26" t="s">
+      <c r="BD4" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="BD4" s="392"/>
-      <c r="BE4" s="393"/>
-      <c r="BF4" s="392"/>
-      <c r="BG4" s="393"/>
+      <c r="BE4" s="392"/>
+      <c r="BF4" s="393"/>
+      <c r="BG4" s="392"/>
+      <c r="BH4" s="393"/>
     </row>
-    <row r="5" spans="2:67" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B5" s="357" t="s">
         <v>250</v>
       </c>
@@ -19826,208 +19829,207 @@
       <c r="E5" s="277" t="s">
         <v>277</v>
       </c>
-      <c r="F5" s="387">
-        <f>H5-2</f>
+      <c r="G5" s="387">
+        <f>I5-2</f>
         <v>46117</v>
       </c>
-      <c r="G5" s="362">
-        <f>H5-1</f>
+      <c r="H5" s="362">
+        <f>I5-1</f>
         <v>46118</v>
       </c>
-      <c r="H5" s="364">
+      <c r="I5" s="364">
         <v>46119</v>
-      </c>
-      <c r="I5" s="361">
-        <f>H5+1</f>
-        <v>46120</v>
       </c>
       <c r="J5" s="361">
         <f>I5+1</f>
-        <v>46121</v>
+        <v>46120</v>
       </c>
       <c r="K5" s="361">
         <f>J5+1</f>
+        <v>46121</v>
+      </c>
+      <c r="L5" s="361">
+        <f>K5+1</f>
         <v>46122</v>
       </c>
-      <c r="L5" s="361">
-        <f t="shared" ref="L5:AG5" si="2">K5+1</f>
+      <c r="M5" s="361">
+        <f t="shared" ref="M5:AH5" si="2">L5+1</f>
         <v>46123</v>
       </c>
-      <c r="M5" s="361">
+      <c r="N5" s="361">
         <f t="shared" si="2"/>
         <v>46124</v>
       </c>
-      <c r="N5" s="361">
+      <c r="O5" s="361">
         <f t="shared" si="2"/>
         <v>46125</v>
       </c>
-      <c r="O5" s="361">
+      <c r="P5" s="361">
         <f t="shared" si="2"/>
         <v>46126</v>
       </c>
-      <c r="P5" s="361">
+      <c r="Q5" s="361">
         <f t="shared" si="2"/>
         <v>46127</v>
       </c>
-      <c r="Q5" s="361">
+      <c r="R5" s="361">
         <f t="shared" si="2"/>
         <v>46128</v>
       </c>
-      <c r="R5" s="361">
+      <c r="S5" s="361">
         <f t="shared" si="2"/>
         <v>46129</v>
       </c>
-      <c r="S5" s="361">
+      <c r="T5" s="361">
         <f t="shared" si="2"/>
         <v>46130</v>
       </c>
-      <c r="T5" s="361">
+      <c r="U5" s="361">
         <f t="shared" si="2"/>
         <v>46131</v>
       </c>
-      <c r="U5" s="361">
+      <c r="V5" s="361">
         <f t="shared" si="2"/>
         <v>46132</v>
       </c>
-      <c r="V5" s="361">
+      <c r="W5" s="361">
         <f t="shared" si="2"/>
         <v>46133</v>
       </c>
-      <c r="W5" s="361">
+      <c r="X5" s="361">
         <f t="shared" si="2"/>
         <v>46134</v>
       </c>
-      <c r="X5" s="361">
+      <c r="Y5" s="361">
         <f t="shared" si="2"/>
         <v>46135</v>
       </c>
-      <c r="Y5" s="361">
+      <c r="Z5" s="361">
         <f t="shared" si="2"/>
         <v>46136</v>
       </c>
-      <c r="Z5" s="361">
+      <c r="AA5" s="361">
         <f t="shared" si="2"/>
         <v>46137</v>
       </c>
-      <c r="AA5" s="361">
+      <c r="AB5" s="361">
         <f t="shared" si="2"/>
         <v>46138</v>
       </c>
-      <c r="AB5" s="361">
+      <c r="AC5" s="361">
         <f t="shared" si="2"/>
         <v>46139</v>
       </c>
-      <c r="AC5" s="361">
+      <c r="AD5" s="361">
         <f t="shared" si="2"/>
         <v>46140</v>
       </c>
-      <c r="AD5" s="361">
+      <c r="AE5" s="361">
         <f t="shared" si="2"/>
         <v>46141</v>
       </c>
-      <c r="AE5" s="361">
+      <c r="AF5" s="361">
         <f t="shared" si="2"/>
         <v>46142</v>
       </c>
-      <c r="AF5" s="361">
+      <c r="AG5" s="361">
         <f t="shared" si="2"/>
         <v>46143</v>
       </c>
-      <c r="AG5" s="361">
+      <c r="AH5" s="361">
         <f t="shared" si="2"/>
         <v>46144</v>
       </c>
-      <c r="AH5" s="361">
-        <f>AG5+1</f>
+      <c r="AI5" s="361">
+        <f>AH5+1</f>
         <v>46145</v>
       </c>
-      <c r="AI5" s="361">
-        <f t="shared" ref="AI5:AM5" si="3">AH5+1</f>
+      <c r="AJ5" s="361">
+        <f t="shared" ref="AJ5:AN5" si="3">AI5+1</f>
         <v>46146</v>
       </c>
-      <c r="AJ5" s="361">
+      <c r="AK5" s="361">
         <f t="shared" si="3"/>
         <v>46147</v>
       </c>
-      <c r="AK5" s="361">
+      <c r="AL5" s="361">
         <f t="shared" si="3"/>
         <v>46148</v>
       </c>
-      <c r="AL5" s="361">
+      <c r="AM5" s="361">
         <f t="shared" si="3"/>
         <v>46149</v>
       </c>
-      <c r="AM5" s="361">
+      <c r="AN5" s="361">
         <f t="shared" si="3"/>
         <v>46150</v>
       </c>
-      <c r="AN5" s="361">
-        <f t="shared" ref="AN5" si="4">AM5+1</f>
+      <c r="AO5" s="361">
+        <f t="shared" ref="AO5" si="4">AN5+1</f>
         <v>46151</v>
       </c>
-      <c r="AO5" s="361">
-        <f t="shared" ref="AO5" si="5">AN5+1</f>
+      <c r="AP5" s="361">
+        <f t="shared" ref="AP5" si="5">AO5+1</f>
         <v>46152</v>
       </c>
-      <c r="AP5" s="361">
-        <f t="shared" ref="AP5" si="6">AO5+1</f>
+      <c r="AQ5" s="361">
+        <f t="shared" ref="AQ5" si="6">AP5+1</f>
         <v>46153</v>
       </c>
-      <c r="AQ5" s="361">
-        <f t="shared" ref="AQ5" si="7">AP5+1</f>
+      <c r="AR5" s="361">
+        <f t="shared" ref="AR5" si="7">AQ5+1</f>
         <v>46154</v>
       </c>
-      <c r="AR5" s="361">
-        <f t="shared" ref="AR5" si="8">AQ5+1</f>
+      <c r="AS5" s="361">
+        <f t="shared" ref="AS5" si="8">AR5+1</f>
         <v>46155</v>
       </c>
-      <c r="AS5" s="361">
-        <f t="shared" ref="AS5" si="9">AR5+1</f>
+      <c r="AT5" s="361">
+        <f t="shared" ref="AT5" si="9">AS5+1</f>
         <v>46156</v>
       </c>
-      <c r="AT5" s="361">
-        <f t="shared" ref="AT5" si="10">AS5+1</f>
+      <c r="AU5" s="361">
+        <f t="shared" ref="AU5" si="10">AT5+1</f>
         <v>46157</v>
       </c>
-      <c r="AU5" s="362">
-        <f t="shared" ref="AU5" si="11">AT5+1</f>
+      <c r="AV5" s="362">
+        <f t="shared" ref="AV5" si="11">AU5+1</f>
         <v>46158</v>
       </c>
-      <c r="AV5" s="5"/>
-      <c r="AW5" s="383" t="s">
+      <c r="AW5" s="5"/>
+      <c r="AX5" s="383" t="s">
         <v>289</v>
-      </c>
-      <c r="AX5" s="384" t="s">
-        <v>284</v>
       </c>
       <c r="AY5" s="384" t="s">
         <v>284</v>
       </c>
       <c r="AZ5" s="384" t="s">
+        <v>284</v>
+      </c>
+      <c r="BA5" s="384" t="s">
         <v>285</v>
       </c>
-      <c r="BA5" s="384" t="s">
+      <c r="BB5" s="384" t="s">
         <v>286</v>
       </c>
-      <c r="BB5" s="385" t="s">
+      <c r="BC5" s="385" t="s">
         <v>287</v>
       </c>
-      <c r="BC5" s="386" t="s">
+      <c r="BD5" s="386" t="s">
         <v>290</v>
       </c>
-      <c r="BD5" s="234" t="s">
+      <c r="BE5" s="234" t="s">
         <v>171</v>
       </c>
-      <c r="BE5" s="236" t="s">
+      <c r="BF5" s="236" t="s">
         <v>172</v>
       </c>
-      <c r="BF5" s="234" t="s">
+      <c r="BG5" s="234" t="s">
         <v>274</v>
       </c>
-      <c r="BG5" s="236" t="s">
+      <c r="BH5" s="236" t="s">
         <v>275</v>
       </c>
-      <c r="BH5" s="5"/>
       <c r="BI5" s="5"/>
       <c r="BJ5" s="5"/>
       <c r="BK5" s="5"/>
@@ -20035,26 +20037,27 @@
       <c r="BM5" s="5"/>
       <c r="BN5" s="5"/>
       <c r="BO5" s="5"/>
+      <c r="BP5" s="5"/>
     </row>
-    <row r="6" spans="2:67" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B6" s="71" t="s">
         <v>281</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
       <c r="E6" s="307"/>
-      <c r="F6" s="25" t="str">
+      <c r="F6" s="307"/>
+      <c r="G6" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B6,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B6,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G6" s="26" t="str">
+      <c r="H6" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B6,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B7,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H6" s="24"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="356"/>
-      <c r="K6" s="18"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="356"/>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
       <c r="N6" s="18"/>
@@ -20062,10 +20065,10 @@
       <c r="P6" s="18"/>
       <c r="Q6" s="18"/>
       <c r="R6" s="18"/>
-      <c r="S6" s="356"/>
+      <c r="S6" s="18"/>
       <c r="T6" s="356"/>
-      <c r="U6" s="18"/>
-      <c r="V6" s="356"/>
+      <c r="U6" s="356"/>
+      <c r="V6" s="18"/>
       <c r="W6" s="356"/>
       <c r="X6" s="356"/>
       <c r="Y6" s="356"/>
@@ -20080,9 +20083,9 @@
       <c r="AH6" s="356"/>
       <c r="AI6" s="356"/>
       <c r="AJ6" s="356"/>
-      <c r="AK6" s="18"/>
+      <c r="AK6" s="356"/>
       <c r="AL6" s="18"/>
-      <c r="AM6" s="356"/>
+      <c r="AM6" s="18"/>
       <c r="AN6" s="356"/>
       <c r="AO6" s="356"/>
       <c r="AP6" s="356"/>
@@ -20090,69 +20093,70 @@
       <c r="AR6" s="356"/>
       <c r="AS6" s="356"/>
       <c r="AT6" s="356"/>
-      <c r="AU6" s="358"/>
-      <c r="AW6" s="42">
-        <f>COUNTIFS(H6:AU6,"R3",$H$2:$AU$2,"&lt;5", $H$1:$AU$1,"&lt;&gt;Y")</f>
-        <v>0</v>
-      </c>
-      <c r="AX6" s="23" cm="1">
-        <f t="array" ref="AX6">SUM(COUNTIFS(H6:AU6,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY6" s="23">
-        <f>COUNTIFS(H6:AU6,"R3",$H$2:$AU$2,"5", $H$1:$AU$1,"&lt;&gt;Y")</f>
-        <v>0</v>
-      </c>
-      <c r="AZ6" s="23" cm="1">
-        <f t="array" ref="AZ6">SUM(COUNTIFS(H6:AU6,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA6" s="23">
-        <f>COUNTIFS(H6:AU6,"R3",$H$2:$AU$2,"6", $H$1:$AU$1,"&lt;&gt;Y")</f>
-        <v>0</v>
-      </c>
-      <c r="BB6" s="278">
-        <f>COUNTIFS(H6:AU6,"R*",$H$2:$AU$2,"7", $H$1:$AU$1,"&lt;&gt;Y") + COUNTIFS(H6:AU6, "R*", $H$1:$AU$1,"Y")</f>
-        <v>0</v>
-      </c>
-      <c r="BC6" s="39">
-        <f>COUNTIF(H6:AU6,"WR")</f>
-        <v>0</v>
-      </c>
-      <c r="BD6" s="25">
-        <f>SUM(AW6:BB6)</f>
-        <v>0</v>
-      </c>
-      <c r="BE6" s="26">
-        <f>AW6*0.5+AX6*1+AY6*1+AZ6*2+BA6*4+BB6*3</f>
-        <v>0</v>
-      </c>
-      <c r="BF6" s="25">
+      <c r="AU6" s="356"/>
+      <c r="AV6" s="358"/>
+      <c r="AX6" s="42">
+        <f>COUNTIFS(I6:AV6,"R3",$I$2:$AV$2,"&lt;5", $I$1:$AV$1,"&lt;&gt;Y")</f>
+        <v>0</v>
+      </c>
+      <c r="AY6" s="23" cm="1">
+        <f t="array" ref="AY6">SUM(COUNTIFS(I6:AV6,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="23">
+        <f>COUNTIFS(I6:AV6,"R3",$I$2:$AV$2,"5", $I$1:$AV$1,"&lt;&gt;Y")</f>
+        <v>0</v>
+      </c>
+      <c r="BA6" s="23" cm="1">
+        <f t="array" ref="BA6">SUM(COUNTIFS(I6:AV6,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB6" s="23">
+        <f>COUNTIFS(I6:AV6,"R3",$I$2:$AV$2,"6", $I$1:$AV$1,"&lt;&gt;Y")</f>
+        <v>0</v>
+      </c>
+      <c r="BC6" s="278">
+        <f>COUNTIFS(I6:AV6,"R*",$I$2:$AV$2,"7", $I$1:$AV$1,"&lt;&gt;Y") + COUNTIFS(I6:AV6, "R*", $I$1:$AV$1,"Y")</f>
+        <v>0</v>
+      </c>
+      <c r="BD6" s="39">
+        <f>COUNTIF(I6:AV6,"WR")</f>
+        <v>0</v>
+      </c>
+      <c r="BE6" s="25">
+        <f>SUM(AX6:BC6)</f>
+        <v>0</v>
+      </c>
+      <c r="BF6" s="26">
+        <f>AX6*0.5+AY6*1+AZ6*1+BA6*2+BB6*4+BC6*3</f>
+        <v>0</v>
+      </c>
+      <c r="BG6" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B6,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG6" s="26">
-        <f>BE6+BF6</f>
+      <c r="BH6" s="26">
+        <f>BF6+BG6</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:67" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B7" s="71"/>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
       <c r="E7" s="307"/>
-      <c r="F7" s="25" t="str">
+      <c r="F7" s="307"/>
+      <c r="G7" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B7,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B7,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G7" s="26" t="str">
+      <c r="H7" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B7,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B8,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H7" s="24"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="356"/>
-      <c r="K7" s="18"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="356"/>
       <c r="L7" s="18"/>
       <c r="M7" s="18"/>
       <c r="N7" s="18"/>
@@ -20160,10 +20164,10 @@
       <c r="P7" s="18"/>
       <c r="Q7" s="18"/>
       <c r="R7" s="18"/>
-      <c r="S7" s="356"/>
+      <c r="S7" s="18"/>
       <c r="T7" s="356"/>
-      <c r="U7" s="18"/>
-      <c r="V7" s="356"/>
+      <c r="U7" s="356"/>
+      <c r="V7" s="18"/>
       <c r="W7" s="356"/>
       <c r="X7" s="356"/>
       <c r="Y7" s="356"/>
@@ -20178,9 +20182,9 @@
       <c r="AH7" s="356"/>
       <c r="AI7" s="356"/>
       <c r="AJ7" s="356"/>
-      <c r="AK7" s="18"/>
+      <c r="AK7" s="356"/>
       <c r="AL7" s="18"/>
-      <c r="AM7" s="356"/>
+      <c r="AM7" s="18"/>
       <c r="AN7" s="356"/>
       <c r="AO7" s="356"/>
       <c r="AP7" s="356"/>
@@ -20188,67 +20192,68 @@
       <c r="AR7" s="356"/>
       <c r="AS7" s="356"/>
       <c r="AT7" s="356"/>
-      <c r="AU7" s="358"/>
-      <c r="AW7" s="42">
-        <f t="shared" ref="AW7:AW55" si="12">COUNTIFS(H7:AU7,"R3",$H$2:$AU$2,"&lt;5", $H$1:$AU$1,"&lt;&gt;Y")</f>
-        <v>0</v>
-      </c>
-      <c r="AX7" s="23" cm="1">
-        <f t="array" ref="AX7">SUM(COUNTIFS(H7:AU7,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY7" s="23">
-        <f t="shared" ref="AY7:AY55" si="13">COUNTIFS(H7:AU7,"R3",$H$2:$AU$2,"5", $H$1:$AU$1,"&lt;&gt;Y")</f>
-        <v>0</v>
-      </c>
-      <c r="AZ7" s="23" cm="1">
-        <f t="array" ref="AZ7">SUM(COUNTIFS(H7:AU7,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA7" s="23">
-        <f t="shared" ref="BA7:BA55" si="14">COUNTIFS(H7:AU7,"R3",$H$2:$AU$2,"6", $H$1:$AU$1,"&lt;&gt;Y")</f>
-        <v>0</v>
-      </c>
-      <c r="BB7" s="278">
-        <f t="shared" ref="BB7:BB55" si="15">COUNTIFS(H7:AU7,"R*",$H$2:$AU$2,"7", $H$1:$AU$1,"&lt;&gt;Y") + COUNTIFS(H7:AU7, "R*", $H$1:$AU$1,"Y")</f>
-        <v>0</v>
-      </c>
-      <c r="BC7" s="39">
-        <f t="shared" ref="BC7:BC55" si="16">COUNTIF(H7:AU7,"WR")</f>
-        <v>0</v>
-      </c>
-      <c r="BD7" s="25">
-        <f t="shared" ref="BD7:BD55" si="17">SUM(AW7:BB7)</f>
-        <v>0</v>
-      </c>
-      <c r="BE7" s="26">
-        <f t="shared" ref="BE7:BE55" si="18">AW7*0.5+AX7*1+AY7*1+AZ7*2+BA7*4+BB7*3</f>
-        <v>0</v>
-      </c>
-      <c r="BF7" s="25">
+      <c r="AU7" s="356"/>
+      <c r="AV7" s="358"/>
+      <c r="AX7" s="42">
+        <f t="shared" ref="AX7:AX55" si="12">COUNTIFS(I7:AV7,"R3",$I$2:$AV$2,"&lt;5", $I$1:$AV$1,"&lt;&gt;Y")</f>
+        <v>0</v>
+      </c>
+      <c r="AY7" s="23" cm="1">
+        <f t="array" ref="AY7">SUM(COUNTIFS(I7:AV7,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="23">
+        <f t="shared" ref="AZ7:AZ55" si="13">COUNTIFS(I7:AV7,"R3",$I$2:$AV$2,"5", $I$1:$AV$1,"&lt;&gt;Y")</f>
+        <v>0</v>
+      </c>
+      <c r="BA7" s="23" cm="1">
+        <f t="array" ref="BA7">SUM(COUNTIFS(I7:AV7,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB7" s="23">
+        <f t="shared" ref="BB7:BB55" si="14">COUNTIFS(I7:AV7,"R3",$I$2:$AV$2,"6", $I$1:$AV$1,"&lt;&gt;Y")</f>
+        <v>0</v>
+      </c>
+      <c r="BC7" s="278">
+        <f t="shared" ref="BC7:BC55" si="15">COUNTIFS(I7:AV7,"R*",$I$2:$AV$2,"7", $I$1:$AV$1,"&lt;&gt;Y") + COUNTIFS(I7:AV7, "R*", $I$1:$AV$1,"Y")</f>
+        <v>0</v>
+      </c>
+      <c r="BD7" s="39">
+        <f t="shared" ref="BD7:BD55" si="16">COUNTIF(I7:AV7,"WR")</f>
+        <v>0</v>
+      </c>
+      <c r="BE7" s="25">
+        <f t="shared" ref="BE7:BE55" si="17">SUM(AX7:BC7)</f>
+        <v>0</v>
+      </c>
+      <c r="BF7" s="26">
+        <f t="shared" ref="BF7:BF55" si="18">AX7*0.5+AY7*1+AZ7*1+BA7*2+BB7*4+BC7*3</f>
+        <v>0</v>
+      </c>
+      <c r="BG7" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B7,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG7" s="26">
-        <f t="shared" ref="BG7:BG55" si="19">BE7+BF7</f>
+      <c r="BH7" s="26">
+        <f t="shared" ref="BH7:BH55" si="19">BF7+BG7</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:67" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B8" s="71"/>
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
       <c r="E8" s="307"/>
-      <c r="F8" s="25" t="str">
+      <c r="F8" s="307"/>
+      <c r="G8" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B8,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B8,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G8" s="26" t="str">
+      <c r="H8" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B8,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B9,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H8" s="24"/>
-      <c r="I8" s="18"/>
+      <c r="I8" s="24"/>
       <c r="J8" s="18"/>
       <c r="K8" s="18"/>
       <c r="L8" s="18"/>
@@ -20264,7 +20269,7 @@
       <c r="V8" s="18"/>
       <c r="W8" s="18"/>
       <c r="X8" s="18"/>
-      <c r="Y8" s="356"/>
+      <c r="Y8" s="18"/>
       <c r="Z8" s="356"/>
       <c r="AA8" s="356"/>
       <c r="AB8" s="356"/>
@@ -20272,7 +20277,7 @@
       <c r="AD8" s="356"/>
       <c r="AE8" s="356"/>
       <c r="AF8" s="356"/>
-      <c r="AG8" s="18"/>
+      <c r="AG8" s="356"/>
       <c r="AH8" s="18"/>
       <c r="AI8" s="18"/>
       <c r="AJ8" s="18"/>
@@ -20286,95 +20291,96 @@
       <c r="AR8" s="18"/>
       <c r="AS8" s="18"/>
       <c r="AT8" s="18"/>
-      <c r="AU8" s="26"/>
-      <c r="AW8" s="42">
+      <c r="AU8" s="18"/>
+      <c r="AV8" s="26"/>
+      <c r="AX8" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX8" s="23" cm="1">
-        <f t="array" ref="AX8">SUM(COUNTIFS(H8:AU8,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY8" s="23">
+      <c r="AY8" s="23" cm="1">
+        <f t="array" ref="AY8">SUM(COUNTIFS(I8:AV8,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ8" s="23" cm="1">
-        <f t="array" ref="AZ8">SUM(COUNTIFS(H8:AU8,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA8" s="23">
+      <c r="BA8" s="23" cm="1">
+        <f t="array" ref="BA8">SUM(COUNTIFS(I8:AV8,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB8" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB8" s="278">
+      <c r="BC8" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC8" s="39">
+      <c r="BD8" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD8" s="25">
+      <c r="BE8" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE8" s="26">
+      <c r="BF8" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF8" s="25">
+      <c r="BG8" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B8,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG8" s="26">
+      <c r="BH8" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:67" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B9" s="71"/>
       <c r="C9" s="18"/>
       <c r="D9" s="18"/>
       <c r="E9" s="307"/>
-      <c r="F9" s="25" t="str">
+      <c r="F9" s="307"/>
+      <c r="G9" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B9,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B9,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G9" s="26" t="str">
+      <c r="H9" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B9,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B10,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H9" s="24"/>
-      <c r="I9" s="356"/>
+      <c r="I9" s="24"/>
       <c r="J9" s="356"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="356"/>
-      <c r="M9" s="18"/>
+      <c r="K9" s="356"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="356"/>
       <c r="N9" s="18"/>
       <c r="O9" s="18"/>
       <c r="P9" s="18"/>
       <c r="Q9" s="18"/>
-      <c r="R9" s="356"/>
-      <c r="S9" s="18"/>
+      <c r="R9" s="18"/>
+      <c r="S9" s="356"/>
       <c r="T9" s="18"/>
       <c r="U9" s="18"/>
       <c r="V9" s="18"/>
       <c r="W9" s="18"/>
       <c r="X9" s="18"/>
       <c r="Y9" s="18"/>
-      <c r="Z9" s="356"/>
+      <c r="Z9" s="18"/>
       <c r="AA9" s="356"/>
-      <c r="AB9" s="18"/>
+      <c r="AB9" s="356"/>
       <c r="AC9" s="18"/>
       <c r="AD9" s="18"/>
       <c r="AE9" s="18"/>
       <c r="AF9" s="18"/>
       <c r="AG9" s="18"/>
-      <c r="AH9" s="356"/>
+      <c r="AH9" s="18"/>
       <c r="AI9" s="356"/>
       <c r="AJ9" s="356"/>
-      <c r="AK9" s="18"/>
+      <c r="AK9" s="356"/>
       <c r="AL9" s="18"/>
       <c r="AM9" s="18"/>
       <c r="AN9" s="18"/>
@@ -20384,95 +20390,96 @@
       <c r="AR9" s="18"/>
       <c r="AS9" s="18"/>
       <c r="AT9" s="18"/>
-      <c r="AU9" s="26"/>
-      <c r="AW9" s="42">
+      <c r="AU9" s="18"/>
+      <c r="AV9" s="26"/>
+      <c r="AX9" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX9" s="23" cm="1">
-        <f t="array" ref="AX9">SUM(COUNTIFS(H9:AU9,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY9" s="23">
+      <c r="AY9" s="23" cm="1">
+        <f t="array" ref="AY9">SUM(COUNTIFS(I9:AV9,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ9" s="23" cm="1">
-        <f t="array" ref="AZ9">SUM(COUNTIFS(H9:AU9,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA9" s="23">
+      <c r="BA9" s="23" cm="1">
+        <f t="array" ref="BA9">SUM(COUNTIFS(I9:AV9,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB9" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB9" s="278">
+      <c r="BC9" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC9" s="39">
+      <c r="BD9" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD9" s="25">
+      <c r="BE9" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE9" s="26">
+      <c r="BF9" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF9" s="25">
+      <c r="BG9" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B9,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG9" s="26">
+      <c r="BH9" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:67" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B10" s="71"/>
       <c r="C10" s="18"/>
       <c r="D10" s="18"/>
       <c r="E10" s="307"/>
-      <c r="F10" s="25" t="str">
+      <c r="F10" s="307"/>
+      <c r="G10" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B10,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B10,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G10" s="26" t="str">
+      <c r="H10" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B10,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B11,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H10" s="24"/>
-      <c r="I10" s="356"/>
+      <c r="I10" s="24"/>
       <c r="J10" s="356"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="356"/>
-      <c r="M10" s="18"/>
+      <c r="K10" s="356"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="356"/>
       <c r="N10" s="18"/>
       <c r="O10" s="18"/>
       <c r="P10" s="18"/>
       <c r="Q10" s="18"/>
-      <c r="R10" s="356"/>
-      <c r="S10" s="18"/>
+      <c r="R10" s="18"/>
+      <c r="S10" s="356"/>
       <c r="T10" s="18"/>
       <c r="U10" s="18"/>
       <c r="V10" s="18"/>
       <c r="W10" s="18"/>
       <c r="X10" s="18"/>
       <c r="Y10" s="18"/>
-      <c r="Z10" s="356"/>
+      <c r="Z10" s="18"/>
       <c r="AA10" s="356"/>
-      <c r="AB10" s="18"/>
+      <c r="AB10" s="356"/>
       <c r="AC10" s="18"/>
       <c r="AD10" s="18"/>
       <c r="AE10" s="18"/>
       <c r="AF10" s="18"/>
       <c r="AG10" s="18"/>
-      <c r="AH10" s="356"/>
+      <c r="AH10" s="18"/>
       <c r="AI10" s="356"/>
       <c r="AJ10" s="356"/>
-      <c r="AK10" s="18"/>
+      <c r="AK10" s="356"/>
       <c r="AL10" s="18"/>
       <c r="AM10" s="18"/>
       <c r="AN10" s="18"/>
@@ -20482,95 +20489,96 @@
       <c r="AR10" s="18"/>
       <c r="AS10" s="18"/>
       <c r="AT10" s="18"/>
-      <c r="AU10" s="26"/>
-      <c r="AW10" s="42">
+      <c r="AU10" s="18"/>
+      <c r="AV10" s="26"/>
+      <c r="AX10" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX10" s="23" cm="1">
-        <f t="array" ref="AX10">SUM(COUNTIFS(H10:AU10,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY10" s="23">
+      <c r="AY10" s="23" cm="1">
+        <f t="array" ref="AY10">SUM(COUNTIFS(I10:AV10,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ10" s="23" cm="1">
-        <f t="array" ref="AZ10">SUM(COUNTIFS(H10:AU10,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA10" s="23">
+      <c r="BA10" s="23" cm="1">
+        <f t="array" ref="BA10">SUM(COUNTIFS(I10:AV10,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB10" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB10" s="278">
+      <c r="BC10" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC10" s="39">
+      <c r="BD10" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD10" s="25">
+      <c r="BE10" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE10" s="26">
+      <c r="BF10" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF10" s="25">
+      <c r="BG10" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B10,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG10" s="26">
+      <c r="BH10" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:67" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B11" s="71"/>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
       <c r="E11" s="307"/>
-      <c r="F11" s="25" t="str">
+      <c r="F11" s="307"/>
+      <c r="G11" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B11,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B11,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G11" s="26" t="str">
+      <c r="H11" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B11,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B12,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H11" s="24"/>
-      <c r="I11" s="356"/>
+      <c r="I11" s="24"/>
       <c r="J11" s="356"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="356"/>
-      <c r="M11" s="18"/>
+      <c r="K11" s="356"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="356"/>
       <c r="N11" s="18"/>
       <c r="O11" s="18"/>
       <c r="P11" s="18"/>
       <c r="Q11" s="18"/>
-      <c r="R11" s="356"/>
-      <c r="S11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="356"/>
       <c r="T11" s="18"/>
       <c r="U11" s="18"/>
       <c r="V11" s="18"/>
       <c r="W11" s="18"/>
       <c r="X11" s="18"/>
       <c r="Y11" s="18"/>
-      <c r="Z11" s="356"/>
+      <c r="Z11" s="18"/>
       <c r="AA11" s="356"/>
-      <c r="AB11" s="18"/>
+      <c r="AB11" s="356"/>
       <c r="AC11" s="18"/>
       <c r="AD11" s="18"/>
       <c r="AE11" s="18"/>
       <c r="AF11" s="18"/>
       <c r="AG11" s="18"/>
-      <c r="AH11" s="356"/>
+      <c r="AH11" s="18"/>
       <c r="AI11" s="356"/>
       <c r="AJ11" s="356"/>
-      <c r="AK11" s="18"/>
+      <c r="AK11" s="356"/>
       <c r="AL11" s="18"/>
       <c r="AM11" s="18"/>
       <c r="AN11" s="18"/>
@@ -20580,69 +20588,70 @@
       <c r="AR11" s="18"/>
       <c r="AS11" s="18"/>
       <c r="AT11" s="18"/>
-      <c r="AU11" s="26"/>
-      <c r="AW11" s="42">
+      <c r="AU11" s="18"/>
+      <c r="AV11" s="26"/>
+      <c r="AX11" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX11" s="23" cm="1">
-        <f t="array" ref="AX11">SUM(COUNTIFS(H11:AU11,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY11" s="23">
+      <c r="AY11" s="23" cm="1">
+        <f t="array" ref="AY11">SUM(COUNTIFS(I11:AV11,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ11" s="23" cm="1">
-        <f t="array" ref="AZ11">SUM(COUNTIFS(H11:AU11,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA11" s="23">
+      <c r="BA11" s="23" cm="1">
+        <f t="array" ref="BA11">SUM(COUNTIFS(I11:AV11,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB11" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB11" s="278">
+      <c r="BC11" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC11" s="39">
+      <c r="BD11" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD11" s="25">
+      <c r="BE11" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE11" s="26">
+      <c r="BF11" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF11" s="25">
+      <c r="BG11" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B11,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG11" s="26">
+      <c r="BH11" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:67" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B12" s="71"/>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
       <c r="E12" s="307"/>
-      <c r="F12" s="25" t="str">
+      <c r="F12" s="307"/>
+      <c r="G12" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B12,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B12,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G12" s="26" t="str">
+      <c r="H12" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B12,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B13,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H12" s="365"/>
-      <c r="I12" s="356"/>
+      <c r="I12" s="365"/>
       <c r="J12" s="356"/>
-      <c r="K12" s="18"/>
+      <c r="K12" s="356"/>
       <c r="L12" s="18"/>
       <c r="M12" s="18"/>
       <c r="N12" s="18"/>
@@ -20653,24 +20662,24 @@
       <c r="S12" s="18"/>
       <c r="T12" s="18"/>
       <c r="U12" s="18"/>
-      <c r="V12" s="356"/>
+      <c r="V12" s="18"/>
       <c r="W12" s="356"/>
       <c r="X12" s="356"/>
       <c r="Y12" s="356"/>
       <c r="Z12" s="356"/>
-      <c r="AA12" s="18"/>
-      <c r="AB12" s="356"/>
-      <c r="AC12" s="18"/>
+      <c r="AA12" s="356"/>
+      <c r="AB12" s="18"/>
+      <c r="AC12" s="356"/>
       <c r="AD12" s="18"/>
       <c r="AE12" s="18"/>
-      <c r="AF12" s="356"/>
+      <c r="AF12" s="18"/>
       <c r="AG12" s="356"/>
       <c r="AH12" s="356"/>
-      <c r="AI12" s="18"/>
+      <c r="AI12" s="356"/>
       <c r="AJ12" s="18"/>
       <c r="AK12" s="18"/>
       <c r="AL12" s="18"/>
-      <c r="AM12" s="356"/>
+      <c r="AM12" s="18"/>
       <c r="AN12" s="356"/>
       <c r="AO12" s="356"/>
       <c r="AP12" s="356"/>
@@ -20678,86 +20687,87 @@
       <c r="AR12" s="356"/>
       <c r="AS12" s="356"/>
       <c r="AT12" s="356"/>
-      <c r="AU12" s="358"/>
-      <c r="AW12" s="42">
+      <c r="AU12" s="356"/>
+      <c r="AV12" s="358"/>
+      <c r="AX12" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX12" s="23" cm="1">
-        <f t="array" ref="AX12">SUM(COUNTIFS(H12:AU12,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY12" s="23">
+      <c r="AY12" s="23" cm="1">
+        <f t="array" ref="AY12">SUM(COUNTIFS(I12:AV12,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ12" s="23" cm="1">
-        <f t="array" ref="AZ12">SUM(COUNTIFS(H12:AU12,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA12" s="23">
+      <c r="BA12" s="23" cm="1">
+        <f t="array" ref="BA12">SUM(COUNTIFS(I12:AV12,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB12" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB12" s="278">
+      <c r="BC12" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC12" s="39">
+      <c r="BD12" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD12" s="25">
+      <c r="BE12" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE12" s="26">
+      <c r="BF12" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF12" s="25">
+      <c r="BG12" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B12,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG12" s="26">
+      <c r="BH12" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:67" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B13" s="71"/>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
       <c r="E13" s="307"/>
-      <c r="F13" s="25" t="str">
+      <c r="F13" s="307"/>
+      <c r="G13" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B13,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B13,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G13" s="26" t="str">
+      <c r="H13" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B13,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B14,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H13" s="24"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="356"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="356"/>
-      <c r="M13" s="18"/>
-      <c r="N13" s="356"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="356"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="356"/>
+      <c r="N13" s="18"/>
       <c r="O13" s="356"/>
       <c r="P13" s="356"/>
       <c r="Q13" s="356"/>
       <c r="R13" s="356"/>
       <c r="S13" s="356"/>
-      <c r="T13" s="18"/>
+      <c r="T13" s="356"/>
       <c r="U13" s="18"/>
       <c r="V13" s="18"/>
       <c r="W13" s="18"/>
-      <c r="X13" s="356"/>
+      <c r="X13" s="18"/>
       <c r="Y13" s="356"/>
       <c r="Z13" s="356"/>
       <c r="AA13" s="356"/>
-      <c r="AB13" s="18"/>
+      <c r="AB13" s="356"/>
       <c r="AC13" s="18"/>
       <c r="AD13" s="18"/>
       <c r="AE13" s="18"/>
@@ -20776,86 +20786,87 @@
       <c r="AR13" s="18"/>
       <c r="AS13" s="18"/>
       <c r="AT13" s="18"/>
-      <c r="AU13" s="26"/>
-      <c r="AW13" s="42">
+      <c r="AU13" s="18"/>
+      <c r="AV13" s="26"/>
+      <c r="AX13" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX13" s="23" cm="1">
-        <f t="array" ref="AX13">SUM(COUNTIFS(H13:AU13,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY13" s="23">
+      <c r="AY13" s="23" cm="1">
+        <f t="array" ref="AY13">SUM(COUNTIFS(I13:AV13,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ13" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ13" s="23" cm="1">
-        <f t="array" ref="AZ13">SUM(COUNTIFS(H13:AU13,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA13" s="23">
+      <c r="BA13" s="23" cm="1">
+        <f t="array" ref="BA13">SUM(COUNTIFS(I13:AV13,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB13" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB13" s="278">
+      <c r="BC13" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC13" s="39">
+      <c r="BD13" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD13" s="25">
+      <c r="BE13" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE13" s="26">
+      <c r="BF13" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF13" s="25">
+      <c r="BG13" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B13,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG13" s="26">
+      <c r="BH13" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:67" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B14" s="71"/>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
       <c r="E14" s="307"/>
-      <c r="F14" s="25" t="str">
+      <c r="F14" s="307"/>
+      <c r="G14" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B14,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B14,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G14" s="26" t="str">
+      <c r="H14" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B14,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B15,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H14" s="24"/>
-      <c r="I14" s="18"/>
+      <c r="I14" s="24"/>
       <c r="J14" s="18"/>
-      <c r="K14" s="356"/>
-      <c r="L14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="356"/>
       <c r="M14" s="18"/>
       <c r="N14" s="18"/>
       <c r="O14" s="18"/>
       <c r="P14" s="18"/>
-      <c r="Q14" s="356"/>
-      <c r="R14" s="18"/>
+      <c r="Q14" s="18"/>
+      <c r="R14" s="356"/>
       <c r="S14" s="18"/>
       <c r="T14" s="18"/>
-      <c r="U14" s="356"/>
+      <c r="U14" s="18"/>
       <c r="V14" s="356"/>
       <c r="W14" s="356"/>
-      <c r="X14" s="18"/>
+      <c r="X14" s="356"/>
       <c r="Y14" s="18"/>
-      <c r="Z14" s="356"/>
+      <c r="Z14" s="18"/>
       <c r="AA14" s="356"/>
-      <c r="AB14" s="18"/>
+      <c r="AB14" s="356"/>
       <c r="AC14" s="18"/>
       <c r="AD14" s="18"/>
       <c r="AE14" s="18"/>
@@ -20874,93 +20885,94 @@
       <c r="AR14" s="18"/>
       <c r="AS14" s="18"/>
       <c r="AT14" s="18"/>
-      <c r="AU14" s="26"/>
-      <c r="AW14" s="42">
+      <c r="AU14" s="18"/>
+      <c r="AV14" s="26"/>
+      <c r="AX14" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX14" s="23" cm="1">
-        <f t="array" ref="AX14">SUM(COUNTIFS(H14:AU14,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY14" s="23">
+      <c r="AY14" s="23" cm="1">
+        <f t="array" ref="AY14">SUM(COUNTIFS(I14:AV14,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ14" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ14" s="23" cm="1">
-        <f t="array" ref="AZ14">SUM(COUNTIFS(H14:AU14,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA14" s="23">
+      <c r="BA14" s="23" cm="1">
+        <f t="array" ref="BA14">SUM(COUNTIFS(I14:AV14,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB14" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB14" s="278">
+      <c r="BC14" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC14" s="39">
+      <c r="BD14" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD14" s="25">
+      <c r="BE14" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE14" s="26">
+      <c r="BF14" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF14" s="25">
+      <c r="BG14" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B14,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG14" s="26">
+      <c r="BH14" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:67" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B15" s="71"/>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
       <c r="E15" s="307"/>
-      <c r="F15" s="25" t="str">
+      <c r="F15" s="307"/>
+      <c r="G15" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B15,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B15,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G15" s="26" t="str">
+      <c r="H15" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B15,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B16,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H15" s="24"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="356"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="356"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="356"/>
+      <c r="L15" s="18"/>
       <c r="M15" s="356"/>
       <c r="N15" s="356"/>
       <c r="O15" s="356"/>
       <c r="P15" s="356"/>
       <c r="Q15" s="356"/>
       <c r="R15" s="356"/>
-      <c r="S15" s="18"/>
-      <c r="T15" s="356"/>
+      <c r="S15" s="356"/>
+      <c r="T15" s="18"/>
       <c r="U15" s="356"/>
       <c r="V15" s="356"/>
       <c r="W15" s="356"/>
-      <c r="X15" s="18"/>
+      <c r="X15" s="356"/>
       <c r="Y15" s="18"/>
-      <c r="Z15" s="356"/>
+      <c r="Z15" s="18"/>
       <c r="AA15" s="356"/>
-      <c r="AB15" s="18"/>
+      <c r="AB15" s="356"/>
       <c r="AC15" s="18"/>
       <c r="AD15" s="18"/>
       <c r="AE15" s="18"/>
-      <c r="AF15" s="356"/>
+      <c r="AF15" s="18"/>
       <c r="AG15" s="356"/>
       <c r="AH15" s="356"/>
-      <c r="AI15" s="18"/>
+      <c r="AI15" s="356"/>
       <c r="AJ15" s="18"/>
       <c r="AK15" s="18"/>
       <c r="AL15" s="18"/>
@@ -20972,97 +20984,98 @@
       <c r="AR15" s="18"/>
       <c r="AS15" s="18"/>
       <c r="AT15" s="18"/>
-      <c r="AU15" s="26"/>
-      <c r="AW15" s="42">
+      <c r="AU15" s="18"/>
+      <c r="AV15" s="26"/>
+      <c r="AX15" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX15" s="23" cm="1">
-        <f t="array" ref="AX15">SUM(COUNTIFS(H15:AU15,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY15" s="23">
+      <c r="AY15" s="23" cm="1">
+        <f t="array" ref="AY15">SUM(COUNTIFS(I15:AV15,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ15" s="23" cm="1">
-        <f t="array" ref="AZ15">SUM(COUNTIFS(H15:AU15,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA15" s="23">
+      <c r="BA15" s="23" cm="1">
+        <f t="array" ref="BA15">SUM(COUNTIFS(I15:AV15,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB15" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB15" s="278">
+      <c r="BC15" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC15" s="39">
+      <c r="BD15" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD15" s="25">
+      <c r="BE15" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE15" s="26">
+      <c r="BF15" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF15" s="25">
+      <c r="BG15" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B15,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG15" s="26">
+      <c r="BH15" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:67" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B16" s="71"/>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
       <c r="E16" s="307"/>
-      <c r="F16" s="25" t="str">
+      <c r="F16" s="307"/>
+      <c r="G16" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B16,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B16,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G16" s="26" t="str">
+      <c r="H16" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B16,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B17,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H16" s="24"/>
-      <c r="I16" s="18"/>
+      <c r="I16" s="24"/>
       <c r="J16" s="18"/>
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
       <c r="M16" s="18"/>
       <c r="N16" s="18"/>
       <c r="O16" s="18"/>
-      <c r="P16" s="356"/>
+      <c r="P16" s="18"/>
       <c r="Q16" s="356"/>
       <c r="R16" s="356"/>
       <c r="S16" s="356"/>
-      <c r="T16" s="18"/>
+      <c r="T16" s="356"/>
       <c r="U16" s="18"/>
       <c r="V16" s="18"/>
       <c r="W16" s="18"/>
       <c r="X16" s="18"/>
       <c r="Y16" s="18"/>
-      <c r="Z16" s="356"/>
+      <c r="Z16" s="18"/>
       <c r="AA16" s="356"/>
-      <c r="AB16" s="18"/>
+      <c r="AB16" s="356"/>
       <c r="AC16" s="18"/>
       <c r="AD16" s="18"/>
       <c r="AE16" s="18"/>
       <c r="AF16" s="18"/>
-      <c r="AG16" s="356"/>
-      <c r="AH16" s="18"/>
+      <c r="AG16" s="18"/>
+      <c r="AH16" s="356"/>
       <c r="AI16" s="18"/>
       <c r="AJ16" s="18"/>
-      <c r="AK16" s="356"/>
-      <c r="AL16" s="18"/>
-      <c r="AM16" s="356"/>
+      <c r="AK16" s="18"/>
+      <c r="AL16" s="356"/>
+      <c r="AM16" s="18"/>
       <c r="AN16" s="356"/>
       <c r="AO16" s="356"/>
       <c r="AP16" s="356"/>
@@ -21070,68 +21083,69 @@
       <c r="AR16" s="356"/>
       <c r="AS16" s="356"/>
       <c r="AT16" s="356"/>
-      <c r="AU16" s="358"/>
-      <c r="AW16" s="42">
+      <c r="AU16" s="356"/>
+      <c r="AV16" s="358"/>
+      <c r="AX16" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX16" s="23" cm="1">
-        <f t="array" ref="AX16">SUM(COUNTIFS(H16:AU16,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY16" s="23">
+      <c r="AY16" s="23" cm="1">
+        <f t="array" ref="AY16">SUM(COUNTIFS(I16:AV16,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ16" s="23" cm="1">
-        <f t="array" ref="AZ16">SUM(COUNTIFS(H16:AU16,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA16" s="23">
+      <c r="BA16" s="23" cm="1">
+        <f t="array" ref="BA16">SUM(COUNTIFS(I16:AV16,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB16" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB16" s="278">
+      <c r="BC16" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC16" s="39">
+      <c r="BD16" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD16" s="25">
+      <c r="BE16" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE16" s="26">
+      <c r="BF16" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF16" s="25">
+      <c r="BG16" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B16,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG16" s="26">
+      <c r="BH16" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B17" s="71"/>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
       <c r="E17" s="307"/>
-      <c r="F17" s="25" t="str">
+      <c r="F17" s="307"/>
+      <c r="G17" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B17,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B17,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G17" s="26" t="str">
+      <c r="H17" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B17,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B18,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H17" s="24"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="356"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="18"/>
       <c r="K17" s="356"/>
       <c r="L17" s="356"/>
       <c r="M17" s="356"/>
@@ -21142,25 +21156,25 @@
       <c r="R17" s="356"/>
       <c r="S17" s="356"/>
       <c r="T17" s="356"/>
-      <c r="U17" s="18"/>
+      <c r="U17" s="356"/>
       <c r="V17" s="18"/>
       <c r="W17" s="18"/>
-      <c r="X17" s="356"/>
-      <c r="Y17" s="18"/>
-      <c r="Z17" s="356"/>
-      <c r="AA17" s="18"/>
+      <c r="X17" s="18"/>
+      <c r="Y17" s="356"/>
+      <c r="Z17" s="18"/>
+      <c r="AA17" s="356"/>
       <c r="AB17" s="18"/>
       <c r="AC17" s="18"/>
       <c r="AD17" s="18"/>
       <c r="AE17" s="18"/>
       <c r="AF17" s="18"/>
-      <c r="AG17" s="356"/>
+      <c r="AG17" s="18"/>
       <c r="AH17" s="356"/>
-      <c r="AI17" s="18"/>
+      <c r="AI17" s="356"/>
       <c r="AJ17" s="18"/>
       <c r="AK17" s="18"/>
       <c r="AL17" s="18"/>
-      <c r="AM17" s="356"/>
+      <c r="AM17" s="18"/>
       <c r="AN17" s="356"/>
       <c r="AO17" s="356"/>
       <c r="AP17" s="356"/>
@@ -21168,78 +21182,79 @@
       <c r="AR17" s="356"/>
       <c r="AS17" s="356"/>
       <c r="AT17" s="356"/>
-      <c r="AU17" s="358"/>
-      <c r="AW17" s="42">
+      <c r="AU17" s="356"/>
+      <c r="AV17" s="358"/>
+      <c r="AX17" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX17" s="23" cm="1">
-        <f t="array" ref="AX17">SUM(COUNTIFS(H17:AU17,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY17" s="23">
+      <c r="AY17" s="23" cm="1">
+        <f t="array" ref="AY17">SUM(COUNTIFS(I17:AV17,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ17" s="23" cm="1">
-        <f t="array" ref="AZ17">SUM(COUNTIFS(H17:AU17,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA17" s="23">
+      <c r="BA17" s="23" cm="1">
+        <f t="array" ref="BA17">SUM(COUNTIFS(I17:AV17,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB17" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB17" s="278">
+      <c r="BC17" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC17" s="39">
+      <c r="BD17" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD17" s="25">
+      <c r="BE17" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE17" s="26">
+      <c r="BF17" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF17" s="25">
+      <c r="BG17" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B17,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG17" s="26">
+      <c r="BH17" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B18" s="71"/>
       <c r="C18" s="18"/>
       <c r="D18" s="18"/>
       <c r="E18" s="307"/>
-      <c r="F18" s="25" t="str">
+      <c r="F18" s="307"/>
+      <c r="G18" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B18,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B18,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G18" s="26" t="str">
+      <c r="H18" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B18,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B19,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H18" s="24"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="356"/>
-      <c r="K18" s="18"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="356"/>
       <c r="L18" s="18"/>
-      <c r="M18" s="356"/>
-      <c r="N18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="356"/>
       <c r="O18" s="18"/>
-      <c r="P18" s="356"/>
-      <c r="Q18" s="18"/>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="356"/>
       <c r="R18" s="18"/>
-      <c r="S18" s="356"/>
-      <c r="T18" s="18"/>
+      <c r="S18" s="18"/>
+      <c r="T18" s="356"/>
       <c r="U18" s="18"/>
       <c r="V18" s="18"/>
       <c r="W18" s="18"/>
@@ -21249,15 +21264,15 @@
       <c r="AA18" s="18"/>
       <c r="AB18" s="18"/>
       <c r="AC18" s="18"/>
-      <c r="AD18" s="356"/>
-      <c r="AE18" s="18"/>
+      <c r="AD18" s="18"/>
+      <c r="AE18" s="356"/>
       <c r="AF18" s="18"/>
-      <c r="AG18" s="356"/>
-      <c r="AH18" s="18"/>
+      <c r="AG18" s="18"/>
+      <c r="AH18" s="356"/>
       <c r="AI18" s="18"/>
       <c r="AJ18" s="18"/>
       <c r="AK18" s="18"/>
-      <c r="AL18" s="356"/>
+      <c r="AL18" s="18"/>
       <c r="AM18" s="356"/>
       <c r="AN18" s="356"/>
       <c r="AO18" s="356"/>
@@ -21266,97 +21281,98 @@
       <c r="AR18" s="356"/>
       <c r="AS18" s="356"/>
       <c r="AT18" s="356"/>
-      <c r="AU18" s="358"/>
-      <c r="AW18" s="42">
+      <c r="AU18" s="356"/>
+      <c r="AV18" s="358"/>
+      <c r="AX18" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX18" s="23" cm="1">
-        <f t="array" ref="AX18">SUM(COUNTIFS(H18:AU18,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY18" s="23">
+      <c r="AY18" s="23" cm="1">
+        <f t="array" ref="AY18">SUM(COUNTIFS(I18:AV18,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ18" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ18" s="23" cm="1">
-        <f t="array" ref="AZ18">SUM(COUNTIFS(H18:AU18,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA18" s="23">
+      <c r="BA18" s="23" cm="1">
+        <f t="array" ref="BA18">SUM(COUNTIFS(I18:AV18,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB18" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB18" s="278">
+      <c r="BC18" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC18" s="39">
+      <c r="BD18" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD18" s="25">
+      <c r="BE18" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE18" s="26">
+      <c r="BF18" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF18" s="25">
+      <c r="BG18" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B18,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG18" s="26">
+      <c r="BH18" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B19" s="71"/>
       <c r="C19" s="18"/>
       <c r="D19" s="18"/>
       <c r="E19" s="307"/>
-      <c r="F19" s="25" t="str">
+      <c r="F19" s="307"/>
+      <c r="G19" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B19,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B19,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G19" s="26" t="str">
+      <c r="H19" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B19,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B20,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H19" s="24"/>
-      <c r="I19" s="18"/>
+      <c r="I19" s="24"/>
       <c r="J19" s="18"/>
       <c r="K19" s="18"/>
       <c r="L19" s="18"/>
       <c r="M19" s="18"/>
       <c r="N19" s="18"/>
       <c r="O19" s="18"/>
-      <c r="P19" s="356"/>
+      <c r="P19" s="18"/>
       <c r="Q19" s="356"/>
       <c r="R19" s="356"/>
-      <c r="S19" s="18"/>
+      <c r="S19" s="356"/>
       <c r="T19" s="18"/>
       <c r="U19" s="18"/>
-      <c r="V19" s="356"/>
-      <c r="W19" s="18"/>
+      <c r="V19" s="18"/>
+      <c r="W19" s="356"/>
       <c r="X19" s="18"/>
       <c r="Y19" s="18"/>
-      <c r="Z19" s="356"/>
-      <c r="AA19" s="18"/>
+      <c r="Z19" s="18"/>
+      <c r="AA19" s="356"/>
       <c r="AB19" s="18"/>
-      <c r="AC19" s="356"/>
-      <c r="AD19" s="18"/>
+      <c r="AC19" s="18"/>
+      <c r="AD19" s="356"/>
       <c r="AE19" s="18"/>
-      <c r="AF19" s="356"/>
+      <c r="AF19" s="18"/>
       <c r="AG19" s="356"/>
-      <c r="AH19" s="18"/>
+      <c r="AH19" s="356"/>
       <c r="AI19" s="18"/>
       <c r="AJ19" s="18"/>
       <c r="AK19" s="18"/>
       <c r="AL19" s="18"/>
-      <c r="AM19" s="356"/>
+      <c r="AM19" s="18"/>
       <c r="AN19" s="356"/>
       <c r="AO19" s="356"/>
       <c r="AP19" s="356"/>
@@ -21364,69 +21380,70 @@
       <c r="AR19" s="356"/>
       <c r="AS19" s="356"/>
       <c r="AT19" s="356"/>
-      <c r="AU19" s="358"/>
-      <c r="AW19" s="42">
+      <c r="AU19" s="356"/>
+      <c r="AV19" s="358"/>
+      <c r="AX19" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX19" s="23" cm="1">
-        <f t="array" ref="AX19">SUM(COUNTIFS(H19:AU19,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY19" s="23">
+      <c r="AY19" s="23" cm="1">
+        <f t="array" ref="AY19">SUM(COUNTIFS(I19:AV19,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ19" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ19" s="23" cm="1">
-        <f t="array" ref="AZ19">SUM(COUNTIFS(H19:AU19,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA19" s="23">
+      <c r="BA19" s="23" cm="1">
+        <f t="array" ref="BA19">SUM(COUNTIFS(I19:AV19,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB19" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB19" s="278">
+      <c r="BC19" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC19" s="39">
+      <c r="BD19" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD19" s="25">
+      <c r="BE19" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE19" s="26">
+      <c r="BF19" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF19" s="25">
+      <c r="BG19" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B19,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG19" s="26">
+      <c r="BH19" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B20" s="71"/>
       <c r="C20" s="18"/>
       <c r="D20" s="18"/>
       <c r="E20" s="307"/>
-      <c r="F20" s="25" t="str">
+      <c r="F20" s="307"/>
+      <c r="G20" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B20,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B20,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G20" s="26" t="str">
+      <c r="H20" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B20,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B21,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H20" s="24"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="356"/>
-      <c r="K20" s="18"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="356"/>
       <c r="L20" s="18"/>
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
@@ -21434,12 +21451,12 @@
       <c r="P20" s="18"/>
       <c r="Q20" s="18"/>
       <c r="R20" s="18"/>
-      <c r="S20" s="356"/>
-      <c r="T20" s="18"/>
+      <c r="S20" s="18"/>
+      <c r="T20" s="356"/>
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
       <c r="W20" s="18"/>
-      <c r="X20" s="356"/>
+      <c r="X20" s="18"/>
       <c r="Y20" s="356"/>
       <c r="Z20" s="356"/>
       <c r="AA20" s="356"/>
@@ -21453,7 +21470,7 @@
       <c r="AI20" s="356"/>
       <c r="AJ20" s="356"/>
       <c r="AK20" s="356"/>
-      <c r="AL20" s="18"/>
+      <c r="AL20" s="356"/>
       <c r="AM20" s="18"/>
       <c r="AN20" s="18"/>
       <c r="AO20" s="18"/>
@@ -21462,67 +21479,68 @@
       <c r="AR20" s="18"/>
       <c r="AS20" s="18"/>
       <c r="AT20" s="18"/>
-      <c r="AU20" s="26"/>
-      <c r="AW20" s="42">
+      <c r="AU20" s="18"/>
+      <c r="AV20" s="26"/>
+      <c r="AX20" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX20" s="23" cm="1">
-        <f t="array" ref="AX20">SUM(COUNTIFS(H20:AU20,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY20" s="23">
+      <c r="AY20" s="23" cm="1">
+        <f t="array" ref="AY20">SUM(COUNTIFS(I20:AV20,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ20" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ20" s="23" cm="1">
-        <f t="array" ref="AZ20">SUM(COUNTIFS(H20:AU20,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA20" s="23">
+      <c r="BA20" s="23" cm="1">
+        <f t="array" ref="BA20">SUM(COUNTIFS(I20:AV20,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB20" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB20" s="278">
+      <c r="BC20" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC20" s="39">
+      <c r="BD20" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD20" s="25">
+      <c r="BE20" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE20" s="26">
+      <c r="BF20" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF20" s="25">
+      <c r="BG20" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B20,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG20" s="26">
+      <c r="BH20" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B21" s="71"/>
       <c r="C21" s="18"/>
       <c r="D21" s="18"/>
       <c r="E21" s="307"/>
-      <c r="F21" s="25" t="str">
+      <c r="F21" s="307"/>
+      <c r="G21" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B21,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B21,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G21" s="26" t="str">
+      <c r="H21" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B21,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B22,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H21" s="24"/>
-      <c r="I21" s="18"/>
+      <c r="I21" s="24"/>
       <c r="J21" s="18"/>
       <c r="K21" s="18"/>
       <c r="L21" s="18"/>
@@ -21530,16 +21548,16 @@
       <c r="N21" s="18"/>
       <c r="O21" s="18"/>
       <c r="P21" s="18"/>
-      <c r="Q21" s="356"/>
-      <c r="R21" s="18"/>
+      <c r="Q21" s="18"/>
+      <c r="R21" s="356"/>
       <c r="S21" s="18"/>
       <c r="T21" s="18"/>
       <c r="U21" s="18"/>
-      <c r="V21" s="356"/>
-      <c r="W21" s="18"/>
-      <c r="X21" s="356"/>
-      <c r="Y21" s="18"/>
-      <c r="Z21" s="356"/>
+      <c r="V21" s="18"/>
+      <c r="W21" s="356"/>
+      <c r="X21" s="18"/>
+      <c r="Y21" s="356"/>
+      <c r="Z21" s="18"/>
       <c r="AA21" s="356"/>
       <c r="AB21" s="356"/>
       <c r="AC21" s="356"/>
@@ -21551,8 +21569,8 @@
       <c r="AI21" s="356"/>
       <c r="AJ21" s="356"/>
       <c r="AK21" s="356"/>
-      <c r="AL21" s="18"/>
-      <c r="AM21" s="356"/>
+      <c r="AL21" s="356"/>
+      <c r="AM21" s="18"/>
       <c r="AN21" s="356"/>
       <c r="AO21" s="356"/>
       <c r="AP21" s="356"/>
@@ -21560,76 +21578,77 @@
       <c r="AR21" s="356"/>
       <c r="AS21" s="356"/>
       <c r="AT21" s="356"/>
-      <c r="AU21" s="358"/>
-      <c r="AW21" s="42">
+      <c r="AU21" s="356"/>
+      <c r="AV21" s="358"/>
+      <c r="AX21" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX21" s="23" cm="1">
-        <f t="array" ref="AX21">SUM(COUNTIFS(H21:AU21,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY21" s="23">
+      <c r="AY21" s="23" cm="1">
+        <f t="array" ref="AY21">SUM(COUNTIFS(I21:AV21,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ21" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ21" s="23" cm="1">
-        <f t="array" ref="AZ21">SUM(COUNTIFS(H21:AU21,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA21" s="23">
+      <c r="BA21" s="23" cm="1">
+        <f t="array" ref="BA21">SUM(COUNTIFS(I21:AV21,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB21" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB21" s="278">
+      <c r="BC21" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC21" s="39">
+      <c r="BD21" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD21" s="25">
+      <c r="BE21" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE21" s="26">
+      <c r="BF21" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF21" s="25">
+      <c r="BG21" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B21,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG21" s="26">
+      <c r="BH21" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B22" s="71"/>
       <c r="C22" s="18"/>
       <c r="D22" s="18"/>
       <c r="E22" s="307"/>
-      <c r="F22" s="25" t="str">
+      <c r="F22" s="307"/>
+      <c r="G22" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B22,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B22,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G22" s="26" t="str">
+      <c r="H22" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B22,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B23,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H22" s="24"/>
-      <c r="I22" s="18"/>
+      <c r="I22" s="24"/>
       <c r="J22" s="18"/>
       <c r="K22" s="18"/>
       <c r="L22" s="18"/>
       <c r="M22" s="18"/>
-      <c r="N22" s="356"/>
+      <c r="N22" s="18"/>
       <c r="O22" s="356"/>
-      <c r="P22" s="18"/>
+      <c r="P22" s="356"/>
       <c r="Q22" s="18"/>
-      <c r="R22" s="356"/>
+      <c r="R22" s="18"/>
       <c r="S22" s="356"/>
       <c r="T22" s="356"/>
       <c r="U22" s="356"/>
@@ -21641,12 +21660,12 @@
       <c r="AA22" s="356"/>
       <c r="AB22" s="356"/>
       <c r="AC22" s="356"/>
-      <c r="AD22" s="18"/>
+      <c r="AD22" s="356"/>
       <c r="AE22" s="18"/>
       <c r="AF22" s="18"/>
-      <c r="AG22" s="356"/>
+      <c r="AG22" s="18"/>
       <c r="AH22" s="356"/>
-      <c r="AI22" s="18"/>
+      <c r="AI22" s="356"/>
       <c r="AJ22" s="18"/>
       <c r="AK22" s="18"/>
       <c r="AL22" s="18"/>
@@ -21658,70 +21677,71 @@
       <c r="AR22" s="18"/>
       <c r="AS22" s="18"/>
       <c r="AT22" s="18"/>
-      <c r="AU22" s="26"/>
-      <c r="AW22" s="42">
+      <c r="AU22" s="18"/>
+      <c r="AV22" s="26"/>
+      <c r="AX22" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX22" s="23" cm="1">
-        <f t="array" ref="AX22">SUM(COUNTIFS(H22:AU22,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY22" s="23">
+      <c r="AY22" s="23" cm="1">
+        <f t="array" ref="AY22">SUM(COUNTIFS(I22:AV22,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ22" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ22" s="23" cm="1">
-        <f t="array" ref="AZ22">SUM(COUNTIFS(H22:AU22,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA22" s="23">
+      <c r="BA22" s="23" cm="1">
+        <f t="array" ref="BA22">SUM(COUNTIFS(I22:AV22,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB22" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB22" s="278">
+      <c r="BC22" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC22" s="39">
+      <c r="BD22" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD22" s="25">
+      <c r="BE22" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE22" s="26">
+      <c r="BF22" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF22" s="25">
+      <c r="BG22" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B22,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG22" s="26">
+      <c r="BH22" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B23" s="71"/>
       <c r="C23" s="18"/>
       <c r="D23" s="18"/>
       <c r="E23" s="307"/>
-      <c r="F23" s="25" t="str">
+      <c r="F23" s="307"/>
+      <c r="G23" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B23,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B23,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G23" s="26" t="str">
+      <c r="H23" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B23,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B24,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H23" s="24"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="356"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="18"/>
       <c r="K23" s="356"/>
-      <c r="L23" s="18"/>
+      <c r="L23" s="356"/>
       <c r="M23" s="18"/>
       <c r="N23" s="18"/>
       <c r="O23" s="18"/>
@@ -21729,12 +21749,12 @@
       <c r="Q23" s="18"/>
       <c r="R23" s="18"/>
       <c r="S23" s="18"/>
-      <c r="T23" s="356"/>
+      <c r="T23" s="18"/>
       <c r="U23" s="356"/>
       <c r="V23" s="356"/>
       <c r="W23" s="356"/>
       <c r="X23" s="356"/>
-      <c r="Y23" s="18"/>
+      <c r="Y23" s="356"/>
       <c r="Z23" s="18"/>
       <c r="AA23" s="18"/>
       <c r="AB23" s="18"/>
@@ -21743,12 +21763,12 @@
       <c r="AE23" s="18"/>
       <c r="AF23" s="18"/>
       <c r="AG23" s="18"/>
-      <c r="AH23" s="356"/>
-      <c r="AI23" s="18"/>
+      <c r="AH23" s="18"/>
+      <c r="AI23" s="356"/>
       <c r="AJ23" s="18"/>
       <c r="AK23" s="18"/>
       <c r="AL23" s="18"/>
-      <c r="AM23" s="356"/>
+      <c r="AM23" s="18"/>
       <c r="AN23" s="356"/>
       <c r="AO23" s="356"/>
       <c r="AP23" s="356"/>
@@ -21756,68 +21776,69 @@
       <c r="AR23" s="356"/>
       <c r="AS23" s="356"/>
       <c r="AT23" s="356"/>
-      <c r="AU23" s="358"/>
-      <c r="AW23" s="42">
+      <c r="AU23" s="356"/>
+      <c r="AV23" s="358"/>
+      <c r="AX23" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX23" s="23" cm="1">
-        <f t="array" ref="AX23">SUM(COUNTIFS(H23:AU23,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY23" s="23">
+      <c r="AY23" s="23" cm="1">
+        <f t="array" ref="AY23">SUM(COUNTIFS(I23:AV23,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ23" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ23" s="23" cm="1">
-        <f t="array" ref="AZ23">SUM(COUNTIFS(H23:AU23,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA23" s="23">
+      <c r="BA23" s="23" cm="1">
+        <f t="array" ref="BA23">SUM(COUNTIFS(I23:AV23,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB23" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB23" s="278">
+      <c r="BC23" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC23" s="39">
+      <c r="BD23" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD23" s="25">
+      <c r="BE23" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE23" s="26">
+      <c r="BF23" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF23" s="25">
+      <c r="BG23" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B23,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG23" s="26">
+      <c r="BH23" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B24" s="71"/>
       <c r="C24" s="18"/>
       <c r="D24" s="18"/>
       <c r="E24" s="307"/>
-      <c r="F24" s="25" t="str">
+      <c r="F24" s="307"/>
+      <c r="G24" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B24,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B24,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G24" s="26" t="str">
+      <c r="H24" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B24,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B25,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H24" s="24"/>
-      <c r="I24" s="356"/>
-      <c r="J24" s="18"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="356"/>
       <c r="K24" s="18"/>
       <c r="L24" s="18"/>
       <c r="M24" s="18"/>
@@ -21826,11 +21847,11 @@
       <c r="P24" s="18"/>
       <c r="Q24" s="18"/>
       <c r="R24" s="18"/>
-      <c r="S24" s="356"/>
+      <c r="S24" s="18"/>
       <c r="T24" s="356"/>
-      <c r="U24" s="18"/>
+      <c r="U24" s="356"/>
       <c r="V24" s="18"/>
-      <c r="W24" s="356"/>
+      <c r="W24" s="18"/>
       <c r="X24" s="356"/>
       <c r="Y24" s="356"/>
       <c r="Z24" s="356"/>
@@ -21839,14 +21860,14 @@
       <c r="AC24" s="356"/>
       <c r="AD24" s="356"/>
       <c r="AE24" s="356"/>
-      <c r="AF24" s="18"/>
-      <c r="AG24" s="356"/>
+      <c r="AF24" s="356"/>
+      <c r="AG24" s="18"/>
       <c r="AH24" s="356"/>
       <c r="AI24" s="356"/>
       <c r="AJ24" s="356"/>
-      <c r="AK24" s="18"/>
+      <c r="AK24" s="356"/>
       <c r="AL24" s="18"/>
-      <c r="AM24" s="356"/>
+      <c r="AM24" s="18"/>
       <c r="AN24" s="356"/>
       <c r="AO24" s="356"/>
       <c r="AP24" s="356"/>
@@ -21854,84 +21875,85 @@
       <c r="AR24" s="356"/>
       <c r="AS24" s="356"/>
       <c r="AT24" s="356"/>
-      <c r="AU24" s="358"/>
-      <c r="AW24" s="42">
+      <c r="AU24" s="356"/>
+      <c r="AV24" s="358"/>
+      <c r="AX24" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX24" s="23" cm="1">
-        <f t="array" ref="AX24">SUM(COUNTIFS(H24:AU24,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY24" s="23">
+      <c r="AY24" s="23" cm="1">
+        <f t="array" ref="AY24">SUM(COUNTIFS(I24:AV24,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ24" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ24" s="23" cm="1">
-        <f t="array" ref="AZ24">SUM(COUNTIFS(H24:AU24,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA24" s="23">
+      <c r="BA24" s="23" cm="1">
+        <f t="array" ref="BA24">SUM(COUNTIFS(I24:AV24,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB24" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB24" s="278">
+      <c r="BC24" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC24" s="39">
+      <c r="BD24" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD24" s="25">
+      <c r="BE24" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE24" s="26">
+      <c r="BF24" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF24" s="25">
+      <c r="BG24" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B24,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG24" s="26">
+      <c r="BH24" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B25" s="71"/>
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>
       <c r="E25" s="307"/>
-      <c r="F25" s="25" t="str">
+      <c r="F25" s="307"/>
+      <c r="G25" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B25,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B25,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G25" s="26" t="str">
+      <c r="H25" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B25,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B26,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H25" s="24"/>
-      <c r="I25" s="18"/>
+      <c r="I25" s="24"/>
       <c r="J25" s="18"/>
-      <c r="K25" s="356"/>
-      <c r="L25" s="18"/>
-      <c r="M25" s="356"/>
-      <c r="N25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="356"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="356"/>
       <c r="O25" s="18"/>
       <c r="P25" s="18"/>
       <c r="Q25" s="18"/>
       <c r="R25" s="18"/>
       <c r="S25" s="18"/>
-      <c r="T25" s="356"/>
-      <c r="U25" s="18"/>
+      <c r="T25" s="18"/>
+      <c r="U25" s="356"/>
       <c r="V25" s="18"/>
       <c r="W25" s="18"/>
-      <c r="X25" s="356"/>
+      <c r="X25" s="18"/>
       <c r="Y25" s="356"/>
-      <c r="Z25" s="18"/>
+      <c r="Z25" s="356"/>
       <c r="AA25" s="18"/>
       <c r="AB25" s="18"/>
       <c r="AC25" s="18"/>
@@ -21944,7 +21966,7 @@
       <c r="AJ25" s="18"/>
       <c r="AK25" s="18"/>
       <c r="AL25" s="18"/>
-      <c r="AM25" s="356"/>
+      <c r="AM25" s="18"/>
       <c r="AN25" s="356"/>
       <c r="AO25" s="356"/>
       <c r="AP25" s="356"/>
@@ -21952,70 +21974,71 @@
       <c r="AR25" s="356"/>
       <c r="AS25" s="356"/>
       <c r="AT25" s="356"/>
-      <c r="AU25" s="358"/>
-      <c r="AW25" s="42">
+      <c r="AU25" s="356"/>
+      <c r="AV25" s="358"/>
+      <c r="AX25" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX25" s="23" cm="1">
-        <f t="array" ref="AX25">SUM(COUNTIFS(H25:AU25,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY25" s="23">
+      <c r="AY25" s="23" cm="1">
+        <f t="array" ref="AY25">SUM(COUNTIFS(I25:AV25,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ25" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ25" s="23" cm="1">
-        <f t="array" ref="AZ25">SUM(COUNTIFS(H25:AU25,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA25" s="23">
+      <c r="BA25" s="23" cm="1">
+        <f t="array" ref="BA25">SUM(COUNTIFS(I25:AV25,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB25" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB25" s="278">
+      <c r="BC25" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC25" s="39">
+      <c r="BD25" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD25" s="25">
+      <c r="BE25" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE25" s="26">
+      <c r="BF25" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF25" s="25">
+      <c r="BG25" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B25,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG25" s="26">
+      <c r="BH25" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B26" s="71"/>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
       <c r="E26" s="307"/>
-      <c r="F26" s="25" t="str">
+      <c r="F26" s="307"/>
+      <c r="G26" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B26,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B26,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G26" s="26" t="str">
+      <c r="H26" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B26,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B27,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H26" s="24"/>
-      <c r="I26" s="18"/>
+      <c r="I26" s="24"/>
       <c r="J26" s="18"/>
-      <c r="K26" s="356"/>
-      <c r="L26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="356"/>
       <c r="M26" s="18"/>
       <c r="N26" s="18"/>
       <c r="O26" s="18"/>
@@ -22028,21 +22051,21 @@
       <c r="V26" s="18"/>
       <c r="W26" s="18"/>
       <c r="X26" s="18"/>
-      <c r="Y26" s="356"/>
+      <c r="Y26" s="18"/>
       <c r="Z26" s="356"/>
       <c r="AA26" s="356"/>
-      <c r="AB26" s="18"/>
+      <c r="AB26" s="356"/>
       <c r="AC26" s="18"/>
       <c r="AD26" s="18"/>
       <c r="AE26" s="18"/>
-      <c r="AF26" s="356"/>
+      <c r="AF26" s="18"/>
       <c r="AG26" s="356"/>
-      <c r="AH26" s="18"/>
+      <c r="AH26" s="356"/>
       <c r="AI26" s="18"/>
       <c r="AJ26" s="18"/>
-      <c r="AK26" s="356"/>
+      <c r="AK26" s="18"/>
       <c r="AL26" s="356"/>
-      <c r="AM26" s="18"/>
+      <c r="AM26" s="356"/>
       <c r="AN26" s="18"/>
       <c r="AO26" s="18"/>
       <c r="AP26" s="18"/>
@@ -22050,70 +22073,71 @@
       <c r="AR26" s="18"/>
       <c r="AS26" s="18"/>
       <c r="AT26" s="18"/>
-      <c r="AU26" s="26"/>
-      <c r="AW26" s="42">
+      <c r="AU26" s="18"/>
+      <c r="AV26" s="26"/>
+      <c r="AX26" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX26" s="23" cm="1">
-        <f t="array" ref="AX26">SUM(COUNTIFS(H26:AU26,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY26" s="23">
+      <c r="AY26" s="23" cm="1">
+        <f t="array" ref="AY26">SUM(COUNTIFS(I26:AV26,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ26" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ26" s="23" cm="1">
-        <f t="array" ref="AZ26">SUM(COUNTIFS(H26:AU26,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA26" s="23">
+      <c r="BA26" s="23" cm="1">
+        <f t="array" ref="BA26">SUM(COUNTIFS(I26:AV26,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB26" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB26" s="278">
+      <c r="BC26" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC26" s="39">
+      <c r="BD26" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD26" s="25">
+      <c r="BE26" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE26" s="26">
+      <c r="BF26" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF26" s="25">
+      <c r="BG26" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B26,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG26" s="26">
+      <c r="BH26" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B27" s="71"/>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
       <c r="E27" s="307"/>
-      <c r="F27" s="25" t="str">
+      <c r="F27" s="307"/>
+      <c r="G27" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B27,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B27,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G27" s="26" t="str">
+      <c r="H27" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B27,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B28,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H27" s="24"/>
-      <c r="I27" s="18"/>
+      <c r="I27" s="24"/>
       <c r="J27" s="18"/>
-      <c r="K27" s="356"/>
-      <c r="L27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="356"/>
       <c r="M27" s="18"/>
       <c r="N27" s="18"/>
       <c r="O27" s="18"/>
@@ -22126,21 +22150,21 @@
       <c r="V27" s="18"/>
       <c r="W27" s="18"/>
       <c r="X27" s="18"/>
-      <c r="Y27" s="356"/>
+      <c r="Y27" s="18"/>
       <c r="Z27" s="356"/>
       <c r="AA27" s="356"/>
-      <c r="AB27" s="18"/>
+      <c r="AB27" s="356"/>
       <c r="AC27" s="18"/>
       <c r="AD27" s="18"/>
       <c r="AE27" s="18"/>
-      <c r="AF27" s="356"/>
+      <c r="AF27" s="18"/>
       <c r="AG27" s="356"/>
-      <c r="AH27" s="18"/>
+      <c r="AH27" s="356"/>
       <c r="AI27" s="18"/>
       <c r="AJ27" s="18"/>
-      <c r="AK27" s="356"/>
+      <c r="AK27" s="18"/>
       <c r="AL27" s="356"/>
-      <c r="AM27" s="18"/>
+      <c r="AM27" s="356"/>
       <c r="AN27" s="18"/>
       <c r="AO27" s="18"/>
       <c r="AP27" s="18"/>
@@ -22148,70 +22172,71 @@
       <c r="AR27" s="18"/>
       <c r="AS27" s="18"/>
       <c r="AT27" s="18"/>
-      <c r="AU27" s="26"/>
-      <c r="AW27" s="42">
+      <c r="AU27" s="18"/>
+      <c r="AV27" s="26"/>
+      <c r="AX27" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX27" s="23" cm="1">
-        <f t="array" ref="AX27">SUM(COUNTIFS(H27:AU27,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY27" s="23">
+      <c r="AY27" s="23" cm="1">
+        <f t="array" ref="AY27">SUM(COUNTIFS(I27:AV27,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ27" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ27" s="23" cm="1">
-        <f t="array" ref="AZ27">SUM(COUNTIFS(H27:AU27,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA27" s="23">
+      <c r="BA27" s="23" cm="1">
+        <f t="array" ref="BA27">SUM(COUNTIFS(I27:AV27,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB27" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB27" s="278">
+      <c r="BC27" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC27" s="39">
+      <c r="BD27" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD27" s="25">
+      <c r="BE27" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE27" s="26">
+      <c r="BF27" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF27" s="25">
+      <c r="BG27" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B27,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG27" s="26">
+      <c r="BH27" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B28" s="71"/>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
       <c r="E28" s="307"/>
-      <c r="F28" s="25" t="str">
+      <c r="F28" s="307"/>
+      <c r="G28" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B28,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B28,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G28" s="26" t="str">
+      <c r="H28" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B28,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B29,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H28" s="24"/>
-      <c r="I28" s="18"/>
+      <c r="I28" s="24"/>
       <c r="J28" s="18"/>
-      <c r="K28" s="356"/>
-      <c r="L28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="356"/>
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
       <c r="O28" s="18"/>
@@ -22224,21 +22249,21 @@
       <c r="V28" s="18"/>
       <c r="W28" s="18"/>
       <c r="X28" s="18"/>
-      <c r="Y28" s="356"/>
+      <c r="Y28" s="18"/>
       <c r="Z28" s="356"/>
       <c r="AA28" s="356"/>
-      <c r="AB28" s="18"/>
+      <c r="AB28" s="356"/>
       <c r="AC28" s="18"/>
       <c r="AD28" s="18"/>
       <c r="AE28" s="18"/>
-      <c r="AF28" s="356"/>
+      <c r="AF28" s="18"/>
       <c r="AG28" s="356"/>
-      <c r="AH28" s="18"/>
+      <c r="AH28" s="356"/>
       <c r="AI28" s="18"/>
       <c r="AJ28" s="18"/>
-      <c r="AK28" s="356"/>
+      <c r="AK28" s="18"/>
       <c r="AL28" s="356"/>
-      <c r="AM28" s="18"/>
+      <c r="AM28" s="356"/>
       <c r="AN28" s="18"/>
       <c r="AO28" s="18"/>
       <c r="AP28" s="18"/>
@@ -22246,70 +22271,71 @@
       <c r="AR28" s="18"/>
       <c r="AS28" s="18"/>
       <c r="AT28" s="18"/>
-      <c r="AU28" s="26"/>
-      <c r="AW28" s="42">
+      <c r="AU28" s="18"/>
+      <c r="AV28" s="26"/>
+      <c r="AX28" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX28" s="23" cm="1">
-        <f t="array" ref="AX28">SUM(COUNTIFS(H28:AU28,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY28" s="23">
+      <c r="AY28" s="23" cm="1">
+        <f t="array" ref="AY28">SUM(COUNTIFS(I28:AV28,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ28" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ28" s="23" cm="1">
-        <f t="array" ref="AZ28">SUM(COUNTIFS(H28:AU28,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA28" s="23">
+      <c r="BA28" s="23" cm="1">
+        <f t="array" ref="BA28">SUM(COUNTIFS(I28:AV28,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB28" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB28" s="278">
+      <c r="BC28" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC28" s="39">
+      <c r="BD28" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD28" s="25">
+      <c r="BE28" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE28" s="26">
+      <c r="BF28" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF28" s="25">
+      <c r="BG28" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B28,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG28" s="26">
+      <c r="BH28" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B29" s="71"/>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
       <c r="E29" s="307"/>
-      <c r="F29" s="25" t="str">
+      <c r="F29" s="307"/>
+      <c r="G29" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B29,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B29,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G29" s="26" t="str">
+      <c r="H29" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B29,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B30,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H29" s="24"/>
-      <c r="I29" s="18"/>
+      <c r="I29" s="24"/>
       <c r="J29" s="18"/>
-      <c r="K29" s="356"/>
-      <c r="L29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="356"/>
       <c r="M29" s="18"/>
       <c r="N29" s="18"/>
       <c r="O29" s="18"/>
@@ -22322,21 +22348,21 @@
       <c r="V29" s="18"/>
       <c r="W29" s="18"/>
       <c r="X29" s="18"/>
-      <c r="Y29" s="356"/>
+      <c r="Y29" s="18"/>
       <c r="Z29" s="356"/>
       <c r="AA29" s="356"/>
-      <c r="AB29" s="18"/>
+      <c r="AB29" s="356"/>
       <c r="AC29" s="18"/>
       <c r="AD29" s="18"/>
       <c r="AE29" s="18"/>
-      <c r="AF29" s="356"/>
+      <c r="AF29" s="18"/>
       <c r="AG29" s="356"/>
-      <c r="AH29" s="18"/>
+      <c r="AH29" s="356"/>
       <c r="AI29" s="18"/>
       <c r="AJ29" s="18"/>
-      <c r="AK29" s="356"/>
+      <c r="AK29" s="18"/>
       <c r="AL29" s="356"/>
-      <c r="AM29" s="18"/>
+      <c r="AM29" s="356"/>
       <c r="AN29" s="18"/>
       <c r="AO29" s="18"/>
       <c r="AP29" s="18"/>
@@ -22344,70 +22370,71 @@
       <c r="AR29" s="18"/>
       <c r="AS29" s="18"/>
       <c r="AT29" s="18"/>
-      <c r="AU29" s="26"/>
-      <c r="AW29" s="42">
+      <c r="AU29" s="18"/>
+      <c r="AV29" s="26"/>
+      <c r="AX29" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX29" s="23" cm="1">
-        <f t="array" ref="AX29">SUM(COUNTIFS(H29:AU29,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY29" s="23">
+      <c r="AY29" s="23" cm="1">
+        <f t="array" ref="AY29">SUM(COUNTIFS(I29:AV29,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ29" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ29" s="23" cm="1">
-        <f t="array" ref="AZ29">SUM(COUNTIFS(H29:AU29,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA29" s="23">
+      <c r="BA29" s="23" cm="1">
+        <f t="array" ref="BA29">SUM(COUNTIFS(I29:AV29,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB29" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB29" s="278">
+      <c r="BC29" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC29" s="39">
+      <c r="BD29" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD29" s="25">
+      <c r="BE29" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE29" s="26">
+      <c r="BF29" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF29" s="25">
+      <c r="BG29" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B29,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG29" s="26">
+      <c r="BH29" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B30" s="71"/>
       <c r="C30" s="18"/>
       <c r="D30" s="18"/>
       <c r="E30" s="307"/>
-      <c r="F30" s="25" t="str">
+      <c r="F30" s="307"/>
+      <c r="G30" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B30,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B30,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G30" s="26" t="str">
+      <c r="H30" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B30,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B31,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H30" s="24"/>
-      <c r="I30" s="18"/>
+      <c r="I30" s="24"/>
       <c r="J30" s="18"/>
-      <c r="K30" s="356"/>
-      <c r="L30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="356"/>
       <c r="M30" s="18"/>
       <c r="N30" s="18"/>
       <c r="O30" s="18"/>
@@ -22420,21 +22447,21 @@
       <c r="V30" s="18"/>
       <c r="W30" s="18"/>
       <c r="X30" s="18"/>
-      <c r="Y30" s="356"/>
+      <c r="Y30" s="18"/>
       <c r="Z30" s="356"/>
       <c r="AA30" s="356"/>
-      <c r="AB30" s="18"/>
+      <c r="AB30" s="356"/>
       <c r="AC30" s="18"/>
       <c r="AD30" s="18"/>
       <c r="AE30" s="18"/>
-      <c r="AF30" s="356"/>
+      <c r="AF30" s="18"/>
       <c r="AG30" s="356"/>
-      <c r="AH30" s="18"/>
+      <c r="AH30" s="356"/>
       <c r="AI30" s="18"/>
       <c r="AJ30" s="18"/>
-      <c r="AK30" s="356"/>
+      <c r="AK30" s="18"/>
       <c r="AL30" s="356"/>
-      <c r="AM30" s="18"/>
+      <c r="AM30" s="356"/>
       <c r="AN30" s="18"/>
       <c r="AO30" s="18"/>
       <c r="AP30" s="18"/>
@@ -22442,70 +22469,71 @@
       <c r="AR30" s="18"/>
       <c r="AS30" s="18"/>
       <c r="AT30" s="18"/>
-      <c r="AU30" s="26"/>
-      <c r="AW30" s="42">
+      <c r="AU30" s="18"/>
+      <c r="AV30" s="26"/>
+      <c r="AX30" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX30" s="23" cm="1">
-        <f t="array" ref="AX30">SUM(COUNTIFS(H30:AU30,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY30" s="23">
+      <c r="AY30" s="23" cm="1">
+        <f t="array" ref="AY30">SUM(COUNTIFS(I30:AV30,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ30" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ30" s="23" cm="1">
-        <f t="array" ref="AZ30">SUM(COUNTIFS(H30:AU30,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA30" s="23">
+      <c r="BA30" s="23" cm="1">
+        <f t="array" ref="BA30">SUM(COUNTIFS(I30:AV30,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB30" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB30" s="278">
+      <c r="BC30" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC30" s="39">
+      <c r="BD30" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD30" s="25">
+      <c r="BE30" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE30" s="26">
+      <c r="BF30" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF30" s="25">
+      <c r="BG30" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B30,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG30" s="26">
+      <c r="BH30" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B31" s="71"/>
       <c r="C31" s="18"/>
       <c r="D31" s="18"/>
       <c r="E31" s="307"/>
-      <c r="F31" s="25" t="str">
+      <c r="F31" s="307"/>
+      <c r="G31" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B31,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B31,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G31" s="26" t="str">
+      <c r="H31" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B31,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B32,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H31" s="24"/>
-      <c r="I31" s="18"/>
+      <c r="I31" s="24"/>
       <c r="J31" s="18"/>
-      <c r="K31" s="356"/>
-      <c r="L31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="356"/>
       <c r="M31" s="18"/>
       <c r="N31" s="18"/>
       <c r="O31" s="18"/>
@@ -22518,21 +22546,21 @@
       <c r="V31" s="18"/>
       <c r="W31" s="18"/>
       <c r="X31" s="18"/>
-      <c r="Y31" s="356"/>
+      <c r="Y31" s="18"/>
       <c r="Z31" s="356"/>
       <c r="AA31" s="356"/>
-      <c r="AB31" s="18"/>
+      <c r="AB31" s="356"/>
       <c r="AC31" s="18"/>
       <c r="AD31" s="18"/>
       <c r="AE31" s="18"/>
-      <c r="AF31" s="356"/>
+      <c r="AF31" s="18"/>
       <c r="AG31" s="356"/>
-      <c r="AH31" s="18"/>
+      <c r="AH31" s="356"/>
       <c r="AI31" s="18"/>
       <c r="AJ31" s="18"/>
-      <c r="AK31" s="356"/>
+      <c r="AK31" s="18"/>
       <c r="AL31" s="356"/>
-      <c r="AM31" s="18"/>
+      <c r="AM31" s="356"/>
       <c r="AN31" s="18"/>
       <c r="AO31" s="18"/>
       <c r="AP31" s="18"/>
@@ -22540,70 +22568,71 @@
       <c r="AR31" s="18"/>
       <c r="AS31" s="18"/>
       <c r="AT31" s="18"/>
-      <c r="AU31" s="26"/>
-      <c r="AW31" s="42">
+      <c r="AU31" s="18"/>
+      <c r="AV31" s="26"/>
+      <c r="AX31" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX31" s="23" cm="1">
-        <f t="array" ref="AX31">SUM(COUNTIFS(H31:AU31,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY31" s="23">
+      <c r="AY31" s="23" cm="1">
+        <f t="array" ref="AY31">SUM(COUNTIFS(I31:AV31,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ31" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ31" s="23" cm="1">
-        <f t="array" ref="AZ31">SUM(COUNTIFS(H31:AU31,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA31" s="23">
+      <c r="BA31" s="23" cm="1">
+        <f t="array" ref="BA31">SUM(COUNTIFS(I31:AV31,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB31" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB31" s="278">
+      <c r="BC31" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC31" s="39">
+      <c r="BD31" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD31" s="25">
+      <c r="BE31" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE31" s="26">
+      <c r="BF31" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF31" s="25">
+      <c r="BG31" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B31,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG31" s="26">
+      <c r="BH31" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B32" s="71"/>
       <c r="C32" s="18"/>
       <c r="D32" s="18"/>
       <c r="E32" s="307"/>
-      <c r="F32" s="25" t="str">
+      <c r="F32" s="307"/>
+      <c r="G32" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B32,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B32,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G32" s="26" t="str">
+      <c r="H32" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B32,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B33,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H32" s="24"/>
-      <c r="I32" s="18"/>
+      <c r="I32" s="24"/>
       <c r="J32" s="18"/>
-      <c r="K32" s="356"/>
-      <c r="L32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="356"/>
       <c r="M32" s="18"/>
       <c r="N32" s="18"/>
       <c r="O32" s="18"/>
@@ -22616,21 +22645,21 @@
       <c r="V32" s="18"/>
       <c r="W32" s="18"/>
       <c r="X32" s="18"/>
-      <c r="Y32" s="356"/>
+      <c r="Y32" s="18"/>
       <c r="Z32" s="356"/>
       <c r="AA32" s="356"/>
-      <c r="AB32" s="18"/>
+      <c r="AB32" s="356"/>
       <c r="AC32" s="18"/>
       <c r="AD32" s="18"/>
       <c r="AE32" s="18"/>
-      <c r="AF32" s="356"/>
+      <c r="AF32" s="18"/>
       <c r="AG32" s="356"/>
-      <c r="AH32" s="18"/>
+      <c r="AH32" s="356"/>
       <c r="AI32" s="18"/>
       <c r="AJ32" s="18"/>
-      <c r="AK32" s="356"/>
+      <c r="AK32" s="18"/>
       <c r="AL32" s="356"/>
-      <c r="AM32" s="18"/>
+      <c r="AM32" s="356"/>
       <c r="AN32" s="18"/>
       <c r="AO32" s="18"/>
       <c r="AP32" s="18"/>
@@ -22638,70 +22667,71 @@
       <c r="AR32" s="18"/>
       <c r="AS32" s="18"/>
       <c r="AT32" s="18"/>
-      <c r="AU32" s="26"/>
-      <c r="AW32" s="42">
+      <c r="AU32" s="18"/>
+      <c r="AV32" s="26"/>
+      <c r="AX32" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX32" s="23" cm="1">
-        <f t="array" ref="AX32">SUM(COUNTIFS(H32:AU32,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY32" s="23">
+      <c r="AY32" s="23" cm="1">
+        <f t="array" ref="AY32">SUM(COUNTIFS(I32:AV32,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ32" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ32" s="23" cm="1">
-        <f t="array" ref="AZ32">SUM(COUNTIFS(H32:AU32,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA32" s="23">
+      <c r="BA32" s="23" cm="1">
+        <f t="array" ref="BA32">SUM(COUNTIFS(I32:AV32,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB32" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB32" s="278">
+      <c r="BC32" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC32" s="39">
+      <c r="BD32" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD32" s="25">
+      <c r="BE32" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE32" s="26">
+      <c r="BF32" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF32" s="25">
+      <c r="BG32" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B32,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG32" s="26">
+      <c r="BH32" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B33" s="71"/>
       <c r="C33" s="18"/>
       <c r="D33" s="18"/>
       <c r="E33" s="307"/>
-      <c r="F33" s="25" t="str">
+      <c r="F33" s="307"/>
+      <c r="G33" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B33,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B33,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G33" s="26" t="str">
+      <c r="H33" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B33,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B34,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H33" s="24"/>
-      <c r="I33" s="18"/>
+      <c r="I33" s="24"/>
       <c r="J33" s="18"/>
-      <c r="K33" s="356"/>
-      <c r="L33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="356"/>
       <c r="M33" s="18"/>
       <c r="N33" s="18"/>
       <c r="O33" s="18"/>
@@ -22714,21 +22744,21 @@
       <c r="V33" s="18"/>
       <c r="W33" s="18"/>
       <c r="X33" s="18"/>
-      <c r="Y33" s="356"/>
+      <c r="Y33" s="18"/>
       <c r="Z33" s="356"/>
       <c r="AA33" s="356"/>
-      <c r="AB33" s="18"/>
+      <c r="AB33" s="356"/>
       <c r="AC33" s="18"/>
       <c r="AD33" s="18"/>
       <c r="AE33" s="18"/>
-      <c r="AF33" s="356"/>
+      <c r="AF33" s="18"/>
       <c r="AG33" s="356"/>
-      <c r="AH33" s="18"/>
+      <c r="AH33" s="356"/>
       <c r="AI33" s="18"/>
       <c r="AJ33" s="18"/>
-      <c r="AK33" s="356"/>
+      <c r="AK33" s="18"/>
       <c r="AL33" s="356"/>
-      <c r="AM33" s="18"/>
+      <c r="AM33" s="356"/>
       <c r="AN33" s="18"/>
       <c r="AO33" s="18"/>
       <c r="AP33" s="18"/>
@@ -22736,70 +22766,71 @@
       <c r="AR33" s="18"/>
       <c r="AS33" s="18"/>
       <c r="AT33" s="18"/>
-      <c r="AU33" s="26"/>
-      <c r="AW33" s="42">
+      <c r="AU33" s="18"/>
+      <c r="AV33" s="26"/>
+      <c r="AX33" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX33" s="23" cm="1">
-        <f t="array" ref="AX33">SUM(COUNTIFS(H33:AU33,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY33" s="23">
+      <c r="AY33" s="23" cm="1">
+        <f t="array" ref="AY33">SUM(COUNTIFS(I33:AV33,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ33" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ33" s="23" cm="1">
-        <f t="array" ref="AZ33">SUM(COUNTIFS(H33:AU33,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA33" s="23">
+      <c r="BA33" s="23" cm="1">
+        <f t="array" ref="BA33">SUM(COUNTIFS(I33:AV33,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB33" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB33" s="278">
+      <c r="BC33" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC33" s="39">
+      <c r="BD33" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD33" s="25">
+      <c r="BE33" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE33" s="26">
+      <c r="BF33" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF33" s="25">
+      <c r="BG33" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B33,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG33" s="26">
+      <c r="BH33" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B34" s="71"/>
       <c r="C34" s="18"/>
       <c r="D34" s="18"/>
       <c r="E34" s="307"/>
-      <c r="F34" s="25" t="str">
+      <c r="F34" s="307"/>
+      <c r="G34" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B34,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B34,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G34" s="26" t="str">
+      <c r="H34" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B34,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B35,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H34" s="24"/>
-      <c r="I34" s="18"/>
+      <c r="I34" s="24"/>
       <c r="J34" s="18"/>
-      <c r="K34" s="356"/>
-      <c r="L34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="356"/>
       <c r="M34" s="18"/>
       <c r="N34" s="18"/>
       <c r="O34" s="18"/>
@@ -22812,21 +22843,21 @@
       <c r="V34" s="18"/>
       <c r="W34" s="18"/>
       <c r="X34" s="18"/>
-      <c r="Y34" s="356"/>
+      <c r="Y34" s="18"/>
       <c r="Z34" s="356"/>
       <c r="AA34" s="356"/>
-      <c r="AB34" s="18"/>
+      <c r="AB34" s="356"/>
       <c r="AC34" s="18"/>
       <c r="AD34" s="18"/>
       <c r="AE34" s="18"/>
-      <c r="AF34" s="356"/>
+      <c r="AF34" s="18"/>
       <c r="AG34" s="356"/>
-      <c r="AH34" s="18"/>
+      <c r="AH34" s="356"/>
       <c r="AI34" s="18"/>
       <c r="AJ34" s="18"/>
-      <c r="AK34" s="356"/>
+      <c r="AK34" s="18"/>
       <c r="AL34" s="356"/>
-      <c r="AM34" s="18"/>
+      <c r="AM34" s="356"/>
       <c r="AN34" s="18"/>
       <c r="AO34" s="18"/>
       <c r="AP34" s="18"/>
@@ -22834,92 +22865,93 @@
       <c r="AR34" s="18"/>
       <c r="AS34" s="18"/>
       <c r="AT34" s="18"/>
-      <c r="AU34" s="26"/>
-      <c r="AW34" s="42">
+      <c r="AU34" s="18"/>
+      <c r="AV34" s="26"/>
+      <c r="AX34" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX34" s="23" cm="1">
-        <f t="array" ref="AX34">SUM(COUNTIFS(H34:AU34,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY34" s="23">
+      <c r="AY34" s="23" cm="1">
+        <f t="array" ref="AY34">SUM(COUNTIFS(I34:AV34,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ34" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ34" s="23" cm="1">
-        <f t="array" ref="AZ34">SUM(COUNTIFS(H34:AU34,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA34" s="23">
+      <c r="BA34" s="23" cm="1">
+        <f t="array" ref="BA34">SUM(COUNTIFS(I34:AV34,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB34" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB34" s="278">
+      <c r="BC34" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC34" s="39">
+      <c r="BD34" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD34" s="25">
+      <c r="BE34" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE34" s="26">
+      <c r="BF34" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF34" s="25">
+      <c r="BG34" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B34,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG34" s="26">
+      <c r="BH34" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B35" s="71"/>
       <c r="C35" s="18"/>
       <c r="D35" s="18"/>
       <c r="E35" s="307"/>
-      <c r="F35" s="25" t="str">
+      <c r="F35" s="307"/>
+      <c r="G35" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B35,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B35,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G35" s="26" t="str">
+      <c r="H35" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B35,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B36,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H35" s="24"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="356"/>
-      <c r="K35" s="18"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="356"/>
       <c r="L35" s="18"/>
       <c r="M35" s="18"/>
-      <c r="N35" s="356"/>
-      <c r="O35" s="18"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="356"/>
       <c r="P35" s="18"/>
       <c r="Q35" s="18"/>
       <c r="R35" s="18"/>
       <c r="S35" s="18"/>
       <c r="T35" s="18"/>
       <c r="U35" s="18"/>
-      <c r="V35" s="356"/>
+      <c r="V35" s="18"/>
       <c r="W35" s="356"/>
-      <c r="X35" s="18"/>
+      <c r="X35" s="356"/>
       <c r="Y35" s="18"/>
-      <c r="Z35" s="356"/>
-      <c r="AA35" s="18"/>
+      <c r="Z35" s="18"/>
+      <c r="AA35" s="356"/>
       <c r="AB35" s="18"/>
-      <c r="AC35" s="356"/>
-      <c r="AD35" s="18"/>
+      <c r="AC35" s="18"/>
+      <c r="AD35" s="356"/>
       <c r="AE35" s="18"/>
       <c r="AF35" s="18"/>
-      <c r="AG35" s="356"/>
-      <c r="AH35" s="18"/>
+      <c r="AG35" s="18"/>
+      <c r="AH35" s="356"/>
       <c r="AI35" s="18"/>
       <c r="AJ35" s="18"/>
       <c r="AK35" s="18"/>
@@ -22932,83 +22964,84 @@
       <c r="AR35" s="18"/>
       <c r="AS35" s="18"/>
       <c r="AT35" s="18"/>
-      <c r="AU35" s="26"/>
-      <c r="AW35" s="42">
+      <c r="AU35" s="18"/>
+      <c r="AV35" s="26"/>
+      <c r="AX35" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX35" s="23" cm="1">
-        <f t="array" ref="AX35">SUM(COUNTIFS(H35:AU35,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY35" s="23">
+      <c r="AY35" s="23" cm="1">
+        <f t="array" ref="AY35">SUM(COUNTIFS(I35:AV35,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ35" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ35" s="23" cm="1">
-        <f t="array" ref="AZ35">SUM(COUNTIFS(H35:AU35,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA35" s="23">
+      <c r="BA35" s="23" cm="1">
+        <f t="array" ref="BA35">SUM(COUNTIFS(I35:AV35,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB35" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB35" s="278">
+      <c r="BC35" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC35" s="39">
+      <c r="BD35" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD35" s="25">
+      <c r="BE35" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE35" s="26">
+      <c r="BF35" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF35" s="25">
+      <c r="BG35" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B35,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG35" s="26">
+      <c r="BH35" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B36" s="71"/>
       <c r="C36" s="18"/>
       <c r="D36" s="18"/>
       <c r="E36" s="307"/>
-      <c r="F36" s="25" t="str">
+      <c r="F36" s="307"/>
+      <c r="G36" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B36,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B36,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G36" s="26" t="str">
+      <c r="H36" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B36,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B37,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H36" s="24"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="356"/>
-      <c r="K36" s="18"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="356"/>
       <c r="L36" s="18"/>
-      <c r="M36" s="356"/>
+      <c r="M36" s="18"/>
       <c r="N36" s="356"/>
       <c r="O36" s="356"/>
       <c r="P36" s="356"/>
       <c r="Q36" s="356"/>
       <c r="R36" s="356"/>
-      <c r="S36" s="18"/>
+      <c r="S36" s="356"/>
       <c r="T36" s="18"/>
       <c r="U36" s="18"/>
-      <c r="V36" s="356"/>
-      <c r="W36" s="18"/>
-      <c r="X36" s="356"/>
-      <c r="Y36" s="18"/>
+      <c r="V36" s="18"/>
+      <c r="W36" s="356"/>
+      <c r="X36" s="18"/>
+      <c r="Y36" s="356"/>
       <c r="Z36" s="18"/>
       <c r="AA36" s="18"/>
       <c r="AB36" s="18"/>
@@ -23017,12 +23050,12 @@
       <c r="AE36" s="18"/>
       <c r="AF36" s="18"/>
       <c r="AG36" s="18"/>
-      <c r="AH36" s="356"/>
+      <c r="AH36" s="18"/>
       <c r="AI36" s="356"/>
       <c r="AJ36" s="356"/>
       <c r="AK36" s="356"/>
       <c r="AL36" s="356"/>
-      <c r="AM36" s="18"/>
+      <c r="AM36" s="356"/>
       <c r="AN36" s="18"/>
       <c r="AO36" s="18"/>
       <c r="AP36" s="18"/>
@@ -23030,79 +23063,80 @@
       <c r="AR36" s="18"/>
       <c r="AS36" s="18"/>
       <c r="AT36" s="18"/>
-      <c r="AU36" s="26"/>
-      <c r="AW36" s="42">
+      <c r="AU36" s="18"/>
+      <c r="AV36" s="26"/>
+      <c r="AX36" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX36" s="23" cm="1">
-        <f t="array" ref="AX36">SUM(COUNTIFS(H36:AU36,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY36" s="23">
+      <c r="AY36" s="23" cm="1">
+        <f t="array" ref="AY36">SUM(COUNTIFS(I36:AV36,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ36" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ36" s="23" cm="1">
-        <f t="array" ref="AZ36">SUM(COUNTIFS(H36:AU36,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA36" s="23">
+      <c r="BA36" s="23" cm="1">
+        <f t="array" ref="BA36">SUM(COUNTIFS(I36:AV36,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB36" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB36" s="278">
+      <c r="BC36" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC36" s="39">
+      <c r="BD36" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD36" s="25">
+      <c r="BE36" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE36" s="26">
+      <c r="BF36" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF36" s="25">
+      <c r="BG36" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B36,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG36" s="26">
+      <c r="BH36" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B37" s="71"/>
       <c r="C37" s="18"/>
       <c r="D37" s="18"/>
       <c r="E37" s="307"/>
-      <c r="F37" s="25" t="str">
+      <c r="F37" s="307"/>
+      <c r="G37" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B37,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B37,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G37" s="26" t="str">
+      <c r="H37" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B37,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B38,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H37" s="24"/>
-      <c r="I37" s="18"/>
+      <c r="I37" s="24"/>
       <c r="J37" s="18"/>
       <c r="K37" s="18"/>
       <c r="L37" s="18"/>
       <c r="M37" s="18"/>
       <c r="N37" s="18"/>
-      <c r="O37" s="356"/>
+      <c r="O37" s="18"/>
       <c r="P37" s="356"/>
-      <c r="Q37" s="18"/>
+      <c r="Q37" s="356"/>
       <c r="R37" s="18"/>
-      <c r="S37" s="356"/>
+      <c r="S37" s="18"/>
       <c r="T37" s="356"/>
-      <c r="U37" s="18"/>
+      <c r="U37" s="356"/>
       <c r="V37" s="18"/>
       <c r="W37" s="18"/>
       <c r="X37" s="18"/>
@@ -23112,8 +23146,8 @@
       <c r="AB37" s="18"/>
       <c r="AC37" s="18"/>
       <c r="AD37" s="18"/>
-      <c r="AE37" s="356"/>
-      <c r="AF37" s="18"/>
+      <c r="AE37" s="18"/>
+      <c r="AF37" s="356"/>
       <c r="AG37" s="18"/>
       <c r="AH37" s="18"/>
       <c r="AI37" s="18"/>
@@ -23128,79 +23162,80 @@
       <c r="AR37" s="18"/>
       <c r="AS37" s="18"/>
       <c r="AT37" s="18"/>
-      <c r="AU37" s="26"/>
-      <c r="AW37" s="42">
+      <c r="AU37" s="18"/>
+      <c r="AV37" s="26"/>
+      <c r="AX37" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX37" s="23" cm="1">
-        <f t="array" ref="AX37">SUM(COUNTIFS(H37:AU37,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY37" s="23">
+      <c r="AY37" s="23" cm="1">
+        <f t="array" ref="AY37">SUM(COUNTIFS(I37:AV37,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ37" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ37" s="23" cm="1">
-        <f t="array" ref="AZ37">SUM(COUNTIFS(H37:AU37,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA37" s="23">
+      <c r="BA37" s="23" cm="1">
+        <f t="array" ref="BA37">SUM(COUNTIFS(I37:AV37,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB37" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB37" s="278">
+      <c r="BC37" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC37" s="39">
+      <c r="BD37" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD37" s="25">
+      <c r="BE37" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE37" s="26">
+      <c r="BF37" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF37" s="25">
+      <c r="BG37" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B37,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG37" s="26">
+      <c r="BH37" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B38" s="71"/>
       <c r="C38" s="18"/>
       <c r="D38" s="18"/>
       <c r="E38" s="307"/>
-      <c r="F38" s="25" t="str">
+      <c r="F38" s="307"/>
+      <c r="G38" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B38,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B38,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G38" s="26" t="str">
+      <c r="H38" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B38,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B39,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H38" s="24"/>
-      <c r="I38" s="18"/>
+      <c r="I38" s="24"/>
       <c r="J38" s="18"/>
       <c r="K38" s="18"/>
       <c r="L38" s="18"/>
       <c r="M38" s="18"/>
       <c r="N38" s="18"/>
-      <c r="O38" s="356"/>
+      <c r="O38" s="18"/>
       <c r="P38" s="356"/>
       <c r="Q38" s="356"/>
       <c r="R38" s="356"/>
       <c r="S38" s="356"/>
       <c r="T38" s="356"/>
-      <c r="U38" s="18"/>
+      <c r="U38" s="356"/>
       <c r="V38" s="18"/>
       <c r="W38" s="18"/>
       <c r="X38" s="18"/>
@@ -23212,13 +23247,13 @@
       <c r="AD38" s="18"/>
       <c r="AE38" s="18"/>
       <c r="AF38" s="18"/>
-      <c r="AG38" s="356"/>
-      <c r="AH38" s="18"/>
+      <c r="AG38" s="18"/>
+      <c r="AH38" s="356"/>
       <c r="AI38" s="18"/>
       <c r="AJ38" s="18"/>
       <c r="AK38" s="18"/>
       <c r="AL38" s="18"/>
-      <c r="AM38" s="356"/>
+      <c r="AM38" s="18"/>
       <c r="AN38" s="356"/>
       <c r="AO38" s="356"/>
       <c r="AP38" s="356"/>
@@ -23226,97 +23261,98 @@
       <c r="AR38" s="356"/>
       <c r="AS38" s="356"/>
       <c r="AT38" s="356"/>
-      <c r="AU38" s="358"/>
-      <c r="AW38" s="42">
+      <c r="AU38" s="356"/>
+      <c r="AV38" s="358"/>
+      <c r="AX38" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX38" s="23" cm="1">
-        <f t="array" ref="AX38">SUM(COUNTIFS(H38:AU38,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY38" s="23">
+      <c r="AY38" s="23" cm="1">
+        <f t="array" ref="AY38">SUM(COUNTIFS(I38:AV38,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ38" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ38" s="23" cm="1">
-        <f t="array" ref="AZ38">SUM(COUNTIFS(H38:AU38,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA38" s="23">
+      <c r="BA38" s="23" cm="1">
+        <f t="array" ref="BA38">SUM(COUNTIFS(I38:AV38,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB38" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB38" s="278">
+      <c r="BC38" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC38" s="39">
+      <c r="BD38" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD38" s="25">
+      <c r="BE38" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE38" s="26">
+      <c r="BF38" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF38" s="25">
+      <c r="BG38" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B38,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG38" s="26">
+      <c r="BH38" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B39" s="71"/>
       <c r="C39" s="18"/>
       <c r="D39" s="18"/>
       <c r="E39" s="307"/>
-      <c r="F39" s="25" t="str">
+      <c r="F39" s="307"/>
+      <c r="G39" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B39,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B39,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G39" s="26" t="str">
+      <c r="H39" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B39,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B40,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H39" s="24"/>
-      <c r="I39" s="18"/>
+      <c r="I39" s="24"/>
       <c r="J39" s="18"/>
       <c r="K39" s="18"/>
-      <c r="L39" s="356"/>
-      <c r="M39" s="18"/>
-      <c r="N39" s="356"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="356"/>
+      <c r="N39" s="18"/>
       <c r="O39" s="356"/>
       <c r="P39" s="356"/>
       <c r="Q39" s="356"/>
       <c r="R39" s="356"/>
-      <c r="S39" s="18"/>
+      <c r="S39" s="356"/>
       <c r="T39" s="18"/>
       <c r="U39" s="18"/>
       <c r="V39" s="18"/>
       <c r="W39" s="18"/>
-      <c r="X39" s="356"/>
+      <c r="X39" s="18"/>
       <c r="Y39" s="356"/>
       <c r="Z39" s="356"/>
       <c r="AA39" s="356"/>
-      <c r="AB39" s="18"/>
-      <c r="AC39" s="356"/>
-      <c r="AD39" s="18"/>
+      <c r="AB39" s="356"/>
+      <c r="AC39" s="18"/>
+      <c r="AD39" s="356"/>
       <c r="AE39" s="18"/>
-      <c r="AF39" s="356"/>
+      <c r="AF39" s="18"/>
       <c r="AG39" s="356"/>
-      <c r="AH39" s="18"/>
+      <c r="AH39" s="356"/>
       <c r="AI39" s="18"/>
-      <c r="AJ39" s="356"/>
+      <c r="AJ39" s="18"/>
       <c r="AK39" s="356"/>
       <c r="AL39" s="356"/>
-      <c r="AM39" s="18"/>
+      <c r="AM39" s="356"/>
       <c r="AN39" s="18"/>
       <c r="AO39" s="18"/>
       <c r="AP39" s="18"/>
@@ -23324,92 +23360,93 @@
       <c r="AR39" s="18"/>
       <c r="AS39" s="18"/>
       <c r="AT39" s="18"/>
-      <c r="AU39" s="26"/>
-      <c r="AW39" s="42">
+      <c r="AU39" s="18"/>
+      <c r="AV39" s="26"/>
+      <c r="AX39" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX39" s="23" cm="1">
-        <f t="array" ref="AX39">SUM(COUNTIFS(H39:AU39,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY39" s="23">
+      <c r="AY39" s="23" cm="1">
+        <f t="array" ref="AY39">SUM(COUNTIFS(I39:AV39,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ39" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ39" s="23" cm="1">
-        <f t="array" ref="AZ39">SUM(COUNTIFS(H39:AU39,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA39" s="23">
+      <c r="BA39" s="23" cm="1">
+        <f t="array" ref="BA39">SUM(COUNTIFS(I39:AV39,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB39" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB39" s="278">
+      <c r="BC39" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC39" s="39">
+      <c r="BD39" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD39" s="25">
+      <c r="BE39" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE39" s="26">
+      <c r="BF39" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF39" s="25">
+      <c r="BG39" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B39,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG39" s="26">
+      <c r="BH39" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B40" s="71"/>
       <c r="C40" s="18"/>
       <c r="D40" s="18"/>
       <c r="E40" s="307"/>
-      <c r="F40" s="25" t="str">
+      <c r="F40" s="307"/>
+      <c r="G40" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B40,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B40,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G40" s="26" t="str">
+      <c r="H40" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B40,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B41,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H40" s="24"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="356"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="18"/>
       <c r="K40" s="356"/>
       <c r="L40" s="356"/>
-      <c r="M40" s="18"/>
+      <c r="M40" s="356"/>
       <c r="N40" s="18"/>
-      <c r="O40" s="356"/>
-      <c r="P40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="356"/>
       <c r="Q40" s="18"/>
-      <c r="R40" s="356"/>
-      <c r="S40" s="18"/>
+      <c r="R40" s="18"/>
+      <c r="S40" s="356"/>
       <c r="T40" s="18"/>
       <c r="U40" s="18"/>
       <c r="V40" s="18"/>
       <c r="W40" s="18"/>
       <c r="X40" s="18"/>
       <c r="Y40" s="18"/>
-      <c r="Z40" s="356"/>
+      <c r="Z40" s="18"/>
       <c r="AA40" s="356"/>
       <c r="AB40" s="356"/>
       <c r="AC40" s="356"/>
-      <c r="AD40" s="18"/>
+      <c r="AD40" s="356"/>
       <c r="AE40" s="18"/>
-      <c r="AF40" s="356"/>
+      <c r="AF40" s="18"/>
       <c r="AG40" s="356"/>
-      <c r="AH40" s="18"/>
+      <c r="AH40" s="356"/>
       <c r="AI40" s="18"/>
       <c r="AJ40" s="18"/>
       <c r="AK40" s="18"/>
@@ -23422,93 +23459,94 @@
       <c r="AR40" s="18"/>
       <c r="AS40" s="18"/>
       <c r="AT40" s="18"/>
-      <c r="AU40" s="26"/>
-      <c r="AW40" s="42">
+      <c r="AU40" s="18"/>
+      <c r="AV40" s="26"/>
+      <c r="AX40" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX40" s="23" cm="1">
-        <f t="array" ref="AX40">SUM(COUNTIFS(H40:AU40,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY40" s="23">
+      <c r="AY40" s="23" cm="1">
+        <f t="array" ref="AY40">SUM(COUNTIFS(I40:AV40,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ40" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ40" s="23" cm="1">
-        <f t="array" ref="AZ40">SUM(COUNTIFS(H40:AU40,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA40" s="23">
+      <c r="BA40" s="23" cm="1">
+        <f t="array" ref="BA40">SUM(COUNTIFS(I40:AV40,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB40" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB40" s="278">
+      <c r="BC40" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC40" s="39">
+      <c r="BD40" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD40" s="25">
+      <c r="BE40" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE40" s="26">
+      <c r="BF40" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF40" s="25">
+      <c r="BG40" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B40,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG40" s="26">
+      <c r="BH40" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B41" s="71"/>
       <c r="C41" s="18"/>
       <c r="D41" s="18"/>
       <c r="E41" s="307"/>
-      <c r="F41" s="25" t="str">
+      <c r="F41" s="307"/>
+      <c r="G41" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B41,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B41,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G41" s="26" t="str">
+      <c r="H41" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B41,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B42,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H41" s="24"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="356"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="18"/>
       <c r="K41" s="356"/>
-      <c r="L41" s="18"/>
+      <c r="L41" s="356"/>
       <c r="M41" s="18"/>
       <c r="N41" s="18"/>
       <c r="O41" s="18"/>
       <c r="P41" s="18"/>
-      <c r="Q41" s="356"/>
-      <c r="R41" s="18"/>
+      <c r="Q41" s="18"/>
+      <c r="R41" s="356"/>
       <c r="S41" s="18"/>
-      <c r="T41" s="356"/>
+      <c r="T41" s="18"/>
       <c r="U41" s="356"/>
-      <c r="V41" s="18"/>
+      <c r="V41" s="356"/>
       <c r="W41" s="18"/>
-      <c r="X41" s="356"/>
-      <c r="Y41" s="18"/>
-      <c r="Z41" s="356"/>
+      <c r="X41" s="18"/>
+      <c r="Y41" s="356"/>
+      <c r="Z41" s="18"/>
       <c r="AA41" s="356"/>
-      <c r="AB41" s="18"/>
+      <c r="AB41" s="356"/>
       <c r="AC41" s="18"/>
       <c r="AD41" s="18"/>
       <c r="AE41" s="18"/>
       <c r="AF41" s="18"/>
       <c r="AG41" s="18"/>
-      <c r="AH41" s="356"/>
-      <c r="AI41" s="18"/>
+      <c r="AH41" s="18"/>
+      <c r="AI41" s="356"/>
       <c r="AJ41" s="18"/>
       <c r="AK41" s="18"/>
       <c r="AL41" s="18"/>
@@ -23520,71 +23558,72 @@
       <c r="AR41" s="18"/>
       <c r="AS41" s="18"/>
       <c r="AT41" s="18"/>
-      <c r="AU41" s="26"/>
-      <c r="AW41" s="42">
+      <c r="AU41" s="18"/>
+      <c r="AV41" s="26"/>
+      <c r="AX41" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX41" s="23" cm="1">
-        <f t="array" ref="AX41">SUM(COUNTIFS(H41:AU41,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY41" s="23">
+      <c r="AY41" s="23" cm="1">
+        <f t="array" ref="AY41">SUM(COUNTIFS(I41:AV41,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ41" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ41" s="23" cm="1">
-        <f t="array" ref="AZ41">SUM(COUNTIFS(H41:AU41,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA41" s="23">
+      <c r="BA41" s="23" cm="1">
+        <f t="array" ref="BA41">SUM(COUNTIFS(I41:AV41,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB41" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB41" s="278">
+      <c r="BC41" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC41" s="39">
+      <c r="BD41" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD41" s="25">
+      <c r="BE41" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE41" s="26">
+      <c r="BF41" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF41" s="25">
+      <c r="BG41" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B41,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG41" s="26">
+      <c r="BH41" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B42" s="71"/>
       <c r="C42" s="18"/>
       <c r="D42" s="18"/>
       <c r="E42" s="307"/>
-      <c r="F42" s="25" t="str">
+      <c r="F42" s="307"/>
+      <c r="G42" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B42,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B42,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G42" s="26" t="str">
+      <c r="H42" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B42,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B43,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H42" s="365"/>
-      <c r="I42" s="356"/>
-      <c r="J42" s="18"/>
+      <c r="I42" s="365"/>
+      <c r="J42" s="356"/>
       <c r="K42" s="18"/>
-      <c r="L42" s="356"/>
-      <c r="M42" s="18"/>
+      <c r="L42" s="18"/>
+      <c r="M42" s="356"/>
       <c r="N42" s="18"/>
       <c r="O42" s="18"/>
       <c r="P42" s="18"/>
@@ -23595,18 +23634,18 @@
       <c r="U42" s="18"/>
       <c r="V42" s="18"/>
       <c r="W42" s="18"/>
-      <c r="X42" s="356"/>
-      <c r="Y42" s="18"/>
+      <c r="X42" s="18"/>
+      <c r="Y42" s="356"/>
       <c r="Z42" s="18"/>
-      <c r="AA42" s="356"/>
+      <c r="AA42" s="18"/>
       <c r="AB42" s="356"/>
       <c r="AC42" s="356"/>
       <c r="AD42" s="356"/>
       <c r="AE42" s="356"/>
-      <c r="AF42" s="18"/>
-      <c r="AG42" s="356"/>
+      <c r="AF42" s="356"/>
+      <c r="AG42" s="18"/>
       <c r="AH42" s="356"/>
-      <c r="AI42" s="18"/>
+      <c r="AI42" s="356"/>
       <c r="AJ42" s="18"/>
       <c r="AK42" s="18"/>
       <c r="AL42" s="18"/>
@@ -23618,97 +23657,98 @@
       <c r="AR42" s="18"/>
       <c r="AS42" s="18"/>
       <c r="AT42" s="18"/>
-      <c r="AU42" s="26"/>
-      <c r="AW42" s="42">
+      <c r="AU42" s="18"/>
+      <c r="AV42" s="26"/>
+      <c r="AX42" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX42" s="23" cm="1">
-        <f t="array" ref="AX42">SUM(COUNTIFS(H42:AU42,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY42" s="23">
+      <c r="AY42" s="23" cm="1">
+        <f t="array" ref="AY42">SUM(COUNTIFS(I42:AV42,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ42" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ42" s="23" cm="1">
-        <f t="array" ref="AZ42">SUM(COUNTIFS(H42:AU42,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA42" s="23">
+      <c r="BA42" s="23" cm="1">
+        <f t="array" ref="BA42">SUM(COUNTIFS(I42:AV42,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB42" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB42" s="278">
+      <c r="BC42" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC42" s="39">
+      <c r="BD42" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD42" s="25">
+      <c r="BE42" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE42" s="26">
+      <c r="BF42" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF42" s="25">
+      <c r="BG42" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B42,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG42" s="26">
+      <c r="BH42" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B43" s="71"/>
       <c r="C43" s="18"/>
       <c r="D43" s="18"/>
       <c r="E43" s="307"/>
-      <c r="F43" s="25" t="str">
+      <c r="F43" s="307"/>
+      <c r="G43" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B43,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B43,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G43" s="26" t="str">
+      <c r="H43" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B43,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B44,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H43" s="365"/>
-      <c r="I43" s="356"/>
+      <c r="I43" s="365"/>
       <c r="J43" s="356"/>
       <c r="K43" s="356"/>
       <c r="L43" s="356"/>
       <c r="M43" s="356"/>
       <c r="N43" s="356"/>
       <c r="O43" s="356"/>
-      <c r="P43" s="18"/>
+      <c r="P43" s="356"/>
       <c r="Q43" s="18"/>
       <c r="R43" s="18"/>
-      <c r="S43" s="356"/>
+      <c r="S43" s="18"/>
       <c r="T43" s="356"/>
       <c r="U43" s="356"/>
-      <c r="V43" s="18"/>
+      <c r="V43" s="356"/>
       <c r="W43" s="18"/>
-      <c r="X43" s="356"/>
-      <c r="Y43" s="18"/>
-      <c r="Z43" s="356"/>
-      <c r="AA43" s="18"/>
+      <c r="X43" s="18"/>
+      <c r="Y43" s="356"/>
+      <c r="Z43" s="18"/>
+      <c r="AA43" s="356"/>
       <c r="AB43" s="18"/>
       <c r="AC43" s="18"/>
       <c r="AD43" s="18"/>
       <c r="AE43" s="18"/>
       <c r="AF43" s="18"/>
-      <c r="AG43" s="356"/>
-      <c r="AH43" s="18"/>
+      <c r="AG43" s="18"/>
+      <c r="AH43" s="356"/>
       <c r="AI43" s="18"/>
       <c r="AJ43" s="18"/>
-      <c r="AK43" s="356"/>
+      <c r="AK43" s="18"/>
       <c r="AL43" s="356"/>
-      <c r="AM43" s="18"/>
+      <c r="AM43" s="356"/>
       <c r="AN43" s="18"/>
       <c r="AO43" s="18"/>
       <c r="AP43" s="18"/>
@@ -23716,96 +23756,97 @@
       <c r="AR43" s="18"/>
       <c r="AS43" s="18"/>
       <c r="AT43" s="18"/>
-      <c r="AU43" s="26"/>
-      <c r="AW43" s="42">
+      <c r="AU43" s="18"/>
+      <c r="AV43" s="26"/>
+      <c r="AX43" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX43" s="23" cm="1">
-        <f t="array" ref="AX43">SUM(COUNTIFS(H43:AU43,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY43" s="23">
+      <c r="AY43" s="23" cm="1">
+        <f t="array" ref="AY43">SUM(COUNTIFS(I43:AV43,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ43" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ43" s="23" cm="1">
-        <f t="array" ref="AZ43">SUM(COUNTIFS(H43:AU43,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA43" s="23">
+      <c r="BA43" s="23" cm="1">
+        <f t="array" ref="BA43">SUM(COUNTIFS(I43:AV43,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB43" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB43" s="278">
+      <c r="BC43" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC43" s="39">
+      <c r="BD43" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD43" s="25">
+      <c r="BE43" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE43" s="26">
+      <c r="BF43" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF43" s="25">
+      <c r="BG43" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B43,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG43" s="26">
+      <c r="BH43" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B44" s="71"/>
       <c r="C44" s="18"/>
       <c r="D44" s="18"/>
       <c r="E44" s="307"/>
-      <c r="F44" s="25" t="str">
+      <c r="F44" s="307"/>
+      <c r="G44" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B44,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B44,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G44" s="26" t="str">
+      <c r="H44" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B44,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B45,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H44" s="365"/>
-      <c r="I44" s="18"/>
+      <c r="I44" s="365"/>
       <c r="J44" s="18"/>
       <c r="K44" s="18"/>
       <c r="L44" s="18"/>
       <c r="M44" s="18"/>
-      <c r="N44" s="356"/>
+      <c r="N44" s="18"/>
       <c r="O44" s="356"/>
       <c r="P44" s="356"/>
       <c r="Q44" s="356"/>
       <c r="R44" s="356"/>
       <c r="S44" s="356"/>
       <c r="T44" s="356"/>
-      <c r="U44" s="18"/>
+      <c r="U44" s="356"/>
       <c r="V44" s="18"/>
       <c r="W44" s="18"/>
       <c r="X44" s="18"/>
-      <c r="Y44" s="356"/>
+      <c r="Y44" s="18"/>
       <c r="Z44" s="356"/>
       <c r="AA44" s="356"/>
-      <c r="AB44" s="18"/>
+      <c r="AB44" s="356"/>
       <c r="AC44" s="18"/>
       <c r="AD44" s="18"/>
       <c r="AE44" s="18"/>
-      <c r="AF44" s="356"/>
+      <c r="AF44" s="18"/>
       <c r="AG44" s="356"/>
       <c r="AH44" s="356"/>
       <c r="AI44" s="356"/>
-      <c r="AJ44" s="18"/>
+      <c r="AJ44" s="356"/>
       <c r="AK44" s="18"/>
-      <c r="AL44" s="356"/>
+      <c r="AL44" s="18"/>
       <c r="AM44" s="356"/>
       <c r="AN44" s="356"/>
       <c r="AO44" s="356"/>
@@ -23814,67 +23855,68 @@
       <c r="AR44" s="356"/>
       <c r="AS44" s="356"/>
       <c r="AT44" s="356"/>
-      <c r="AU44" s="358"/>
-      <c r="AW44" s="42">
+      <c r="AU44" s="356"/>
+      <c r="AV44" s="358"/>
+      <c r="AX44" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX44" s="23" cm="1">
-        <f t="array" ref="AX44">SUM(COUNTIFS(H44:AU44,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY44" s="23">
+      <c r="AY44" s="23" cm="1">
+        <f t="array" ref="AY44">SUM(COUNTIFS(I44:AV44,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ44" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ44" s="23" cm="1">
-        <f t="array" ref="AZ44">SUM(COUNTIFS(H44:AU44,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA44" s="23">
+      <c r="BA44" s="23" cm="1">
+        <f t="array" ref="BA44">SUM(COUNTIFS(I44:AV44,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB44" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB44" s="278">
+      <c r="BC44" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC44" s="39">
+      <c r="BD44" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD44" s="25">
+      <c r="BE44" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE44" s="26">
+      <c r="BF44" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF44" s="25">
+      <c r="BG44" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B44,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG44" s="26">
+      <c r="BH44" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B45" s="71"/>
       <c r="C45" s="18"/>
       <c r="D45" s="18"/>
       <c r="E45" s="307"/>
-      <c r="F45" s="25" t="str">
+      <c r="F45" s="307"/>
+      <c r="G45" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B45,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B45,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G45" s="26" t="str">
+      <c r="H45" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B45,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B46,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H45" s="365"/>
-      <c r="I45" s="18"/>
+      <c r="I45" s="365"/>
       <c r="J45" s="18"/>
       <c r="K45" s="18"/>
       <c r="L45" s="18"/>
@@ -23885,16 +23927,16 @@
       <c r="Q45" s="18"/>
       <c r="R45" s="18"/>
       <c r="S45" s="18"/>
-      <c r="T45" s="356"/>
-      <c r="U45" s="18"/>
-      <c r="V45" s="356"/>
-      <c r="W45" s="18"/>
+      <c r="T45" s="18"/>
+      <c r="U45" s="356"/>
+      <c r="V45" s="18"/>
+      <c r="W45" s="356"/>
       <c r="X45" s="18"/>
-      <c r="Y45" s="352"/>
-      <c r="Z45" s="18"/>
-      <c r="AA45" s="356"/>
-      <c r="AB45" s="18"/>
-      <c r="AC45" s="356"/>
+      <c r="Y45" s="18"/>
+      <c r="Z45" s="352"/>
+      <c r="AA45" s="18"/>
+      <c r="AB45" s="356"/>
+      <c r="AC45" s="18"/>
       <c r="AD45" s="356"/>
       <c r="AE45" s="356"/>
       <c r="AF45" s="356"/>
@@ -23903,7 +23945,7 @@
       <c r="AI45" s="356"/>
       <c r="AJ45" s="356"/>
       <c r="AK45" s="356"/>
-      <c r="AL45" s="18"/>
+      <c r="AL45" s="356"/>
       <c r="AM45" s="18"/>
       <c r="AN45" s="18"/>
       <c r="AO45" s="18"/>
@@ -23912,92 +23954,93 @@
       <c r="AR45" s="18"/>
       <c r="AS45" s="18"/>
       <c r="AT45" s="18"/>
-      <c r="AU45" s="26"/>
-      <c r="AW45" s="42">
+      <c r="AU45" s="18"/>
+      <c r="AV45" s="26"/>
+      <c r="AX45" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX45" s="23" cm="1">
-        <f t="array" ref="AX45">SUM(COUNTIFS(H45:AU45,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY45" s="23">
+      <c r="AY45" s="23" cm="1">
+        <f t="array" ref="AY45">SUM(COUNTIFS(I45:AV45,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ45" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ45" s="23" cm="1">
-        <f t="array" ref="AZ45">SUM(COUNTIFS(H45:AU45,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA45" s="23">
+      <c r="BA45" s="23" cm="1">
+        <f t="array" ref="BA45">SUM(COUNTIFS(I45:AV45,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB45" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB45" s="278">
+      <c r="BC45" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC45" s="39">
+      <c r="BD45" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD45" s="25">
+      <c r="BE45" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE45" s="26">
+      <c r="BF45" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF45" s="25">
+      <c r="BG45" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B45,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG45" s="26">
+      <c r="BH45" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B46" s="71"/>
       <c r="C46" s="18"/>
       <c r="D46" s="18"/>
       <c r="E46" s="307"/>
-      <c r="F46" s="25" t="str">
+      <c r="F46" s="307"/>
+      <c r="G46" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B46,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B46,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G46" s="26" t="str">
+      <c r="H46" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B46,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B47,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H46" s="24"/>
-      <c r="I46" s="18"/>
+      <c r="I46" s="24"/>
       <c r="J46" s="18"/>
       <c r="K46" s="18"/>
       <c r="L46" s="18"/>
       <c r="M46" s="18"/>
       <c r="N46" s="18"/>
-      <c r="O46" s="356"/>
-      <c r="P46" s="18"/>
-      <c r="Q46" s="356"/>
-      <c r="R46" s="18"/>
+      <c r="O46" s="18"/>
+      <c r="P46" s="356"/>
+      <c r="Q46" s="18"/>
+      <c r="R46" s="356"/>
       <c r="S46" s="18"/>
       <c r="T46" s="18"/>
-      <c r="U46" s="356"/>
+      <c r="U46" s="18"/>
       <c r="V46" s="356"/>
-      <c r="W46" s="18"/>
+      <c r="W46" s="356"/>
       <c r="X46" s="18"/>
       <c r="Y46" s="18"/>
-      <c r="Z46" s="356"/>
+      <c r="Z46" s="18"/>
       <c r="AA46" s="356"/>
-      <c r="AB46" s="18"/>
+      <c r="AB46" s="356"/>
       <c r="AC46" s="18"/>
       <c r="AD46" s="18"/>
       <c r="AE46" s="18"/>
-      <c r="AF46" s="356"/>
+      <c r="AF46" s="18"/>
       <c r="AG46" s="356"/>
-      <c r="AH46" s="18"/>
+      <c r="AH46" s="356"/>
       <c r="AI46" s="18"/>
       <c r="AJ46" s="18"/>
       <c r="AK46" s="18"/>
@@ -24010,91 +24053,92 @@
       <c r="AR46" s="18"/>
       <c r="AS46" s="18"/>
       <c r="AT46" s="18"/>
-      <c r="AU46" s="26"/>
-      <c r="AW46" s="42">
+      <c r="AU46" s="18"/>
+      <c r="AV46" s="26"/>
+      <c r="AX46" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX46" s="23" cm="1">
-        <f t="array" ref="AX46">SUM(COUNTIFS(H46:AU46,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY46" s="23">
+      <c r="AY46" s="23" cm="1">
+        <f t="array" ref="AY46">SUM(COUNTIFS(I46:AV46,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ46" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ46" s="23" cm="1">
-        <f t="array" ref="AZ46">SUM(COUNTIFS(H46:AU46,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA46" s="23">
+      <c r="BA46" s="23" cm="1">
+        <f t="array" ref="BA46">SUM(COUNTIFS(I46:AV46,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB46" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB46" s="278">
+      <c r="BC46" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC46" s="39">
+      <c r="BD46" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD46" s="25">
+      <c r="BE46" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE46" s="26">
+      <c r="BF46" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF46" s="25">
+      <c r="BG46" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B46,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG46" s="26">
+      <c r="BH46" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B47" s="71"/>
       <c r="C47" s="18"/>
       <c r="D47" s="18"/>
       <c r="E47" s="307"/>
-      <c r="F47" s="25" t="str">
+      <c r="F47" s="307"/>
+      <c r="G47" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B47,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B47,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G47" s="26" t="str">
+      <c r="H47" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B47,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B48,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H47" s="365"/>
-      <c r="I47" s="18"/>
+      <c r="I47" s="365"/>
       <c r="J47" s="18"/>
       <c r="K47" s="18"/>
       <c r="L47" s="18"/>
-      <c r="M47" s="356"/>
+      <c r="M47" s="18"/>
       <c r="N47" s="356"/>
       <c r="O47" s="356"/>
-      <c r="P47" s="18"/>
-      <c r="Q47" s="356"/>
-      <c r="R47" s="18"/>
-      <c r="S47" s="356"/>
+      <c r="P47" s="356"/>
+      <c r="Q47" s="18"/>
+      <c r="R47" s="356"/>
+      <c r="S47" s="18"/>
       <c r="T47" s="356"/>
-      <c r="U47" s="18"/>
+      <c r="U47" s="356"/>
       <c r="V47" s="18"/>
       <c r="W47" s="18"/>
       <c r="X47" s="18"/>
-      <c r="Y47" s="356"/>
+      <c r="Y47" s="18"/>
       <c r="Z47" s="356"/>
       <c r="AA47" s="356"/>
-      <c r="AB47" s="18"/>
-      <c r="AC47" s="356"/>
+      <c r="AB47" s="356"/>
+      <c r="AC47" s="18"/>
       <c r="AD47" s="356"/>
       <c r="AE47" s="356"/>
       <c r="AF47" s="356"/>
-      <c r="AG47" s="18"/>
+      <c r="AG47" s="356"/>
       <c r="AH47" s="18"/>
       <c r="AI47" s="18"/>
       <c r="AJ47" s="18"/>
@@ -24108,84 +24152,85 @@
       <c r="AR47" s="18"/>
       <c r="AS47" s="18"/>
       <c r="AT47" s="18"/>
-      <c r="AU47" s="26"/>
-      <c r="AW47" s="42">
+      <c r="AU47" s="18"/>
+      <c r="AV47" s="26"/>
+      <c r="AX47" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX47" s="23" cm="1">
-        <f t="array" ref="AX47">SUM(COUNTIFS(H47:AU47,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY47" s="23">
+      <c r="AY47" s="23" cm="1">
+        <f t="array" ref="AY47">SUM(COUNTIFS(I47:AV47,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ47" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ47" s="23" cm="1">
-        <f t="array" ref="AZ47">SUM(COUNTIFS(H47:AU47,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA47" s="23">
+      <c r="BA47" s="23" cm="1">
+        <f t="array" ref="BA47">SUM(COUNTIFS(I47:AV47,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB47" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB47" s="278">
+      <c r="BC47" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC47" s="39">
+      <c r="BD47" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD47" s="25">
+      <c r="BE47" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE47" s="26">
+      <c r="BF47" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF47" s="25">
+      <c r="BG47" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B47,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG47" s="26">
+      <c r="BH47" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B48" s="71"/>
       <c r="C48" s="18"/>
       <c r="D48" s="18"/>
       <c r="E48" s="307"/>
-      <c r="F48" s="25" t="str">
+      <c r="F48" s="307"/>
+      <c r="G48" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B48,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B48,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G48" s="26" t="str">
+      <c r="H48" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B48,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B49,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H48" s="365"/>
-      <c r="I48" s="18"/>
-      <c r="J48" s="356"/>
-      <c r="K48" s="18"/>
+      <c r="I48" s="365"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="356"/>
       <c r="L48" s="18"/>
-      <c r="M48" s="356"/>
+      <c r="M48" s="18"/>
       <c r="N48" s="356"/>
-      <c r="O48" s="18"/>
+      <c r="O48" s="356"/>
       <c r="P48" s="18"/>
-      <c r="Q48" s="356"/>
-      <c r="R48" s="18"/>
-      <c r="S48" s="356"/>
+      <c r="Q48" s="18"/>
+      <c r="R48" s="356"/>
+      <c r="S48" s="18"/>
       <c r="T48" s="356"/>
-      <c r="U48" s="18"/>
+      <c r="U48" s="356"/>
       <c r="V48" s="18"/>
       <c r="W48" s="18"/>
-      <c r="X48" s="356"/>
-      <c r="Y48" s="18"/>
-      <c r="Z48" s="356"/>
+      <c r="X48" s="18"/>
+      <c r="Y48" s="356"/>
+      <c r="Z48" s="18"/>
       <c r="AA48" s="356"/>
       <c r="AB48" s="356"/>
       <c r="AC48" s="356"/>
@@ -24194,7 +24239,7 @@
       <c r="AF48" s="356"/>
       <c r="AG48" s="356"/>
       <c r="AH48" s="356"/>
-      <c r="AI48" s="18"/>
+      <c r="AI48" s="356"/>
       <c r="AJ48" s="18"/>
       <c r="AK48" s="18"/>
       <c r="AL48" s="18"/>
@@ -24206,67 +24251,68 @@
       <c r="AR48" s="18"/>
       <c r="AS48" s="18"/>
       <c r="AT48" s="18"/>
-      <c r="AU48" s="26"/>
-      <c r="AW48" s="42">
+      <c r="AU48" s="18"/>
+      <c r="AV48" s="26"/>
+      <c r="AX48" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX48" s="23" cm="1">
-        <f t="array" ref="AX48">SUM(COUNTIFS(H48:AU48,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY48" s="23">
+      <c r="AY48" s="23" cm="1">
+        <f t="array" ref="AY48">SUM(COUNTIFS(I48:AV48,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ48" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ48" s="23" cm="1">
-        <f t="array" ref="AZ48">SUM(COUNTIFS(H48:AU48,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA48" s="23">
+      <c r="BA48" s="23" cm="1">
+        <f t="array" ref="BA48">SUM(COUNTIFS(I48:AV48,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB48" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB48" s="278">
+      <c r="BC48" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC48" s="39">
+      <c r="BD48" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD48" s="25">
+      <c r="BE48" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE48" s="26">
+      <c r="BF48" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF48" s="25">
+      <c r="BG48" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B48,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG48" s="26">
+      <c r="BH48" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B49" s="71"/>
       <c r="C49" s="18"/>
       <c r="D49" s="18"/>
       <c r="E49" s="307"/>
-      <c r="F49" s="25" t="str">
+      <c r="F49" s="307"/>
+      <c r="G49" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B49,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B49,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G49" s="26" t="str">
+      <c r="H49" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B49,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B50,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H49" s="24"/>
-      <c r="I49" s="356"/>
+      <c r="I49" s="24"/>
       <c r="J49" s="356"/>
       <c r="K49" s="356"/>
       <c r="L49" s="356"/>
@@ -24275,24 +24321,24 @@
       <c r="O49" s="356"/>
       <c r="P49" s="356"/>
       <c r="Q49" s="356"/>
-      <c r="R49" s="18"/>
-      <c r="S49" s="356"/>
-      <c r="T49" s="18"/>
+      <c r="R49" s="356"/>
+      <c r="S49" s="18"/>
+      <c r="T49" s="356"/>
       <c r="U49" s="18"/>
       <c r="V49" s="18"/>
-      <c r="W49" s="356"/>
+      <c r="W49" s="18"/>
       <c r="X49" s="356"/>
       <c r="Y49" s="356"/>
       <c r="Z49" s="356"/>
-      <c r="AA49" s="18"/>
+      <c r="AA49" s="356"/>
       <c r="AB49" s="18"/>
       <c r="AC49" s="18"/>
-      <c r="AD49" s="356"/>
-      <c r="AE49" s="18"/>
-      <c r="AF49" s="356"/>
-      <c r="AG49" s="18"/>
-      <c r="AH49" s="356"/>
-      <c r="AI49" s="18"/>
+      <c r="AD49" s="18"/>
+      <c r="AE49" s="356"/>
+      <c r="AF49" s="18"/>
+      <c r="AG49" s="356"/>
+      <c r="AH49" s="18"/>
+      <c r="AI49" s="356"/>
       <c r="AJ49" s="18"/>
       <c r="AK49" s="18"/>
       <c r="AL49" s="18"/>
@@ -24304,97 +24350,98 @@
       <c r="AR49" s="18"/>
       <c r="AS49" s="18"/>
       <c r="AT49" s="18"/>
-      <c r="AU49" s="26"/>
-      <c r="AW49" s="42">
+      <c r="AU49" s="18"/>
+      <c r="AV49" s="26"/>
+      <c r="AX49" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX49" s="23" cm="1">
-        <f t="array" ref="AX49">SUM(COUNTIFS(H49:AU49,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY49" s="23">
+      <c r="AY49" s="23" cm="1">
+        <f t="array" ref="AY49">SUM(COUNTIFS(I49:AV49,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ49" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ49" s="23" cm="1">
-        <f t="array" ref="AZ49">SUM(COUNTIFS(H49:AU49,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA49" s="23">
+      <c r="BA49" s="23" cm="1">
+        <f t="array" ref="BA49">SUM(COUNTIFS(I49:AV49,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB49" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB49" s="278">
+      <c r="BC49" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC49" s="39">
+      <c r="BD49" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD49" s="25">
+      <c r="BE49" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE49" s="26">
+      <c r="BF49" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF49" s="25">
+      <c r="BG49" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B49,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG49" s="26">
+      <c r="BH49" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B50" s="71"/>
       <c r="C50" s="18"/>
       <c r="D50" s="18"/>
       <c r="E50" s="307"/>
-      <c r="F50" s="25" t="str">
+      <c r="F50" s="307"/>
+      <c r="G50" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B50,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B50,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G50" s="26" t="str">
+      <c r="H50" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B50,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B51,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H50" s="24"/>
-      <c r="I50" s="18"/>
+      <c r="I50" s="24"/>
       <c r="J50" s="18"/>
-      <c r="K50" s="356"/>
-      <c r="L50" s="18"/>
+      <c r="K50" s="18"/>
+      <c r="L50" s="356"/>
       <c r="M50" s="18"/>
       <c r="N50" s="18"/>
       <c r="O50" s="18"/>
       <c r="P50" s="18"/>
-      <c r="Q50" s="356"/>
-      <c r="R50" s="18"/>
+      <c r="Q50" s="18"/>
+      <c r="R50" s="356"/>
       <c r="S50" s="18"/>
-      <c r="T50" s="356"/>
+      <c r="T50" s="18"/>
       <c r="U50" s="356"/>
-      <c r="V50" s="18"/>
+      <c r="V50" s="356"/>
       <c r="W50" s="18"/>
       <c r="X50" s="18"/>
-      <c r="Y50" s="356"/>
+      <c r="Y50" s="18"/>
       <c r="Z50" s="356"/>
       <c r="AA50" s="356"/>
-      <c r="AB50" s="18"/>
-      <c r="AC50" s="356"/>
+      <c r="AB50" s="356"/>
+      <c r="AC50" s="18"/>
       <c r="AD50" s="356"/>
       <c r="AE50" s="356"/>
       <c r="AF50" s="356"/>
-      <c r="AG50" s="18"/>
+      <c r="AG50" s="356"/>
       <c r="AH50" s="18"/>
       <c r="AI50" s="18"/>
       <c r="AJ50" s="18"/>
       <c r="AK50" s="18"/>
       <c r="AL50" s="18"/>
-      <c r="AM50" s="356"/>
+      <c r="AM50" s="18"/>
       <c r="AN50" s="356"/>
       <c r="AO50" s="356"/>
       <c r="AP50" s="356"/>
@@ -24402,82 +24449,83 @@
       <c r="AR50" s="356"/>
       <c r="AS50" s="356"/>
       <c r="AT50" s="356"/>
-      <c r="AU50" s="358"/>
-      <c r="AW50" s="42">
+      <c r="AU50" s="356"/>
+      <c r="AV50" s="358"/>
+      <c r="AX50" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX50" s="23" cm="1">
-        <f t="array" ref="AX50">SUM(COUNTIFS(H50:AU50,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY50" s="23">
+      <c r="AY50" s="23" cm="1">
+        <f t="array" ref="AY50">SUM(COUNTIFS(I50:AV50,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ50" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ50" s="23" cm="1">
-        <f t="array" ref="AZ50">SUM(COUNTIFS(H50:AU50,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA50" s="23">
+      <c r="BA50" s="23" cm="1">
+        <f t="array" ref="BA50">SUM(COUNTIFS(I50:AV50,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB50" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB50" s="278">
+      <c r="BC50" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC50" s="39">
+      <c r="BD50" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD50" s="25">
+      <c r="BE50" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE50" s="26">
+      <c r="BF50" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF50" s="25">
+      <c r="BG50" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B50,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG50" s="26">
+      <c r="BH50" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B51" s="71"/>
       <c r="C51" s="18"/>
       <c r="D51" s="18"/>
       <c r="E51" s="307"/>
-      <c r="F51" s="25" t="str">
+      <c r="F51" s="307"/>
+      <c r="G51" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B51,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B51,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G51" s="26" t="str">
+      <c r="H51" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B51,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B52,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H51" s="24"/>
-      <c r="I51" s="18"/>
-      <c r="J51" s="356"/>
+      <c r="I51" s="24"/>
+      <c r="J51" s="18"/>
       <c r="K51" s="356"/>
       <c r="L51" s="356"/>
       <c r="M51" s="356"/>
       <c r="N51" s="356"/>
-      <c r="O51" s="18"/>
+      <c r="O51" s="356"/>
       <c r="P51" s="18"/>
       <c r="Q51" s="18"/>
       <c r="R51" s="18"/>
       <c r="S51" s="18"/>
-      <c r="T51" s="356"/>
+      <c r="T51" s="18"/>
       <c r="U51" s="356"/>
-      <c r="V51" s="18"/>
-      <c r="W51" s="356"/>
-      <c r="X51" s="18"/>
+      <c r="V51" s="356"/>
+      <c r="W51" s="18"/>
+      <c r="X51" s="356"/>
       <c r="Y51" s="18"/>
       <c r="Z51" s="18"/>
       <c r="AA51" s="18"/>
@@ -24485,14 +24533,14 @@
       <c r="AC51" s="18"/>
       <c r="AD51" s="18"/>
       <c r="AE51" s="18"/>
-      <c r="AF51" s="356"/>
-      <c r="AG51" s="18"/>
-      <c r="AH51" s="356"/>
-      <c r="AI51" s="18"/>
+      <c r="AF51" s="18"/>
+      <c r="AG51" s="356"/>
+      <c r="AH51" s="18"/>
+      <c r="AI51" s="356"/>
       <c r="AJ51" s="18"/>
       <c r="AK51" s="18"/>
       <c r="AL51" s="18"/>
-      <c r="AM51" s="356"/>
+      <c r="AM51" s="18"/>
       <c r="AN51" s="356"/>
       <c r="AO51" s="356"/>
       <c r="AP51" s="356"/>
@@ -24500,82 +24548,83 @@
       <c r="AR51" s="356"/>
       <c r="AS51" s="356"/>
       <c r="AT51" s="356"/>
-      <c r="AU51" s="358"/>
-      <c r="AW51" s="42">
+      <c r="AU51" s="356"/>
+      <c r="AV51" s="358"/>
+      <c r="AX51" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX51" s="23" cm="1">
-        <f t="array" ref="AX51">SUM(COUNTIFS(H51:AU51,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY51" s="23">
+      <c r="AY51" s="23" cm="1">
+        <f t="array" ref="AY51">SUM(COUNTIFS(I51:AV51,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ51" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ51" s="23" cm="1">
-        <f t="array" ref="AZ51">SUM(COUNTIFS(H51:AU51,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA51" s="23">
+      <c r="BA51" s="23" cm="1">
+        <f t="array" ref="BA51">SUM(COUNTIFS(I51:AV51,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB51" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB51" s="278">
+      <c r="BC51" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC51" s="39">
+      <c r="BD51" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD51" s="25">
+      <c r="BE51" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE51" s="26">
+      <c r="BF51" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF51" s="25">
+      <c r="BG51" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B51,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG51" s="26">
+      <c r="BH51" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B52" s="71"/>
       <c r="C52" s="18"/>
       <c r="D52" s="18"/>
       <c r="E52" s="307"/>
-      <c r="F52" s="25" t="str">
+      <c r="F52" s="307"/>
+      <c r="G52" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B52,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B52,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G52" s="26" t="str">
+      <c r="H52" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B52,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B53,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H52" s="24"/>
-      <c r="I52" s="18"/>
-      <c r="J52" s="356"/>
+      <c r="I52" s="24"/>
+      <c r="J52" s="18"/>
       <c r="K52" s="356"/>
       <c r="L52" s="356"/>
       <c r="M52" s="356"/>
       <c r="N52" s="356"/>
-      <c r="O52" s="18"/>
+      <c r="O52" s="356"/>
       <c r="P52" s="18"/>
       <c r="Q52" s="18"/>
       <c r="R52" s="18"/>
       <c r="S52" s="18"/>
-      <c r="T52" s="356"/>
+      <c r="T52" s="18"/>
       <c r="U52" s="356"/>
-      <c r="V52" s="18"/>
-      <c r="W52" s="356"/>
-      <c r="X52" s="18"/>
+      <c r="V52" s="356"/>
+      <c r="W52" s="18"/>
+      <c r="X52" s="356"/>
       <c r="Y52" s="18"/>
       <c r="Z52" s="18"/>
       <c r="AA52" s="18"/>
@@ -24583,14 +24632,14 @@
       <c r="AC52" s="18"/>
       <c r="AD52" s="18"/>
       <c r="AE52" s="18"/>
-      <c r="AF52" s="356"/>
-      <c r="AG52" s="18"/>
-      <c r="AH52" s="356"/>
-      <c r="AI52" s="18"/>
+      <c r="AF52" s="18"/>
+      <c r="AG52" s="356"/>
+      <c r="AH52" s="18"/>
+      <c r="AI52" s="356"/>
       <c r="AJ52" s="18"/>
       <c r="AK52" s="18"/>
       <c r="AL52" s="18"/>
-      <c r="AM52" s="356"/>
+      <c r="AM52" s="18"/>
       <c r="AN52" s="356"/>
       <c r="AO52" s="356"/>
       <c r="AP52" s="356"/>
@@ -24598,82 +24647,83 @@
       <c r="AR52" s="356"/>
       <c r="AS52" s="356"/>
       <c r="AT52" s="356"/>
-      <c r="AU52" s="358"/>
-      <c r="AW52" s="42">
+      <c r="AU52" s="356"/>
+      <c r="AV52" s="358"/>
+      <c r="AX52" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX52" s="23" cm="1">
-        <f t="array" ref="AX52">SUM(COUNTIFS(H52:AU52,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY52" s="23">
+      <c r="AY52" s="23" cm="1">
+        <f t="array" ref="AY52">SUM(COUNTIFS(I52:AV52,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ52" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ52" s="23" cm="1">
-        <f t="array" ref="AZ52">SUM(COUNTIFS(H52:AU52,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA52" s="23">
+      <c r="BA52" s="23" cm="1">
+        <f t="array" ref="BA52">SUM(COUNTIFS(I52:AV52,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB52" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB52" s="278">
+      <c r="BC52" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC52" s="39">
+      <c r="BD52" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD52" s="25">
+      <c r="BE52" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE52" s="26">
+      <c r="BF52" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF52" s="25">
+      <c r="BG52" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B52,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG52" s="26">
+      <c r="BH52" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B53" s="71"/>
       <c r="C53" s="18"/>
       <c r="D53" s="18"/>
       <c r="E53" s="307"/>
-      <c r="F53" s="25" t="str">
+      <c r="F53" s="307"/>
+      <c r="G53" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B53,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B53,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G53" s="26" t="str">
+      <c r="H53" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B53,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B54,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H53" s="24"/>
-      <c r="I53" s="18"/>
-      <c r="J53" s="356"/>
+      <c r="I53" s="24"/>
+      <c r="J53" s="18"/>
       <c r="K53" s="356"/>
       <c r="L53" s="356"/>
       <c r="M53" s="356"/>
       <c r="N53" s="356"/>
-      <c r="O53" s="18"/>
+      <c r="O53" s="356"/>
       <c r="P53" s="18"/>
       <c r="Q53" s="18"/>
       <c r="R53" s="18"/>
       <c r="S53" s="18"/>
-      <c r="T53" s="356"/>
+      <c r="T53" s="18"/>
       <c r="U53" s="356"/>
-      <c r="V53" s="18"/>
-      <c r="W53" s="356"/>
-      <c r="X53" s="18"/>
+      <c r="V53" s="356"/>
+      <c r="W53" s="18"/>
+      <c r="X53" s="356"/>
       <c r="Y53" s="18"/>
       <c r="Z53" s="18"/>
       <c r="AA53" s="18"/>
@@ -24681,14 +24731,14 @@
       <c r="AC53" s="18"/>
       <c r="AD53" s="18"/>
       <c r="AE53" s="18"/>
-      <c r="AF53" s="356"/>
-      <c r="AG53" s="18"/>
-      <c r="AH53" s="356"/>
-      <c r="AI53" s="18"/>
+      <c r="AF53" s="18"/>
+      <c r="AG53" s="356"/>
+      <c r="AH53" s="18"/>
+      <c r="AI53" s="356"/>
       <c r="AJ53" s="18"/>
       <c r="AK53" s="18"/>
       <c r="AL53" s="18"/>
-      <c r="AM53" s="356"/>
+      <c r="AM53" s="18"/>
       <c r="AN53" s="356"/>
       <c r="AO53" s="356"/>
       <c r="AP53" s="356"/>
@@ -24696,82 +24746,83 @@
       <c r="AR53" s="356"/>
       <c r="AS53" s="356"/>
       <c r="AT53" s="356"/>
-      <c r="AU53" s="358"/>
-      <c r="AW53" s="42">
+      <c r="AU53" s="356"/>
+      <c r="AV53" s="358"/>
+      <c r="AX53" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX53" s="23" cm="1">
-        <f t="array" ref="AX53">SUM(COUNTIFS(H53:AU53,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY53" s="23">
+      <c r="AY53" s="23" cm="1">
+        <f t="array" ref="AY53">SUM(COUNTIFS(I53:AV53,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ53" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ53" s="23" cm="1">
-        <f t="array" ref="AZ53">SUM(COUNTIFS(H53:AU53,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA53" s="23">
+      <c r="BA53" s="23" cm="1">
+        <f t="array" ref="BA53">SUM(COUNTIFS(I53:AV53,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB53" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB53" s="278">
+      <c r="BC53" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC53" s="39">
+      <c r="BD53" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD53" s="25">
+      <c r="BE53" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE53" s="26">
+      <c r="BF53" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF53" s="25">
+      <c r="BG53" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B53,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG53" s="26">
+      <c r="BH53" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B54" s="71"/>
       <c r="C54" s="18"/>
       <c r="D54" s="18"/>
       <c r="E54" s="307"/>
-      <c r="F54" s="25" t="str">
+      <c r="F54" s="307"/>
+      <c r="G54" s="25" t="str">
         <f>IFERROR(IF(VLOOKUP($B54,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B54,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G54" s="26" t="str">
+      <c r="H54" s="26" t="str">
         <f>IFERROR(IF(VLOOKUP($B54,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B55,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H54" s="24"/>
-      <c r="I54" s="18"/>
-      <c r="J54" s="356"/>
+      <c r="I54" s="24"/>
+      <c r="J54" s="18"/>
       <c r="K54" s="356"/>
       <c r="L54" s="356"/>
       <c r="M54" s="356"/>
       <c r="N54" s="356"/>
-      <c r="O54" s="18"/>
+      <c r="O54" s="356"/>
       <c r="P54" s="18"/>
       <c r="Q54" s="18"/>
       <c r="R54" s="18"/>
       <c r="S54" s="18"/>
-      <c r="T54" s="356"/>
+      <c r="T54" s="18"/>
       <c r="U54" s="356"/>
-      <c r="V54" s="18"/>
-      <c r="W54" s="356"/>
-      <c r="X54" s="18"/>
+      <c r="V54" s="356"/>
+      <c r="W54" s="18"/>
+      <c r="X54" s="356"/>
       <c r="Y54" s="18"/>
       <c r="Z54" s="18"/>
       <c r="AA54" s="18"/>
@@ -24779,14 +24830,14 @@
       <c r="AC54" s="18"/>
       <c r="AD54" s="18"/>
       <c r="AE54" s="18"/>
-      <c r="AF54" s="356"/>
-      <c r="AG54" s="18"/>
-      <c r="AH54" s="356"/>
-      <c r="AI54" s="18"/>
+      <c r="AF54" s="18"/>
+      <c r="AG54" s="356"/>
+      <c r="AH54" s="18"/>
+      <c r="AI54" s="356"/>
       <c r="AJ54" s="18"/>
       <c r="AK54" s="18"/>
       <c r="AL54" s="18"/>
-      <c r="AM54" s="356"/>
+      <c r="AM54" s="18"/>
       <c r="AN54" s="356"/>
       <c r="AO54" s="356"/>
       <c r="AP54" s="356"/>
@@ -24794,97 +24845,98 @@
       <c r="AR54" s="356"/>
       <c r="AS54" s="356"/>
       <c r="AT54" s="356"/>
-      <c r="AU54" s="358"/>
-      <c r="AW54" s="42">
+      <c r="AU54" s="356"/>
+      <c r="AV54" s="358"/>
+      <c r="AX54" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX54" s="23" cm="1">
-        <f t="array" ref="AX54">SUM(COUNTIFS(H54:AU54,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY54" s="23">
+      <c r="AY54" s="23" cm="1">
+        <f t="array" ref="AY54">SUM(COUNTIFS(I54:AV54,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ54" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ54" s="23" cm="1">
-        <f t="array" ref="AZ54">SUM(COUNTIFS(H54:AU54,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA54" s="23">
+      <c r="BA54" s="23" cm="1">
+        <f t="array" ref="BA54">SUM(COUNTIFS(I54:AV54,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB54" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB54" s="278">
+      <c r="BC54" s="278">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC54" s="39">
+      <c r="BD54" s="39">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD54" s="25">
+      <c r="BE54" s="25">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE54" s="26">
+      <c r="BF54" s="26">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF54" s="25">
+      <c r="BG54" s="25">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B54,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG54" s="26">
+      <c r="BH54" s="26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:59" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:60" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B55" s="75"/>
       <c r="C55" s="34"/>
       <c r="D55" s="34"/>
       <c r="E55" s="308"/>
-      <c r="F55" s="33" t="str">
+      <c r="F55" s="308"/>
+      <c r="G55" s="33" t="str">
         <f>IFERROR(IF(VLOOKUP($B55,'Month-1'!$B$3:$D$53,2,0)=0,"",VLOOKUP($B55,'Month-1'!$B$3:$D$53,2,0)),"")</f>
         <v/>
       </c>
-      <c r="G55" s="41" t="str">
+      <c r="H55" s="41" t="str">
         <f>IFERROR(IF(VLOOKUP($B55,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B56,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
-      <c r="H55" s="38"/>
-      <c r="I55" s="34"/>
-      <c r="J55" s="359"/>
-      <c r="K55" s="34"/>
-      <c r="L55" s="359"/>
-      <c r="M55" s="34"/>
+      <c r="I55" s="38"/>
+      <c r="J55" s="34"/>
+      <c r="K55" s="359"/>
+      <c r="L55" s="34"/>
+      <c r="M55" s="359"/>
       <c r="N55" s="34"/>
       <c r="O55" s="34"/>
       <c r="P55" s="34"/>
-      <c r="Q55" s="359"/>
-      <c r="R55" s="34"/>
+      <c r="Q55" s="34"/>
+      <c r="R55" s="359"/>
       <c r="S55" s="34"/>
       <c r="T55" s="34"/>
       <c r="U55" s="34"/>
-      <c r="V55" s="359"/>
+      <c r="V55" s="34"/>
       <c r="W55" s="359"/>
       <c r="X55" s="359"/>
-      <c r="Y55" s="34"/>
+      <c r="Y55" s="359"/>
       <c r="Z55" s="34"/>
-      <c r="AA55" s="359"/>
-      <c r="AB55" s="34"/>
+      <c r="AA55" s="34"/>
+      <c r="AB55" s="359"/>
       <c r="AC55" s="34"/>
-      <c r="AD55" s="359"/>
+      <c r="AD55" s="34"/>
       <c r="AE55" s="359"/>
       <c r="AF55" s="359"/>
-      <c r="AG55" s="34"/>
+      <c r="AG55" s="359"/>
       <c r="AH55" s="34"/>
       <c r="AI55" s="34"/>
       <c r="AJ55" s="34"/>
-      <c r="AK55" s="359"/>
-      <c r="AL55" s="34"/>
-      <c r="AM55" s="359"/>
+      <c r="AK55" s="34"/>
+      <c r="AL55" s="359"/>
+      <c r="AM55" s="34"/>
       <c r="AN55" s="359"/>
       <c r="AO55" s="359"/>
       <c r="AP55" s="359"/>
@@ -24892,60 +24944,57 @@
       <c r="AR55" s="359"/>
       <c r="AS55" s="359"/>
       <c r="AT55" s="359"/>
-      <c r="AU55" s="360"/>
-      <c r="AW55" s="49">
+      <c r="AU55" s="359"/>
+      <c r="AV55" s="360"/>
+      <c r="AX55" s="49">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AX55" s="48" cm="1">
-        <f t="array" ref="AX55">SUM(COUNTIFS(H55:AU55,{"R1","R2"},$H$2:$AU$2,"&lt;5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="AY55" s="48">
+      <c r="AY55" s="48" cm="1">
+        <f t="array" ref="AY55">SUM(COUNTIFS(I55:AV55,{"R1","R2"},$I$2:$AV$2,"&lt;5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ55" s="48">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ55" s="48" cm="1">
-        <f t="array" ref="AZ55">SUM(COUNTIFS(H55:AU55,{"R1","R2"},$H$2:$AU$2,"5",$H$1:$AU$1,"&lt;&gt;Y"))</f>
-        <v>0</v>
-      </c>
-      <c r="BA55" s="48">
+      <c r="BA55" s="48" cm="1">
+        <f t="array" ref="BA55">SUM(COUNTIFS(I55:AV55,{"R1","R2"},$I$2:$AV$2,"5",$I$1:$AV$1,"&lt;&gt;Y"))</f>
+        <v>0</v>
+      </c>
+      <c r="BB55" s="48">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB55" s="279">
+      <c r="BC55" s="279">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC55" s="50">
+      <c r="BD55" s="50">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BD55" s="33">
+      <c r="BE55" s="33">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BE55" s="41">
+      <c r="BF55" s="41">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BF55" s="33">
+      <c r="BG55" s="33">
         <f>IFERROR(INDEX('Month-1'!$F$3:$F$53,MATCH($B55,'Month-1'!$B$3:$B$53,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="BG55" s="41">
+      <c r="BH55" s="41">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:59" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:60" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D57" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="H57" s="389" t="str">
-        <f>IFERROR(INDEX($B$6:$B$55,MATCH($D57,H$6:H$55,0)), "")</f>
-        <v/>
-      </c>
       <c r="I57" s="389" t="str">
         <f>IFERROR(INDEX($B$6:$B$55,MATCH($D57,I$6:I$55,0)), "")</f>
         <v/>
@@ -24955,11 +25004,11 @@
         <v/>
       </c>
       <c r="K57" s="389" t="str">
-        <f t="shared" ref="K57:AU62" si="20">IFERROR(INDEX($B$6:$B$55,MATCH($D57,K$6:K$55,0)), "")</f>
+        <f>IFERROR(INDEX($B$6:$B$55,MATCH($D57,K$6:K$55,0)), "")</f>
         <v/>
       </c>
       <c r="L57" s="389" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="L57:AV62" si="20">IFERROR(INDEX($B$6:$B$55,MATCH($D57,L$6:L$55,0)), "")</f>
         <v/>
       </c>
       <c r="M57" s="389" t="str">
@@ -25070,14 +25119,14 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN57" s="389"/>
+      <c r="AN57" s="389" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
       <c r="AO57" s="389"/>
       <c r="AP57" s="389"/>
       <c r="AQ57" s="389"/>
-      <c r="AR57" s="389" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
+      <c r="AR57" s="389"/>
       <c r="AS57" s="389" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -25090,17 +25139,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
+      <c r="AV57" s="389" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
     </row>
-    <row r="58" spans="2:59" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:60" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D58" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="H58" s="389" t="str">
-        <f t="shared" ref="H58:W62" si="21">IFERROR(INDEX($B$6:$B$55,MATCH($D58,H$6:H$55,0)), "")</f>
-        <v/>
-      </c>
       <c r="I58" s="389" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="I58:X62" si="21">IFERROR(INDEX($B$6:$B$55,MATCH($D58,I$6:I$55,0)), "")</f>
         <v/>
       </c>
       <c r="J58" s="389" t="str">
@@ -25160,7 +25209,7 @@
         <v/>
       </c>
       <c r="X58" s="389" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Y58" s="389" t="str">
@@ -25223,14 +25272,14 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN58" s="389"/>
+      <c r="AN58" s="389" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
       <c r="AO58" s="389"/>
       <c r="AP58" s="389"/>
       <c r="AQ58" s="389"/>
-      <c r="AR58" s="389" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
+      <c r="AR58" s="389"/>
       <c r="AS58" s="389" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -25243,15 +25292,15 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
+      <c r="AV58" s="389" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
     </row>
-    <row r="59" spans="2:59" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:60" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D59" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="H59" s="389" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
       <c r="I59" s="389" t="str">
         <f t="shared" si="21"/>
         <v/>
@@ -25261,7 +25310,7 @@
         <v/>
       </c>
       <c r="K59" s="389" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="L59" s="389" t="str">
@@ -25376,14 +25425,14 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN59" s="389"/>
+      <c r="AN59" s="389" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
       <c r="AO59" s="389"/>
       <c r="AP59" s="389"/>
       <c r="AQ59" s="389"/>
-      <c r="AR59" s="389" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
+      <c r="AR59" s="389"/>
       <c r="AS59" s="389" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -25396,15 +25445,15 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
+      <c r="AV59" s="389" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
     </row>
-    <row r="60" spans="2:59" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:60" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D60" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="H60" s="389" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
       <c r="I60" s="389" t="str">
         <f t="shared" si="21"/>
         <v/>
@@ -25414,7 +25463,7 @@
         <v/>
       </c>
       <c r="K60" s="389" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="L60" s="389" t="str">
@@ -25529,14 +25578,14 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN60" s="389"/>
+      <c r="AN60" s="389" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
       <c r="AO60" s="389"/>
       <c r="AP60" s="389"/>
       <c r="AQ60" s="389"/>
-      <c r="AR60" s="389" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
+      <c r="AR60" s="389"/>
       <c r="AS60" s="389" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -25549,15 +25598,15 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
+      <c r="AV60" s="389" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
     </row>
-    <row r="61" spans="2:59" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:60" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D61" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H61" s="389" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
       <c r="I61" s="389" t="str">
         <f t="shared" si="21"/>
         <v/>
@@ -25567,7 +25616,7 @@
         <v/>
       </c>
       <c r="K61" s="389" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="L61" s="389" t="str">
@@ -25682,14 +25731,14 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN61" s="389"/>
+      <c r="AN61" s="389" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
       <c r="AO61" s="389"/>
       <c r="AP61" s="389"/>
       <c r="AQ61" s="389"/>
-      <c r="AR61" s="389" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
+      <c r="AR61" s="389"/>
       <c r="AS61" s="389" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -25702,15 +25751,15 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
+      <c r="AV61" s="389" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
     </row>
-    <row r="62" spans="2:59" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:60" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D62" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H62" s="389" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
       <c r="I62" s="389" t="str">
         <f t="shared" si="21"/>
         <v/>
@@ -25720,7 +25769,7 @@
         <v/>
       </c>
       <c r="K62" s="389" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="L62" s="389" t="str">
@@ -25835,14 +25884,14 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN62" s="389"/>
+      <c r="AN62" s="389" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
       <c r="AO62" s="389"/>
       <c r="AP62" s="389"/>
       <c r="AQ62" s="389"/>
-      <c r="AR62" s="389" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
+      <c r="AR62" s="389"/>
       <c r="AS62" s="389" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -25855,13 +25904,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
+      <c r="AV62" s="389" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
     </row>
-    <row r="64" spans="2:59" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B64" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B65" s="333" t="s">
         <v>244</v>
       </c>
@@ -25871,8 +25924,9 @@
       <c r="E65" s="327"/>
       <c r="F65" s="327"/>
       <c r="G65" s="327"/>
+      <c r="H65" s="327"/>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B66" s="334" t="s">
         <v>291</v>
       </c>
@@ -25882,8 +25936,9 @@
       <c r="E66" s="327"/>
       <c r="F66" s="327"/>
       <c r="G66" s="327"/>
+      <c r="H66" s="327"/>
     </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B67" s="335" t="s">
         <v>243</v>
       </c>
@@ -25893,8 +25948,9 @@
       <c r="E67" s="327"/>
       <c r="F67" s="327"/>
       <c r="G67" s="327"/>
+      <c r="H67" s="327"/>
     </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B68" s="376" t="s">
         <v>267</v>
       </c>
@@ -25902,7 +25958,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B69" s="377" t="s">
         <v>268</v>
       </c>
@@ -25910,7 +25966,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B70" s="17" t="s">
         <v>247</v>
       </c>
@@ -25918,7 +25974,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B71" s="336" t="s">
         <v>212</v>
       </c>
@@ -25928,26 +25984,27 @@
       <c r="E71" s="327"/>
       <c r="F71" s="327"/>
       <c r="G71" s="327"/>
+      <c r="H71" s="327"/>
     </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C72" s="3"/>
     </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B74" s="3" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="75" spans="2:7" ht="48" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:8" ht="48" x14ac:dyDescent="0.2">
       <c r="B75" s="388" t="s">
         <v>296</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="BD3:BE4"/>
-    <mergeCell ref="BF3:BG4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="AW3:BC3"/>
+    <mergeCell ref="BE3:BF4"/>
+    <mergeCell ref="BG3:BH4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="AX3:BD3"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C4 C6:C1048576">
     <cfRule type="beginsWith" dxfId="4" priority="1" operator="beginsWith" text="HA">
@@ -25994,11 +26051,11 @@
         <v>250</v>
       </c>
       <c r="C2" s="58">
-        <f>Month!H5-2</f>
+        <f>Month!I5-2</f>
         <v>46117</v>
       </c>
       <c r="D2" s="290">
-        <f>Month!H5-1</f>
+        <f>Month!I5-1</f>
         <v>46118</v>
       </c>
       <c r="E2" s="66" t="s">
@@ -26449,7 +26506,7 @@
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="371">
-        <f>Month!H5</f>
+        <f>Month!I5</f>
         <v>46119</v>
       </c>
       <c r="B4" s="372" t="str">
@@ -26457,27 +26514,27 @@
         <v>Tuesday</v>
       </c>
       <c r="C4" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A4,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A4,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D4" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A4,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A4,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E4" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A4,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A4,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F4" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A4,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A4,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G4" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A4,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A4,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H4" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A4,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A4,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26491,27 +26548,27 @@
         <v>Wednesday</v>
       </c>
       <c r="C5" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A5,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A5,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D5" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A5,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A5,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E5" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A5,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A5,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F5" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A5,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A5,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G5" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A5,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A5,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H5" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A5,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A5,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26525,27 +26582,27 @@
         <v>Thursday</v>
       </c>
       <c r="C6" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A6,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A6,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D6" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A6,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A6,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E6" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A6,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A6,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F6" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A6,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A6,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G6" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A6,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A6,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H6" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A6,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A6,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26559,27 +26616,27 @@
         <v>Friday</v>
       </c>
       <c r="C7" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A7,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A7,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D7" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A7,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A7,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E7" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A7,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A7,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F7" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A7,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A7,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G7" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A7,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A7,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H7" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A7,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A7,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26593,27 +26650,27 @@
         <v>Saturday</v>
       </c>
       <c r="C8" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A8,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A8,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A8,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A8,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E8" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A8,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A8,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F8" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A8,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A8,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G8" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A8,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A8,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H8" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A8,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A8,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26627,27 +26684,27 @@
         <v>Sunday</v>
       </c>
       <c r="C9" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A9,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A9,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A9,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A9,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E9" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A9,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A9,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F9" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A9,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A9,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G9" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A9,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A9,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H9" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A9,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A9,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26661,27 +26718,27 @@
         <v>Monday</v>
       </c>
       <c r="C10" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A10,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A10,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A10,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A10,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E10" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A10,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A10,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F10" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A10,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A10,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G10" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A10,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A10,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H10" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A10,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A10,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26695,27 +26752,27 @@
         <v>Tuesday</v>
       </c>
       <c r="C11" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A11,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A11,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A11,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A11,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E11" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A11,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A11,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F11" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A11,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A11,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G11" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A11,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A11,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H11" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A11,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A11,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26729,27 +26786,27 @@
         <v>Wednesday</v>
       </c>
       <c r="C12" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A12,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A12,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A12,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A12,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E12" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A12,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A12,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F12" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A12,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A12,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G12" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A12,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A12,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H12" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A12,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A12,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26763,27 +26820,27 @@
         <v>Thursday</v>
       </c>
       <c r="C13" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A13,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A13,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A13,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A13,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E13" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A13,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A13,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F13" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A13,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A13,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G13" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A13,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A13,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H13" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A13,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A13,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26797,27 +26854,27 @@
         <v>Friday</v>
       </c>
       <c r="C14" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A14,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A14,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A14,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A14,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E14" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A14,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A14,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F14" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A14,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A14,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G14" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A14,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A14,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H14" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A14,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A14,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26831,27 +26888,27 @@
         <v>Saturday</v>
       </c>
       <c r="C15" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A15,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A15,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A15,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A15,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E15" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A15,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A15,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F15" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A15,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A15,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G15" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A15,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A15,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H15" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A15,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A15,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26865,27 +26922,27 @@
         <v>Sunday</v>
       </c>
       <c r="C16" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A16,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A16,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A16,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A16,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E16" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A16,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A16,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F16" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A16,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A16,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G16" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A16,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A16,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H16" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A16,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A16,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26899,27 +26956,27 @@
         <v>Monday</v>
       </c>
       <c r="C17" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A17,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A17,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A17,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A17,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E17" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A17,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A17,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F17" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A17,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A17,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G17" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A17,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A17,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H17" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A17,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A17,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26933,27 +26990,27 @@
         <v>Tuesday</v>
       </c>
       <c r="C18" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A18,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A18,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A18,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A18,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E18" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A18,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A18,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F18" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A18,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A18,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G18" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A18,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A18,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H18" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A18,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A18,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -26967,27 +27024,27 @@
         <v>Wednesday</v>
       </c>
       <c r="C19" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A19,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A19,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A19,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A19,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E19" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A19,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A19,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F19" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A19,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A19,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G19" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A19,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A19,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H19" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A19,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A19,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27001,27 +27058,27 @@
         <v>Thursday</v>
       </c>
       <c r="C20" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A20,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A20,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D20" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A20,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A20,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E20" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A20,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A20,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F20" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A20,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A20,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G20" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A20,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A20,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H20" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A20,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A20,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27035,27 +27092,27 @@
         <v>Friday</v>
       </c>
       <c r="C21" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A21,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A21,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A21,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A21,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E21" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A21,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A21,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F21" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A21,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A21,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G21" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A21,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A21,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H21" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A21,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A21,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27069,27 +27126,27 @@
         <v>Saturday</v>
       </c>
       <c r="C22" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A22,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A22,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A22,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A22,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E22" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A22,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A22,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F22" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A22,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A22,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G22" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A22,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A22,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H22" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A22,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A22,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27103,27 +27160,27 @@
         <v>Sunday</v>
       </c>
       <c r="C23" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A23,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A23,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A23,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A23,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E23" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A23,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A23,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F23" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A23,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A23,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G23" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A23,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A23,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H23" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A23,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A23,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27137,27 +27194,27 @@
         <v>Monday</v>
       </c>
       <c r="C24" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A24,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A24,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A24,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A24,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E24" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A24,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A24,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F24" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A24,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A24,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G24" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A24,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A24,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H24" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A24,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A24,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27171,27 +27228,27 @@
         <v>Tuesday</v>
       </c>
       <c r="C25" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A25,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A25,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A25,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A25,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A25,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A25,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F25" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A25,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A25,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G25" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A25,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A25,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H25" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A25,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A25,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27205,27 +27262,27 @@
         <v>Wednesday</v>
       </c>
       <c r="C26" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A26,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A26,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A26,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A26,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E26" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A26,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A26,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F26" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A26,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A26,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G26" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A26,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A26,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H26" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A26,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A26,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27239,27 +27296,27 @@
         <v>Thursday</v>
       </c>
       <c r="C27" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A27,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A27,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A27,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A27,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E27" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A27,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A27,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F27" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A27,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A27,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G27" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A27,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A27,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H27" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A27,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A27,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27273,27 +27330,27 @@
         <v>Friday</v>
       </c>
       <c r="C28" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A28,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A28,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A28,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A28,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E28" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A28,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A28,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F28" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A28,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A28,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G28" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A28,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A28,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H28" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A28,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A28,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27307,27 +27364,27 @@
         <v>Saturday</v>
       </c>
       <c r="C29" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A29,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A29,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A29,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A29,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E29" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A29,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A29,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F29" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A29,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A29,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G29" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A29,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A29,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H29" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A29,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A29,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27341,27 +27398,27 @@
         <v>Sunday</v>
       </c>
       <c r="C30" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A30,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A30,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A30,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A30,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E30" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A30,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A30,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F30" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A30,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A30,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G30" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A30,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A30,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H30" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A30,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A30,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27375,27 +27432,27 @@
         <v>Monday</v>
       </c>
       <c r="C31" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A31,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A31,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A31,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A31,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E31" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A31,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A31,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F31" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A31,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A31,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G31" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A31,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A31,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H31" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A31,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A31,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27409,27 +27466,27 @@
         <v>Tuesday</v>
       </c>
       <c r="C32" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A32,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A32,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A32,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A32,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E32" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A32,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A32,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F32" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A32,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A32,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G32" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A32,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A32,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H32" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A32,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A32,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27443,27 +27500,27 @@
         <v>Wednesday</v>
       </c>
       <c r="C33" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A33,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A33,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A33,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A33,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E33" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A33,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A33,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F33" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A33,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A33,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G33" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A33,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A33,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H33" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A33,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A33,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27477,27 +27534,27 @@
         <v>Thursday</v>
       </c>
       <c r="C34" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A34,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A34,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A34,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A34,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A34,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A34,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F34" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A34,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A34,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G34" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A34,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A34,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H34" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A34,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A34,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27511,27 +27568,27 @@
         <v>Friday</v>
       </c>
       <c r="C35" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A35,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A35,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D35" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A35,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A35,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E35" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A35,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A35,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F35" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A35,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A35,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G35" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A35,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A35,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H35" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A35,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A35,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27545,27 +27602,27 @@
         <v>Saturday</v>
       </c>
       <c r="C36" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A36,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A36,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D36" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A36,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A36,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E36" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A36,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A36,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F36" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A36,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A36,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G36" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A36,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A36,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H36" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A36,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A36,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27579,27 +27636,27 @@
         <v>Sunday</v>
       </c>
       <c r="C37" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A37,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A37,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D37" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A37,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A37,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E37" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A37,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A37,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F37" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A37,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A37,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G37" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A37,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A37,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H37" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A37,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A37,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27613,27 +27670,27 @@
         <v>Monday</v>
       </c>
       <c r="C38" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A38,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A38,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D38" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A38,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A38,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E38" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A38,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A38,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F38" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A38,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A38,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G38" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A38,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A38,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H38" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A38,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A38,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27647,27 +27704,27 @@
         <v>Tuesday</v>
       </c>
       <c r="C39" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A39,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A39,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D39" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A39,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A39,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E39" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A39,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A39,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F39" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A39,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A39,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G39" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A39,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A39,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H39" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A39,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A39,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27681,27 +27738,27 @@
         <v>Wednesday</v>
       </c>
       <c r="C40" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A40,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A40,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D40" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A40,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A40,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E40" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A40,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A40,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F40" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A40,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A40,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G40" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A40,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A40,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H40" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A40,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A40,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27715,27 +27772,27 @@
         <v>Thursday</v>
       </c>
       <c r="C41" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A41,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A41,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D41" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A41,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A41,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E41" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A41,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A41,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F41" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A41,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A41,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G41" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A41,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A41,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H41" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A41,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A41,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27749,27 +27806,27 @@
         <v>Friday</v>
       </c>
       <c r="C42" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A42,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A42,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D42" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A42,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A42,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E42" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A42,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A42,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F42" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A42,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A42,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G42" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A42,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A42,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H42" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A42,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A42,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -27783,27 +27840,27 @@
         <v>Saturday</v>
       </c>
       <c r="C43" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A43,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(C$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A43,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="D43" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A43,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(D$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A43,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="E43" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A43,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(E$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A43,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="F43" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A43,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(F$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A43,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="G43" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A43,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(G$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A43,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
       <c r="H43" s="373" t="str">
-        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$H$6:$AU$55,0,MATCH($A43,Month!$H$5:$AU$5,0)),0)),"")</f>
+        <f>IFERROR(INDEX(Month!$B$6:$B$55,MATCH(H$2,INDEX(Month!$I$6:$AV$55,0,MATCH($A43,Month!$I$5:$AV$5,0)),0)),"")</f>
         <v/>
       </c>
     </row>

--- a/templates/Templates_REG.xlsx
+++ b/templates/Templates_REG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aletheia/Desktop/Paediatrics/Admin/RosterApp/roster/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB5A403-9353-C140-97E2-1970FA2E5835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7D6617-6B0B-7A41-B985-78E9F7C9D7A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="840" yWindow="1280" windowWidth="28560" windowHeight="16600" activeTab="2" xr2:uid="{B6EBF472-D0B5-0C4E-A945-41133059122F}"/>
   </bookViews>
@@ -26006,23 +26006,6 @@
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="AX3:BD3"/>
   </mergeCells>
-  <conditionalFormatting sqref="C1:C4 C6:C1048576">
-    <cfRule type="beginsWith" dxfId="4" priority="1" operator="beginsWith" text="HA">
-      <formula>LEFT(C1,LEN("HA"))="HA"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="3" priority="2" operator="beginsWith" text="D">
-      <formula>LEFT(C1,LEN("D"))="D"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="2" priority="3" operator="beginsWith" text="C">
-      <formula>LEFT(C1,LEN("C"))="C"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="1" priority="4" operator="beginsWith" text="B">
-      <formula>LEFT(C1,LEN("B"))="B"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="0" priority="5" stopIfTrue="1" operator="beginsWith" text="A">
-      <formula>LEFT(C1,LEN("A"))="A"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/templates/Templates_REG.xlsx
+++ b/templates/Templates_REG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aletheia/Desktop/Paediatrics/Admin/RosterApp/roster/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B29A168-094D-474C-94FC-CCF52ED750C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885275F3-B642-A043-BD49-C5F4BDAE6EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="840" yWindow="1280" windowWidth="28560" windowHeight="16600" activeTab="2" xr2:uid="{B6EBF472-D0B5-0C4E-A945-41133059122F}"/>
   </bookViews>
@@ -20082,7 +20082,7 @@
         <v>0</v>
       </c>
       <c r="BD6" s="39">
-        <f>COUNTIF(I6:AV6,"WR")</f>
+        <f>COUNTIF(I6:AV6,"WR*")</f>
         <v>0</v>
       </c>
       <c r="BE6" s="25">
@@ -20181,7 +20181,7 @@
         <v>0</v>
       </c>
       <c r="BD7" s="39">
-        <f t="shared" ref="BD7:BD49" si="16">COUNTIF(I7:AV7,"WR")</f>
+        <f t="shared" ref="BD7:BD49" si="16">COUNTIF(I7:AV7,"WR*")</f>
         <v>0</v>
       </c>
       <c r="BE7" s="25">
@@ -24364,131 +24364,131 @@
         <v>278</v>
       </c>
       <c r="I51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,I$6:I$49,0)), "")</f>
+        <f t="shared" ref="I51:R56" si="20">IFERROR(INDEX($B$6:$B$49,MATCH($D51,I$6:I$49,0)), "")</f>
         <v/>
       </c>
       <c r="J51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,J$6:J$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="K51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,K$6:K$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="L51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,L$6:L$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="M51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,M$6:M$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="N51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,N$6:N$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,O$6:O$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="P51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,P$6:P$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="Q51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,Q$6:Q$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,R$6:R$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="S51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,S$6:S$49,0)), "")</f>
+        <f t="shared" ref="S51:AB56" si="21">IFERROR(INDEX($B$6:$B$49,MATCH($D51,S$6:S$49,0)), "")</f>
         <v/>
       </c>
       <c r="T51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,T$6:T$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,U$6:U$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="V51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,V$6:V$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="W51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,W$6:W$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="X51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,X$6:X$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Y51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,Y$6:Y$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Z51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,Z$6:Z$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="AA51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,AA$6:AA$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="AB51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,AB$6:AB$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="AC51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,AC$6:AC$49,0)), "")</f>
+        <f t="shared" ref="AC51:AN56" si="22">IFERROR(INDEX($B$6:$B$49,MATCH($D51,AC$6:AC$49,0)), "")</f>
         <v/>
       </c>
       <c r="AD51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,AD$6:AD$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AE51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,AE$6:AE$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AF51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,AF$6:AF$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AG51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,AG$6:AG$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AH51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,AH$6:AH$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AI51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,AI$6:AI$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AJ51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,AJ$6:AJ$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AK51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,AK$6:AK$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AL51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,AL$6:AL$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AM51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,AM$6:AM$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AN51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,AN$6:AN$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AO51" s="388"/>
@@ -24496,19 +24496,19 @@
       <c r="AQ51" s="388"/>
       <c r="AR51" s="388"/>
       <c r="AS51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,AS$6:AS$49,0)), "")</f>
+        <f t="shared" ref="AS51:AV56" si="23">IFERROR(INDEX($B$6:$B$49,MATCH($D51,AS$6:AS$49,0)), "")</f>
         <v/>
       </c>
       <c r="AT51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,AT$6:AT$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AU51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,AU$6:AU$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AV51" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D51,AV$6:AV$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
@@ -24517,131 +24517,131 @@
         <v>279</v>
       </c>
       <c r="I52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,I$6:I$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,J$6:J$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="K52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,K$6:K$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="L52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,L$6:L$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="M52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,M$6:M$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="N52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,N$6:N$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,O$6:O$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="P52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,P$6:P$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="Q52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,Q$6:Q$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,R$6:R$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="S52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,S$6:S$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="T52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,T$6:T$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,U$6:U$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="V52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,V$6:V$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="W52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,W$6:W$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="X52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,X$6:X$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Y52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,Y$6:Y$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Z52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,Z$6:Z$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="AA52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,AA$6:AA$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="AB52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,AB$6:AB$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="AC52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,AC$6:AC$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AD52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,AD$6:AD$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AE52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,AE$6:AE$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AF52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,AF$6:AF$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AG52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,AG$6:AG$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AH52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,AH$6:AH$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AI52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,AI$6:AI$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AJ52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,AJ$6:AJ$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AK52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,AK$6:AK$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AL52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,AL$6:AL$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AM52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,AM$6:AM$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AN52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,AN$6:AN$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AO52" s="388"/>
@@ -24649,19 +24649,19 @@
       <c r="AQ52" s="388"/>
       <c r="AR52" s="388"/>
       <c r="AS52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,AS$6:AS$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AT52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,AT$6:AT$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AU52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,AU$6:AU$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AV52" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D52,AV$6:AV$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
@@ -24670,131 +24670,131 @@
         <v>280</v>
       </c>
       <c r="I53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,I$6:I$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,J$6:J$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="K53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,K$6:K$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="L53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,L$6:L$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="M53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,M$6:M$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="N53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,N$6:N$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,O$6:O$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="P53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,P$6:P$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="Q53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,Q$6:Q$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,R$6:R$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="S53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,S$6:S$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="T53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,T$6:T$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,U$6:U$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="V53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,V$6:V$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="W53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,W$6:W$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="X53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,X$6:X$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Y53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,Y$6:Y$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Z53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,Z$6:Z$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="AA53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,AA$6:AA$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="AB53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,AB$6:AB$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="AC53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,AC$6:AC$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AD53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,AD$6:AD$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AE53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,AE$6:AE$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AF53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,AF$6:AF$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AG53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,AG$6:AG$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AH53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,AH$6:AH$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AI53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,AI$6:AI$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AJ53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,AJ$6:AJ$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AK53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,AK$6:AK$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AL53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,AL$6:AL$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AM53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,AM$6:AM$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AN53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,AN$6:AN$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AO53" s="388"/>
@@ -24802,19 +24802,19 @@
       <c r="AQ53" s="388"/>
       <c r="AR53" s="388"/>
       <c r="AS53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,AS$6:AS$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AT53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,AT$6:AT$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AU53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,AU$6:AU$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AV53" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D53,AV$6:AV$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
@@ -24823,131 +24823,131 @@
         <v>297</v>
       </c>
       <c r="I54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,I$6:I$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,J$6:J$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="K54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,K$6:K$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="L54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,L$6:L$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="M54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,M$6:M$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="N54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,N$6:N$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,O$6:O$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="P54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,P$6:P$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="Q54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,Q$6:Q$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,R$6:R$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="S54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,S$6:S$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="T54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,T$6:T$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,U$6:U$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="V54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,V$6:V$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="W54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,W$6:W$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="X54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,X$6:X$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Y54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,Y$6:Y$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Z54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,Z$6:Z$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="AA54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,AA$6:AA$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="AB54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,AB$6:AB$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="AC54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,AC$6:AC$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AD54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,AD$6:AD$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AE54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,AE$6:AE$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AF54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,AF$6:AF$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AG54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,AG$6:AG$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AH54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,AH$6:AH$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AI54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,AI$6:AI$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AJ54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,AJ$6:AJ$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AK54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,AK$6:AK$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AL54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,AL$6:AL$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AM54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,AM$6:AM$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AN54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,AN$6:AN$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AO54" s="388"/>
@@ -24955,19 +24955,19 @@
       <c r="AQ54" s="388"/>
       <c r="AR54" s="388"/>
       <c r="AS54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,AS$6:AS$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AT54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,AT$6:AT$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AU54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,AU$6:AU$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AV54" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D54,AV$6:AV$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
@@ -24976,131 +24976,131 @@
         <v>20</v>
       </c>
       <c r="I55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,I$6:I$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,J$6:J$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="K55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,K$6:K$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="L55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,L$6:L$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="M55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,M$6:M$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="N55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,N$6:N$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,O$6:O$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="P55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,P$6:P$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="Q55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,Q$6:Q$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,R$6:R$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="S55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,S$6:S$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="T55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,T$6:T$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,U$6:U$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="V55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,V$6:V$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="W55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,W$6:W$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="X55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,X$6:X$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Y55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,Y$6:Y$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Z55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,Z$6:Z$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="AA55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,AA$6:AA$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="AB55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,AB$6:AB$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="AC55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,AC$6:AC$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AD55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,AD$6:AD$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AE55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,AE$6:AE$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AF55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,AF$6:AF$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AG55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,AG$6:AG$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AH55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,AH$6:AH$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AI55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,AI$6:AI$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AJ55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,AJ$6:AJ$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AK55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,AK$6:AK$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AL55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,AL$6:AL$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AM55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,AM$6:AM$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AN55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,AN$6:AN$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AO55" s="388"/>
@@ -25108,19 +25108,19 @@
       <c r="AQ55" s="388"/>
       <c r="AR55" s="388"/>
       <c r="AS55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,AS$6:AS$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AT55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,AT$6:AT$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AU55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,AU$6:AU$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AV55" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D55,AV$6:AV$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
@@ -25129,131 +25129,131 @@
         <v>21</v>
       </c>
       <c r="I56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,I$6:I$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,J$6:J$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="K56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,K$6:K$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="L56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,L$6:L$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="M56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,M$6:M$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="N56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,N$6:N$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,O$6:O$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="P56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,P$6:P$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="Q56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,Q$6:Q$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,R$6:R$49,0)), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="S56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,S$6:S$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="T56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,T$6:T$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,U$6:U$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="V56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,V$6:V$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="W56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,W$6:W$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="X56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,X$6:X$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Y56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,Y$6:Y$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Z56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,Z$6:Z$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="AA56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,AA$6:AA$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="AB56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,AB$6:AB$49,0)), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="AC56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,AC$6:AC$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AD56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,AD$6:AD$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AE56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,AE$6:AE$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AF56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,AF$6:AF$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AG56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,AG$6:AG$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AH56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,AH$6:AH$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AI56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,AI$6:AI$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AJ56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,AJ$6:AJ$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AK56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,AK$6:AK$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AL56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,AL$6:AL$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AM56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,AM$6:AM$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AN56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,AN$6:AN$49,0)), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AO56" s="388"/>
@@ -25261,19 +25261,19 @@
       <c r="AQ56" s="388"/>
       <c r="AR56" s="388"/>
       <c r="AS56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,AS$6:AS$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AT56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,AT$6:AT$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AU56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,AU$6:AU$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AV56" s="388" t="str">
-        <f>IFERROR(INDEX($B$6:$B$49,MATCH($D56,AV$6:AV$49,0)), "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>

--- a/templates/Templates_REG.xlsx
+++ b/templates/Templates_REG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aletheia/Desktop/Paediatrics/Admin/RosterApp/roster/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885275F3-B642-A043-BD49-C5F4BDAE6EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E02B79A6-FA2A-5640-BE8C-1743B5F07A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="840" yWindow="1280" windowWidth="28560" windowHeight="16600" activeTab="2" xr2:uid="{B6EBF472-D0B5-0C4E-A945-41133059122F}"/>
   </bookViews>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3166" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3164" uniqueCount="298">
   <si>
     <t>Old cycle</t>
   </si>
@@ -19469,12 +19469,8 @@
       <c r="J1" s="353"/>
       <c r="K1" s="353"/>
       <c r="L1" s="353"/>
-      <c r="M1" s="353" t="s">
-        <v>193</v>
-      </c>
-      <c r="N1" s="353" t="s">
-        <v>193</v>
-      </c>
+      <c r="M1" s="353"/>
+      <c r="N1" s="353"/>
       <c r="O1" s="353"/>
       <c r="P1" s="353"/>
       <c r="Q1" s="353"/>

--- a/templates/Templates_REG.xlsx
+++ b/templates/Templates_REG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aletheia/Desktop/Paediatrics/Admin/RosterApp/roster/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E02B79A6-FA2A-5640-BE8C-1743B5F07A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7585A6A8-7779-AA4E-ABDA-D6B6984E7C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="840" yWindow="1280" windowWidth="28560" windowHeight="16600" activeTab="2" xr2:uid="{B6EBF472-D0B5-0C4E-A945-41133059122F}"/>
   </bookViews>
@@ -20010,7 +20010,7 @@
         <v/>
       </c>
       <c r="H6" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B6,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B7,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B6,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B6,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I6" s="24"/>
@@ -20109,7 +20109,7 @@
         <v/>
       </c>
       <c r="H7" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B7,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B8,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B7,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B7,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I7" s="24"/>
@@ -20208,7 +20208,7 @@
         <v/>
       </c>
       <c r="H8" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B8,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B9,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B8,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B8,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I8" s="24"/>
@@ -20307,7 +20307,7 @@
         <v/>
       </c>
       <c r="H9" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B9,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B10,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B9,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B9,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I9" s="24"/>
@@ -20406,7 +20406,7 @@
         <v/>
       </c>
       <c r="H10" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B10,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B11,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B10,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B10,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I10" s="24"/>
@@ -20505,7 +20505,7 @@
         <v/>
       </c>
       <c r="H11" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B11,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B12,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B11,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B11,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I11" s="24"/>
@@ -20604,7 +20604,7 @@
         <v/>
       </c>
       <c r="H12" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B12,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B13,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B12,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B12,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I12" s="364"/>
@@ -20703,7 +20703,7 @@
         <v/>
       </c>
       <c r="H13" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B13,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B14,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B13,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B13,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I13" s="24"/>
@@ -20802,7 +20802,7 @@
         <v/>
       </c>
       <c r="H14" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B14,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B15,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B14,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B14,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I14" s="24"/>
@@ -20901,7 +20901,7 @@
         <v/>
       </c>
       <c r="H15" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B15,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B16,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B15,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B15,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I15" s="24"/>
@@ -21000,7 +21000,7 @@
         <v/>
       </c>
       <c r="H16" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B16,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B17,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B16,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B16,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I16" s="24"/>
@@ -21099,7 +21099,7 @@
         <v/>
       </c>
       <c r="H17" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B17,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B18,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B17,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B17,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I17" s="24"/>
@@ -21198,7 +21198,7 @@
         <v/>
       </c>
       <c r="H18" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B18,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B19,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B18,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B18,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I18" s="24"/>
@@ -21297,7 +21297,7 @@
         <v/>
       </c>
       <c r="H19" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B19,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B20,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B19,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B19,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I19" s="24"/>
@@ -21396,7 +21396,7 @@
         <v/>
       </c>
       <c r="H20" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B20,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B21,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B20,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B20,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I20" s="24"/>
@@ -21495,7 +21495,7 @@
         <v/>
       </c>
       <c r="H21" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B21,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B22,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B21,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B21,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I21" s="24"/>
@@ -21594,7 +21594,7 @@
         <v/>
       </c>
       <c r="H22" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B22,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B23,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B22,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B22,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I22" s="24"/>
@@ -21693,7 +21693,7 @@
         <v/>
       </c>
       <c r="H23" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B23,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B24,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B23,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B23,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I23" s="24"/>
@@ -21792,7 +21792,7 @@
         <v/>
       </c>
       <c r="H24" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B24,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B25,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B24,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B24,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I24" s="24"/>
@@ -21891,7 +21891,7 @@
         <v/>
       </c>
       <c r="H25" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B25,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B26,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B25,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B25,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I25" s="24"/>
@@ -21990,7 +21990,7 @@
         <v/>
       </c>
       <c r="H26" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B26,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B27,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B26,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B26,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I26" s="24"/>
@@ -22089,7 +22089,7 @@
         <v/>
       </c>
       <c r="H27" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B27,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B28,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B27,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B27,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I27" s="24"/>
@@ -22188,7 +22188,7 @@
         <v/>
       </c>
       <c r="H28" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B28,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B29,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B28,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B28,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I28" s="24"/>
@@ -22287,7 +22287,7 @@
         <v/>
       </c>
       <c r="H29" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B29,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B30,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B29,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B29,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I29" s="24"/>
@@ -22386,7 +22386,7 @@
         <v/>
       </c>
       <c r="H30" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B30,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B31,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B30,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B30,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I30" s="24"/>
@@ -22485,7 +22485,7 @@
         <v/>
       </c>
       <c r="H31" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B31,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B32,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B31,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B31,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I31" s="24"/>
@@ -22584,7 +22584,7 @@
         <v/>
       </c>
       <c r="H32" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B32,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B33,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B32,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B32,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I32" s="24"/>
@@ -22683,7 +22683,7 @@
         <v/>
       </c>
       <c r="H33" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B33,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B34,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B33,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B33,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I33" s="24"/>
@@ -22782,7 +22782,7 @@
         <v/>
       </c>
       <c r="H34" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B34,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B35,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B34,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B34,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I34" s="24"/>
@@ -22881,7 +22881,7 @@
         <v/>
       </c>
       <c r="H35" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B35,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B36,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B35,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B35,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I35" s="24"/>
@@ -22980,7 +22980,7 @@
         <v/>
       </c>
       <c r="H36" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B36,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B37,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B36,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B36,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I36" s="24"/>
@@ -23079,7 +23079,7 @@
         <v/>
       </c>
       <c r="H37" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B37,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B38,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B37,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B37,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I37" s="24"/>
@@ -23178,7 +23178,7 @@
         <v/>
       </c>
       <c r="H38" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B38,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B39,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B38,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B38,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I38" s="24"/>
@@ -23277,7 +23277,7 @@
         <v/>
       </c>
       <c r="H39" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B39,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B40,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B39,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B39,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I39" s="24"/>
@@ -23376,7 +23376,7 @@
         <v/>
       </c>
       <c r="H40" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B40,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B41,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B40,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B40,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I40" s="24"/>
@@ -23475,7 +23475,7 @@
         <v/>
       </c>
       <c r="H41" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B41,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP(#REF!,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B41,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B41,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I41" s="24"/>
@@ -23574,7 +23574,7 @@
         <v/>
       </c>
       <c r="H42" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B42,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B43,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B42,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B42,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I42" s="364"/>
@@ -23673,7 +23673,7 @@
         <v/>
       </c>
       <c r="H43" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B43,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B44,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B43,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B43,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I43" s="24"/>
@@ -23772,7 +23772,7 @@
         <v/>
       </c>
       <c r="H44" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B44,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B45,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B44,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B44,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I44" s="24"/>
@@ -23871,7 +23871,7 @@
         <v/>
       </c>
       <c r="H45" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B45,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B46,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B45,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B45,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I45" s="24"/>
@@ -23970,7 +23970,7 @@
         <v/>
       </c>
       <c r="H46" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B46,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B47,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B46,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B46,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I46" s="24"/>
@@ -24069,7 +24069,7 @@
         <v/>
       </c>
       <c r="H47" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B47,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B48,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B47,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B47,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I47" s="24"/>
@@ -24168,7 +24168,7 @@
         <v/>
       </c>
       <c r="H48" s="26" t="str">
-        <f>IFERROR(IF(VLOOKUP($B48,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B49,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B48,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B48,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I48" s="24"/>
@@ -24267,7 +24267,7 @@
         <v/>
       </c>
       <c r="H49" s="41" t="str">
-        <f>IFERROR(IF(VLOOKUP($B49,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B50,'Month-1'!$B$3:$D$53,3,0)),"")</f>
+        <f>IFERROR(IF(VLOOKUP($B49,'Month-1'!$B$3:$D$53,3,0)=0,"",VLOOKUP($B49,'Month-1'!$B$3:$D$53,3,0)),"")</f>
         <v/>
       </c>
       <c r="I49" s="38"/>
@@ -24440,7 +24440,7 @@
         <v/>
       </c>
       <c r="AC51" s="388" t="str">
-        <f t="shared" ref="AC51:AN56" si="22">IFERROR(INDEX($B$6:$B$49,MATCH($D51,AC$6:AC$49,0)), "")</f>
+        <f t="shared" ref="AC51:AR56" si="22">IFERROR(INDEX($B$6:$B$49,MATCH($D51,AC$6:AC$49,0)), "")</f>
         <v/>
       </c>
       <c r="AD51" s="388" t="str">
@@ -24487,12 +24487,24 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AO51" s="388"/>
-      <c r="AP51" s="388"/>
-      <c r="AQ51" s="388"/>
-      <c r="AR51" s="388"/>
+      <c r="AO51" s="388" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AP51" s="388" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AQ51" s="388" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AR51" s="388" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
       <c r="AS51" s="388" t="str">
-        <f t="shared" ref="AS51:AV56" si="23">IFERROR(INDEX($B$6:$B$49,MATCH($D51,AS$6:AS$49,0)), "")</f>
+        <f t="shared" ref="AK51:AV56" si="23">IFERROR(INDEX($B$6:$B$49,MATCH($D51,AS$6:AS$49,0)), "")</f>
         <v/>
       </c>
       <c r="AT51" s="388" t="str">
@@ -24625,25 +24637,37 @@
         <v/>
       </c>
       <c r="AK52" s="388" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AL52" s="388" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AM52" s="388" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AN52" s="388" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="AO52" s="388"/>
-      <c r="AP52" s="388"/>
-      <c r="AQ52" s="388"/>
-      <c r="AR52" s="388"/>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AO52" s="388" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AP52" s="388" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AQ52" s="388" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AR52" s="388" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
       <c r="AS52" s="388" t="str">
         <f t="shared" si="23"/>
         <v/>
@@ -24778,25 +24802,37 @@
         <v/>
       </c>
       <c r="AK53" s="388" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AL53" s="388" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AM53" s="388" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AN53" s="388" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="AO53" s="388"/>
-      <c r="AP53" s="388"/>
-      <c r="AQ53" s="388"/>
-      <c r="AR53" s="388"/>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AO53" s="388" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AP53" s="388" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AQ53" s="388" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AR53" s="388" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
       <c r="AS53" s="388" t="str">
         <f t="shared" si="23"/>
         <v/>
@@ -24931,25 +24967,37 @@
         <v/>
       </c>
       <c r="AK54" s="388" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AL54" s="388" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AM54" s="388" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AN54" s="388" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="AO54" s="388"/>
-      <c r="AP54" s="388"/>
-      <c r="AQ54" s="388"/>
-      <c r="AR54" s="388"/>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AO54" s="388" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AP54" s="388" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AQ54" s="388" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AR54" s="388" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
       <c r="AS54" s="388" t="str">
         <f t="shared" si="23"/>
         <v/>
@@ -25084,25 +25132,37 @@
         <v/>
       </c>
       <c r="AK55" s="388" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AL55" s="388" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AM55" s="388" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AN55" s="388" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="AO55" s="388"/>
-      <c r="AP55" s="388"/>
-      <c r="AQ55" s="388"/>
-      <c r="AR55" s="388"/>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AO55" s="388" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AP55" s="388" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AQ55" s="388" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AR55" s="388" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
       <c r="AS55" s="388" t="str">
         <f t="shared" si="23"/>
         <v/>
@@ -25237,25 +25297,37 @@
         <v/>
       </c>
       <c r="AK56" s="388" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AL56" s="388" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AM56" s="388" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AN56" s="388" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="AO56" s="388"/>
-      <c r="AP56" s="388"/>
-      <c r="AQ56" s="388"/>
-      <c r="AR56" s="388"/>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AO56" s="388" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AP56" s="388" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AQ56" s="388" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AR56" s="388" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
       <c r="AS56" s="388" t="str">
         <f t="shared" si="23"/>
         <v/>
